--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,7518 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4 Marathi films selected for Cannes Film Festival: Maharashtra Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/4-marathi-films-selected-for-cannes-film-festival-maharashtra-minister-ashish-shelar-9955439/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BCCI appoints Rajeev Shukla and Ashish Shelar to Asian Cricket Council Board</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/sports/bcci-appoints-rajeev-shukla-and-ashish-shelar-to-acc-board/articleshow/118789089.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BCCI Vice-President Rajeev Shukla, Former Treasurer Ashish Shelar To Represent India In Asian Cricke..</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Have urged Netflix to provide space for Marathi content on platform, says Maharashtra Cultural Affairs Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/usibc-la-waves-summit-requested-netflix-to-provide-space-for-marathi-content-on-platform-says-maharashtra-cultural-affairs-minister-ashish-shelar-23587606</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Rajeev Shukla, Ashish Shelar to represent BCCI on the ACC Board</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://sportstar.thehindu.com/cricket/rajeev-shukla-ashish-shelar-bcci-acc-board-asian-cricket-council-jay-shah-icc/article69303350.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shiv Sena (UBT)’s condition in Mumbai is dangerous and dilapidated, says BJP MLA Ashish Shelar; welcomes</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Maha govt firms up plan to celebrate Ganeshotsav as ‘Rajya Mahotsav’</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.ap7am.com/en/105045/maha-govt-firms-up-plan-to-celebrate-ganeshotsav-as-rajya-mahotsav</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Maharashtra government to extend curricular support to Marathi schools in US: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-extend-curricular-support-marathi-schools-us-ashish-shelar-10148734/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4 Marathi Films Selected for Cannes Film Festival: Ashish Shelar Announces</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/4-marathi-films-selected-for-cannes-film-festival-minister-ashish-shelar-3501652</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rajeev Shukla, Ashish Shelar get important roles in Asian Cricket Council</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cricket/rajeev-shukla-ashish-shelar-get-important-roles-in-asian-cricket-council-101741359366251.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>"What's The Difference?" BJP Leader's Religion-Language Remark Amid Slapgate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Air safety: As bird hits rise, Maharashtra minister Ashish Shelar chairs high level meeting to find soluti</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>‘Khalid Ka Shivaji’ to be removed from Cannes festival listings; ‘won’t allow tampering with history,’ says Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/khalid-ka-shivaji-removed-cannes-festival-listings-tampering-history-ashish-shelar-10177555/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ashish Shelar gets coveted Malabar Hill bungalow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ashish-shelar-gets-coveted-malabar-hill-bungalow-101736364223566.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>"Hindi Not Compulsory": Maharashtra Minister Amid Language Row</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Minister Ashish Shelar slams BJP MP over remarks against Marathi people</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/ashish-shelar-slams-bjp-mp-marathi-10112152/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Maharashtra delegation led by Ashish Shelar in Paris to seek UNESCO World Heritage status for Shivaji Maharaj’s forts</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-paris-unesco-world-heritage-site-shivaji-maharaj-fort-9851720/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>No need to question capabilities of Marathi speakers: BJP minister Ashish Shelar after Nishikant Dubey remarks</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Loudspeakers may be used till midnight on 7 days: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Shelar likens attacks on non-Marathi speakers in Mumbai to Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-attack-non-marathi-speakers-mumbai-pahalgam-massacre-10109991/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Shelar-led delegation off to Paris to obtain UNESCO heritage status for 12 forts of Shivaji</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/shelar-led-delegation-off-to-paris-to-obtain-unesco-heritage-status-for-12-forts-of-shivaji/article69255530.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mahayuti, BJP disown Jharkhand MP remarks on Marathi manoos</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mumbai: Play Marathi devotional songs on private radio stations, says Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>New Roles For Rajeev Shukla, Ashish Shelar In Asian Cricket Council As BCCI Expands Its Influence</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>"Only Marathi Is Mandatory In Maharashtra Schools, Not Hindi": Minister</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saif Ali Khan attack case: Ashish Shelar dares Uddhav Thackeray to confront Mamata Banerjee over Bangladesh infiltration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BJP's Ashish Shelar dismisses Thackeray rally as political gimmick on Marathi language</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/story/maharashtra-minister-bjp-leader-ashish-shelar-compares-attacks-hindi-speakers-pahalgam-terror-2751745-2025-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>POP idol ban lifted: Will continue to raise issues while upholding devotion, sustainability, says Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/pop-idol-ban-lifted-will-continue-to-raise-issues-while-upholding-devotion-sustainability-says-ashish-shelar-10057291/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Over 50 Marathi schools in US to get support from Maharashtra government</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/education-today/news/story/over-50-marathi-schools-in-us-to-get-support-from-maharashtra-government-2761714-2025-07-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Beaten for language, killed for religion: BJP leader compares Maharashtra language row to Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Maharashtra minister's Pahalgam attack parallel amid attacks over language row | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ganeshotsav is ‘a powerful symbol of Hindutva’: Ashish Shelar | Mumbai news</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ganeshotsav-is-a-powerful-symbol-of-hindutva-ashish-shelar-101753039758492.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Maharashtra govt will not impose censorship on films: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-will-not-impose-censorship-on-films-ashish-shelar-10116698/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Inquiry must be conducted in rat extermination drive: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to develop cyber security policy, IT minister Ashish Shelar announces taskforce</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-cyber-security-policy-it-minister-ashish-shelar-9784459/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ashish Shelar Reviews Mumbai Covid-19 Preparedness Amid New Case Spike</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BCCI Names Rajeev Shukla, Ashish Shelar As Representatives For ACC Board</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ashish Shelar slams Thackeray brothers joint rally as ‘Vague and Politically Motivated'</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1285504</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>How was ‘Khalid Ka Shivaji’ sent to Cannes Film Festival, asks Maharashtra cultural minister Shelar</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>'Even a dog becomes a lion in its own house': Marathi row spills beyond Maharashtra; BJP minister Ashish</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Leopard safari to begin soon at Sanjay Gandhi National Park: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-ashish-shelar-9810427/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ahead of BMC polls, BJP asks review reports from party members | Mumbai news</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ahead-of-bmc-polls-bjp-asks-review-reports-from-party-members-101751138056408.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Attacks on Hindi-speaking people: BJP leader draws Pahalgam parallel to target Thackeray cousins</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/attacks-on-hindi-speaking-people-bjp-leader-draws-pahalgam-parallel-to-target-thackeray-cousins/article69782349.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>http://www.msn.com/en-in/news/India/shelar-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra/ar-AA1L1WDR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Asha Bhosle's Cryptic Comment Add Twist to Thackeray Reunion Speculation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://english.lokshahi.com/top-stories/asha-bhosles-cryptic-comment-add-twist-to-thackeray-reunion-speculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Maharashtra minister's shocker! BJP's Ashish Shelar compares MNS assault over language with Pahalgam terror attack</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/india/maharashtra-ministers-shocker-bjps-ashish-shelar-compares-mns-assault-over-language-with-pahalgam-terror-attack-11751802600494.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI audit found irregularities in drain cleaning works in Mumbai: Maharashtra Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>‘We take full responsibility for Mumbai’s roads’: Shelar after visiting eastern suburbs</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Marathi Cinema At Cannes Film Festival: 4 Movies Selected, Confirms Maharashtra Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://www.timesnownews.com/entertainment-news/bollywood/marathi-cinema-at-cannes-film-festival-4-movies-selected-confirms-maharashtra-minister-ashish-shelar-article-151459918</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sena UBT's condition akin to 'dangerous', 'dilapidated' buildings of Mumbai, says Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ashish Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Saif needs rest after 5-hour surgery, cops have formed 10 teams to nab culprit: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/ashish-shelar-3359084</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Maharashtra Cultural Affairs Ministry to probe obscenity plaints against entertainment programmes</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra-cultural-affairs-ministry-to-probe-obscenity-plaints-against-entertainment-programmes/article69220801.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ashish Shelar lauds Pune’s startup culture</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BJP’s Ashish Shelar Likens MNS' Marathi Assaults To Pahalgam Attack: ‘What’s The Difference?'</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/politics/ashish-shelar-compares-mns-assault-over-marathi-with-pahalgam-attack-whats-the-difference-9424380.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Maharashtra delegation in Paris to seek Unesco tag for Shivaji's forts</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/story/maharashtra-delegation-in-paris-to-seek-unesco-tag-for-shivaji-maharajs-forts-2684249-2025-02-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>State’s AI policy to be released in April: Shelar</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Rajeev Shukla, Ashish Shelar named BCCI’s representatives on ACC board</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Artworks of Ravi Paranjape handed over to govt, to be preserved in museum</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/artworks-of-ravi-paranjape-handed-over-to-govt-to-be-preserved-in-museum-10201536/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ashish Shelar Slams Shiv Sena (UBT) Faction for "Fake Drama" and Political Theatrics</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BJP pans UBT over Deonar dump remarks</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Maharashtra: BJP's Shelar Condemns Attacks on Hindi Speakers, Cites Pahalgam Parallel</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Tech experts will study use of PoP in Ganesh idols: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mumbai: MNS protests alleged ill-treatment to Marathi speakers over non-veg food; Ashish Shelar issues warning</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Shelar-led delegation in Paris to secure UNESCO Heritage status for 12 Shivaji forts</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to support Marathi schools in US with official curriculum</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>'Sarvajanik Ganehotsav' announced as ‘State Festival of Maharashtra', confirms Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/sarvajanik-ganehotsav-announced-as-state-festival-of-maharashtra-confirms-ashish-shelar-11752164479346.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Highlight power of Operation Sindoor during Ganeshotsav: Ashish Shelar tells organisers</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Maharashtra to unveil AI policy by April; Ashish Shelar warns against over-reliance</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Maharashtra minister addresses AI concerns, assures policy will complement, not replace, education</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to set up research centre for experimental arts in Mumbai, name it after Shahir Sable: M</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>'Where did Pahalgam attackers go?': Aaditya Thackeray's 'poison' reply to Maharashtra minister's remark amid Marathi row | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Allahbadia remarks: Maharashtra minister Ashish Shelar asks cultural affairs department to probe obscene programmes</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Renovated Ravindra Natya Mandir in Mumbai to be reopened on February 28: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/renovated-ravindra-natya-mandir-reopening-mumbai-9843008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Not an inch of Dharavi will be given to Adani, says Maharashtra minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BJP demands 'white paper' from BMC on monsoon related spending</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Leopard Safari to begin soon at Sanjay Gandhi National Park: Maha minister</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://travel.economictimes.indiatimes.com/news/destination/states/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-maha-minister/117794576</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Firebrand legislator and Fadnavis confidante Ameet Satam made BJP’s Mumbai chief ahead of BMC polls</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/firebrand-legislator-and-fadnavis-confidante-ameet-satam-made-bjps-mumbai-chiefahead-of-bmc-polls-3696247</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>74 roads in H West ward will be completed by May 31: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Warring BJP factions clash in Kandivali public meeting</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Ashish Shelar chairs Covid-19 review meet; suggests masks, re-vaccination for high-risk individuals</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to crack down on lane-cutting, draw up integrated traffic management plan for Mumbai: Su</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Expert committee set up to look into 'tamasha' artistes' problems: Shelar</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Maharashtra Cabinet Minister Ashish Shelar to be the Chief Guest of e4m IDMA 2025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>BJP politician calls Uddhav Thackeray badshah of land scams in Mumbai</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Asha Bhosle, Minister Ashish Shelar visit RD Burman's residence to celebrate singer's 86th birth anniversary</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Raghuji Bhonsale’s legendary sword set to arrive in Mumbai tomorrow, ‘darshan’ ceremony to be held at PL Deshpande Maharashtra Kala Academy</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/raghuji-bhonsales-legendary-sword-mumbai-10194874/</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Maharashtra minister Ashish Shelar urges transfer of Shivaji’s forts under ASI to state govt</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>No Dharavi land being handed over to Adani: Shelar</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Maharashtra cultural centre and museum to come up at BKC</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>"Maharashtra won, Marathi Manus won, BJP won in this fight", says BJP Mumbai chief Ashish Shelar as Mahayuti slams MVA over three-language policy issue</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ashish Shelar praises Mukta Arts Marathi Productions and Subhash Ghai for backing regional cinema</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>BJP’s Shelar, not Sena neta, is advisor for Maha tech hub</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Veteran actor Vivek Lagoo passes away, Maha minister Shelar pays tribute</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Maharashtra govt. wants CBFC to re-examine certification for Khalid ka Shivaji, halt release of movie</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-govt-wants-cbfc-to-re-examine-certification-for-khalid-ka-shivaji-halt-release-of-movie/article69906718.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Mumbai Looted Of Rs 1 Lakh Crore Under Uddhav Thackeray's Watch, Alleges BJP’s Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/cities/shiv-sena-ubt-looted-mumbai-of-rs-1-lakh-crore-alleges-bjps-ashish-shelar-9358239.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Don’t question capabilities of Marathi speakers: BJP minister Shelar after Dubey remarks</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/dont-question-capabilities-of-marathi-speakers-bjp-minister-shelar-after-dubey-remarks/2682767/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>"Police working meticulously, truth will be out soon": Maharashtra Minister Ashish Shelar on Saif Ali Khan attack case</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Maharashtra govt orders cultural dept probe, ‘absconding’ Ranveer Allahbadia to face cops today? All you</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-orders-cultural-dept-probe-absconding-ranveer-allahbadia-to-face-cops-today-all-you-need-to-know/articleshow/118267899.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Maharashtra minister condemns assault on Hindi-speaking people, draws parallel with Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-minister-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack/articleshow/122281220.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Rajiv Shukla, Ashish Shelar To Represent BCCI On ACC Board</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Culture minister Ashish Shelar seeks MoU between state archives of Maharashtra and Gujarat</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ashish Shelar demands report from MMRDA; slams ‘deception’ behind axed Bandra-Kurla rail route</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Maharashtra Spearheading India’s First AI University Says Maharashtra IT Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Minister Shelar criticises UBT over education policy, says Cong started Hindi mandate &amp; Thackeray continu</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Prepare monsoon contingency plan for Mumbai Metro stations: Ashish Shelar to officials</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Science and Innovation Activity centres to be set up across Maharashtra</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/science-and-innovation-activity-centres-to-be-set-up-across-maharashtra-10133570/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Mannat inspection: Maharashtra govt fumes at forest department officials for visiting SRK residence</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Only Marathi is mandatory in Maharashtra, and not Hindi: Mumbai BJP chief Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Video | BJP Minister Condemns MNS Attacks, Compares Them To Pahalgam Shooting Over Religious Identity</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Plot in Marol transforms into urban forest, mercury drops</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Maharashtra government forms panel for Artificial Intelligence policy</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>UBT looted Mumbai to the tune of ₹1 lakh crore, alleges BJP’s Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>‘Celebrate Ganeshotsav Like Never Before’: Shelar Blames Urban Naxals For Attack On Hindu Fests</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/celebrate-ganeshotsav-like-never-before-shelar-blames-urban-naxals-for-attacks-on-hindu-fests-ws-kl-9452155.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Will Raj Thackeray Join Mahayuti Ahead Of Civic Polls? His Meeting With Mumbai BJP Chief Sparks Buzz</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/politics/brihanmumbai-municipal-corporation-bmc-elections-mumbai-mns-raj-thackeray-bjp-ashish-shelar-mahayuti-shiv-sena-eknath-shinde-9181677.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Khalid Ka Shivaji to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Satam Appointed As Mumbai BJP Chief Ahead Of Crucial BMC Polls</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/nation/satam-appointed-as-mumbai-bjp-chief-ahead-of-crucial-bmc-polls-1899682</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BJP's Ameet Satam named Mumbai party chief to counter Thackerays in civic polls</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/story/bjp-leader-ameet-satam-appointed-party-chief-in-mumbai-to-counter-thackerays-in-the-upcoming-civic-polls-2776671-2025-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AID strongly advocates GCC Policy: Ashish Kale</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar pays tribute to Savarkar at Andaman's Cellular Jail</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mumbai Confidential: Brother trouble</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>‘Reclassify SGNP slums land as non-forest to avoid relocation’</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/reclassify-sgnp-slums-land-as-non-forest-to-avoid-relocation/articleshow/121523748.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>News On Click</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to form panel to study issues faced by single-screen cinemas</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-panel-to-study-issues-faced-by-single-screen-cinemas-10176447/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>23rd Pune International Film Festival begins with a grand opening</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/pune/23rd-pune-international-film-festival-begins-with-a-grand-opening-9835047/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ganeshotsav to Get Status of Maharashtra’s ‘State Festival’</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/nation/current-affairs/ganeshotsav-to-get-status-of-maharashtras-state-festival-1890637</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar calls for urgent desilting plan for key lakes in Mumbai</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>State grants ‘Maharashtra State Festival’ status to Ganeshotsav, promises funds</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-grants-maharashtra-state-festival-status-to-ganeshotsav-promises-funds/articleshow/122373114.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guardian ministers appointed in Maharashtra; Dhananjay Munde not in list</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray's Shiv Sena (UBT) failed to improve Mumbai's stormwater drain system despite Rs 1 lakh crore spending: BJP</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Prize money, production grants and daily allowance hiked for Maharashtra State Drama Competition: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Shelar invokes Pahalgam: ‘Here, Hindus attacked over language’</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Not all road works in Mumbai will be completed before May 31 monsoon deadline: Maharashtra Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>All govt departments, implementing agencies must ensure 100 per cent fund utilisation: Shelar</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Nearly 60% of bakeries in Mumbai yet to switch to cleaner fuel</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/nearly-60-of-bakeries-in-mumbai-yet-to-switch-to-cleaner-fuel-10088723/</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Submit action plan within 3 months to desilt three lakes in Mumbai: Shelar</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/submit-action-plan-within-3-months-to-desilt-three-lakes-in-mumbai-shelar-10088728/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Maharashtra Cultural Minister Ashish Shelar inaugurates Kala Ghoda Arts Festival 2025</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Rajeev Shukla, Ashish Shellar appointed as reps to ACC board</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Maharashtra orders inquiry by cultural dept officials into Ranveer Allahbadia controversy</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Feb/15/maharashtra-orders-inquiry-by-cultural-dept-officials-into-ranveer-allahbadia-controversy</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Shelar &amp; Cong MP get into spat over Dharavi master plan</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Veer Savarkar’s iconic song ‘Anadi Me Anant Me...’ to be honoured with award named after Sambhaji Maharaj: Minister</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/veer-savarkars-iconic-song-anadi-me-anant-me-to-be-honoured-with-award-named-after-sambhaji-maharaj-minister-3421353</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Maharashtra to get India's first AI university led by industry experts</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/education-today/news/story/ai-education-indias-first-ai-university-to-set-up-in-maharashtra-2673858-2025-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>FTII and Maharashtra Film, Stage &amp; Cultural Development Corporation Ltd. sign MoU to expand film and media training in Maharashtra</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Give Custodianship Of Historic Forts To Maharashtra Government: Minister Ashish Shelar To Centre</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/hand-over-custodianship-of-historic-forts-to-maharashtra-government-minister-ashish-shelar-to-centre-9274572.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Shelar announces taskforce for cyber security norms in Maharashtra</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/en/politics/shelar-announces-taskforce-for-cyber-security-norms-in-maharashtra-87382</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Mumbai's Sanjay Gandhi National Park To Introduce 'Leopard Safari' For Visitors Soon</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/sanjay-gandhi-national-park-in-mumbai-to-introduce-leopard-safari-for-visitors-soon-ashish-shelar-9209891.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Ameet Satam Appointed BJP Mumbai Chief Ahead Of Polls</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>https://www.bwpeople.in/article/ameet-satam-appointed-bjp-mumbai-chief-ahead-of-polls-568808</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Maharashtra government aims to make forts encroachment-free by May 31</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>New Mumbai BJP chief Ameet Satam is 3-time MLA with corporate background, Thackeray critic</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://theprint.in/politics/new-mumbai-bjp-chief-ameet-satam-is-3-time-mla-with-corporate-background-thackeray-critic/2728464/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Maharashtra govt forms 16-member panel to draft first-ever AI policy</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-16-member-panel-draft-ai-policy-9784605/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Maharashtra Declares Ganeshotsav As State Festival</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Maharashtra to Establish India’s First Artificial Intelligence University</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Maharashtra: Honorarium of Aadhaar centre operators raised; 12.8 cr Aadhaar registrations recorded till date</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-aadhaar-centre-operators-honorarium-raised-registrations-recorded-9952118/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Mumbai rains: Sena (UBT), contractors misappropriated funds meant for drainage system, claims Shelar</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>https://theprint.in/india/mumbai-rains-sena-ubt-contractors-misappropriated-funds-meant-for-drainage-system-claims-shelar/2637642/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Highlight power of Operation Sindoor during Ganesh festival: Shelar tells organisers</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/Highlight-power-of-Operation-Sindoor-during-Ganesh-festival--Shelar-tells-organisers/2841354</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Roads in Mumbai will be pothole-free before Ganesh festival: BJP ministers</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Play Marathi devotional songs on private radio stations: Shelar</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>BCCI issues update on appointment to ACC's Board of Directors</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>BCCI appoints Jay Shah and Ashish Shelar's successor ahead of Champions Trophy 2025</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Mumbai BJP Chief Ashish Shelar Slams Uddhav &amp; Raj Thackeray For Pushing Personal Agendas Under Marathi Pride</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-chief-ashish-shelar-slams-uddhav-raj-thackeray-for-pushing-personal-agendas-under-marathi-pride-video</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Maharashtra News: Minister Ashish Shelar Accuses Opposition Of Urban Naxalite Agenda To Curtail Ganeshotsav</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-minister-ashish-shelar-accuses-opposition-of-urban-naxalite-agenda-to-curtail-ganeshotsav-traditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Urges Netflix To Promote Marathi Content On OTT Platform</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-urges-netflix-to-promote-marathi-content-on-ott-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Targets Uddhav Thackeray, Raj Thackeray Over Hindi Row; Says Marathi</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-targets-uddhav-thackeray-raj-thackeray-over-hindi-row-says-marathi-mandatory-hindi-optional-video</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Ashish Shelar Slams Uddhav-Raj Thackeray Rally As Irrelevant, Accuses Duo Of Distorting Facts</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/entertainment/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>No New Restrictions On Political Portrayals In Films, Says Minister Ashish Shelar During Council Debate</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/no-new-restrictions-on-political-portrayals-in-films-says-minister-ashish-shelar-during-council-debate</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Mumbai Minister Ashish Shelar Gives 72-Hour Deadline To Fix Potholes Ahead Of Ganeshotsav 2025</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-ashish-shelar-gives-72-hour-deadline-to-fix-potholes-ahead-of-ganeshotsav-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>No One Should Hurt Sentiments..: Maha Minister Ashish Shelar On Row Over Viral Ganeshotsav Reel By Content</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/no-one-should-hurt-sentiments-maha-minister-ashish-shelar-on-row-over-viral-ganeshotsav-reel-by-content-creator-atharva-sudame</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Mumbai Rains: Minister Ashish Shelar Meets BMC Chief Bhushan Gagrani, Demands White Paper On ₹1 Lakh Crore</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-minister-ashish-shelar-meets-bmc-chief-bhushan-gagrani-demands-white-paper-on-1-lakh-crore-flood-control-spending-over-past-20-years</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Ashish Shelar Addresses Media on Hindi as Third Language in Schools #Gallery</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>https://www.socialnews.xyz/?p=6712027</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Visits Cellular Jail, Seeks Support For Veer Savarkar Memorial In Andaman</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-visits-cellular-jail-seeks-support-for-veer-savarkar-memorial-in-andaman-islands</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Second Arm Of Andheris Gokhale Bridge Inaugurated, Minister Ashish Shelar Hails Fast-Track Completion As</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/second-arm-of-andheris-gokhale-bridge-inaugurated-minister-ashish-shelar-hails-fast-track-completion-as-success-story-see-pics</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Maharashtra: Ganeshotsav Declared State Festival; Ashish Shelar Alleges Conspiracy Against Hindu Traditions</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-ganeshotsav-declared-state-festival-ashish-shelar-alleges-conspiracy-against-hindu-traditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Proposes Grand National Memorial For Veer Savarkar At Andaman’s Cellular</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-proposes-grand-national-memorial-for-veer-savarkar-at-andamans-cellular-jail</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ashish Shelar inaugurates Art Show by IAS Officers Nidhi Choudhari &amp; Rajanvir Singh Kapur</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>https://culturecrossroads.ca/posts/ashish-shelar-inaugurates-art-show-by-ias-officers-nidhi-choudhari-rajanvir-singh-kapur/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Ashish Shelar Directs BMC To Deploy 1,000 Volunteers With 1916 Helpline For Dahi Handi Safety</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-bmc-to-deploy-1000-volunteers-with-1916-helpline-for-dahi-handi-safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead Of BMC Polls; CM Devendra Fadnavis, Ashish Shelar Extend</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Historic Sword Of Maratha Sardar Raghuji Bhosale To Return To Maharashtra By July-End, Says Minister Ashish</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-maratha-sardar-raghuji-bhosale-to-return-to-maharashtra-by-july-end-says-minister-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir’s ‘SUR Music’ Label</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VIDEO: Uddhav Thackerays Party Failed To improve Mumbais Stormwater Drain System Despite ₹1 Lakh Crore</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/video-uddhav-thackerays-party-failed-to-improve-mumbais-stormwater-drain-system-despite-1-lakh-crore-spend-says-minister-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Mumbai News: Displaced Residents Near Elphinstone Bridge To Get Redeveloped Homes At Same Location, Announces</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-displaced-residents-near-elphinstone-bridge-to-get-redeveloped-homes-at-same-location-announces-minister-ashish-shelar-video</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Calls For Action To Boost Marathi Films &amp; Save Single-Screen Cinemas</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-calls-for-action-to-boost-marathi-films-save-single-screen-cinemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Vikram Gaikwad Death: Maharashtra Deputy CM Eknath Shinde, Ashish Shelar Express Condolences</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/national-award-winning-makeup-artist-vikram-gaikwad-passes-away-in-mumbai-maharashtra-deputy-cm-eknath-shinde-expresses-condolences</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Maharashtra Minister Ashish Shelar Criticises Desilting Works In Mumbai, Demands Accountability From</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Read Finally Gokhale Bridge Andheri Poora Ready Hua, Finally Ready, Guardian Minister Ashish Shelar Ke Hathon Open Kiya Gaya</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: Ashish Shelar Slams Thackeray Rally As Theatrical, Draws Pahalgam Parallel; Kishori</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ashish-shelar-slams-thackeray-rally-as-theatrical-draws-pahalgam-parallel-kishori-pednekar-hits-back</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Mumbai Politics: Two Ex-UBT Corporators Join BJP; Shelar Declares Party Now Largest In Civic Body Ahead Of BMC</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-two-ex-ubt-corporators-join-bjp-shelar-declares-party-now-largest-in-civic-body-ahead-of-bmc-polls</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Mumbai News: BJP To Celebrate Maharashtra Day And Labour Day At 106 Locations Under Minister Ashish Shelars</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bjp-to-celebrate-maharashtra-day-and-labour-day-at-106-locations-under-minister-ashish-shelars-leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Pune: Sinhagad Fort Development Plan Meeting to Be Held Within 15 Days, Says Cultural Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-sinhagad-fort-development-plan-meeting-to-be-held-within-15-days-says-cultural-minister-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Mumbai: Siddhivinayak Temple Trust Felicitates Ashish Shelar For Declaring Ganeshotsav As State Festival</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-siddhivinayak-temple-trust-felicitates-ashish-shelar-for-declaring-ganeshotsav-as-state-festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Maharashtra: Gondan Kala To Enter Maharashtras Art Curriculum, Says Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-gondan-kala-to-enter-maharashtras-art-curriculum-says-minister-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Mumbai News: Relief For 86 Stalled SRA Projects As Residents Allowed To Appoint New Developers; Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-relief-for-86-stalled-sra-projects-as-residents-allowed-to-appoint-new-developers-ashish-shelar-reviews-progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Mumbai News: Minister Ashish Shelar Directs BMC To Submit 3-Month Action Plan For Desilting Powai, Tulsi And</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-directs-bmc-to-submit-3-month-action-plan-for-desilting-powai-tulsi-and-vihar-lakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>No New Road Works After May 20, Ensure Motorable Roads Before Monsoon: Ashish Shelar To BMC</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/no-new-road-works-after-may-20-ensure-motorable-roads-before-monsoon-ashish-shelar-to-bmc</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/07/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Pune: Maharashtra Declares Ganesh Festival as ‘State Festival,’ Plans Global Promotion: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Hindi Not Mandatory in Maharashtra Schools, Marathi Remains Only Compulsory Language: Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/hindi-not-mandatory-in-maharashtra-schools-marathi-remains-only-compulsory-language-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Mahesh Kale’s ‘Abhangwari’ Unveiled by Ashish Shelar on Ashadi Ekadashi!</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Maharashtra News: Shivchaturya Din Celebrated With Agra-To-Rajgad Cycle Yatra Flagged Off By Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shivchaturya-din-celebrated-with-agra-to-rajgad-cycle-yatra-flagged-off-by-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>POP idol ban lifted: A triumph for artisans, says Maha Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/pop-idol-ban-lifted-a-triumph-for-artisans-says-maha-minister-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Ganeshotsav declared as ‘State Festival of Maharashtra’: Cultural Affairs Minister Ashish Shelar announces ...</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra minister Ashish Shelar pays tribute</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Cultural Minister Ashish Shelar Gives Muhurat Clap for a Marathi Film ‘Ladki Bahin’!</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>मुंबई में 2.5 लाख चूहों को मारने का दावा, जांच के आदेश, क्या है पूरा सच? आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव को मिला `राज्य महोत्सव` का दर्जा, सांस्कृतिक कार्य मंत्री आशिष शेलार ने किया बड़ा ऐलान</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा, मंत्री आशिष शेलार ने किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://hindi.news24online.com/state/mumbai/maharashtra-ganesh-utsav-latest-news-ashish-shelar-new-announcement/1248697/</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Hindi-Marathi Row: मराठी लोगों पर निशिकांत दुबे के बयान से भाजपा का किनारा, फडणवीस के मंत्री ने दी सख्त हिदायत</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>'शिवतीर्थ' पहुंचकर राज ठाकरे से मिले मुंबई बीजेपी अध्यक्ष, बीएमसी चुनावों में किससे हिसाब बराबर करेगी मनसे?</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Maharashtra: मंत्री आशीष शेलार का बड़ा बयान- 'महाराष्ट्र में केवल मराठी अनिवार्य, हिंदी नहीं'</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>`मुंबई हमारी है` बीजेपी नेता आशिष शेलार के दावे पर सुषमा अंधारे ने दिया करारा जवाब</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>अमित साटम को मुंबई BJP का अध्यक्ष नियुक्त किया गया</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/hi/politics/amit-satam-appointed-as-mumbai-bjp-president-89721</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>राज ठाकरे के बयान पर आशीष शेलार बोले, 'पहलगाम में धर्म पूछकर मारा जाता है, यहां</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के गणेशोत्सव को मिलेगा वैश्विक दर्जा, मंत्री आशीष शेलार ने की खास घोषणा</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Maharashtra: निशिकांत दुबे के बयान पर बीजेपी ने बनाई दूरी! आशीष शेलार बोले- 'मराठी व्यक्ति</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>आशीष शेलार की जगह कौन होगा मुंबई BJP का अगला अध्यक्ष? रेस में ये नाम सबसे आगे</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BJP सांसद निशिकांत दुबे के पटककर मारने वाले बयान पर उद्धव ठाकरे बोले, 'ऐसे कई लकड़बग्घे...'</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>बीजेपी नेता आशीष शेलार के बयान से मची सियासी हलचल, बोले- 'राज ठाकरे और मैं...'</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>शाहरुख खान के घर 'मन्नत' अचानक पहुंचे वन विभाग के अधिकारी, भड़की महाराष्ट्र सरकार</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>BMC चुनाव से पहले BJP का बड़ा फैसला, इस नेता को बनाया मुंबई का पार्टी अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र : आशीष शेलार ने सांस्कृतिक पुरस्कारों का किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>4,066 new Aadhaar kits to be distributed to collector's office across Maharashtra: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>MLA: File report in 7 days on status of H-West rd works, finish them by May 31</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>मंत्री आशीष शेलार ने गणेशोत्सव गीत और पोर्टल का किया शुभारंभ, नागरिकों से भागीदारी की अपील</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/minister-ashish-shelar-launched-ganeshotsav-song-and-portal-appealed-to-citizens-for-participation-1328512.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ऐतिहासिक धरोहरें होंगी सुरक्षित, मंत्री शेलार का ऐलान-दस्तावेजों के संरक्षण को सरकार देगी मदद</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-historical-heritage-will-be-protected-minister-shelar-announced-government-will-help-in-preservation-of-documents-1324840.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>दुनिया में होगी महाराष्ट्र के गणेशोत्सव की धूम, आशीष शेलार कहा इसे बनाएंगे वर्ल्ड क्लास</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/pune/maharashtras-ganeshotsav-will-become-world-class-1325768.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>मुंबई भाजपा अध्यक्ष पद पर अमित साटम की नियुक्ति, फडणवीस और शेलार ने दी बधाई</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/maharashtra/bjp-mumbai-amit-satam-ashish-shelar-devendra-fadnavis-54-807644</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Maharashtras First International Marathi Film Festival, Chitrapataka, Begins April 21; Cultural Affairs</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-first-international-marathi-film-festival-chitrapataka-begins-april-21-cultural-affairs-minister-ashish-shelar-reveals-emblem</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>BJP leader likens attacks on non-Marathi speakers to Pahalgam massacre</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Complete all dug up roads in Mumbai by May 31: Ashish Shelar to BMC</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/shelar-directs-bmc-to-stop-road-concretisation-works-from-today-10016418/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BCCI announces Rajeev Shukla, Ashish Shelar as new representatives for ACC Board</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://www.storyboard18.com/brand-makers/bcci-announces-rajeev-shukla-ashish-shelar-as-new-representatives-for-acc-board-58707.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>No land in Dharavi has been given to Adani, Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/no-land-in-dharavi-has-been-given-to-adani-ashish-shelar-9899366/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Have urged Netflix to provide space for Marathi content on platform: Shelar</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Rajeev Shukla, Ashish Shelar To Represent India In Asian Cricket Council</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/cricket/rajeev-shukla-ashish-shelar-to-represent-india-in-asian-cricket-council-9253383.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir's 'SUR Music' Label</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>BJP Leader Compares Attack on Hindi-speaking People with Pahalgam Incident</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/nation/politics/bjp-leader-compares-attack-on-hindi-speaking-people-with-pahalgam-incident-1889788</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Days after Raj met CM Fadnavis, his son meets Shelar; sets tongues wagging</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/days-after-raj-met-cm-fadnavis-his-son-meets-shelar-sets-tongues-wagging-10207422/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Maharashtra govt will make arrangements for immersion of large Ganesh idols: Ashish Shelar on PoP use</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Reema Lagoos Ex-Husband And Veteran Actor Vivek Lagoo Dies, Last Rites To Be Held Today; Maharashtra Minister Ashish Shelar Pays Tribute</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>BMC told to finish all roadworks in Mumbai suburbs by May 31, says minister</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>It's a Public Appeasement Campaign: BJP on Thackerays Reunion</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>https://www.deccanchronicle.com/nation/politics/its-a-public-appeasement-campaign-bjp-on-thackerays-reunion-1889545</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>BJP's Nishikant Dubey dares Uddhav, Raj Thackeray to visit north India, Tamil Nadu | Reactions so far</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Maharashtra govt taking balanced approach to pigeon feeding issue: Minister Shelar</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>BJP likely to appoint new Mumbai chief ahead of BMC polls</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/news/india/bjp-likely-to-appoint-new-mumbai-chief-ahead-of-bmc-polls-13375950.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Good News For Marathi Filmmakers: Maharashtra Govt Plans Revival Of Single-Screen Cinemas</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/good-news-for-marathi-filmmakers-maharashtra-govt-plans-revival-of-single-screen-cinemas-ws-l-9492408.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Barely 10% nullah desilting work completed in 35 days: Shelar</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/barely-10-nullah-desilting-work-completed-in-35-days-shelar-9991132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Minister Shelar warns of ‘urban naxal’ threat</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>4 Marathi films selected for 2025 Cannes Film Festival reveals Maharashtra cultural affairs minister...</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Sword of Raghuji-1 Bhonsale to be brought to India on Aug 18</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Ameet Satam appointed BJP Mumbai Chief</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://www.exchange4media.com/industry-briefing-news/ameet-satam-appointed-bjp-mumbai-chief-146770.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Who Is Ameet Satam? Three-Term MLA Picked As BJP's Mumbai Chief Ahead Of BMC Polls</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/politics/ameet-satam-mumbai-bjp-chief-andheri-west-mla-bmc-polls-ws-l-9526976.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Maharashtra minister Shelar asks govt departments to step up Ganeshotsav participation; Rs 10 crore for cultural events</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-minister-shelar-asks-govt-departments-to-step-up-ganeshotsav-participation-rs-10-crore-for-cultural-events-10205121/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>No one wants to stay in Shiv Sena (UBT): BJP</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://uniindia.com/no-one-wants-to-stay-in-shiv-sena-ubt--bjp/west/news/3496190.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BJP names three-term MLA Ameet Satam as Mumbai chief before BMC polls</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://tripuratimes.com/ttimes/bjp-names-three-term-mla-ameet-satam-as-mumbai-chief-before-bmc-polls-30851.html/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Worli BDD Chawl redevelopment residents will get their new homes before 'Shravan': Maharashtra Minister</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Mumbai To Get Rid of Flood-Like Situations? New Plan Announced After 180 mm Rainfall Chaos</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Culture Minister Ashish Shelar Praises Mukta Arts Productions, Subhash Ghai For Backing Regional Cinema</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Expert Panel To Study PoP Use For Ganesh Idols, Assures Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/expert-panel-to-study-pop-use-for-ganesh-idols-assures-minister-ashish-shelar-9260345.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Task force formed to set up AI university in Maharashtra, says IT Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Maharashtra minister compares assaults on non-Marathi speakers in state to Pahalgam terror attack</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://scroll.in/latest/1084239/maharashtra-minister-compares-assaults-on-non-marathi-speakers-in-state-to-pahalgam-terror-attack</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Forest department officials suddenly reached Shahrukh Khan's house 'Mannat', Maharashtra government got angry. ..?</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://www.indiaherald.com/Breaking/Read/994828609/Forest-department-officials-suddenly-reached-Shahrukh-Khans-house-Mannat-Maharashtra-government-got-angry-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://www.thehawk.in/news/india/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Amit Satam Takes Charge as Mumbai BJP President Ahead of Crucial BMC Elections</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/politics/3601925-amit-satam-takes-charge-as-mumbai-bjp-president-ahead-of-crucial-bmc-elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror: BJP’s Shelar says some leaders ...</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Agency News | ⚡Reema Lagoo’s Ex-Huband Vivek Lagoo No More</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://www.latestly.com/quickly/agency-news/reema-lagoo-s-ex-huband-vivek-lagoo-no-more-6939671.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to grant Rs 25,000 each to 'bhajani mandals' for Ganesh festival</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://www.newsdrum.in/national/maharashtra-govt-to-grant-rs-25000-each-to-bhajani-mandals-for-ganesh-festival-9690752</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sword of Maratha glory returns after two centuries: Maharashtra minister Shelar brings home Raghuji ...</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/sword-of-maratha-glory-returns-after-two-centuries-maharashtra-brings-home-raghuji-bhosales-legendary-weapon-from-london-auction-135656002.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Minister Shelar inaugurates Gokhale bridge: After almost 2.5 years waiting, Andheri's Gokhale bridge second...</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Maharashtra To Extend Official Curriculum Support To Marathi Schools In US</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Amid Language Row At Home, Maharashtra Govt To Provide Curriculum To Marathi Schools In US</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>https://www.news18.com/india/amid-language-row-at-home-maharashtra-govt-to-provide-curriculum-to-marathi-schools-in-us-ws-l-9462862.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>4 Marathi films selected for Cannes Film Festival: Minister</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/entertainment/marathi/movies/news/4-marathi-films-selected-for-cannes-film-festival-minister/articleshow/120451522.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>अमेरिकेतील मराठी शाळांना महाराष्ट्र सरकारतर्फे अभ्यासक्रम पुरवणार; आशिष शेलारांचे आश्वासन</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/international/bjp-minister-ashish-shelar-on-america-tour-said-maharashtra-government-will-provide-curriculum-to-marathi-schools-in-america-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : पहलगाममध्ये धर्म विचारून हिंदूंना गोळ्या मारल्या अन् इथे निष्पाप हिंदूंना</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Avinash Jadhav on Ashish Shelar : आशिष शेलारांकडून मनसेच्या मराठी भाषा आंदोलनाची पहलगाम हल्ल्याशी</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>मुंबई भाजपच्या अध्यक्षपदी आशिष शेलार कायम राहणार?</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/will-ashish-shelar-continue-as-mumbai-bjp-president-a-a285-c941/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BMC Election : मनसैनिकांची तुलना पहलगामच्या दहशतवाद्यांशी, आशिष शेलारांचा तोल कसा सुटला? की</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>राज्यातील भजनी मंडळांना शासनाकडून २५ हजार</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-announced-grant-of-rs-25000-for-1800-bhajani-mandals-across-maharashtra-for-ganesh-festival-zws-70-5324659/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>BJP : आशिष शेलारांच्या गाडीसमोर मोठा राडा, भाजप पदाधिकाऱ्यांमध्ये थेट हाणामारी</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dispute-between-bjp-party-workers-in-front-of-minister-ashish-shelar-car/articleshow/121829032.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : अहो ‘बाता’शिष शेलार… मुंबईची तुंबई होताच ठाकरेंच्या सेनेकडून...</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Mumbai BEST Elections Result: मुंबई ही आमचीच...! बेस्टच्या निकालानंतर शेलारांनी BMC साठी शड्डू ठोकला, ठाकरे...</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>कोल्हापुरात जुन्या मराठी चित्रपटांचे मोफत प्रदर्शन; ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/kolhapur/ashish-shelar-announces-free-screening-of-old-marathi-films-in-kolhapur-news-amy-95-5196886/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>मराठी चित्रपटांसाठी महाराष्ट्र सरकार थेट Netflix च्या अमेरिकेतील हेडक्वॉर्टर्समध्ये पोहोचलं; अमेरिका...</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>मराठी आंदोलनाची ‘पहलगाम’शी तुलना, आशीष शेलार यांच्या विधानामुळे वाद; विरोधकांचे टीकास्त्र</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-compared-marathi-movement-with-pahalgam-terrorist-attack-css-98-5209656/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meets Ashish Shelar : आशिष शेलारांच्या कार्यालयाच्या बाहेरूनच अमित ठाकरे म्हणाले,</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Ashish Shelar praises Raj Thackeray : राज ठाकरेंचा 'दानपट्टा' फिरणार? 'मनसे'च्या गुढीपाडवा मेळाव्यापूर्वीच भाजप मंत्री शेलारांनी गोंजारलं</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-minister-ashish-shelar-praises-raj-thackeray-at-marathi-film-event-mumbai-pp82</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : कांदिवलीत मंत्री आशिष शेलारांसमोर भाजपच्या दोन गटात राडा; नेमकं प्रकरण काय?</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>“राज्यात सक्ती फक्त मराठीची, हिंदीची नाही; चर्चा अवास्तव, अवाजवी, अतार्किक”: आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-said-compulsion-in-the-state-is-only-marathi-not-hindi-and-the-discussion-is-unrealistic-unreasonable-illogical-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Bala Nandgaonkar:आजच्या तारखेला अख्ख्या भारतात आशिष शेलार साहेब एक नंबरचे वक्ते बाळा नांदगावकरांचा</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>मराठी माणसाने काळानुरुप नाट्यकलेत नवनवीन प्रयोग केले – ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-says-marathi-people-experimented-new-ways-of-performing-arts-mumbai-print-news-css-98-5158726/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : राज्य शासना तर्फे गतवर्षापासून आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव होणार</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ashish-shelar-announces-international-marathi-film-festival/32779</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>शून्य + शून्य = भोपळा; आशिष शेलारांचा मनसे-उबाठावर घणाघात</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/pune/pune-news-bjp-mumbai-president-ashish-shelar-strongly-criticized-the-opposition-while-speaking-to-moderates-in-pune-after-the-best-election-results-a-a1008/</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>“मुंबईकर उद्धव ठाकरेंना त्यांची जागा दाखवतील, मविआच्या ५० जागाही येणार नाही”; भाजपाचा दावा</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-and-said-mahayuti-to-win-upcoming-mumbai-municipal-corporation-election-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>विद्यार्थ्यांमधील असमानता दूर करण्यासाठी त्रिभाषा सूत्र स्वीकारले, मंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/maharashtra-three-language-formula-ashish-shelar-on-third-language-debate-schools-policy-mumbai-print-news-vsd-99-5179405/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>‘खालिद का शिवाजी’ चित्रपटासंदर्भात आशिष शेलार आक्रमक; सेन्सॉर बोर्डाचा उल्लेख केला, थेट फेरविचार करण्याचे आदेश..</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-is-aggressive-regarding-the-film-khalid-ka-shivaji-mumbai-print-news-phm-00-5285093/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: रघुजी भोसलेंची तलवार परत मिळवण्यात यश | Marathi News</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://lokmat.news18.com/videos/video/ashish-shelar-success-in-regaining-raghuji-bhosle-s-sword-marathi-news-1043330.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : मनसेच्या आंदोलनाची तुलना पहलगाम हल्ल्याशी; आशीष शेलारांचं मोठं विधान</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>शेलारजी फार डिंग्या मारू नका, बेस्ट निवडणुकीतही तुम्ही तीर मारले नाहीत. तुम्हाला</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>शिवाजी महाराजांच्या पराक्रमाची साक्ष असणारे किल्ले आमच्या ताब्यात द्या, राज्य</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-demand-to-asi-central-government-to-handover-forts-to-maharashtra-govt-raigad-archaeological-survey-of-india-marathi-news-1351013</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : ठाकरे बंधूंच्या विजय मेळाव्यावर आशीष शेलार यांची खोचक टीका</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>राज्य शासनातर्फे यंदा आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव, आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/marathi-film-festival-in-2025-ashish-shelar-announced-rajya-shasan-marathi-movie-nomination-a-a998/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>“सार्वजनिक गणेशोत्सव आता ‘महाराष्ट्र राज्य महोत्सव’”; आशिष शेलार यांची विधानसभेत घोषणा</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-is-now-maharashtra-state-festival-bjp-minister-ashish-shelar-announcement-in-the-vidhan-sabha-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>"राजकारणात फक्त आशिष शेलारांना ओळखते..."; ठाकरे बंधूंच्या मराठी मोर्चावर आशा भोसले काय म्हणाल्या?</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/filmy/in-politics-i-only-know-ashish-shelar-what-did-singer-asha-bhosle-say-about-the-raj-and-uddhav-thackeray-brothers-marathi-morcha-a-a629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>कान फिल्म फेस्टिव्हलमध्ये 'या' चार मराठी सिनेमांची झाली निवड, सांस्कृतिक मंत्री आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/four-marathi-films-have-been-selected-for-the-cannes-film-festival-announced-by-cultural-minister-ashish-shelar-a-a998/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>माहिती तंत्रज्ञान विभागातर्फे 4066 नवे आधार किट जिल्हाधिकाऱ्यांना देणार तुमच्या</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/4066-new-aadhaar-kits-will-be-given-to-district-collectors-by-information-technology-department-says-ashish-shelar-how-much-in-your-district-1341609</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>सांस्कृतिक मंत्री म्हणतात ” पोळा करा, शहरी नक्षलवाद संपवा”</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/wardha-to-end-urban-naxalism-traditional-festivals-like-bail-pola-must-be-celebrated-with-enthusiasm-adv-ashish-shelar-sud-02-5325172/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>राज ठाकरेंच्या ‘त्या’ टीकेला शेलारांचं खोचक प्रत्युत्तर; म्हणाले ज्यांना निवडून येता येत...</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रयत्न - आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/pune/efforts-to-get-unesco-cultural-status-for-ganeshotsav-ashish-shelar-a-a727/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>ते मुंबईतल्या लँड स्कॅमचे…बड्या नेत्याचे उद्धव ठाकरेंवर खळबळजनक आरोप!</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-said-uddhav-thackeray-is-baadshah-of-land-scam-amid-bmc-election-2025-1389756.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Mumbai News : मुंबईत १९ इमारतींचा पुनर्विकास, एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी घरं मिळणार</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment-latest-marathi-news-pp0731</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Ladki Bahin Movie : 'लाडकी बहीण' मोठ्या पडद्यावर झळकणार, चित्रपटात 'या' कलाकारांची लागली वर्णी</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/entertainment/ladki-bahin-movie-muhurat-cultural-minister-ashish-shelar-gives-clap-see-photos-list-of-actors-mukhyamantri-ladki-bahin-yojana-sm2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>धारावीची एक इंचही जागा अदानी यांना देणार नाही; शेलार यांनी स्पष्टच सांगितलं, नेमकं काय म्हणाले?</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/adani-will-not-be-given-an-inch-of-space-in-dharavi-what-exactly-did-shelar-say-1370721.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Amit Thackeray : मनसे-भाजप जवळीक वाढतेय? सख्ख्या मित्रांमधला दुरावा मिटला, अमित ठाकरे शेलारांच्या भेटीला; म्हणाले, राज साहेबांनी...</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/amit-thackeray-meets-ashish-shelar-amid-mns-shiv-sena-ubt-alliance-talks-on-raj-thackeray-uddhav-thackeray/articleshow/123466514.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>वाघनख्यानंतर आणखी एक ठेवा महाराष्ट्रात, नागपूरच्या रघुजीराजे भोसलेंची लंडनमधील</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Ganeshutsav : गणेशोत्सवासंदर्भात सर्वात मोठी बातमी, राज्य सरकारची मोठी घोषणा</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/ganeshotsav-declared-maharashtra-official-festival-announces-ashish-shelar-mumbai-pune-latest-marathi-nck90</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Chhatrapati Shivaji Maharaj: छत्रपती शिवाजी महाराजांच्या 'या' गडकिल्ल्यांना नामांकन; जागतिक वारसा यादीत स्थान मिळणार</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/chhatrapati-shivaji-maharaj-12-forts-place-on-unesco-world-heritage-list-said-maharashtra-government-minister-ashish-shelar-marathi-news-795328.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Ashish Shelar News: निवडणुका होऊ नयेत म्हणून कुणाचे प्रयत्न सुरू आहेत?, शेलारांचा कुणावर निशाणा?</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Amit Thackeray-Ashish Shelar : गणेशोत्सवासाठी ‘मनविसे’ आक्रमक; अमित ठाकरेंनी थेट आशिष शेलारांना भेटून केली</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://maharashtramirror.com/amit-thackeray-ashish-shelar-manvise-aggressive-for-ganeshotsav-amit-thackeray-directly-met-ashish-shelar-and-demanded-to-postpone-the-exams/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>गणेशोउत्सवात मुंबईकरांना खड्डांचा त्रास होणार नाही, यासाठी प्रशासनाने सणापूर्वी खड्डे भरावे, पालकमंत्री आशिष शेलारांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/mumbaikars-do-not-face-problem-due-to-potholes-during-ganesh-chaturthi-should-fill-the-potholes-before-festival-says-minister-ashish-shelar-05-693364</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>यंदा दहिहंडी उत्सव साजरा करण्यासाठी पालिका आगळावेगळा उपक्रम राबविणार, मंत्री आशिष शेलारांची माहिती</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/this-year-the-municipality-will-implement-a-unique-initiative-to-celebrate-dahihandi-festival-according-to-minister-ashish-shelar-05-688129?utm_source=website&amp;utm_medium=related&amp;utm_campaign=relatedpost</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार महाराष्ट्रात लवकरच येणार , सांस्कृतिक कार्यमंत्री आशिष शेलारांची माहिती</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/the-state-government-has-achieved-great-success-in-obtaining-the-historical-sword-of-the-brave-maratha-sardar-raghuji-bhosale-according-to-cultural-affairs-minister-ashish-shelar-05-675383</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Mumbai News: 'मुंबई में निर्दोष हिंदुओं को पहलगाम की तरह उनकी भाषा पूछकर पीटा गया', BJP नेता आशीष शेलार का चौंकाने वाला बयान</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>आम्ही तोडणारे नव्हे, तर जोडणारे- आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>NDTV Emerging Business: मुंबईत AI विद्यापीठ स्थापण करणार, आशिष शेलारांनी दिली माहिती</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र : आशीष शेलार का ठाकरे ब्रदर्स पर हमला, कहा- सिर्फ घर बैठकर करते हैं राजनीति</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>लोकमान्य तिलक का गणपति उत्सव बना राज्य उत्सव, जानिए मंत्री आशीष शेलार ने क्या कहा</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : “तुम्हारे पाँव के नीचे कोई जमीन नही…”, आशिष शेलारांचा शेरोशायरीतून उद्धव ठाकरेंवर हल्लाबोल</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/bjp-mumbai-president-ashish-shelar-criticizes-uddhav-thackeray-and-mahavikas-aghadi-politics-gkt-96-4820917/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला, आशिष शेलारांचे वक्तव्य</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र के स्कूलों में हिंदी जरूरी? विवाद पर देवेंद्र फडणवीस का बड़ा फैसला, जानें क्या बोले आशीष शेलार</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray &amp; Ashish Shelar: उद्धव ठाकरे हा मुंबईतील लँड स्कॅमचा बादशाह आशिष शेलारांनी दुसऱ्या</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>सरकारच्या विभागांमधील रिक्त पदे नेमकी किती? मंत्री आशिष शेलार यांनी विधान परिषदेत दिली माहिती</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/information-technology-minister-ashish-shelar-announced-that-these-vacant-posts-will-be-filled-through-mahabharti-phm-00-5219670/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Nagpur Film City: नागपुरातील फिल्मसिटीची जागा ठरली! मुंबई, कोल्हापूरनंतर उपराजधानीत 128</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>‘खालिद का शिवाजी’मुळे भावना दुखावतायत तर कान्सला का पाठवला? आशिष शेलार स्पष्टीकरण देत म्हणाले….</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-explain-why-govt-sent-khalid-ka-shivaji-movie-to-cannes-film-festival-2025-asc-95-5290043/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>मराठी चित्रपट योग्य दरात घेण्याची नेटफ्लिक्सला सूचना : ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/maharashtra-state-film-awards-ashish-shelar-discusses-marathi-cinema-pricing-with-netflix-mumbai-print-news-rds-00-5283289/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>धारावीतील एक इंचही जागा ‘अदानी’ला देणार नाही, मंत्री आशीष शेलार यांची ग्वाही</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-assures-that-not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-mumbai-print-news-ssb-93-4964971/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>“शहरी नक्षलवाद्यांचा डाव हाणून पाडू, गणेशोत्सव धुमधडाक्यात साजरा करू”: आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/maharashtra/bjp-ashish-shelar-said-celebrate-ganeshotsav-on-big-scale-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : राज ठाकरेंसोबतच्या मैत्रीचा प्रश्न, आशिष शेलारांनी दोन शब्दात संपवला विषय</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-speak-on-issue-of-mumbai-potholes-friendship-with-raj-thackeray-sanjay-raut-letter-india-pakistan-match-1476373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>'खालिद का शिवाजी' चित्रपटावरून आशिष शेलार आक्रमक; सेन्सॉर बोर्डाला धारेवर धरत घेतला मोठा निर्णय</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Raj Thackeray &amp; Ashish Shelar: आम्ही अन्नपाणी सोडलंय, आम्हाला खूप दु:ख झालंय आशिष शेलारांनी राज</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>BJP : भाजपच्या दोन गटांमध्ये मुंबईत तुफान हाणामारी, आशिष शेलारांसमोरच कार्यकर्ते भिडले, Video</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/mumbai/bjp-supporters-fight-with-each-other-in-front-of-ashish-shelar-in-mumbai-watch-video-1414857.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>मुंबई महापालिकेचा महापौर महायुतीचा होणार संजय राऊत यांच्या बुद्धिमतेची चाचणी</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>रवी परांजपे यांचा चित्रठेवा शासनाकडून जतन; सांस्कृतिकमंत्री आशिष शेलार यांच्या उपस्थितीत सामंजस्य करारावर स्वाक्षरी</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/pune/signing-of-mou-by-ashish-shelar-on-preservation-of-ravi-paranjpe-paintings-pune-print-news-amy-95-5319485/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>उद्धव ठाकरे यांच्या काळापेक्षा रस्ते कामाचा वेग अधिक; पालकमंत्री ऍड. आशिष शेलार यांचे मत</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-slams-uddhav-thackeray-over-concrete-road-construction-mumbai-print-news-zws-70-5098492/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>आताची सर्वात मोठी बातमी! मनसे नेते अमित ठाकरे आशिष शेलार यांच्या भेटीला</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>“पहलगाममध्ये धर्म विचारुन गोळ्या घातल्या अन् इथे भाषा विचारुन…”; आशिष शेलारांचा...</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-controversy-bjp-leader-aashish-shelar-target-thackeray-brothers-rally-1439702.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार दोन दिवसांआधी राज</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : राज ठाकरे-उद्धव ठाकरे युतीच्या चर्चे दरम्यान आशिष शेलारांचे मोठं वक्तव्य; म्हणाले, "आता वैयक्तिक संबंधही संपले"</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-says-his-personal-relationship-with-raj-thackeray-has-ended-amid-talks-of-mns-and-uddhav-thackerays-shiv-sena-alliance-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव आता, महाराष्ट्र राज्य महोत्सव विधानसभेत घोषणा, आशिष शेलार म्हणाले</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>प्रस्तावित वांद्रे-कुर्ला मार्गिकेचे संरेखन रद्द का? आशिष शेलार यांचे ‘एमएमआरडीए’ला अवहाल देण्याचे आदेश</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-orders-mmrda-to-take-cognizance-of-the-proposed-bandra-kurla-corridor-mumbai-print-news-amy-95-5175404/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>‘पुरातत्व’कडील गडकिल्ले राज्याकडे देण्याची विनंती; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे पत्र</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-letter-to-union-minister-demanded-to-handed-over-forts-in-maharashtra-to-state-government-zws-70-4975719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : “राज ठाकरेंशी वैयक्तिक संबंध होते ते आता संपले…”, आशिष शेलार यांचं वक्तव्य</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-said-friendship-with-raj-thackeray-is-now-over-what-he-said-scj-81-5033142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>मुंबईत घरे देण्यासाठी आता थेट मुख्यमंत्र्यांनाच साकडे; संयुक्त बैठकीचे आशिष शेलार यांचे गिरणी कामगार एकजुटीला आश्वासन</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-now-directly-appeals-to-chief-minister-devendra-fadnavis-to-provide-houses-to-mill-workers-in-mumbai-mumbai-print-news-phm-00-5061388/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>खोक्याभाईचे काय घेऊन बसलात, विधानसभेत सगळे तेच भरलेत: राज ठाकरेंचा सरकारला टोला, भाजप नेते आशिष शेलारांनीही...</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : “निवडणुकीत हरणार म्हणून कुटुंब तहात…”, ठाकरे बंधूंच्या मेळाव्यानंतर भाजपाची पहिली प्रतिक्रिया; शेलार म्हणाले, “भाऊबंदकी…”</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-on-mns-raj-thackeray-and-shivsena-ubt-uddhav-thackeray-victory-rally-in-mumbai-politics-gkt-96-5206150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>पारंपारिक गोंदण कलेचा समावेश कला अभ्यासक्रमात; सांस्कृतिक कार्य मंत्री ॲड आशिष शेलार यांच्या सूचना</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-adv-ashish-shelar-instructions-regarding-tattoo-art-courses-mumbai-print-news-amy-95-5196545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>“आशिष शेलार माझ्याव्यतिरिक्त कोणालाच छळत नाहीत”, देवेंद्र फडणवीसांचं वक्तव्य</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-says-ashish-shelar-not-bothering-anyone-except-me-asc-95-4973334/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Uddhav Thackeray: " ...तर उध्दव ठाकरेंना 'बेईमान ऑफ द महाराष्ट्र' अवॉर्ड द्यावा लागेल!"; भाजप मंत्र्यांचं वादग्रस्त विधान</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-controversial-remark-uddhav-thackeray-dishonest-of-maharashtra-award-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: “मित्र म्हणून तुम्हाला सल्ला देतो की…”, राज ठाकरेंनी निकालावर संशय घेताच भाजपाचा पलटवार</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/bjp-leader-ashish-shelar-slams-raj-thackeray-over-his-speech-alleges-his-fake-narrative-kvg-85-4859728/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>मुंबईतच घरे हवीत… गिरणी कामगार पुन्हा आक्रमक…आशिष शेलार यांच्या वांद्रे कार्यालयावर २७ एप्रिल रोजी मोर्चा</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>गडकिल्ल्यांच्या संवर्धनासाठी शासन सक्षम: मंत्री आशिष शेलार यांचे राज ठाकरेंना उत्तर, म्हणाले - जागतिक वारशा...</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>राज ठाकरे - आशिष शेलार यांच्या मैत्रीत दुरावा; शेलार म्हणाले, "माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला"</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/ashish-shelar-says-friendship-with-raj-thackeray-over-amid-mns-shiv-sena-ubt-alliance-maharashtra-news-mhs25042004504</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>प्रयोगात्मक कलांसाठी पु.ल. देशपांडे अकादमीमध्ये शाहीर साबळेच्या नावाने संशोधन केंद्र; सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announces-research-center-named-after-shahir-sable-at-p-l-deshpande-academy-mumbai-print-news-amy-95-5170476/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>युनेस्कोच्या यादीत 12 किल्ले मोदी सरकारचे कान टोचणाऱ्या राज ठाकरेंना मंत्री</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Video: मोठी बातमी! अमित ठाकरेंनी घेतली भाजपाच्या आशिष शेलारांची भेट; दोन दिवसांपूर्वीच राज ठाकरेंनी घेतली होती फडणवीसांची भेट</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-after-meeting-he-says-kvg-85-5325003/</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>जिथं तुरुंगवास तिथंच सावरकरांचं भव्य स्मारक मंत्री आशिष शेलार यांची घोषणा,</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : रायगडच्या पालकमंत्री पदाचा तिढा अमित शाह नाहीतर यांच्या अखत्यारितला? आशिष शेलारांनी थेट नावच सांगितलं</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/raigad-guardian-minister-dispute-to-be-decided-by-devendra-fadnavis-says-ashish-shelar-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>वांद्रे येथे राज्याचे नवीन महापुराभिलेख भवन, सांस्कृतिक कार्यमंत्री आशीष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>के. बी. भाभा रुग्णालयाच्या विस्तारित इमारतीचे लोकार्पण!</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-inaugurated-newly-expanded-khurshedji-behramji-bhabha-hospital-in-bandra-on-wednesday-mumbai-print-news-sud-02-4872371/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>मुंबई तुंबण्यावरून आशिष शेलार यांची ठाकरे गटावर टीका, वीस वर्षातील कामांची श्वेतपत्रिका काढण्याची पालिका आयुक्तांकडे मागणी</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-alleged-uddhav-thackeray-group-has-been-dishonest-with-mumbaikars-on-wednesday-mumbai-print-news-sud-02-5119394/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार ताब्यात; १८ ऑगस्टला मुंबईत दाखल : आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/in-mumbai-ashish-shelar-to-bring-maharashtra-auction-win-of-maratha-sword-on-august-18-mumbai-print-news-rds-00-5297158/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>मुंबई अध्यक्षपदावरून भाजपमध्ये तिढा; आशिष शेलारांकडे पद कायम राहणार?</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/politics/bjp-undecided-on-mumbai-president-ahead-of-elections-print-politics-news-ocd-94-5259220/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>“राज्य महोत्सव गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभाग वाढवावा”: आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/every-government-department-should-increase-participation-in-the-state-festival-of-ganeshotsav-said-bjp-minister-ashish-shelar-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>शेलार मामाला पोटदुखी सुरू झाली आहे, मनसे प्रवक्ता गजानन काळेंची पोस्ट चर्चेत</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/thane/gajanan-kale-counterattacks-ashish-shelar-on-uddhav-thackeray-raj-thackeray-alliance-vsd-99-5206583/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : मराठा सरदार रघुजीराजे भोसलेंची ऐतिहासिक तलवार १५ ऑगस्टच्या आधी महाराष्ट्रात आणणार, मंत्री आशिष शेलार यांची माहिती</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-sai-historic-sword-of-the-brave-maratha-sardar-raghuji-raje-bhosale-to-return-to-maharashtra-before-august-15-scj-81-5212150/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Asha Bhosle : राजकारणात मला फक्त आशिष शेलार माहिती; ठाकरे बंधूंवरील प्रश्नावर आशा भोसलेंचं उत्तर</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/famous-singer-asha-bhosle-comment-on-raj-uddhav-thackeray-morcha-in-mumbai-on-hindi-language-impose-912626.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र क्वांटम विज्ञान व तंत्रज्ञानाचे आंतरराष्ट्रीय वर्ष साजरे करणार – मंत्री ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>https://www.mahasamvad.in/154669/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>BJP Mumbai President :बीएमसी निवडणुकीआधी भाजपने भाकरी फिरवली, शेलारांना नारळ, मुंबईची धुरा कोणाकडे?</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>लोककलांना पुनरुज्जीवन करणे गरजेचे : ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/thane/in-thane-bjp-mla-ashish-shelar-says-need-to-revive-folk-arts-css-98-4953399/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>संगीत नाटकांसाठी रवींद्र नाट्य मंदिर २५ टक्के सवलतीत उपलब्ध होणार; ॲड.आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announced-that-ravindra-natya-mandir-will-be-available-at-a-25-percent-discount-mumbai-print-news-phm-00-5232212/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>“परिस्थितीच्या माऱ्याने दोघे एकत्र, आता नवा चित्रपट…”, आशिष शेलारांचा ठाकरे बंधूंना चिमटा; सिनेमाचं नावंही सांगितलं!</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-slams-raj-and-uddhav-thackeray-mentions-zenda-and-yek-number-movie-asc-95-5217275/</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>"मी फक्त आशिष शेलारांना ओळखते, बाकी कोणा राजकारण्याला ओळखत नाही", ठाकरे बंधूंच्या युतीवर आशा भोसलेंचं विधान</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>कातळशिल्पांचा ‘जागतिक वारसा स्थळा’च्या यादीत समावेशासाठी रोडमॅप तयार करा, मंत्री आशिष शेलार यांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/prepare-a-roadmap-for-the-inclusion-of-rock-sculptures-in-the-world-heritage-site-list-directed-by-minister-ashish-shelar-scj-81-5114434/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>महाराष्ट्राच्या राजकारणात उद्धव ठाकरेंची सर्वात मोठी बेईमानी; आशिष शेलार यांची जोरदार टीका</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-strongly-criticizes-uddhav-thackeray-over-tree-cutting-in-mumbai-zws-70-5151721/</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Ganeshotsav State Festival : गणेशोत्सव आता 'राज्य उत्सव'... शेलारांची मोठी घोषणा, उत्सव निर्बंध मुक्त अन् 500 कोटींचा निधी</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>पैठणीचे व्हिक्टोरिया अल्बर्ट संग्रहालयामध्ये प्रदर्शन, सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची विनंती मान्य</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: ठाकरे बंधूंचा एकत्र मोर्चा; आशिष शेलार थेटच म्हणाले…</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5187751/thackeray-brothers-raj-thackeray-and-uddhav-thackeray-protest-against-state-government-over-hindi-launguage-ashish-shelar-gave-a-reaction/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>"महाराष्ट्रद्वेष हाच भाजपाचा खरा डीएनए", शेलार व निशिकांत दुबेंच्या वक्तव्यावरून आदित्य ठाकरेंचा संताप</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/aditya-thackeray-says-hate-for-maharashtra-is-true-dna-of-bjp-over-nishikant-dubey-ashish-shelar-statement-asc-95-5211821/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meet Ashish Shelar : अमित ठाकरे घेणार शेलारांची भेट, कारण गुलदस्त्यात</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/amit-thackeray-meet-ashish-shelar-bjp-minister-mns-party-leader/914757/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>‘खालिद का शिवाजी’ची स्तुती करणारे मंत्री शेलार आता कारवाई का करतायत? विरोधकांचा सरकारमधील लोकांवर संशय</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/khalid-ka-shivaji-rohit-pawar-oppess-ashish-shelar-action-against-marathi-movie-asc-95-5289901/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>आशिष शेलारांचा पर्यावरणवाद्यांवर बनावट हिंदू सणविरोधी असल्याचा ठपका, पर्यावरणवाद्यांकडूनही खरपूस समाचार</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nagpur/cultural-minister-ashish-shelar-calls-environmentalists-anti-hindu-phm-00-5246668/</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>राजकारणातले सच्चे मित्र दुरावले? आशिष शेलार आणि राज ठाकरेंमध्ये दुरावा?</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/ashish-shelar-still-upset-with-his-friens-mns-president-raj-thackeray/934652</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>चित्रकार रवी परांजपे यांच्या कलाकृती मंत्री ॲड. आशिष शेलार यांच्या उपस्थितीत शासनाकडे सुपूर्द</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176545/</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>टीका करताना शेलारांचा तोल सुटला! मनसे कार्यकर्त्यांची पहलगामच्या दहशतवाद्यांशी तुलना; म्हणाले, त्यांनी...</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/bjp-ashish-shelar-compare-raj-thackeray-mns-workers-with-pahalgam-terrorist-after-shivsena-victory-rally-vijayi-melava-in-mumbai-with-uddhav-thackeray/921560</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>महापालिका निवडणुकीच्या तोंडावर भाजपमधील धुसफुस चव्हाट्यावर, आशीष शेलार यांच्यासमोरच हाणामारी, खडाजंगी</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/bjp-workers-clashed-with-each-other-in-front-of-minister-ashish-shelar-in-kandivali-zws-70-5156138/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Ashish Shelar And Mungantiwar : मुनगंटीवार म्हणाले, मी देखील चुकून काही काळ, आशिष शेलारांनीच दिले उत्तर</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>गणेशोत्सवात यंदा सात दिवस रात्री उशिरापर्यंत ध्वनिक्षेपक? मंत्री शेलारांनी स्पष्टच सांगितले…!</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/pune/pune-ashish-shelar-says-district-collectors-can-allow-loudspeaker-use-till-midnight-during-ganeshotsav-pune-print-news-rds-00-5320532/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!entertainment/publication-of-the-biography-book-manik-moti-based-on-the-veteran-singer-manik-verma-maharashtra-news-mhs25051306533</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Ganesh visarjan guidelines : उंच गणेशमूर्तींच्या विसर्जनाबाबत 30 तारखेपर्यंत भूमिका मांडणार</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/tall-ganesh-idol-immersion-guidelines-2025-ab96</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>पवई व तुळशी तलावातील गाळ काढण्यासाठी तीन महिन्यांत कृती आराखडा तयार करा; मुंबई उपनगर पालकमंत्री आशिष शेलार यांचे आदेश</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/mumbai-suburban-guardian-minister-ashish-shelar-order-regarding-removal-of-silt-from-powai-and-tulsi-lakes-mumabi-print-news-amy-95-5183942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>राज ठाकरेंशी संबधित ‘येक नंबर’ हिट की फ्लॉप? शेलारांची थेट विधीमंडळात माहिती, बजेट व बॉक्स ऑफिस कलेक्शनची तुलना करत म्हणाले…</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/raj-thackeray-yek-number-movie-box-office-collection-ashish-shelar-teases-at-assembly-monsoon-session-asc-95-5217195/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: मनसेकडून ठाकरे गटाला निमंत्रण दिल्यानं भाजप नाराज प्रतिसभागृहात सहभागी</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>विमान सुरक्षेसाठी पक्ष्यांचा वावर कमी करण्याच्या नव्या संकल्पना शोधण्याचे मुंबई उपनगर पालकमंत्री ॲड आशिष शेलार यांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-instructed-to-find-new-concepts-to-reduce-bird-strike-on-aircraft-zws-70-5186222/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>चित्रनगरीतील कामांची पाहणी मंत्री आशिष शेलार यांनी केली.</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-minister-ashish-shelar-inspected-ongoing-works-in-chitranagari-ocd-94-5192132/</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>नालेसफाईच्या कामात यंदाही घोटाळा,उपनगर पालकमंत्री ॲड. आशिष शेलार यांचा आरोप</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/mumbai-bmc-administration-scam-has-been-revealed-in-drain-cleaning-work-this-year-as-well-mumbai-print-news-sud-02-5079088/</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>साताऱ्यातील ‘फाशीचा वड’ स्थळाच्या राज्य स्मारकासाठी प्रस्ताव पाठवावा, मंत्री आशिष शेलार यांची सूचना</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-on-satara-s-fashicha-wad-state-memorial-proposal-css-98-5153794/</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Prakash Mahajan : ‘पाळीव प्राण्यापासून सर्वच अस्वस्थ अन् शोकाकूल’, शेलारांनी राज...</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/bjp-ashish-shelar-mocks-mns-leader-prakash-mahajan-raj-thackeray-friendship-1389288.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>‘राज्य महोत्सव’ गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी - सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/176672/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव आंतरराष्ट्रीय पातळीवर पोहचविणार, सांस्कृतिक कार्यमंत्री आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announcement-in-assembly-session-ganeshotsav-international-level-publicity-asj-82-5238641/</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>गणेशोत्सवाला राज्य महोत्सवाचा दर्जा, गणेशभक्तांमध्ये उत्साहाचे वातावरण</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>पीओपी गणेश मूर्तींवर बंदीला काँग्रेस जबाबदार, सांस्कृतीक कार्य मंत्री आशिष शेलार यांचा आरोप</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-alleged-congress-and-mahavikas-aghadi-for-conspired-to-ban-pop-ganesh-idols-sud-02-5242178/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>महेश मांजरेकरांना व्ही. शांताराम जीवन गौरव पुरस्कार, तर विशेष योगदान पुरस्काराने होणार मुक्ता बर्वेचा सन्मान; आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/manoranjan/mahesh-manjrekar-shantaram-jeevan-gaurav-award-mukta-barve-to-be-honored-with-special-contribution-award-announced-by-ashish-shelar-scj-81-5026480/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>उद्धव ठाकरेंचा तो नेता भाजपाच्या दरबारात; चर्चांना उधाण, म्हणाला मी आमदार झाल्यापासून...</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/mumbai/shivsena-uddhav-thackeray-mla-mahesh-sawant-attends-janta-darbar-of-bjp-leader-ashish-shelar/930835</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>मुंबईत भरणार देशातील पहिला ‘रेडिओ’ महोत्सव - आशिष शेलार यांची घोषणा; मराठी भाषा आणि कलाकारांसाठी नवे व्यासपीठ</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/6/17/maharashtra-radio-festival-for-the-first-time.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>BJP MNS Friendship: हिंदी सक्तीच्या निर्णयावरुन भाजप-मनसेची मैत्री तुटणार? राजकीय वॉर सुरु</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Mumbai News : मोठी बातमी! एल्फिन्स्टन पुलाच्या परिसरातील 19 इमारतींमधील सर्व रहिवाशांना त्याच ठिकाणी घरे मिळणार</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment/articleshow/120695379.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Thackeray : ठाकरे पितापुत्र भाजपा नेत्यांच्या भेटीला, नेमकं कारण काय?</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/thackeray-father-and-son-meet-bjp-leaders-what-is-the-real-reason-281903/amp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>मुंढेगाव चित्रनगरीविषयी अधिवेशनानंतर बैठक; आशिष शेलार यांचे अजित पवार गटाला आश्वासन</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/nashik/dadasaheb-phalke-film-city-to-come-up-at-igatpuri-near-nashik-cultural-development-vsd-99-5218532/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>वांद्रे येथे पहिले बालकुमार साहित्य संमेलन, सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते १० फेब्रुवारीला संमेलनाचे उद्घाटन</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/national-library-and-maharashtra-state-sahitya-sanskrit-mandal-organize-balakumar-sahitya-sammelan-on-february-10-mumbai-print-news-sud-02-4876644/</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>गणेशोत्सवाला राज्य महोत्सव दर्जाच्या निर्णयाचे स्वागत; गणेश मंडळाच्या पदाधिकाऱ्यांकडून आंनदोत्सव</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/pune/ganesh-mandal-office-bearers-celebrate-with-joy-over-decision-to-grant-state-festival-status-to-ganeshotsav-pune-print-news-phm-00-5219942/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>राहुल गांधींच्या डोक्यातील चीप चोरीला गेली; मुख्यमंत्री देवेंद्र फडणवीस यांची बोचरी टीका</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-criticizes-rahul-gandhi-mumbai-print-news-phm-00-5288682/</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी मिळणार घरे; मुख्यमंत्री फडणवीसांच्या बैठकीत निर्णय</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/mmrda-to-redevelop-19-buildings-near-elphinstone-bridge-a-a1001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र जिंकला, मराठी माणूस जिंकला, भाजप जिंकला: मंत्री आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-wins-marathi-people-win-bjp-wins-says-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy/articleshow-odudhrc</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>आशिष शेलार यांना ‘नाफा’ मराठी चित्रपट महोत्सवाचे विशेष निमंत्रण !</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>आशिष शेलार यांचे आवाहन,“राज्य महोत्सवा” करिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>“राज्य महोत्सव” गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी – सांस्कृतिक कार्य मंत्री आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Pune Ganesh Festival 2025 : पुण्यातील मंडळांनी लक्ष द्या! सांस्कृतिक मंत्र्याच्या अध्यक्षतेखाली बैठक, कोणते मोठे निर्णय झाले? जाणून घ्या...</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>आग्र्यावरून सुटकेचा दिवस ‘शिवचातुर्य दिन’ म्हणून साजरा होणार; मंत्री Ashish Shelar यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Maharashtra: एमवीए के अंत को लेकर अपनी भविष्यवाणी पर आशीष शेलार बोले- सच साबित हुई, घोषणा की औपचारिकता बाकी</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/maharashtra-minister-ashish-shelar-says-my-prediction-about-mva-end-come-true-2025-02-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>'मुंबई में हिंदुओं को भाषा के कारण पीटा', BJP नेता आशीष शेलार ने पहलगाम हमले से की थप्‍पड़कांड की तुलना</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>सैफ अली खान पर हमले के बाद मंत्री आशीष शेलार का बड़ा बयान, 'बॅालीवुड वालों डरना...'</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>मंत्री आशीष शेलार के 'मराठी और पहलगाम' वाले बयान पर भड़के संजय राउत, बोले- 'भाषा</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Maharashtra won, Marathi Manus won, BJP won in this fight, says BJP Mumbai chief Ashish Shelar slams MVA over three-language policy issue</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Maharashtra: मुंबई में जलभराव पर सियासत तेज, मंत्री आशीष शेलार ने कर दी बड़ी मांग, उद्धव</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में 'खालिद का शिवाजी' मूवी को बैन करने की मांग के बीच मंत्री आशीष शेलार का बड़ा बयान, जानें क्या कुछ कहा?</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>मुंबई: मंत्री की मौजूदगी में BJP कार्यकर्ताओं के दो गुटों में हिंसक झड़प, हिरासत में लिए गए देवांग दवे</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Maharashta: भाजपा नेता आशीष शेलार ने की हिंदी भाषी लोगों पर हमले की निंदा, पहलगाम आतंकी हमले से की तुलना</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-2025-07-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>‘इन गानों को नियमित रूप से बजाएं’, प्राइवेट रेडियो स्टेशनों से महाराष्ट्र के</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Marathi School in USA: अमेरिकतील मराठी शाळांना महाराष्ट्र शासन अभ्यासक्रम पुरवणार, आशिष शेलार यांचे आश्वासन</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>BJP नेता आशीष शेलार का उद्धव ठाकरे पर गंभीर आरोप, 'मुंबई में जितने भी जमीन से जुड़े</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>मुंबई की सड़कों के सारे गड्ढे भरेगी बीएमसी, आशीष शेलार का ऐलान</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>'पहलगाम की तरह महाराष्ट्र में भी...', MNS कार्यकर्ताओं की गुंडागर्दी पर महाराष्ट्र के मंत्री ने कसा तंज - Maharashtra Minister Ashish Shelar Compares Violence with Pahalgam Terror Attack amid Marathi Language Controv</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Maharashtra Language Row: Ashish Shelar के बयान से सियासी संग्राम, Aaditya Thackeray का पलटवार!</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>राज-उद्धव ठाकरे के साथ आने पर BJP का बड़ा बयान- 'जब वह मुख्यमंत्री थे तो...'</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Maharashtra: IT विभाग में 1000 करोड़ के घोटाला का दावा, मंत्री आशीष शेलार का एक्शन, अफसर को</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>एकनाथ शिंदे के सम्मान को लेकर शरद पवार पर भड़की शिवसेना-यूबीटी तो BJP ने कसा तंज,</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Politics: 'राहुल गांधी के दिमाग की चिप चोरी और हार्ड डिस्क करप्ट हो गई', EC पर धांधली के आरोपों पर बोले फडणवीस</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-election-commission-allegations-devendra-fadnavis-ashish-shelar-response-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>इतिहास से छेड़छाड़ बर्दाश्त नहीं की जाएगी... विवादों में घिरी फिल्‍म 'खालिद का शिवाजी' पर मंत्री आशीष शेलार</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>‘हिंदुओं पर उनकी भाषा के कारण हमला…’, महाराष्ट्र सरकार के मंत्री ने मराठी विवाद को पहलगाम से जोड़ा</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>रघुजी भोसले की पौराणिक तलवार लौटेगी भारत, आशीष शेलार ने जताई खुशी</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Cannes: कान फिल्म फेस्टिवल के लिए चयनित हुईं चार मराठी फिल्में, मंत्री आशीष शेलार ने दी सभी को बधाई</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>मुंबई में हिंदी भाषा के कारण पीटा… मंत्री आशीष सलार ने पहलगाम आतंकी हमले से की तुलना</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-hindi-speaker-attacks-bjp-ashish-shelar-condemns-violence-compares-to-pulwama-3376913.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Asha Bhosle News: 'मी फक्त आशिष शेलारांना ओळखते..', ठाकरे बंधुंच्या मनोमिलनावर आशा भोसले काय म्हणाल्या?</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>भाषा विवाद पर महाराष्ट्र में तनाव, मंत्री आशीष शेलार ने की पहलगाम हमले से तुलना</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://hindi.asianetnews.com/state/maharashtra/ashish-shelar-compares-pahalgam-terror-attack-marathi-hindi-row-controversy/articleshow-ma03grc</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>मराठी पर बवाल जारी! रोहित पवार ने पंडित धीरेंद्र शास्त्री को दे दी चेतावनी- 'जहां</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>फडणवीस इफेक्ट या ठाकरे इम्पैक्ट? आशीष शेलार की जगह अमित साटम को मुंबई BJP की कमान के पीछे क्या</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/amit-satam-mumbai-bjp-new-president-cm-devendra-fadnavish-ashish-shelar-civic-polls-ntcpbt-rpti-2318125-2025-08-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>तणावाच्या परिस्थितीमुळे माहिती तंत्रज्ञान आणि सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचा दौरा रद्द</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/165514/</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>सर्वात मोठी बातमी ! गणेशोत्सव महाराष्ट्राचा महोत्सव म्हणून घोषित; आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-declares-ganeshotsav-as-state-festival-bjp-leader-ashish-shalar-announcement-1442515.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>मुंबई भाजपा पदाधिकाऱ्यांमध्ये राडा; आशिष शेलार कारमधून उतरताच दोन गटांत हाणामारी</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/mumbai-bjp-office-bearers-clash-in-front-of-ashish-shelar-car-a-fight-broke-out-between-two-groups-at-kandivali-a-a629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>देवेंद्र फडणवीस से मिले राज ठाकरे, अब बेटे अमित ठाकरे की आशीष शेलार से मुलाकात, महाराष्ट्र में कुछ पक रहा है?</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार; दोन दिवसांआधी राज ठाकरेंनीही देवेंद्र फडणवीसांची घेतली होती भेट</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>BJP on Raj Uddhav Alliance: ठाकरे बंधूंच्या एकत्र येण्याची पोस्ट अमित शाहांना टॅग केली, आशिष</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Big announcement: मराठ्यांच्या पराक्रमाची साक्ष असलेली ऐतिहासिक तलवार लवकरच महाराष्ट्रात येणार</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Clerk-Typist Exam Result: लिपिक-टंकलेखक परीक्षेचा निकाल कधी लागणार? आशिष शेलारांनी दिली माहिती</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>आपले सरकार सेवा केंद्रांच्या संख्येत वाढ – माहिती तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/160573/</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>भजनी मंडळांना २५ हजारांचे अनुदान; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची माहिती</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-bhajani-mandals-grant-25000-ashish-shelar</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>स्थानीय राजनीति को इंटरनेशनल मुद्दों से नहीं जोड़ना चाहिए… संजय राउत के बयान पर बोले शरद पवार</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://www.tv9hindi.com/india/maharashtra-bjp-leader-ashish-shelar-sharad-pawar-reaction-on-sanjay-raut-over-all-party-delegation-row-3297804.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Hindi Controversy: 'मराठी'वरुन दहशतवाद्यांशी तुलना, आशिष शेलारांच्या वक्तव्याचा मनसेकडून समाचार</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>शिवसेना UBT की हालत मुंबई की 'खतरनाक' और 'जर्जर' इमारतों जैसी, महाराष्ट्र के मंत्री आशीष शेलार ने कसा तंज</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र में कुछ होने वाला है बड़ा? पहले CM फडणवीस से मिले राज ठाकरे, अब बेटे ने BJP नेता से की मुलाकात</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/hindi/india/maharashtra-politics-amit-thackeray-met-minister-ashish-shelar-after-raj-thackeray-meeting-with-cm-fadnavis/2893316</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>नागरिकांना डिजिटल सेवा देण्यासाठी शासन प्रयत्नशील – मंत्री ॲड.आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/159784/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>हिंदी भाषा सक्ती प्रकरण: महाराष्ट्रात सक्ती फक्त मराठीची, हिंदीची नाही पण... : आशिष शेलार यांनी मांडली भूमिका</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/only-marathi-is-compulsory-in-maharashtra-says-minister-ashish-shelar-on-hindi-language-controversy-maharashtra-news-mhs25062401471</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>मुंबईत उभारणार सांस्कृतिक केंद्र आणि वस्तुसंग्रहालय: आशिष शेलारांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-cultural-center-and-museum-to-be-set-up-in-bkc-mumbai-said-minister-ashish-shelar-in-assembly-budget-session-2025-maharashtra-news-mhs25031900644</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>NDTV Emerging Business Conclave : "उद्धवजींची अवस्था पाहता महायुतीचा विजय पक्का"; आशिष शेलारांचा निशाणा</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Marathi Language Controversy : भाषा वादावर आशिष शेलारांचं मोठं विधान; मनसैनिकांची थेट पहलगाममधील दहशतवाद्यांशी तुलना</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Emerging Business Conclave : 'तुम्ही काय केलं, ठाकरे बंधूंना सवाल'; शेलारांनी 1995 पासून कामाचा पाढाच वाचला</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>महराष्ट्र में राजकीय उत्सव के रूप में मनाया जाएगा गणेशोत्सव, संस्कृति मंत्री आशीष शेलार ने विधानमंडल में किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>शिवसेना UBT के दो पूर्व पार्षद BJP में शामिल, मुंबई में उद्धव ठाकरे को फिर बड़ा झटका, शेलार ने छोड़े तीर</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Kishori Pednekar : ठाकरेंना ‘लँड माफिया’ म्हणताच पेडणेकरांकडून ‘झोलर’ची आठवण,...</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Ganeshotsav 2025: गणेशोत्सव महाराष्ट्र राज्याचा महोत्सव म्हणून घोषित; आशिष शेलार यांची विधानसभेत माहिती</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा; आशिष शेलार यांचे अधिकाऱ्यांना निर्देश</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Pen News : रायगडमध्ये पालकमंत्रिपद वादात, भाजपचे संपर्कमंत्री वेगात, मूर्तिकारांच्या प्रश्नाच्या निमित्ताने आशिष शेलार सक्रिय</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव को 'राज्य उत्सव' के रूप में मनाने की तैयारी - मंत्री एडवोकेट आशीष शेलार की घोषणा</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/hi/festivals/preparations-to-celebrate-ganeshotsav-as-state-festival-announcement-by-minister-advocate-ashish-shelar-89618</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Ganeshotsav: गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रस्ताव सादर करणार; आशिष शेलार यांची माहिती</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/pune/unesco-cultural-status-proposal-for-ganeshotsav-ashish-shelar-sb97</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>'पहलगामसारखं मुंबईत निष्पाप हिंदूंना भाषा विचारुन चोपलं', आशिष शेलार यांचं धक्कादायक वक्तव्य</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>उद्धव ठाकरे हे मुंबईतील लँड स्कॅमचे बादशहा: त्यांच्या डोक्यात सतत स्कॅमचेच विचार येतात, भाजप नेते आशिष शेला...</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/ashish-shelar-says-uddhav-thackeray-land-scam-king-in-mumbai-politics-134886158.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ठाकरे बंधुमुळे भाजप अलर्ट मोडवर मुंबईच्या प्रत्येक वॉर्डमधील आढावा घेतला जाणार,</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ठाकरेंना ज्यांनी धूळ चारली त्या जोडीला भाजपकडून मोठी जबाबदारी, आशिष शेलार यांची सर्वात मोठी घोषणा</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>निवडणुका आणि सत्तेसाठी पक्ष फोडता, भ्रष्टाचाऱ्यांना शुद्ध करून पक्षात घेता,</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Mumbai Politics: आशिष शेलारांच्या वक्तव्यावर बाळा नांदगावकरांचे प्रत्युत्तर, म्हणाले...</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/bala-nandgaonkar-hits-back-at-ashish-shelar-statement-mk94</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Asha Bhosle : ठाकरे बंधू एकत्र येणार? सवाल करताच आशा भोसले थेट म्हणाल्या, मला फक्त आशिष शेलार…</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>मराठी माणसांची तुलना पहलगाम अतिरेक्यांशी उद्धव ठाकरेंचा आशिष शेलार अन् निशिकांत</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव 'महाराष्ट्र का राजकीय उत्सव' घोषित, मंत्री आशीष शेलार ने जताई खुशी</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-ganeshotsav-declared-state-festival-of-maharashtra-minister-ashish-shelar-expressed-happiness-news-hindi-1-735521-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>‘देवनार’च्या निविदेचे ४,५०० कोटी गेले कुठे? मंत्री आशिष शेलार यांचा आदित्य ठाकरेंना सवाल</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/where-did-the-4500-crores-of-the-deonar-tender-go-minister-ashish-shelar-questions-aaditya-thackeray-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>मुंबईत भाजप पदाधिकारी एकमेकांना भिडले: मंत्री आशिष शेलारांच्या गाडीसमोरच झाला राडा, पक्षातील अंतर्गत वाद चव...</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-infighting-ashish-shelar-kandivali-janupada-135227690.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Special Report Shelar Vs Thackeray | आशिष शेलारांचे उद्धव ठाकरेंवर गंभीर आरोप, सेनेकडून प्रत्युत्तर</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/india-special-report-ashish-shelar-bjp-slams-on-uddhav-thackeray-shivsena-maharashtra-politics-abp-majha-1355752</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Amit Thackeray-Ashish Shelar :अमित ठाकरे-आशिष शेलार भेट, राजकीय वर्तुळात चर्चांना उधाण</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>'स्कूलों में केवल मराठी अनिवार्य, हिंदी नहीं...', भाषा विवाद के बीच महाराष्ट्र के मंत्री का बड़ा बयान - only marathi is compulsory in schools not hindi maharashtra minister big statement amid language controversy</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://www.jagran.com/maharashtra/mumbai-only-marathi-is-compulsory-in-schools-not-hindi-maharashtra-minister-big-statement-amid-language-controversy-40001615.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>15 ऑगस्टच्या आधी सरदार रघुजी राजे भोसलेंची तलवार महाराष्ट्रात येणार, मंत्री शेलार</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Vijay Wadettiwar : महाराष्ट्राच्या राजकारणातून मोठी बातमी! वडेट्टीवारांच्या मनात चाललंय तरी काय? भाजप मंत्र्यासोबतच्या 'त्या' फोटोमुळे रंगली चर्चा</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/chandrapur/congress-leader-vijay-wadettiwar-met-bjp-leader-and-minister-ashish-shelar-in-chandrapur-marathi-news/articleshow/119940732.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>'राज ठाकरे यांचा चित्रपटही लोकांनी स्वीकारला नाही...' मनसे अध्यक्षांबद्दल हे काय बोलून गेले आशिष शेलार?</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>धारावी पुनर्वसन: भाजपाचे आशिष शेलार अन् काँग्रेसच्या वर्षा गायकवाड यांच्यात ‘तू तू मै मै’</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/dharavi-rehabilitation-project-dispute-between-bjps-ashish-shelar-and-congresss-varsha-gaikwad-a-a747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>गणेशोत्सवाआधी मुंबईतील खड्ड्यांचं विघ्न दूर करा; पालकमंत्री आशिष शेलार यांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Ashish Shelar On Raj Uddhav Thackeray: उद्धव ठाकरेंची टीका आशिष शेलारांच्या जिव्हारी विजयी मेळाव्यावरुन</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : बॉम्बे स्कॉटिशमध्ये शिकताना बॉम्बे नको मुंबई हे तुम्ही बोललात का? आशिष</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : आता कसा झेंडा घेऊ हाती? शेलारांनी ठाकरे बंधूंना डिवचलं अन्…</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: आशिष शेलारांनी ठाकरे बंधूंच्या जखमेवर मीठ चोळलं, म्हणाले, बेस्ट पतपेढीच्या</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>PoP Ganesh Idols | Ashish Shelar यांचा विरोधकांवर हल्लाबोल, मूर्तिकारांच्या पाठीशी BJP</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते 'लाडकी बहीण'चा मुहूर्त संपन्न!</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>उबाठा सेना, राऊतांना तुकडे गँगची चिंता: भाजपच्या आशिष शेलार यांचा आरोप; महाराष्ट्र जनसुरक्षा विधेयकावरून सा...</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-public-security-bill-opposition-shiv-sena-uddhav-sanjay-raut-ashish-shelar-attack-135430375.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: "विभाग प्रमुखांनी 100 टक्के निधी..."; मंत्री आशीष शेलारांचे अधिकाऱ्यांना निर्देश</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/minister-ashish-shelar-said-all-department-head-use-100-percent-fund-for-peoples-886116.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>जास्त गर्दीच्या मेट्रो स्थानकांचा आपत्कालीन प्लॅन तयार करा; आशिष शेलारांचे MMRDAला निर्देश</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/prepare-an-emergency-plan-for-overcrowded-metro-stations-ashish-shelar-directs-mmrda-a-a747/</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव झाला महाराष्ट्र राज्य महोत्सव; सांस्कृतिक कार्यमंत्री आशिष शेलार यांची विधानसभेत घोषणा</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-has-become-maharashtra-state-festival-cultural-affairs-minister-ashish-shelar-announced-in-the-legislative-assembly-a-a629/</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Sanjay Raut : मनसे-शिवसेना युतीची चर्चा, शेलारांनी मैत्री संपवली, राऊतांचं मर्मावर बोट, मी आणि राज ठाकरे...</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sanjay-raut-talk-on-ashish-shelar-statement-about-friendship-with-raj-thackeray-news-in-marathi/articleshow/120507660.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meets Ashish Shelar: आशिष शेलारांची भेट घेत अमित ठाकरेंच्या विविध मागण्या मुंबईत आज</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>भारतीय पुरातत्व विभागातील किल्ले देखभालीसाठी राज्याकडे द्या, मंत्री आशिष शेलार यांची केंद्राला विनंती</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>“गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा”; आशिष शेलारांचे स्पष्ट निर्देश</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/bjp-minister-ashish-shelar-instruction-that-fill-all-the-potholes-on-mumbai-roads-completely-before-ganesh-chaturthi-2025-a-a719/</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Amit Thackeray Meet Ashish Shelar : 'गणेशोत्सवातील शाळा-कॉलेजच्या परीक्षा पुढे ढकला'; अमित ठाकरेंची मागणी</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://www.jaimaharashtranews.com/mumbai/mumbai-amit-thackeray-meets-ashish-shelar-demands-ganesh-festival-exam-postponement/40235</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>मनोज जरांगेंच्या टोकदार भाषेवर मंत्री शेलार कडाडले; म्हणाले, 'मुंबईला या, बाप्पांचं दर्शन घ्या, पण...'</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-reacts-over-manoj-jarange-patil-warns-mahayuti-government-due-to-maratha-reservation-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>‘बीडीडी चाळीतील रहिवाशांना येत्या श्रावण महिन्याच्या आत मिळणार चाव्या’, आशिष शेलार यांचं आश्वासन</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/residents-of-bdd-chawl-will-get-keys-within-the-coming-month-of-shravan-assures-ashish-shelar-a-a301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Hindus in Pahalgam killed over religion, assaulted over language in Maha: Shelar | CM Fadnavis had also condemned the incident | Inshorts</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://inshorts.com/en/news/hindus-in-pahalgam-killed-over-religion--over-language-in-maha--shelar-1751789540577</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>अमित ठाकरेंची आशिष शेलारांसोबत बैठक; नेमकी काय चर्चा झाली? अमित ठाकरेंनी स्पष्टच सांगितलं</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/maharashtra/mns-chief-amit-thackeray-submits-memorandum-to-bjp-leader-ashish-shelar-political-news-bdk97</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : दहावी, बारावीच्या निकालावर बैठक, संकेतस्थळ ‘क्रॅश’ होऊ नये : आशिष शेलार</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/maharashtra/ashish-shelar-orders-increased-capacity-for-education-board-website-to-handle-exam-result-traffic-amp17</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>ॲड.आशिष शेलार यांच्या हस्ते मुंबई उपनगर जिल्हाधिकारी कार्यालयात ध्वजारोहण</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/175532/</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>आशा भोसले, नात जनाई साई बाबांच्या दर्शनाला; मंत्री आशिष शेलार यांनीही घेतले शिर्डीतील समाधीचे दर्शन</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार | Singer Manik Varma Autobiogrpahy Launched</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/premier/advocate-ashish-shelar-praised-late-veteran-singer-manik-varma-on-book-launch-prorgram-of-her-autobiography-manik-moti-entertainment-news-kds07</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>महाराष्ट्रातील गणेशोत्सव राष्ट्रीय, आंतरराष्ट्रीय पातळीवर पोहचवणार, आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/maharashtra/maharashtra-assembly-monsoon-session-2025-ashish-shelar-announces-that-maharashtras-ganeshotsav-will-be-taken-to-national-and-international-levels-a-a301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव ‘राज्य महोत्सव’ म्हणून साजरा करणार शासनाची जोरदार तयारी ; मंत्री ॲड.आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: निवडणूक तोंडावर तरीही का बदलला मुंबई भाजप अध्यक्ष? आशिष शेलार यांनी सांगितली रणनीती</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-changes-mumbai-president-ahead-of-elections-amit-satam-takes-charge-ashish-shelar-reveals-strategy-bbj88</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>राज ठाकरेंच्या मतचोरीच्या आरोपावर शेलारांचा हल्लाबोल: म्हणाले - अमितची मते सावंतांनी, देशपांडेंची मते आदित्...</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/asish-shelar-criticizes-raj-uddhav-thackeray-best-election-135757049.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>मुंबईमधील चौकाला स्व. भापसे यांचे नाव दिल्याने झाला पाथर्डीचाही गौरव: मंत्री आशिष शेलार यांचे मत; माजी आ. स...</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/pathardi-also-became-proud-by-naming-a-square-in-mumbai-after-the-late-baburao-bhapse-says-minister-ashish-shelar-former-mla-named-the-square-after-the-late-baburao-bhapse-135398508.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान उपक्रम केंद्र सुरू करणार, आशिष शेलार यांची घोषणा</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>ठाकरे बंधूंच्या प्रश्नावर आशा भोसलेंचं भुवया उंचावणारं विधान, मी कोणाला ओळखत नाही फक्त आशिष शेलारांना ओळखते</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://zeenews.india.com/marathi/maharashtra/asha-bhosle-statement-on-thackeray-brothers-coming-together-i-only-know-ashish-shelar-in-politics/918599</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>एक पडदा सिनेमागृहाबाबत संयुक्त समिती करा – सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचे निर्देश</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/174804/</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>आपले सरकार सेवा केंद्रांची संख्या वाढविणे आणि सेवा दरवाढीबाबत माहिती तंत्रज्ञान मंत्री आशिष शेलार यांचे विधानसभेत निवेदन</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://mahasamvad.in/160568/</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>सिनेमावर सेन्सॉर अथवा निर्बंध घालणार नाही: परिणय फुकेंच्या लक्षवेधी सूचनेवर सांस्कृतिक कार्य मंत्री आशिष शे...</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/entertainment/marathi-cinema/news/maharashtra-film-policy-ashish-shelar-censorship-135409939.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Dahi Handi 2025: गोविंदांसाठी आनंदाची बातमी! यंदा दीड लाख गोविंदांना मिळणार विम्याचे कवच</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>‘खालिद का शिवाजी’ कान्स चित्रपट महोत्सवाच्या यादीतून बाहेर? चित्रपटातील ‘आक्षेपार्ह’ मजकुरावरून आशिष शेलार यांचे संकेत</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://marathi.freepressjournal.in/entertainment/khalid-ka-shivaji-excluded-from-cannes-film-festival-ashish-shelar-comments</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>ज्ञानेश्वर महाराजांचा जन्म सप्तशताब्दी सुवर्ण महोत्सव राज्यभर साजरा करणार: मंत्री आशिष शेलार यांची घोषणा, न...</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/the-golden-jubilee-of-the-birth-of-dnyaneshwar-maharaj-will-be-celebrated-across-the-state-minister-ashish-shelar-announced-mogra-phulla-program-will-be-held-during-narli-week-134770599.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Tuljabhavani Temple : धार्मिक भावना आणि परंपरेचा आदर करूनच तुळजाभवानी मंदिराचा जीर्णोद्धार; आशिष शेलारांची माहिती</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Ashish Shelar: आनंदाची बातमी! चित्रीकरणासाठी नि:शुल्क परवानगी अन् चित्रपट निर्मिती स्थळांवर...; मंत्री आशिष शेलारांची मोठी घोषणा</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/mumbai/minister-ashish-shelar-announces-free-permission-for-filming-anywhere-in-mumbai-vru98</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>हिंदूना मारत आहेत म्हणत मुंबईकर आशिष शेलारांची मनसैनिकांची थेट पहलगाम दहशतवाद्यांशी</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>रघुजी भोसले महाराजांची तलवार राज्य सरकारकडे; मंत्री शेलार यांनी लंडनच्या मध्यस्थाकडून घेतली ताब्यात</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://marathi.freepressjournal.in/maharashtra/raghuji-bhosale-maharaj-sword-handover-to-maharashtra-government</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>मंत्री आशिष शेलारांकडून नामदेव ढसाळ यांचा अवमान</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/ashish-shelar-statement-on-namdev-dhasal</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Mumbai : मराठी चित्रपट कट्टा सुरू, मंत्री आशिष शेलार यांच्या हस्ते लोकार्पण</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://www.mymahanagar.com/mahamumbai/mumbai/marathi-film-katta-was-launched-by-ashish-shelar/844408/</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Maharashtra Heritage News | कातळशिल्पांच्या वय निश्चितीसाठी तज्ज्ञांची समिती</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-rock-carvings-unesco-heritage-committee-ashish-shelar-maharashtra-archaeology-sp96</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Aaple Sarkar Seva Kendra: राज्यात 'आपले सरकार सेवा केंद्रां'ची संख्या वाढणार; आशिष शेलारांनी जाहीर केले 'हे' निकष</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/aple-sarkar-seva-kendra-center-increased-in-state-said-minister-ashish-shelar-825241.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>आपले सरकार सेवा केंद्रांची संख्या वाढवणार, 5000 पेक्षा कमी लोकसंख्येच्या गावात</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-declare-aaple-sarkar-numbers-increased-in-maharashtra-and-also-rates-also-modified-marathi-news-1351214</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Ashish Shelar : ठाकरेंच्या हाती सभेत दाखवण्यासाठी रुद्राक्षांची माळ, तोंडी औरंगजेबाचाच</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-criticizes-uddhav-thackeray-wears-rudraksha-mala-to-his-rally-and-chants-aurangzeb-mantra-maharashtra-politics-marathi-news-1346679</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>मुंबई उपनगर जिल्हाधिकारी कार्यालयात मंत्री ॲड.आशिष शेलार यांच्या हस्ते ध्वजारोहण; तिरंगा यात्रेचेही आयोजन</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Singer Asha Bhosle On Ashish Shelar: राज-उद्धव एकत्र येण्याबाबत प्रश्न, आशाताई म्हणाल्या, 'मला फक्त</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/entertainment/singer-asha-bhosle-on-raj-thackrey-uddhav-thackrey-togater-she-says-i-only-know-ashish-shelar-i-don-t-know-any-other-politician-1366511</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>नालेसफाईच्या पाहणीवेळी तुम्ही कुठे होता? आशिष शेलार यांचा आदित्य ठाकरे यांना सवाल</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://www.lokmat.com/mumbai/where-were-you-during-the-inspection-of-drain-cleaning-ashish-shelar-questions-aditya-thackeray-a-a1001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Aditya Thackeray On Ashish Shelar And Nishikant Dubey: ठाकरे बंधूंवर भाजपकडून हल्लाबोल आदित्य ठाकरेंनी आशिष</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Asha Bhosle News: आशा भोसले म्हणतात, “मला राजकारणातले फक्त आशिष शेलार माहिती आहेत”, ठाकरे बंधूंबाबतच्या प्रश्नावर दिलं उत्तर!</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://www.loksatta.com/maharashtra/singer-asha-bhosle-reaction-on-raj-uddhav-thackeray-morcha-in-mumbai-pmw-88-5187805/</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>छत्रपती शिवाजी महाराज यांच्या १२ गडकिल्ल्यांना नामांकन, जागतिक वारसा यादीत मिळणार स्थान; मंत्री आशिष शेलारांची माहिती</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chhatrapati-shivaji-maharaj-fort-place-on-the-world-heritage-list-minister-ashish-shelar-said/articleshow/118510900.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>दरवर्षी २१ एप्रिल दरम्यान रंगणार आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची घोषणा!</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Aasha Bhosle on Raj-Uddhav : राज-उद्धव युतीचा प्रश्न, आशाताई म्हणाल्या, मला फक्त आशिष शेलार माहिती</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Marathi Not Hindi: BJP Clarifies Language Policy in Maharashtra Schools</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Mumbai Monsoon Mess: MVA Blames MahaYuti Govt, BJP Points to 25 Yrs of BMC Misrule</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Ganpati mandals get political colours ahead of civic polls</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ganpati-mandals-and-the-politics-around-it-10211504/</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Live telecast of Ganeshotsav events: Minister | Mumbai News</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/live-telecast-of-ganeshotsav-events-minister/articleshow/122770675.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://www.tribuneindia.com/news/business/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment/</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Shiv Sena UBT exodus continues, BJP gains two more corporators</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Maharashtra govt to grant ₹25,000 each to 1,800 bhajani mandals for Ganesh festival</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-grant-25000-each-to-1800-bhajani-mandals-for-ganesh-festival/articleshow/123453964.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>‘Insult to people’s mandate’: Devendra Fadnavis slams Rahul Gandhi’s voter fraud allegations as ‘baseless’</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/devendra-fadnavis-slams-rahul-gandhi-voter-fraud-allegations-10177483/</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Maharashtra BJP leader flays attack on Hindi-speaking people, cites Pahalgam parallel</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-bjp-leader-attack-on-hindi-speaking-people-pahalgam-parallel-195564</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Maharashtra govt declares ‘Sarvajanik Ganeshotsav’ as state festival; says it will ‘bear expenses for grand celebrations’</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-declares-sarvajanik-ganeshotsav-as-state-festival-10118535/</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Major fire at mall in Mumbai's Bandra; firefighting on after 18 hours</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/29/major-fire-at-mall-in-mumbais-bandra-firefighting-on-after-18-hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Pune Declares 10-Day Dry Spell</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Maharashtra BJP Minister links Mira Road assault to Pahalgam attack</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: BJP's Ashish Shelar Slams Raj, Uddhav's Joint Rally as Misleading</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Talk of Thackeray cousins reunion 'rattles' Eknath Shinde; BJP says 'wait and watch'</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/20/talk-of-thackeray-cousins-reunion-rattles-eknath-shinde-bjp-says-wait-and-watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Ex-CJI Chandrachud’s call for inclusion spurs immediate government action</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/cities/mumbai/ex-cji-chandrachuds-call-for-inclusion-spurs-immediate-government-action/article69972187.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Thackeray Reunion Fallout: BJP Targets Uddhav, Spares Raj</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Primary education should be in mother tongue, says RSS</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/primary-education-should-be-in-mother-tongue-says-rss/article69785053.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Desperate bid to control BMC &amp; loot Mumbai: BJP</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>'India's Got Latent' row: Maharashtra government orders inquiry into Ranveer Allahbadia controversy | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Khamenei says won't surrender, warns US of 'irreparable damage' if it intervenes - India Today</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/world/video/khamenei-says-wont-surrender-warns-us-of-irreparable-damage-if-it-intervenes-2742623-2025-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>PM Modi-Trump meet among most successful bilateral talks, says US political expert - India Today</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/pm-modi-trump-meet-among-most-successful-bilateral-talks-us-political-expert-2687329-2025-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>Final decision on three-language formula after talks with stakeholders: Maharashtra CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Jun/24/final-decision-on-three-language-formula-after-talks-with-stakeholders-maharashtra-cm-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Ranveer Allahbadia Controversy News Highlights: Ranveer Allahbadia's Mumbai flat found locked; cops summon him again</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/ranveer-allahbadia-controversy-live-updates-youtuber-samay-raina-indias-got-mumbai-police-ashish-chanchlani-apoorva-11739266598623.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Kajol Gets Emotional While Receiving Late Raj Kapoor Life Gaurav Award: "Today I Feel..."</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>https://english.lokshahi.com/latest-news/actress-kajol-received-maharashtra-state-film-award-which-was-held-in-mumbai-in-presence-of-cm-devedra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Asaduddin Owaisi slams Pakistan's fakery with fake Chinese military drill photo - India Today</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/asaduddin-owaisi-slams-pakistans-fakery-with-fake-chinese-military-drill-photo-2731277-2025-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>India Highlights News Updates: Government appoints former cabinet secretary Rajiv Gauba as full-time memb...</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Maharashtra: NCP-SCP MLA Rohit Pawar hit back at BJP MP Nishikant Dubey for comparing opposition parties to terrorists</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>England New Captain CONFIRMED? ECB Director Rob Key Gives BOLD Statement For The Captaincy Hunt</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>https://news24online.com/sports/england-new-captain-confirmed-ecb-director-rob-key-gives-bold-statement-for-the-captaincy-hunt/496413/</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Maharashtra CM Fadnavis Mocks Uddhav’s Rally Speech As Rudali, BJP Hits Out At Thackeray Cousins Over</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cm-fadnavis-mocks-uddhavs-rally-speech-as-rudali-bjp-hits-out-at-thackeray-cousins-over-political-reunion</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>MNS Chief Raj Thackeray Questions Maharashtra Poll Results, Raises Doubts Over Ajit Pawars Sudden Rise In</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mns-chief-raj-thackeray-questions-maharashtra-poll-results-raises-doubts-over-ajit-pawars-sudden-rise-in-assembly-elections</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>मुंबई बीजेपी को मिला नया अध्यक्ष, अमीत साटम के सामने बीएमसी है चुनौती</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/mumbai-bjp-new-president-appointed-three-time-mla-ameet-satam-bmc-elections-big-challenge/4109409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>बीजेपी ने तैनात की नई 'मिसाइल': तीन बार MLA रहे अमित साटम को बनाया मुंबई भाजपा का अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!bharat/ahead-of-bmc-polls-mla-ameet-satam-named-new-mumbai-bjp-chief-hindi-news-hin25082501591</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र विधानसभा परिसर में भिड़े विधायक जितेंद्र आव्हाड और गोपीचंद पडलकर के समर्थक, गाड़ी टच होने पर हुआ था विवाद</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/a-scuffle-broke-out-between-bjp-mla-gopichand-padalkar-and-ncp-jitendra-awhad-ntc-rpti-2289942-2025-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>देश संक्षेप: गणेशोत्सव महाराष्ट्र का राज्य उत्सव घोषित</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-officially-declares-ganeshotsav-as-state-festival-cultural-heritage-emphasized-201752157149955.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Ganeshotsav now Maharashtra State Festival: गणेशोत्सव बना महाराष्ट्र का राजकीय त्योहार, अब होगा राज्योत्सव</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>https://thecsrjournal.in/maharashtra-declares-ganeshotsav-as-state-festival-hindi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>फडणवीस सरकार का बड़ा फैसला, गणेशोत्सव को घोषित किया महाराष्ट्र का 'राज्य महोत्सव'</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/maharashtra/devendra-fadnavis-govt-declare-ganesh-festival-as-maharashtra-state-festival-2025-07-10-1148320</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>मुंबई में विधायक अमीत साटम संभालेंगे बीजेपी की कमान, देवेंद्र फडणवीस ने नए अध्यक्ष के तौर पर नाम का किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-andheri-west-mla-ameet-satam-appointed-mumbai-bjp-chief-ahead-of-bmc-polls-know-all/articleshow/123499476.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>‘गणपति उत्सव’ बना महाराष्ट्र का राज्य उत्सव, कार्यक्रम का खर्च उठाएगी फडणवीस सरकार</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/ganpati-festival-becomes-maharashtra-state-festival-fadnavis-government-will-bear-expenses-of-program/4040819/</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Ganeshotsav 2025: गणेशोत्सव में भाग लेगी महाराष्ट्र सरकार, राज्य उत्सव मनाने के लिए किया गया ये ऐलान</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-devendra-fadnavis-govt-also-participates-in-ganeshotsav-2025-made-a-big-announcement/articleshow/122785708.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>सावरकर के गीत 'अनादि मैं, अनंत मैं' को प्रेरणा गीत का पुरस्कार, महाराष्ट्र सरकार का बड़ा ऐलान</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/savarkar-song-anadi-me-anant-me-gets-inspirational-song-award-maharashtra-government-makes-a-big-announcement-ntc-dskc-2176549-2025-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>निकाय चुनाव से पहले आशीष शेलार की हुई छुट्टी, अमित साटम को मिली मुंबई बीजेपी की कमान</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-removed-post-before-civic-elections-amit-satam-given-command-mumbai-bjp-1329777.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>मनपा चुनाव से पहले बीजेपी का मास्टरस्ट्रोक, अमित साटम बने मुंबई अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bjp-masterstroke-before-municipal-elections-amit-satam-becomes-mumbai-president-1330683.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>मुंबई भाजपा अध्यक्ष की हुई नियुक्ति, भगवा दल ने इस चेहरे पर जताया भरोसा; कितनी बड़ी जिम्मेदारी</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/national/mla-ameet-satnam-named-mumbai-bjp-chief-ahead-of-civic-body-polls-big-decesion-55-807941</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र सरकार ने गणेशोत्सव को राज्य उत्सव घोषित किया |</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://hindicurrentaffairs.adda247.com/maharashtra-government-declares-ganeshotsav-as-state-festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>'राहुल गांधी के दिमाग की चिप चोरी और हार्ड डिस्क करप्ट हो गई', EC पर वोट चोरी के आरोपों पर बोले सीएम फडणवीस</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://lalluram.com/rahul-gandhis-brain-chip-stolen-and-hard-disk-corrupted/</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Mumbai: मुंबई भाजपा अध्यक्ष के तौर पर अमित साटम का चयन</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-amit-satam-selected-as-mumbai-bjp-president-mumbai--4230449</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Maharashtra में गणेशोत्सव को मिला ‘राज्य महोत्सव’ का दर्जा… फडणवीस सरकार का बड़ा फैसला</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://dainiksaveratimes.com/big-1/ganeshotsav-gets-status-state-festival-in-maharashtra-fadnavis-government/</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Ganeshotsav 2025: महाराष्ट्र का 'राज्य उत्सव' बना गणेशोत्सव, अब सरकार उठाएगी जश्न का पूरा खर्च</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/lifestyle/festivals-events/ganeshotsav-now-maharashtras-official-state-festival-govt-to-fund-celebrations-2689983.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>जय शाह की जगह देवजीत सैकिया बने BCCI सचिव, प्रभतेज सिंह भाटिया कोषाध्यक्ष नियुक्त</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://bharat24live.com/news/devajit-saikia-replaces-jay-shah-as-bcci-secretary</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B627"/>
+  <dimension ref="A1:B614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,72 +467,72 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar</t>
+          <t>BCCI Vice-President Rajeev Shukla, Former Treasurer Ashish Shelar To Represent India In Asian Cricke..</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
+          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCCI Vice-President Rajeev Shukla, Former Treasurer Ashish Shelar To Represent India In Asian Cricke..</t>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Have urged Netflix to provide space for Marathi content on platform, says Maharashtra Cultural Affairs Minister Ashish Shelar</t>
+          <t>Culture push at AOI as Maharashtra minister announces new art award</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/usibc-la-waves-summit-requested-netflix-to-provide-space-for-marathi-content-on-platform-says-maharashtra-cultural-affairs-minister-ashish-shelar-23587606</t>
+          <t>https://timesofindia.indiatimes.com/india/culture-push-at-aoi-as-maharashtra-minister-announces-new-art-award/articleshow/118311062.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shelar to represent BCCI on the ACC Board</t>
+          <t>Have urged Netflix to provide space for Marathi content on platform, says Maharashtra Cultural Affairs Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://sportstar.thehindu.com/cricket/rajeev-shukla-ashish-shelar-bcci-acc-board-asian-cricket-council-jay-shah-icc/article69303350.ece</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/usibc-la-waves-summit-requested-netflix-to-provide-space-for-marathi-content-on-platform-says-maharashtra-cultural-affairs-minister-ashish-shelar-23587606</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT)’s condition in Mumbai is dangerous and dilapidated, says BJP MLA Ashish Shelar; welcomes</t>
+          <t>Rajeev Shukla, Ashish Shelar to represent BCCI on the ACC Board</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
+          <t>https://sportstar.thehindu.com/cricket/rajeev-shukla-ashish-shelar-bcci-acc-board-asian-cricket-council-jay-shah-icc/article69303350.ece</t>
         </is>
       </c>
     </row>
@@ -587,264 +587,264 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>"What's The Difference?" BJP Leader's Religion-Language Remark Amid Slapgate</t>
+          <t>Air safety: As bird hits rise, Maharashtra minister Ashish Shelar chairs high level meeting to find soluti</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
+          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Air safety: As bird hits rise, Maharashtra minister Ashish Shelar chairs high level meeting to find soluti</t>
+          <t>"What's The Difference?" BJP Leader's Religion-Language Remark Amid Slapgate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
+          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>‘Khalid Ka Shivaji’ to be removed from Cannes festival listings; ‘won’t allow tampering with history,’ says Ashish Shelar</t>
+          <t>Shiv Sena (UBT)’s condition in Mumbai is dangerous and dilapidated, says BJP MLA Ashish Shelar; welcomes</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/khalid-ka-shivaji-removed-cannes-festival-listings-tampering-history-ashish-shelar-10177555/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ashish Shelar gets coveted Malabar Hill bungalow</t>
+          <t>‘Khalid Ka Shivaji’ to be removed from Cannes festival listings; ‘won’t allow tampering with history,’ says Ashish Shelar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ashish-shelar-gets-coveted-malabar-hill-bungalow-101736364223566.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/khalid-ka-shivaji-removed-cannes-festival-listings-tampering-history-ashish-shelar-10177555/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>"Hindi Not Compulsory": Maharashtra Minister Amid Language Row</t>
+          <t>Ashish Shelar gets coveted Malabar Hill bungalow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ashish-shelar-gets-coveted-malabar-hill-bungalow-101736364223566.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Minister Ashish Shelar slams BJP MP over remarks against Marathi people</t>
+          <t>POP idol ban lifted: Will continue to raise issues while upholding devotion, sustainability, says Ashish Shelar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/ashish-shelar-slams-bjp-mp-marathi-10112152/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/pop-idol-ban-lifted-will-continue-to-raise-issues-while-upholding-devotion-sustainability-says-ashish-shelar-10057291/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maharashtra delegation led by Ashish Shelar in Paris to seek UNESCO World Heritage status for Shivaji Maharaj’s forts</t>
+          <t>Minister Ashish Shelar slams BJP MP over remarks against Marathi people</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-paris-unesco-world-heritage-site-shivaji-maharaj-fort-9851720/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/ashish-shelar-slams-bjp-mp-marathi-10112152/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>No need to question capabilities of Marathi speakers: BJP minister Ashish Shelar after Nishikant Dubey remarks</t>
+          <t>Maharashtra delegation led by Ashish Shelar in Paris to seek UNESCO World Heritage status for Shivaji Maharaj’s forts</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-paris-unesco-world-heritage-site-shivaji-maharaj-fort-9851720/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Loudspeakers may be used till midnight on 7 days: Ashish Shelar</t>
+          <t>No need to question capabilities of Marathi speakers: BJP minister Ashish Shelar after Nishikant Dubey remarks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Shelar likens attacks on non-Marathi speakers in Mumbai to Pahalgam attack</t>
+          <t>Loudspeakers may be used till midnight on 7 days: Ashish Shelar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-attack-non-marathi-speakers-mumbai-pahalgam-massacre-10109991/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shelar-led delegation off to Paris to obtain UNESCO heritage status for 12 forts of Shivaji</t>
+          <t>Shelar likens attacks on non-Marathi speakers in Mumbai to Pahalgam attack</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/shelar-led-delegation-off-to-paris-to-obtain-unesco-heritage-status-for-12-forts-of-shivaji/article69255530.ece</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-attack-non-marathi-speakers-mumbai-pahalgam-massacre-10109991/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mahayuti, BJP disown Jharkhand MP remarks on Marathi manoos</t>
+          <t>Shelar-led delegation off to Paris to obtain UNESCO heritage status for 12 forts of Shivaji</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/shelar-led-delegation-off-to-paris-to-obtain-unesco-heritage-status-for-12-forts-of-shivaji/article69255530.ece</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mumbai: Play Marathi devotional songs on private radio stations, says Ashish Shelar</t>
+          <t>"Hindi Not Compulsory": Maharashtra Minister Amid Language Row</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
+          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>New Roles For Rajeev Shukla, Ashish Shelar In Asian Cricket Council As BCCI Expands Its Influence</t>
+          <t>Mahayuti, BJP disown Jharkhand MP remarks on Marathi manoos</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>"Only Marathi Is Mandatory In Maharashtra Schools, Not Hindi": Minister</t>
+          <t>Have urged Netflix to provide space for Marathi content on platform: Shelar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
+          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saif Ali Khan attack case: Ashish Shelar dares Uddhav Thackeray to confront Mamata Banerjee over Bangladesh infiltration</t>
+          <t>Mumbai: Play Marathi devotional songs on private radio stations, says Ashish Shelar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BJP's Ashish Shelar dismisses Thackeray rally as political gimmick on Marathi language</t>
+          <t>New Roles For Rajeev Shukla, Ashish Shelar In Asian Cricket Council As BCCI Expands Its Influence</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
+          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror</t>
+          <t>BJP's Ashish Shelar dismisses Thackeray rally as political gimmick on Marathi language</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-minister-bjp-leader-ashish-shelar-compares-attacks-hindi-speakers-pahalgam-terror-2751745-2025-07-07</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>POP idol ban lifted: Will continue to raise issues while upholding devotion, sustainability, says Ashish Shelar</t>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/pop-idol-ban-lifted-will-continue-to-raise-issues-while-upholding-devotion-sustainability-says-ashish-shelar-10057291/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-minister-bjp-leader-ashish-shelar-compares-attacks-hindi-speakers-pahalgam-terror-2751745-2025-07-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Over 50 Marathi schools in US to get support from Maharashtra government</t>
+          <t>Maharashtra minister's Pahalgam attack parallel amid attacks over language row | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/over-50-marathi-schools-in-us-to-get-support-from-maharashtra-government-2761714-2025-07-26</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Beaten for language, killed for religion: BJP leader compares Maharashtra language row to Pahalgam attack</t>
+          <t>Over 50 Marathi schools in US to get support from Maharashtra government</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
+          <t>https://www.indiatoday.in/education-today/news/story/over-50-marathi-schools-in-us-to-get-support-from-maharashtra-government-2761714-2025-07-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maharashtra minister's Pahalgam attack parallel amid attacks over language row | Latest News India - Hindustan Times</t>
+          <t>Beaten for language, killed for religion: BJP leader compares Maharashtra language row to Pahalgam attack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-minister-ashish-shelars-pahalgam-attack-parallel-amid-attacks-over-language-row-101751802620532.html</t>
+          <t>https://timesofindia.indiatimes.com/city/delhi/religion-there-language-here-maharashtra-minister-ashish-shelar-compares-pahalgam-attack-to-marathi-slapgate-row-says-bjp-will-protect-everyone-in-state/articleshow/122278710.cms</t>
         </is>
       </c>
     </row>
@@ -863,24 +863,24 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Maharashtra govt will not impose censorship on films: Ashish Shelar</t>
+          <t>Inquiry must be conducted in rat extermination drive: Ashish Shelar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-will-not-impose-censorship-on-films-ashish-shelar-10116698/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Inquiry must be conducted in rat extermination drive: Ashish Shelar</t>
+          <t>Maharashtra govt will not impose censorship on films: Ashish Shelar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-will-not-impose-censorship-on-films-ashish-shelar-10116698/</t>
         </is>
       </c>
     </row>
@@ -899,36 +899,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ashish Shelar Reviews Mumbai Covid-19 Preparedness Amid New Case Spike</t>
+          <t>BCCI Names Rajeev Shukla, Ashish Shelar As Representatives For ACC Board</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
+          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCCI Names Rajeev Shukla, Ashish Shelar As Representatives For ACC Board</t>
+          <t>Ashish Shelar Reviews Mumbai Covid-19 Preparedness Amid New Case Spike</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashish Shelar slams Thackeray brothers joint rally as ‘Vague and Politically Motivated'</t>
+          <t>Ashish Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1285504</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Leopard safari to begin soon at Sanjay Gandhi National Park: Ashish Shelar</t>
+          <t>Ashish Shelar slams Thackeray brothers joint rally as ‘Vague and Politically Motivated'</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-ashish-shelar-9810427/</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1285504</t>
         </is>
       </c>
     </row>
@@ -995,96 +995,96 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
+          <t>Leopard safari to begin soon at Sanjay Gandhi National Park: Ashish Shelar</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/shelar-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra/ar-AA1L1WDR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://indianexpress.com/article/cities/mumbai/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-ashish-shelar-9810427/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Asha Bhosle's Cryptic Comment Add Twist to Thackeray Reunion Speculation</t>
+          <t>Maharashtra minister's shocker! BJP's Ashish Shelar compares MNS assault over language with Pahalgam terror attack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/top-stories/asha-bhosles-cryptic-comment-add-twist-to-thackeray-reunion-speculation</t>
+          <t>https://www.livemint.com/news/india/maharashtra-ministers-shocker-bjps-ashish-shelar-compares-mns-assault-over-language-with-pahalgam-terror-attack-11751802600494.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Maharashtra minister's shocker! BJP's Ashish Shelar compares MNS assault over language with Pahalgam terror attack</t>
+          <t>Asha Bhosle's Cryptic Comment Add Twist to Thackeray Reunion Speculation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/india/maharashtra-ministers-shocker-bjps-ashish-shelar-compares-mns-assault-over-language-with-pahalgam-terror-attack-11751802600494.html</t>
+          <t>https://english.lokshahi.com/top-stories/asha-bhosles-cryptic-comment-add-twist-to-thackeray-reunion-speculation</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI audit found irregularities in drain cleaning works in Mumbai: Maharashtra Minister Ashish Shelar</t>
+          <t>No land in Dharavi has been given to Adani, Ashish Shelar</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
+          <t>https://indianexpress.com/article/cities/mumbai/no-land-in-dharavi-has-been-given-to-adani-ashish-shelar-9899366/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>‘We take full responsibility for Mumbai’s roads’: Shelar after visiting eastern suburbs</t>
+          <t>Complete all dug up roads in Mumbai by May 31: Ashish Shelar to BMC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/shelar-directs-bmc-to-stop-road-concretisation-works-from-today-10016418/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marathi Cinema At Cannes Film Festival: 4 Movies Selected, Confirms Maharashtra Minister Ashish Shelar</t>
+          <t>AI audit found irregularities in drain cleaning works in Mumbai: Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/entertainment-news/bollywood/marathi-cinema-at-cannes-film-festival-4-movies-selected-confirms-maharashtra-minister-ashish-shelar-article-151459918</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sena UBT's condition akin to 'dangerous', 'dilapidated' buildings of Mumbai, says Ashish Shelar</t>
+          <t>Marathi Cinema At Cannes Film Festival: 4 Movies Selected, Confirms Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
+          <t>https://www.timesnownews.com/entertainment-news/bollywood/marathi-cinema-at-cannes-film-festival-4-movies-selected-confirms-maharashtra-minister-ashish-shelar-article-151459918</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ashish Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
+          <t>Sena UBT's condition akin to 'dangerous', 'dilapidated' buildings of Mumbai, says Ashish Shelar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-says-ashish-shelar-23575542</t>
         </is>
       </c>
     </row>
@@ -1103,36 +1103,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Maharashtra Cultural Affairs Ministry to probe obscenity plaints against entertainment programmes</t>
+          <t>BJP Leader Compares Attack on Hindi-speaking People with Pahalgam Incident</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra-cultural-affairs-ministry-to-probe-obscenity-plaints-against-entertainment-programmes/article69220801.ece</t>
+          <t>https://www.deccanchronicle.com/nation/politics/bjp-leader-compares-attack-on-hindi-speaking-people-with-pahalgam-incident-1889788</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ashish Shelar lauds Pune’s startup culture</t>
+          <t>Maharashtra Cultural Affairs Ministry to probe obscenity plaints against entertainment programmes</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra-cultural-affairs-ministry-to-probe-obscenity-plaints-against-entertainment-programmes/article69220801.ece</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BJP’s Ashish Shelar Likens MNS' Marathi Assaults To Pahalgam Attack: ‘What’s The Difference?'</t>
+          <t>Ashish Shelar lauds Pune’s startup culture</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/ashish-shelar-compares-mns-assault-over-marathi-with-pahalgam-attack-whats-the-difference-9424380.html</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
         </is>
       </c>
     </row>
@@ -1163,468 +1163,468 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shelar named BCCI’s representatives on ACC board</t>
+          <t>BJP’s Ashish Shelar Likens MNS' Marathi Assaults To Pahalgam Attack: ‘What’s The Difference?'</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
+          <t>https://www.news18.com/politics/ashish-shelar-compares-mns-assault-over-marathi-with-pahalgam-attack-whats-the-difference-9424380.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Artworks of Ravi Paranjape handed over to govt, to be preserved in museum</t>
+          <t>Sinhagad Fort Restoration Plan: Development Meeting Scheduled Within 15 Days</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/artworks-of-ravi-paranjape-handed-over-to-govt-to-be-preserved-in-museum-10201536/</t>
+          <t>https://www.thebridgechronicle.com/news/sinhagad-fort-restoration-plan-development-meeting-scheduled-within-15-days</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ashish Shelar Slams Shiv Sena (UBT) Faction for "Fake Drama" and Political Theatrics</t>
+          <t>Rajeev Shukla, Ashish Shelar named BCCI’s representatives on ACC board</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
+          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BJP pans UBT over Deonar dump remarks</t>
+          <t>Ashish Shelar Slams Shiv Sena (UBT) Faction for "Fake Drama" and Political Theatrics</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
+          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP's Shelar Condemns Attacks on Hindi Speakers, Cites Pahalgam Parallel</t>
+          <t>BJP pans UBT over Deonar dump remarks</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tech experts will study use of PoP in Ganesh idols: Minister Ashish Shelar</t>
+          <t>Maharashtra: BJP's Shelar Condemns Attacks on Hindi Speakers, Cites Pahalgam Parallel</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mumbai: MNS protests alleged ill-treatment to Marathi speakers over non-veg food; Ashish Shelar issues warning</t>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
+          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Shelar-led delegation in Paris to secure UNESCO Heritage status for 12 Shivaji forts</t>
+          <t>Marathi Not Hindi: BJP Clarifies Language Policy in Maharashtra Schools</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maharashtra govt to support Marathi schools in US with official curriculum</t>
+          <t>Days after Raj met CM Fadnavis, his son meets Shelar; sets tongues wagging</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
+          <t>https://indianexpress.com/article/cities/mumbai/days-after-raj-met-cm-fadnavis-his-son-meets-shelar-sets-tongues-wagging-10207422/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>'Sarvajanik Ganehotsav' announced as ‘State Festival of Maharashtra', confirms Ashish Shelar</t>
+          <t>Mumbai: MNS protests alleged ill-treatment to Marathi speakers over non-veg food; Ashish Shelar issues warning</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/sarvajanik-ganehotsav-announced-as-state-festival-of-maharashtra-confirms-ashish-shelar-11752164479346.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Highlight power of Operation Sindoor during Ganeshotsav: Ashish Shelar tells organisers</t>
+          <t>Shelar-led delegation in Paris to secure UNESCO Heritage status for 12 Shivaji forts</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maharashtra to unveil AI policy by April; Ashish Shelar warns against over-reliance</t>
+          <t>Tech experts will study use of PoP in Ganesh idols: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maharashtra minister addresses AI concerns, assures policy will complement, not replace, education</t>
+          <t>Maharashtra govt to support Marathi schools in US with official curriculum</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
+          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maharashtra govt to set up research centre for experimental arts in Mumbai, name it after Shahir Sable: M</t>
+          <t>'Sarvajanik Ganehotsav' announced as ‘State Festival of Maharashtra', confirms Ashish Shelar</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
+          <t>https://www.livemint.com/news/sarvajanik-ganehotsav-announced-as-state-festival-of-maharashtra-confirms-ashish-shelar-11752164479346.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>'Where did Pahalgam attackers go?': Aaditya Thackeray's 'poison' reply to Maharashtra minister's remark amid Marathi row | Latest News India - Hindustan Times</t>
+          <t>Highlight power of Operation Sindoor during Ganeshotsav: Ashish Shelar tells organisers</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Allahbadia remarks: Maharashtra minister Ashish Shelar asks cultural affairs department to probe obscene programmes</t>
+          <t>Maharashtra to unveil AI policy by April; Ashish Shelar warns against over-reliance</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Renovated Ravindra Natya Mandir in Mumbai to be reopened on February 28: Ashish Shelar</t>
+          <t>Maharashtra minister addresses AI concerns, assures policy will complement, not replace, education</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/renovated-ravindra-natya-mandir-reopening-mumbai-9843008/</t>
+          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Not an inch of Dharavi will be given to Adani, says Maharashtra minister Ashish Shelar</t>
+          <t>Maharashtra govt to set up research centre for experimental arts in Mumbai, name it after Shahir Sable: M</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BJP demands 'white paper' from BMC on monsoon related spending</t>
+          <t>'Where did Pahalgam attackers go?': Aaditya Thackeray's 'poison' reply to Maharashtra minister's remark amid Marathi row | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
+          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leopard Safari to begin soon at Sanjay Gandhi National Park: Maha minister</t>
+          <t>Allahbadia remarks: Maharashtra minister Ashish Shelar asks cultural affairs department to probe obscene programmes</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://travel.economictimes.indiatimes.com/news/destination/states/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-maha-minister/117794576</t>
+          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Firebrand legislator and Fadnavis confidante Ameet Satam made BJP’s Mumbai chief ahead of BMC polls</t>
+          <t>Renovated Ravindra Natya Mandir in Mumbai to be reopened on February 28: Ashish Shelar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/firebrand-legislator-and-fadnavis-confidante-ameet-satam-made-bjps-mumbai-chiefahead-of-bmc-polls-3696247</t>
+          <t>https://indianexpress.com/article/cities/mumbai/renovated-ravindra-natya-mandir-reopening-mumbai-9843008/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>74 roads in H West ward will be completed by May 31: Ashish Shelar</t>
+          <t>Not an inch of Dharavi will be given to Adani, says Maharashtra minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Warring BJP factions clash in Kandivali public meeting</t>
+          <t>BJP demands 'white paper' from BMC on monsoon related spending</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ashish Shelar chairs Covid-19 review meet; suggests masks, re-vaccination for high-risk individuals</t>
+          <t>74 roads in H West ward will be completed by May 31: Ashish Shelar</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Maharashtra govt to crack down on lane-cutting, draw up integrated traffic management plan for Mumbai: Su</t>
+          <t>Ashish Shelar chairs Covid-19 review meet; suggests masks, re-vaccination for high-risk individuals</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Expert committee set up to look into 'tamasha' artistes' problems: Shelar</t>
+          <t>‘We take full responsibility for Mumbai’s roads’: Shelar after visiting eastern suburbs</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maharashtra Cabinet Minister Ashish Shelar to be the Chief Guest of e4m IDMA 2025</t>
+          <t>Warring BJP factions clash in Kandivali public meeting</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BJP politician calls Uddhav Thackeray badshah of land scams in Mumbai</t>
+          <t>Maharashtra govt to crack down on lane-cutting, draw up integrated traffic management plan for Mumbai: Su</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Asha Bhosle, Minister Ashish Shelar visit RD Burman's residence to celebrate singer's 86th birth anniversary</t>
+          <t>Expert committee set up to look into 'tamasha' artistes' problems: Shelar</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
+          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsale’s legendary sword set to arrive in Mumbai tomorrow, ‘darshan’ ceremony to be held at PL Deshpande Maharashtra Kala Academy</t>
+          <t>Maharashtra Cabinet Minister Ashish Shelar to be the Chief Guest of e4m IDMA 2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/raghuji-bhonsales-legendary-sword-mumbai-10194874/</t>
+          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Maharashtra minister Ashish Shelar urges transfer of Shivaji’s forts under ASI to state govt</t>
+          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>No Dharavi land being handed over to Adani: Shelar</t>
+          <t>BJP politician calls Uddhav Thackeray badshah of land scams in Mumbai</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Maharashtra cultural centre and museum to come up at BKC</t>
+          <t>Asha Bhosle, Minister Ashish Shelar visit RD Burman's residence to celebrate singer's 86th birth anniversary</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>"Maharashtra won, Marathi Manus won, BJP won in this fight", says BJP Mumbai chief Ashish Shelar as Mahayuti slams MVA over three-language policy issue</t>
+          <t>Maharashtra minister Ashish Shelar urges transfer of Shivaji’s forts under ASI to state govt</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
+          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ashish Shelar praises Mukta Arts Marathi Productions and Subhash Ghai for backing regional cinema</t>
+          <t>No Dharavi land being handed over to Adani: Shelar</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BJP’s Shelar, not Sena neta, is advisor for Maha tech hub</t>
+          <t>Maharashtra cultural centre and museum to come up at BKC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maha minister Shelar pays tribute</t>
+          <t>"Maharashtra won, Marathi Manus won, BJP won in this fight", says BJP Mumbai chief Ashish Shelar as Mahayuti slams MVA over three-language policy issue</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
+          <t>BJP’s Shelar, not Sena neta, is advisor for Maha tech hub</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Maharashtra govt. wants CBFC to re-examine certification for Khalid ka Shivaji, halt release of movie</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maha minister Shelar pays tribute</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-govt-wants-cbfc-to-re-examine-certification-for-khalid-ka-shivaji-halt-release-of-movie/article69906718.ece</t>
+          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
         </is>
       </c>
     </row>
@@ -1655,120 +1655,120 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>"Police working meticulously, truth will be out soon": Maharashtra Minister Ashish Shelar on Saif Ali Khan attack case</t>
+          <t>Ashish Shelar praises Mukta Arts Marathi Productions and Subhash Ghai for backing regional cinema</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
+          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maharashtra govt orders cultural dept probe, ‘absconding’ Ranveer Allahbadia to face cops today? All you</t>
+          <t>"Police working meticulously, truth will be out soon": Maharashtra Minister Ashish Shelar on Saif Ali Khan attack case</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-orders-cultural-dept-probe-absconding-ranveer-allahbadia-to-face-cops-today-all-you-need-to-know/articleshow/118267899.cms</t>
+          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maharashtra minister condemns assault on Hindi-speaking people, draws parallel with Pahalgam attack</t>
+          <t>Rajiv Shukla, Ashish Shelar To Represent BCCI On ACC Board</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-minister-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack/articleshow/122281220.cms</t>
+          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Rajiv Shukla, Ashish Shelar To Represent BCCI On ACC Board</t>
+          <t>Culture minister Ashish Shelar seeks MoU between state archives of Maharashtra and Gujarat</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Culture minister Ashish Shelar seeks MoU between state archives of Maharashtra and Gujarat</t>
+          <t>Ashish Shelar demands report from MMRDA; slams ‘deception’ behind axed Bandra-Kurla rail route</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ashish Shelar demands report from MMRDA; slams ‘deception’ behind axed Bandra-Kurla rail route</t>
+          <t>Maharashtra Spearheading India’s First AI University Says Maharashtra IT Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
+          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Maharashtra Spearheading India’s First AI University Says Maharashtra IT Minister Ashish Shelar</t>
+          <t>Minister Shelar criticises UBT over education policy, says Cong started Hindi mandate &amp; Thackeray continu</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Minister Shelar criticises UBT over education policy, says Cong started Hindi mandate &amp; Thackeray continu</t>
+          <t>Prepare monsoon contingency plan for Mumbai Metro stations: Ashish Shelar to officials</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Prepare monsoon contingency plan for Mumbai Metro stations: Ashish Shelar to officials</t>
+          <t>Science and Innovation Activity centres to be set up across Maharashtra</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
+          <t>https://indianexpress.com/article/cities/mumbai/science-and-innovation-activity-centres-to-be-set-up-across-maharashtra-10133570/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Science and Innovation Activity centres to be set up across Maharashtra</t>
+          <t>‘Celebrate Ganeshotsav Like Never Before’: Shelar Blames Urban Naxals For Attack On Hindu Fests</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/science-and-innovation-activity-centres-to-be-set-up-across-maharashtra-10133570/</t>
+          <t>https://www.news18.com/india/celebrate-ganeshotsav-like-never-before-shelar-blames-urban-naxals-for-attacks-on-hindu-fests-ws-kl-9452155.html</t>
         </is>
       </c>
     </row>
@@ -1799,6156 +1799,6000 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Video | BJP Minister Condemns MNS Attacks, Compares Them To Pahalgam Shooting Over Religious Identity</t>
+          <t>Plot in Marol transforms into urban forest, mercury drops</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Plot in Marol transforms into urban forest, mercury drops</t>
+          <t>Video | BJP Minister Condemns MNS Attacks, Compares Them To Pahalgam Shooting Over Religious Identity</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
+          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Maharashtra government forms panel for Artificial Intelligence policy</t>
+          <t>UBT looted Mumbai to the tune of ₹1 lakh crore, alleges BJP’s Ashish Shelar</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
+          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UBT looted Mumbai to the tune of ₹1 lakh crore, alleges BJP’s Ashish Shelar</t>
+          <t>Prize money, production grants and daily allowance hiked for Maharashtra State Drama Competition: Ashish Shelar</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+          <t>Will Raj Thackeray Join Mahayuti Ahead Of Civic Polls? His Meeting With Mumbai BJP Chief Sparks Buzz</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+          <t>https://www.news18.com/politics/brihanmumbai-municipal-corporation-bmc-elections-mumbai-mns-raj-thackeray-bjp-ashish-shelar-mahayuti-shiv-sena-eknath-shinde-9181677.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>‘Celebrate Ganeshotsav Like Never Before’: Shelar Blames Urban Naxals For Attack On Hindu Fests</t>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/celebrate-ganeshotsav-like-never-before-shelar-blames-urban-naxals-for-attacks-on-hindu-fests-ws-kl-9452155.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Will Raj Thackeray Join Mahayuti Ahead Of Civic Polls? His Meeting With Mumbai BJP Chief Sparks Buzz</t>
+          <t>Khalid Ka Shivaji to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/brihanmumbai-municipal-corporation-bmc-elections-mumbai-mns-raj-thackeray-bjp-ashish-shelar-mahayuti-shiv-sena-eknath-shinde-9181677.html</t>
+          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Khalid Ka Shivaji to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
+          <t>Maharashtra government forms panel for Artificial Intelligence policy</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Satam Appointed As Mumbai BJP Chief Ahead Of Crucial BMC Polls</t>
+          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/satam-appointed-as-mumbai-bjp-chief-ahead-of-crucial-bmc-polls-1899682</t>
+          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BJP's Ameet Satam named Mumbai party chief to counter Thackerays in civic polls</t>
+          <t>Satam Appointed As Mumbai BJP Chief Ahead Of Crucial BMC Polls</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/bjp-leader-ameet-satam-appointed-party-chief-in-mumbai-to-counter-thackerays-in-the-upcoming-civic-polls-2776671-2025-08-25</t>
+          <t>https://www.deccanchronicle.com/nation/satam-appointed-as-mumbai-bjp-chief-ahead-of-crucial-bmc-polls-1899682</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AID strongly advocates GCC Policy: Ashish Kale</t>
+          <t>Maharashtra govt will make arrangements for immersion of large Ganesh idols: Ashish Shelar on PoP use</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+          <t>AID strongly advocates GCC Policy: Ashish Kale</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar pays tribute to Savarkar at Andaman's Cellular Jail</t>
+          <t>4 Marathi films selected for 2025 Cannes Film Festival reveals Maharashtra cultural affairs minister...</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
+          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Brother trouble</t>
+          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
+          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>‘Reclassify SGNP slums land as non-forest to avoid relocation’</t>
+          <t>Sword of Raghuji-1 Bhonsale to be brought to India on Aug 18</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/reclassify-sgnp-slums-land-as-non-forest-to-avoid-relocation/articleshow/121523748.cms</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>News On Click</t>
+          <t>Maharashtra to launch India’s first AI University</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-to-launch-indias-first-ai-university-9797631/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Maharashtra govt to form panel to study issues faced by single-screen cinemas</t>
+          <t>AI in education: Maharashtra to launch new AI policy in April, says IT Minister</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-panel-to-study-issues-faced-by-single-screen-cinemas-10176447/</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>23rd Pune International Film Festival begins with a grand opening</t>
+          <t>Reema Lagoos Ex-Husband And Veteran Actor Vivek Lagoo Dies, Last Rites To Be Held Today; Maharashtra Minister Ashish Shelar Pays Tribute</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/23rd-pune-international-film-festival-begins-with-a-grand-opening-9835047/</t>
+          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ganeshotsav to Get Status of Maharashtra’s ‘State Festival’</t>
+          <t>Maharashtra Minister Ashish Shelar pays tribute to Savarkar at Andaman's Cellular Jail</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/current-affairs/ganeshotsav-to-get-status-of-maharashtras-state-festival-1890637</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar calls for urgent desilting plan for key lakes in Mumbai</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>State grants ‘Maharashtra State Festival’ status to Ganeshotsav, promises funds</t>
+          <t>News On Click</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/state-grants-maharashtra-state-festival-status-to-ganeshotsav-promises-funds/articleshow/122373114.cms</t>
+          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Guardian ministers appointed in Maharashtra; Dhananjay Munde not in list</t>
+          <t>23rd Pune International Film Festival begins with a grand opening</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
+          <t>https://indianexpress.com/article/cities/pune/23rd-pune-international-film-festival-begins-with-a-grand-opening-9835047/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray's Shiv Sena (UBT) failed to improve Mumbai's stormwater drain system despite Rs 1 lakh crore spending: BJP</t>
+          <t>Ganeshotsav to Get Status of Maharashtra’s ‘State Festival’</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
+          <t>https://www.deccanchronicle.com/nation/current-affairs/ganeshotsav-to-get-status-of-maharashtras-state-festival-1890637</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Prize money, production grants and daily allowance hiked for Maharashtra State Drama Competition: Ashish Shelar</t>
+          <t>Maharashtra Minister Ashish Shelar calls for urgent desilting plan for key lakes in Mumbai</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
+          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Shelar invokes Pahalgam: ‘Here, Hindus attacked over language’</t>
+          <t>Minister Shelar warns of ‘urban naxal’ threat</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Not all road works in Mumbai will be completed before May 31 monsoon deadline: Maharashtra Minister Ashish Shelar</t>
+          <t>Maharashtra govt to form panel to study issues faced by single-screen cinemas</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-panel-to-study-issues-faced-by-single-screen-cinemas-10176447/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>All govt departments, implementing agencies must ensure 100 per cent fund utilisation: Shelar</t>
+          <t>‘Khalid Ka Shivaji’ to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
+          <t>https://www.dtnext.in/entertainment/cinema/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-842675</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Nearly 60% of bakeries in Mumbai yet to switch to cleaner fuel</t>
+          <t>Maharashtra govt taking balanced approach to pigeon feeding issue: Minister Shelar</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/nearly-60-of-bakeries-in-mumbai-yet-to-switch-to-cleaner-fuel-10088723/</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Submit action plan within 3 months to desilt three lakes in Mumbai: Shelar</t>
+          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/submit-action-plan-within-3-months-to-desilt-three-lakes-in-mumbai-shelar-10088728/</t>
+          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Maharashtra Cultural Minister Ashish Shelar inaugurates Kala Ghoda Arts Festival 2025</t>
+          <t>Guardian ministers appointed in Maharashtra; Dhananjay Munde not in list</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
+          <t>https://www.deccanherald.com/india/maharashtra/guardian-ministers-appointed-in-maharashtra-dhananjay-munde-not-in-list-2-3362442</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shellar appointed as reps to ACC board</t>
+          <t>Advantage Vidarbha 2025 to be inaugurated today</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Maharashtra orders inquiry by cultural dept officials into Ranveer Allahbadia controversy</t>
+          <t>State forms district-level panels to remove encroachments on forts</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Feb/15/maharashtra-orders-inquiry-by-cultural-dept-officials-into-ranveer-allahbadia-controversy</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Shelar &amp; Cong MP get into spat over Dharavi master plan</t>
+          <t>BMC told to finish all roadworks in Mumbai suburbs by May 31, says minister</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Veer Savarkar’s iconic song ‘Anadi Me Anant Me...’ to be honoured with award named after Sambhaji Maharaj: Minister</t>
+          <t>India’s Got Latent row: Maharashtra govt orders inquiry into controversy involving Ranveer Allahbadia, Samay Raina</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/veer-savarkars-iconic-song-anadi-me-anant-me-to-be-honoured-with-award-named-after-sambhaji-maharaj-minister-3421353</t>
+          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Maharashtra to get India's first AI university led by industry experts</t>
+          <t>Uddhav Thackeray's Shiv Sena (UBT) failed to improve Mumbai's stormwater drain system despite Rs 1 lakh crore spending: BJP</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/ai-education-indias-first-ai-university-to-set-up-in-maharashtra-2673858-2025-02-03</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FTII and Maharashtra Film, Stage &amp; Cultural Development Corporation Ltd. sign MoU to expand film and media training in Maharashtra</t>
+          <t>Film City in Ramtek inches closer to reality</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Give Custodianship Of Historic Forts To Maharashtra Government: Minister Ashish Shelar To Centre</t>
+          <t>Shelar invokes Pahalgam: ‘Here, Hindus attacked over language’</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/hand-over-custodianship-of-historic-forts-to-maharashtra-government-minister-ashish-shelar-to-centre-9274572.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Shelar announces taskforce for cyber security norms in Maharashtra</t>
+          <t>Not all road works in Mumbai will be completed before May 31 monsoon deadline: Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/politics/shelar-announces-taskforce-for-cyber-security-norms-in-maharashtra-87382</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Mumbai's Sanjay Gandhi National Park To Introduce 'Leopard Safari' For Visitors Soon</t>
+          <t>All govt departments, implementing agencies must ensure 100 per cent fund utilisation: Shelar</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/sanjay-gandhi-national-park-in-mumbai-to-introduce-leopard-safari-for-visitors-soon-ashish-shelar-9209891.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed BJP Mumbai Chief Ahead Of Polls</t>
+          <t>Maharashtra minister Shelar asks govt departments to step up Ganeshotsav participation; Rs 10 crore for cultural events</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.bwpeople.in/article/ameet-satam-appointed-bjp-mumbai-chief-ahead-of-polls-568808</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-minister-shelar-asks-govt-departments-to-step-up-ganeshotsav-participation-rs-10-crore-for-cultural-events-10205121/</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Maharashtra government aims to make forts encroachment-free by May 31</t>
+          <t>Submit action plan within 3 months to desilt three lakes in Mumbai: Shelar</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
+          <t>https://indianexpress.com/article/cities/mumbai/submit-action-plan-within-3-months-to-desilt-three-lakes-in-mumbai-shelar-10088728/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>New Mumbai BJP chief Ameet Satam is 3-time MLA with corporate background, Thackeray critic</t>
+          <t>Rajeev Shukla, Ashish Shellar appointed as reps to ACC board</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/new-mumbai-bjp-chief-ameet-satam-is-3-time-mla-with-corporate-background-thackeray-critic/2728464/</t>
+          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Maharashtra govt forms 16-member panel to draft first-ever AI policy</t>
+          <t>Maharashtra orders inquiry by cultural dept officials into Ranveer Allahbadia controversy</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-16-member-panel-draft-ai-policy-9784605/</t>
+          <t>https://www.newindianexpress.com/nation/2025/Feb/15/maharashtra-orders-inquiry-by-cultural-dept-officials-into-ranveer-allahbadia-controversy</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Maharashtra Declares Ganeshotsav As State Festival</t>
+          <t>Shelar &amp; Cong MP get into spat over Dharavi master plan</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Maharashtra to Establish India’s First Artificial Intelligence University</t>
+          <t>Veer Savarkar’s iconic song ‘Anadi Me Anant Me...’ to be honoured with award named after Sambhaji Maharaj: Minister</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/veer-savarkars-iconic-song-anadi-me-anant-me-to-be-honoured-with-award-named-after-sambhaji-maharaj-minister-3421353</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Maharashtra: Honorarium of Aadhaar centre operators raised; 12.8 cr Aadhaar registrations recorded till date</t>
+          <t>FTII and Maharashtra Film, Stage &amp; Cultural Development Corporation Ltd. sign MoU to expand film and media training in Maharashtra</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-aadhaar-centre-operators-honorarium-raised-registrations-recorded-9952118/</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Mumbai rains: Sena (UBT), contractors misappropriated funds meant for drainage system, claims Shelar</t>
+          <t>Give Custodianship Of Historic Forts To Maharashtra Government: Minister Ashish Shelar To Centre</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/mumbai-rains-sena-ubt-contractors-misappropriated-funds-meant-for-drainage-system-claims-shelar/2637642/</t>
+          <t>https://www.news18.com/india/hand-over-custodianship-of-historic-forts-to-maharashtra-government-minister-ashish-shelar-to-centre-9274572.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Highlight power of Operation Sindoor during Ganesh festival: Shelar tells organisers</t>
+          <t>Maharashtra to get India's first AI university led by industry experts</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/Highlight-power-of-Operation-Sindoor-during-Ganesh-festival--Shelar-tells-organisers/2841354</t>
+          <t>https://www.indiatoday.in/education-today/news/story/ai-education-indias-first-ai-university-to-set-up-in-maharashtra-2673858-2025-02-03</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Roads in Mumbai will be pothole-free before Ganesh festival: BJP ministers</t>
+          <t>Mumbai's Sanjay Gandhi National Park To Introduce 'Leopard Safari' For Visitors Soon</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
+          <t>https://www.news18.com/india/sanjay-gandhi-national-park-in-mumbai-to-introduce-leopard-safari-for-visitors-soon-ashish-shelar-9209891.html</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Play Marathi devotional songs on private radio stations: Shelar</t>
+          <t>New Mumbai BJP chief Ameet Satam is 3-time MLA with corporate background, Thackeray critic</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
+          <t>https://theprint.in/politics/new-mumbai-bjp-chief-ameet-satam-is-3-time-mla-with-corporate-background-thackeray-critic/2728464/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BCCI issues update on appointment to ACC's Board of Directors</t>
+          <t>Maharashtra government aims to make forts encroachment-free by May 31</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+          <t>Maharashtra govt forms 16-member panel to draft first-ever AI policy</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-16-member-panel-draft-ai-policy-9784605/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BCCI appoints Jay Shah and Ashish Shelar's successor ahead of Champions Trophy 2025</t>
+          <t>Maharashtra: Honorarium of Aadhaar centre operators raised; 12.8 cr Aadhaar registrations recorded till date</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-aadhaar-centre-operators-honorarium-raised-registrations-recorded-9952118/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mumbai BJP Chief Ashish Shelar Slams Uddhav &amp; Raj Thackeray For Pushing Personal Agendas Under Marathi Pride</t>
+          <t>Mumbai rains: Sena (UBT), contractors misappropriated funds meant for drainage system, claims Shelar</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-chief-ashish-shelar-slams-uddhav-raj-thackeray-for-pushing-personal-agendas-under-marathi-pride-video</t>
+          <t>https://theprint.in/india/mumbai-rains-sena-ubt-contractors-misappropriated-funds-meant-for-drainage-system-claims-shelar/2637642/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Maharashtra News: Minister Ashish Shelar Accuses Opposition Of Urban Naxalite Agenda To Curtail Ganeshotsav</t>
+          <t>Maharashtra to Establish India’s First Artificial Intelligence University</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-minister-ashish-shelar-accuses-opposition-of-urban-naxalite-agenda-to-curtail-ganeshotsav-traditions</t>
+          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Urges Netflix To Promote Marathi Content On OTT Platform</t>
+          <t>Roads in Mumbai will be pothole-free before Ganesh festival: BJP ministers</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-urges-netflix-to-promote-marathi-content-on-ott-platform</t>
+          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Targets Uddhav Thackeray, Raj Thackeray Over Hindi Row; Says Marathi</t>
+          <t>Play Marathi devotional songs on private radio stations: Shelar</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-targets-uddhav-thackeray-raj-thackeray-over-hindi-row-says-marathi-mandatory-hindi-optional-video</t>
+          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ashish Shelar Slams Uddhav-Raj Thackeray Rally As Irrelevant, Accuses Duo Of Distorting Facts</t>
+          <t>Maharashtra to have India's first AI university, says minister</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
+          <t>Maharashtra Declares Ganeshotsav As State Festival</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>No New Restrictions On Political Portrayals In Films, Says Minister Ashish Shelar During Council Debate</t>
+          <t>Major fire at mall in Mumbai's Bandra; firefighting on after 18 hours</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-new-restrictions-on-political-portrayals-in-films-says-minister-ashish-shelar-during-council-debate</t>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/29/major-fire-at-mall-in-mumbais-bandra-firefighting-on-after-18-hours</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Mumbai Minister Ashish Shelar Gives 72-Hour Deadline To Fix Potholes Ahead Of Ganeshotsav 2025</t>
+          <t>Culture Minister Ashish Shelar Praises Mukta Arts Productions, Subhash Ghai For Backing Regional Cinema</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-ashish-shelar-gives-72-hour-deadline-to-fix-potholes-ahead-of-ganeshotsav-2025</t>
+          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>No One Should Hurt Sentiments..: Maha Minister Ashish Shelar On Row Over Viral Ganeshotsav Reel By Content</t>
+          <t>Uddhav Thackeray, Rohit Pawar Hit Back After BJP Minister’s ‘Terrorist’ Remark</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-one-should-hurt-sentiments-maha-minister-ashish-shelar-on-row-over-viral-ganeshotsav-reel-by-content-creator-atharva-sudame</t>
+          <t>https://www.thestatesman.com/india/uddhav-thackeray-rohit-pawar-hit-back-after-bjp-ministers-terrorist-remark-1503454822.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Minister Ashish Shelar Meets BMC Chief Bhushan Gagrani, Demands White Paper On ₹1 Lakh Crore</t>
+          <t>Highlight power of Operation Sindoor during Ganesh festival: Shelar tells organisers</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-minister-ashish-shelar-meets-bmc-chief-bhushan-gagrani-demands-white-paper-on-1-lakh-crore-flood-control-spending-over-past-20-years</t>
+          <t>https://www.ptinews.com/story/national/highlight-power-of-operation-sindoor-during-ganesh-festival-shelar-tells-organisers/2841354</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ashish Shelar Addresses Media on Hindi as Third Language in Schools #Gallery</t>
+          <t>Maharashtra to establish country's first Artificial Intelligence university</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6712027</t>
+          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+          <t>Maharashtra seeks custodianship of ASI-protected forts for better conservation</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-seeks-custodianship-of-asi-protected-forts-for-better-conservation/article69373142.ece</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Visits Cellular Jail, Seeks Support For Veer Savarkar Memorial In Andaman</t>
+          <t>Shelar criticises desilting works in Mumbai, demands accountability from contractors</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-visits-cellular-jail-seeks-support-for-veer-savarkar-memorial-in-andaman-islands</t>
+          <t>https://theprint.in/india/shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors/2619256/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Second Arm Of Andheris Gokhale Bridge Inaugurated, Minister Ashish Shelar Hails Fast-Track Completion As</t>
+          <t>Good News For Marathi Filmmakers: Maharashtra Govt Plans Revival Of Single-Screen Cinemas</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/second-arm-of-andheris-gokhale-bridge-inaugurated-minister-ashish-shelar-hails-fast-track-completion-as-success-story-see-pics</t>
+          <t>https://www.news18.com/india/good-news-for-marathi-filmmakers-maharashtra-govt-plans-revival-of-single-screen-cinemas-ws-l-9492408.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Maharashtra: Ganeshotsav Declared State Festival; Ashish Shelar Alleges Conspiracy Against Hindu Traditions</t>
+          <t>Maharashtra minister compares assaults on non-Marathi speakers in state to Pahalgam terror attack</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-ganeshotsav-declared-state-festival-ashish-shelar-alleges-conspiracy-against-hindu-traditions</t>
+          <t>https://scroll.in/latest/1084239/maharashtra-minister-compares-assaults-on-non-marathi-speakers-in-state-to-pahalgam-terror-attack</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Proposes Grand National Memorial For Veer Savarkar At Andaman’s Cellular</t>
+          <t>Maharashtra to Set up The India First Artificial Intelligence University Details Here</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-proposes-grand-national-memorial-for-veer-savarkar-at-andamans-cellular-jail</t>
+          <t>https://www.jagranjosh.com/news/maharashtra-to-set-up-the-india-first-artificial-intelligence-university-details-here-175203</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ashish Shelar inaugurates Art Show by IAS Officers Nidhi Choudhari &amp; Rajanvir Singh Kapur</t>
+          <t>Task force formed to set up AI university in Maharashtra, says IT Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://culturecrossroads.ca/posts/ashish-shelar-inaugurates-art-show-by-ias-officers-nidhi-choudhari-rajanvir-singh-kapur/</t>
+          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ashish Shelar Directs BMC To Deploy 1,000 Volunteers With 1916 Helpline For Dahi Handi Safety</t>
+          <t>Residents of BDD chawls in Worli will get homes before July: Maharashtra minister</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-bmc-to-deploy-1000-volunteers-with-1916-helpline-for-dahi-handi-safety</t>
+          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed As Mumbai BJP President Ahead Of BMC Polls; CM Devendra Fadnavis, Ashish Shelar Extend</t>
+          <t>Expert Panel To Study PoP Use For Ganesh Idols, Assures Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls</t>
+          <t>https://www.news18.com/india/expert-panel-to-study-pop-use-for-ganesh-idols-assures-minister-ashish-shelar-9260345.html</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Historic Sword Of Maratha Sardar Raghuji Bhosale To Return To Maharashtra By July-End, Says Minister Ashish</t>
+          <t>Film City to come up near Khindsi lake in Ramtek</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-maratha-sardar-raghuji-bhosale-to-return-to-maharashtra-by-july-end-says-minister-ashish-shelar</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir’s ‘SUR Music’ Label</t>
+          <t>Maharashtra Govt Selects Savarkar's Composition For Its 1st Sambhaji Maharaj Song Award</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-government-selects-savarkar-composition-for-its-1st-sambhaji-maharaj-song-award-enn25022600100</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>VIDEO: Uddhav Thackerays Party Failed To improve Mumbais Stormwater Drain System Despite ₹1 Lakh Crore</t>
+          <t>Maharashtra govt arranges buses, special trains for people travelling to celebrate Ganesh Utsav</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-uddhav-thackerays-party-failed-to-improve-mumbais-stormwater-drain-system-despite-1-lakh-crore-spend-says-minister-ashish-shelar</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Mumbai News: Displaced Residents Near Elphinstone Bridge To Get Redeveloped Homes At Same Location, Announces</t>
+          <t>NIAT Students Shine at Mumbai Tech Week, Earning Recognition from Industry Leaders and IT Minister</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-displaced-residents-near-elphinstone-bridge-to-get-redeveloped-homes-at-same-location-announces-minister-ashish-shelar-video</t>
+          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Calls For Action To Boost Marathi Films &amp; Save Single-Screen Cinemas</t>
+          <t>Maharashtra govt declares Ganesh festival as Rajya Mahotsav'; launches portal</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-calls-for-action-to-boost-marathi-films-save-single-screen-cinemas</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Vikram Gaikwad Death: Maharashtra Deputy CM Eknath Shinde, Ashish Shelar Express Condolences</t>
+          <t>BCCI issues update on appointment to ACC's Board of Directors</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/national-award-winning-makeup-artist-vikram-gaikwad-passes-away-in-mumbai-maharashtra-deputy-cm-eknath-shinde-expresses-condolences</t>
+          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Criticises Desilting Works In Mumbai, Demands Accountability From</t>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Read Finally Gokhale Bridge Andheri Poora Ready Hua, Finally Ready, Guardian Minister Ashish Shelar Ke Hathon Open Kiya Gaya</t>
+          <t>BCCI appoints Jay Shah and Ashish Shelar's successor ahead of Champions Trophy 2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
+          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Ashish Shelar Slams Thackeray Rally As Theatrical, Draws Pahalgam Parallel; Kishori</t>
+          <t>Mumbai BJP Chief Ashish Shelar Slams Uddhav &amp; Raj Thackeray For Pushing Personal Agendas Under Marathi Pride</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ashish-shelar-slams-thackeray-rally-as-theatrical-draws-pahalgam-parallel-kishori-pednekar-hits-back</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-chief-ashish-shelar-slams-uddhav-raj-thackeray-for-pushing-personal-agendas-under-marathi-pride-video</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Mumbai Politics: Two Ex-UBT Corporators Join BJP; Shelar Declares Party Now Largest In Civic Body Ahead Of BMC</t>
+          <t>Maharashtra News: Minister Ashish Shelar Accuses Opposition Of Urban Naxalite Agenda To Curtail Ganeshotsav</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-two-ex-ubt-corporators-join-bjp-shelar-declares-party-now-largest-in-civic-body-ahead-of-bmc-polls</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-minister-ashish-shelar-accuses-opposition-of-urban-naxalite-agenda-to-curtail-ganeshotsav-traditions</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Mumbai News: BJP To Celebrate Maharashtra Day And Labour Day At 106 Locations Under Minister Ashish Shelars</t>
+          <t>Maharashtra Minister Ashish Shelar Urges Netflix To Promote Marathi Content On OTT Platform</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bjp-to-celebrate-maharashtra-day-and-labour-day-at-106-locations-under-minister-ashish-shelars-leadership</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-urges-netflix-to-promote-marathi-content-on-ott-platform</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Pune: Sinhagad Fort Development Plan Meeting to Be Held Within 15 Days, Says Cultural Minister Ashish Shelar</t>
+          <t>Maharashtra Minister Ashish Shelar Targets Uddhav Thackeray, Raj Thackeray Over Hindi Row; Says Marathi</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-sinhagad-fort-development-plan-meeting-to-be-held-within-15-days-says-cultural-minister-ashish-shelar/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-targets-uddhav-thackeray-raj-thackeray-over-hindi-row-says-marathi-mandatory-hindi-optional-video</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Mumbai: Siddhivinayak Temple Trust Felicitates Ashish Shelar For Declaring Ganeshotsav As State Festival</t>
+          <t>Ashish Shelar Slams Uddhav-Raj Thackeray Rally As Irrelevant, Accuses Duo Of Distorting Facts</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-siddhivinayak-temple-trust-felicitates-ashish-shelar-for-declaring-ganeshotsav-as-state-festival</t>
+          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Maharashtra: Gondan Kala To Enter Maharashtras Art Curriculum, Says Minister Ashish Shelar</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-gondan-kala-to-enter-maharashtras-art-curriculum-says-minister-ashish-shelar</t>
+          <t>https://www.lokmattimes.com/entertainment/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mumbai News: Relief For 86 Stalled SRA Projects As Residents Allowed To Appoint New Developers; Ashish Shelar</t>
+          <t>No New Restrictions On Political Portrayals In Films, Says Minister Ashish Shelar During Council Debate</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-relief-for-86-stalled-sra-projects-as-residents-allowed-to-appoint-new-developers-ashish-shelar-reviews-progress</t>
+          <t>https://www.freepressjournal.in/mumbai/no-new-restrictions-on-political-portrayals-in-films-says-minister-ashish-shelar-during-council-debate</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Mumbai News: Minister Ashish Shelar Directs BMC To Submit 3-Month Action Plan For Desilting Powai, Tulsi And</t>
+          <t>Mumbai Minister Ashish Shelar Gives 72-Hour Deadline To Fix Potholes Ahead Of Ganeshotsav 2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-directs-bmc-to-submit-3-month-action-plan-for-desilting-powai-tulsi-and-vihar-lakes</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-ashish-shelar-gives-72-hour-deadline-to-fix-potholes-ahead-of-ganeshotsav-2025</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>No New Road Works After May 20, Ensure Motorable Roads Before Monsoon: Ashish Shelar To BMC</t>
+          <t>No One Should Hurt Sentiments..: Maha Minister Ashish Shelar On Row Over Viral Ganeshotsav Reel By Content</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-new-road-works-after-may-20-ensure-motorable-roads-before-monsoon-ashish-shelar-to-bmc</t>
+          <t>https://www.freepressjournal.in/mumbai/no-one-should-hurt-sentiments-maha-minister-ashish-shelar-on-row-over-viral-ganeshotsav-reel-by-content-creator-atharva-sudame</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
+          <t>Mumbai Rains: Minister Ashish Shelar Meets BMC Chief Bhushan Gagrani, Demands White Paper On ₹1 Lakh Crore</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/07/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-minister-ashish-shelar-meets-bmc-chief-bhushan-gagrani-demands-white-paper-on-1-lakh-crore-flood-control-spending-over-past-20-years</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Pune: Maharashtra Declares Ganesh Festival as ‘State Festival,’ Plans Global Promotion: Ashish Shelar</t>
+          <t>Ashish Shelar Addresses Media on Hindi as Third Language in Schools #Gallery</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
+          <t>https://www.socialnews.xyz/?p=6712027</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Hindi Not Mandatory in Maharashtra Schools, Marathi Remains Only Compulsory Language: Ashish Shelar</t>
+          <t>Maharashtra govt to assist Marathi schools in USA: Support promised with curriculum and recommendations to ...</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/hindi-not-mandatory-in-maharashtra-schools-marathi-remains-only-compulsory-language-ashish-shelar</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/50-marathi-teaching-schools-in-america-support-promised-with-curriculum-and-recommendations-to-over-50-schools-teaching-nearly-300-students-135526242.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Mahesh Kale’s ‘Abhangwari’ Unveiled by Ashish Shelar on Ashadi Ekadashi!</t>
+          <t>Maharashtra: Ganeshotsav Declared State Festival; Ashish Shelar Alleges Conspiracy Against Hindu Traditions</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-ganeshotsav-declared-state-festival-ashish-shelar-alleges-conspiracy-against-hindu-traditions</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Maharashtra News: Shivchaturya Din Celebrated With Agra-To-Rajgad Cycle Yatra Flagged Off By Ashish Shelar</t>
+          <t>Ashish Shelar inaugurates Art Show by IAS Officers Nidhi Choudhari &amp; Rajanvir Singh Kapur</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shivchaturya-din-celebrated-with-agra-to-rajgad-cycle-yatra-flagged-off-by-ashish-shelar</t>
+          <t>https://culturecrossroads.ca/posts/ashish-shelar-inaugurates-art-show-by-ias-officers-nidhi-choudhari-rajanvir-singh-kapur/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>POP idol ban lifted: A triumph for artisans, says Maha Minister Ashish Shelar</t>
+          <t>Ashish Shelar Directs BMC To Deploy 1,000 Volunteers With 1916 Helpline For Dahi Handi Safety</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/pop-idol-ban-lifted-a-triumph-for-artisans-says-maha-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-bmc-to-deploy-1000-volunteers-with-1916-helpline-for-dahi-handi-safety</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ganeshotsav declared as ‘State Festival of Maharashtra’: Cultural Affairs Minister Ashish Shelar announces ...</t>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead Of BMC Polls; CM Devendra Fadnavis, Ashish Shelar Extend</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
+          <t>https://www.freepressjournal.in/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maharashtra minister Ashish Shelar pays tribute</t>
+          <t>Historic Sword Of Maratha Sardar Raghuji Bhosale To Return To Maharashtra By July-End, Says Minister Ashish</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-maratha-sardar-raghuji-bhosale-to-return-to-maharashtra-by-july-end-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Cultural Minister Ashish Shelar Gives Muhurat Clap for a Marathi Film ‘Ladki Bahin’!</t>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir’s ‘SUR Music’ Label</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
+          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
+          <t>Maharashtra Minister Ashish Shelar Calls For Action To Boost Marathi Films &amp; Save Single-Screen Cinemas</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-calls-for-action-to-boost-marathi-films-save-single-screen-cinemas</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>मुंबई में 2.5 लाख चूहों को मारने का दावा, जांच के आदेश, क्या है पूरा सच? आशिष शेलार</t>
+          <t>Read Finally Gokhale Bridge Andheri Poora Ready Hua, Finally Ready, Guardian Minister Ashish Shelar Ke Hathon Open Kiya Gaya</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
+          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>गणेशोत्सव को मिला `राज्य महोत्सव` का दर्जा, सांस्कृतिक कार्य मंत्री आशिष शेलार ने किया बड़ा ऐलान</t>
+          <t>Maharashtra Politics: Ashish Shelar Slams Thackeray Rally As Theatrical, Draws Pahalgam Parallel; Kishori</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ashish-shelar-slams-thackeray-rally-as-theatrical-draws-pahalgam-parallel-kishori-pednekar-hits-back</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा, मंत्री आशिष शेलार ने किया ऐलान</t>
+          <t>Mumbai Politics: Two Ex-UBT Corporators Join BJP; Shelar Declares Party Now Largest In Civic Body Ahead Of BMC</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/maharashtra-ganesh-utsav-latest-news-ashish-shelar-new-announcement/1248697/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-two-ex-ubt-corporators-join-bjp-shelar-declares-party-now-largest-in-civic-body-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+          <t>Mumbai: Siddhivinayak Temple Trust Felicitates Ashish Shelar For Declaring Ganeshotsav As State Festival</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-siddhivinayak-temple-trust-felicitates-ashish-shelar-for-declaring-ganeshotsav-as-state-festival</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hindi-Marathi Row: मराठी लोगों पर निशिकांत दुबे के बयान से भाजपा का किनारा, फडणवीस के मंत्री ने दी सख्त हिदायत</t>
+          <t>Maharashtra: Gondan Kala To Enter Maharashtras Art Curriculum, Says Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-gondan-kala-to-enter-maharashtras-art-curriculum-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>'शिवतीर्थ' पहुंचकर राज ठाकरे से मिले मुंबई बीजेपी अध्यक्ष, बीएमसी चुनावों में किससे हिसाब बराबर करेगी मनसे?</t>
+          <t>Mumbai News: Relief For 86 Stalled SRA Projects As Residents Allowed To Appoint New Developers; Ashish Shelar</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-relief-for-86-stalled-sra-projects-as-residents-allowed-to-appoint-new-developers-ashish-shelar-reviews-progress</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Maharashtra: मंत्री आशीष शेलार का बड़ा बयान- 'महाराष्ट्र में केवल मराठी अनिवार्य, हिंदी नहीं'</t>
+          <t>Mumbai News: Minister Ashish Shelar Directs BMC To Submit 3-Month Action Plan For Desilting Powai, Tulsi And</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-directs-bmc-to-submit-3-month-action-plan-for-desilting-powai-tulsi-and-vihar-lakes</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>`मुंबई हमारी है` बीजेपी नेता आशिष शेलार के दावे पर सुषमा अंधारे ने दिया करारा जवाब</t>
+          <t>Maharashtra: BJP Leader Sudhir Mungantiwar Slams Ministers’ Absenteeism, Pushes For Ban On Alcohol At</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-leader-sudhir-mungantiwar-slams-ministers-absenteeism-pushes-for-ban-on-alcohol-at-heritage-forts</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>अमित साटम को मुंबई BJP का अध्यक्ष नियुक्त किया गया</t>
+          <t>Maharashtra News: Shiv Sena (UBT) Chief Uddhav Thackeray Slams CM Devendra Fadnavis Over Rudali Remark,</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/amit-satam-appointed-as-mumbai-bjp-president-89721</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shiv-sena-ubt-chief-uddhav-thackeray-slams-cm-devendra-fadnavis-over-rudali-remark-defends-marathi-identity-video</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>राज ठाकरे के बयान पर आशीष शेलार बोले, 'पहलगाम में धर्म पूछकर मारा जाता है, यहां</t>
+          <t>Pune: Maharashtra Declares Ganesh Festival as ‘State Festival,’ Plans Global Promotion: Ashish Shelar</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के गणेशोत्सव को मिलेगा वैश्विक दर्जा, मंत्री आशीष शेलार ने की खास घोषणा</t>
+          <t>Hindi Not Mandatory in Maharashtra Schools, Marathi Remains Only Compulsory Language: Ashish Shelar</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
+          <t>https://www.freepressjournal.in/mumbai/hindi-not-mandatory-in-maharashtra-schools-marathi-remains-only-compulsory-language-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Maharashtra: निशिकांत दुबे के बयान पर बीजेपी ने बनाई दूरी! आशीष शेलार बोले- 'मराठी व्यक्ति</t>
+          <t>POP idol ban lifted: A triumph for artisans, says Maha Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
+          <t>https://www.thehawk.in/news/india/pop-idol-ban-lifted-a-triumph-for-artisans-says-maha-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>आशीष शेलार की जगह कौन होगा मुंबई BJP का अगला अध्यक्ष? रेस में ये नाम सबसे आगे</t>
+          <t>Maharashtra News: Shivchaturya Din Celebrated With Agra-To-Rajgad Cycle Yatra Flagged Off By Ashish Shelar</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shivchaturya-din-celebrated-with-agra-to-rajgad-cycle-yatra-flagged-off-by-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BJP सांसद निशिकांत दुबे के पटककर मारने वाले बयान पर उद्धव ठाकरे बोले, 'ऐसे कई लकड़बग्घे...'</t>
+          <t>Mahesh Kale’s ‘Abhangwari’ Unveiled by Ashish Shelar on Ashadi Ekadashi!</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
+          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>बीजेपी नेता आशीष शेलार के बयान से मची सियासी हलचल, बोले- 'राज ठाकरे और मैं...'</t>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror: BJP’s Shelar says some leaders ...</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>शाहरुख खान के घर 'मन्नत' अचानक पहुंचे वन विभाग के अधिकारी, भड़की महाराष्ट्र सरकार</t>
+          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
+          <t>https://www.socialnews.xyz/2025/08/19/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले BJP का बड़ा फैसला, इस नेता को बनाया मुंबई का पार्टी अध्यक्ष</t>
+          <t>Ganeshotsav declared as ‘State Festival of Maharashtra’: Cultural Affairs Minister Ashish Shelar announces ...</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : आशीष शेलार ने सांस्कृतिक पुरस्कारों का किया ऐलान</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
+          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>4,066 new Aadhaar kits to be distributed to collector's office across Maharashtra: Minister Ashish Shelar</t>
+          <t>Cultural Minister Ashish Shelar Gives Muhurat Clap for a Marathi Film ‘Ladki Bahin’!</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
+          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>MLA: File report in 7 days on status of H-West rd works, finish them by May 31</t>
+          <t>Rajeev Shukla Replaces Jay Shah in ACC Leadership</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
+          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार ने गणेशोत्सव गीत और पोर्टल का किया शुभारंभ, नागरिकों से भागीदारी की अपील</t>
+          <t>Minister Shelar inaugurates Gokhale bridge: After almost 2.5 years waiting, Andheri's Gokhale bridge second...</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/minister-ashish-shelar-launched-ganeshotsav-song-and-portal-appealed-to-citizens-for-participation-1328512.html</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ऐतिहासिक धरोहरें होंगी सुरक्षित, मंत्री शेलार का ऐलान-दस्तावेजों के संरक्षण को सरकार देगी मदद</t>
+          <t>मुंबई में 2.5 लाख चूहों को मारने का दावा, जांच के आदेश, क्या है पूरा सच? आशिष शेलार</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-historical-heritage-will-be-protected-minister-shelar-announced-government-will-help-in-preservation-of-documents-1324840.html</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>दुनिया में होगी महाराष्ट्र के गणेशोत्सव की धूम, आशीष शेलार कहा इसे बनाएंगे वर्ल्ड क्लास</t>
+          <t>गणेशोत्सव को मिला `राज्य महोत्सव` का दर्जा, सांस्कृतिक कार्य मंत्री आशिष शेलार ने किया बड़ा ऐलान</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/maharashtras-ganeshotsav-will-become-world-class-1325768.html</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>मुंबई भाजपा अध्यक्ष पद पर अमित साटम की नियुक्ति, फडणवीस और शेलार ने दी बधाई</t>
+          <t>महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा, मंत्री आशिष शेलार ने किया ऐलान</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bjp-mumbai-amit-satam-ashish-shelar-devendra-fadnavis-54-807644</t>
+          <t>https://hindi.news24online.com/state/mumbai/maharashtra-ganesh-utsav-latest-news-ashish-shelar-new-announcement/1248697/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Maharashtras First International Marathi Film Festival, Chitrapataka, Begins April 21; Cultural Affairs</t>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtras-first-international-marathi-film-festival-chitrapataka-begins-april-21-cultural-affairs-minister-ashish-shelar-reveals-emblem</t>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>BJP leader likens attacks on non-Marathi speakers to Pahalgam massacre</t>
+          <t>Hindi-Marathi Row: मराठी लोगों पर निशिकांत दुबे के बयान से भाजपा का किनारा, फडणवीस के मंत्री ने दी सख्त हिदायत</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
+          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Complete all dug up roads in Mumbai by May 31: Ashish Shelar to BMC</t>
+          <t>'शिवतीर्थ' पहुंचकर राज ठाकरे से मिले मुंबई बीजेपी अध्यक्ष, बीएमसी चुनावों में किससे हिसाब बराबर करेगी मनसे?</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/shelar-directs-bmc-to-stop-road-concretisation-works-from-today-10016418/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>BCCI announces Rajeev Shukla, Ashish Shelar as new representatives for ACC Board</t>
+          <t>Maharashtra: मंत्री आशीष शेलार का बड़ा बयान- 'महाराष्ट्र में केवल मराठी अनिवार्य, हिंदी नहीं'</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.storyboard18.com/brand-makers/bcci-announces-rajeev-shukla-ashish-shelar-as-new-representatives-for-acc-board-58707.htm</t>
+          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>No land in Dharavi has been given to Adani, Ashish Shelar</t>
+          <t>`मुंबई हमारी है` बीजेपी नेता आशिष शेलार के दावे पर सुषमा अंधारे ने दिया करारा जवाब</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/no-land-in-dharavi-has-been-given-to-adani-ashish-shelar-9899366/</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Have urged Netflix to provide space for Marathi content on platform: Shelar</t>
+          <t>अमित साटम को मुंबई BJP का अध्यक्ष नियुक्त किया गया</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
+          <t>https://www.mumbailive.com/hi/politics/amit-satam-appointed-as-mumbai-bjp-president-89721</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shelar To Represent India In Asian Cricket Council</t>
+          <t>राज ठाकरे के बयान पर आशीष शेलार बोले, 'पहलगाम में धर्म पूछकर मारा जाता है, यहां</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.news18.com/cricket/rajeev-shukla-ashish-shelar-to-represent-india-in-asian-cricket-council-9253383.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir's 'SUR Music' Label</t>
+          <t>महाराष्ट्र के गणेशोत्सव को मिलेगा वैश्विक दर्जा, मंत्री आशीष शेलार ने की खास घोषणा</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BJP Leader Compares Attack on Hindi-speaking People with Pahalgam Incident</t>
+          <t>Maharashtra: निशिकांत दुबे के बयान पर बीजेपी ने बनाई दूरी! आशीष शेलार बोले- 'मराठी व्यक्ति</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/politics/bjp-leader-compares-attack-on-hindi-speaking-people-with-pahalgam-incident-1889788</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Days after Raj met CM Fadnavis, his son meets Shelar; sets tongues wagging</t>
+          <t>सैफ अली खान पर हमले के बाद मंत्री आशीष शेलार का बड़ा बयान, 'बॅालीवुड वालों डरना...'</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/days-after-raj-met-cm-fadnavis-his-son-meets-shelar-sets-tongues-wagging-10207422/</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Maharashtra govt will make arrangements for immersion of large Ganesh idols: Ashish Shelar on PoP use</t>
+          <t>आशीष शेलार की जगह कौन होगा मुंबई BJP का अगला अध्यक्ष? रेस में ये नाम सबसे आगे</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
+          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Reema Lagoos Ex-Husband And Veteran Actor Vivek Lagoo Dies, Last Rites To Be Held Today; Maharashtra Minister Ashish Shelar Pays Tribute</t>
+          <t>BJP सांसद निशिकांत दुबे के पटककर मारने वाले बयान पर उद्धव ठाकरे बोले, 'ऐसे कई लकड़बग्घे...'</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>BMC told to finish all roadworks in Mumbai suburbs by May 31, says minister</t>
+          <t>बीजेपी नेता आशीष शेलार के बयान से मची सियासी हलचल, बोले- 'राज ठाकरे और मैं...'</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>It's a Public Appeasement Campaign: BJP on Thackerays Reunion</t>
+          <t>शाहरुख खान के घर 'मन्नत' अचानक पहुंचे वन विभाग के अधिकारी, भड़की महाराष्ट्र सरकार</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/politics/its-a-public-appeasement-campaign-bjp-on-thackerays-reunion-1889545</t>
+          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BJP's Nishikant Dubey dares Uddhav, Raj Thackeray to visit north India, Tamil Nadu | Reactions so far</t>
+          <t>BMC चुनाव से पहले BJP का बड़ा फैसला, इस नेता को बनाया मुंबई का पार्टी अध्यक्ष</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Maharashtra govt taking balanced approach to pigeon feeding issue: Minister Shelar</t>
+          <t>Saif Ali Khan attack case: Ashish Shelar dares Uddhav Thackeray to confront Mamata Banerjee over Bangladesh infiltration</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>BJP likely to appoint new Mumbai chief ahead of BMC polls</t>
+          <t>महाराष्ट्र : आशीष शेलार ने सांस्कृतिक पुरस्कारों का किया ऐलान</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/bjp-likely-to-appoint-new-mumbai-chief-ahead-of-bmc-polls-13375950.html</t>
+          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Good News For Marathi Filmmakers: Maharashtra Govt Plans Revival Of Single-Screen Cinemas</t>
+          <t>4,066 new Aadhaar kits to be distributed to collector's office across Maharashtra: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/good-news-for-marathi-filmmakers-maharashtra-govt-plans-revival-of-single-screen-cinemas-ws-l-9492408.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Barely 10% nullah desilting work completed in 35 days: Shelar</t>
+          <t>MLA: File report in 7 days on status of H-West rd works, finish them by May 31</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/barely-10-nullah-desilting-work-completed-in-35-days-shelar-9991132/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Minister Shelar warns of ‘urban naxal’ threat</t>
+          <t>Worli BDD Chawl redevelopment residents will get their new homes before 'Shravan': Maharashtra Minister</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
+          <t>मंत्री आशीष शेलार ने गणेशोत्सव गीत और पोर्टल का किया शुभारंभ, नागरिकों से भागीदारी की अपील</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/minister-ashish-shelar-launched-ganeshotsav-song-and-portal-appealed-to-citizens-for-participation-1328512.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4 Marathi films selected for 2025 Cannes Film Festival reveals Maharashtra cultural affairs minister...</t>
+          <t>ऐतिहासिक धरोहरें होंगी सुरक्षित, मंत्री शेलार का ऐलान-दस्तावेजों के संरक्षण को सरकार देगी मदद</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-historical-heritage-will-be-protected-minister-shelar-announced-government-will-help-in-preservation-of-documents-1324840.html</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Sword of Raghuji-1 Bhonsale to be brought to India on Aug 18</t>
+          <t>दुनिया में होगी महाराष्ट्र के गणेशोत्सव की धूम, आशीष शेलार कहा इसे बनाएंगे वर्ल्ड क्लास</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://navbharatlive.com/maharashtra/pune/maharashtras-ganeshotsav-will-become-world-class-1325768.html</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ameet Satam appointed BJP Mumbai Chief</t>
+          <t>मुंबई भाजपा अध्यक्ष पद पर अमित साटम की नियुक्ति, फडणवीस और शेलार ने दी बधाई</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/industry-briefing-news/ameet-satam-appointed-bjp-mumbai-chief-146770.html</t>
+          <t>https://mpbreakingnews.in/maharashtra/bjp-mumbai-amit-satam-ashish-shelar-devendra-fadnavis-54-807644</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Who Is Ameet Satam? Three-Term MLA Picked As BJP's Mumbai Chief Ahead Of BMC Polls</t>
+          <t>Maharashtras First International Marathi Film Festival, Chitrapataka, Begins April 21; Cultural Affairs</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/ameet-satam-mumbai-bjp-chief-andheri-west-mla-bmc-polls-ws-l-9526976.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-first-international-marathi-film-festival-chitrapataka-begins-april-21-cultural-affairs-minister-ashish-shelar-reveals-emblem</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Maharashtra minister Shelar asks govt departments to step up Ganeshotsav participation; Rs 10 crore for cultural events</t>
+          <t>Maharashtra Minister Ashish Shelar Visits Cellular Jail, Seeks Support For Veer Savarkar Memorial In Andaman</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-minister-shelar-asks-govt-departments-to-step-up-ganeshotsav-participation-rs-10-crore-for-cultural-events-10205121/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-visits-cellular-jail-seeks-support-for-veer-savarkar-memorial-in-andaman-islands</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>No one wants to stay in Shiv Sena (UBT): BJP</t>
+          <t>Mumbai News: Displaced Residents Near Elphinstone Bridge To Get Redeveloped Homes At Same Location, Announces</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://uniindia.com/no-one-wants-to-stay-in-shiv-sena-ubt--bjp/west/news/3496190.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-displaced-residents-near-elphinstone-bridge-to-get-redeveloped-homes-at-same-location-announces-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>BJP names three-term MLA Ameet Satam as Mumbai chief before BMC polls</t>
+          <t>VIDEO: Uddhav Thackerays Party Failed To improve Mumbais Stormwater Drain System Despite ₹1 Lakh Crore</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://tripuratimes.com/ttimes/bjp-names-three-term-mla-ameet-satam-as-mumbai-chief-before-bmc-polls-30851.html/</t>
+          <t>https://www.freepressjournal.in/mumbai/video-uddhav-thackerays-party-failed-to-improve-mumbais-stormwater-drain-system-despite-1-lakh-crore-spend-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Worli BDD Chawl redevelopment residents will get their new homes before 'Shravan': Maharashtra Minister</t>
+          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Mumbai To Get Rid of Flood-Like Situations? New Plan Announced After 180 mm Rainfall Chaos</t>
+          <t>Vikram Gaikwad Death: Maharashtra Deputy CM Eknath Shinde, Ashish Shelar Express Condolences</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
+          <t>https://www.freepressjournal.in/mumbai/national-award-winning-makeup-artist-vikram-gaikwad-passes-away-in-mumbai-maharashtra-deputy-cm-eknath-shinde-expresses-condolences</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Culture Minister Ashish Shelar Praises Mukta Arts Productions, Subhash Ghai For Backing Regional Cinema</t>
+          <t>Ganeshotsav 2025: Maharashtra Govt Gears Up For Grand Celebrations; Awards For Mandals, Drone Shows At Girgaon</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
+          <t>https://www.freepressjournal.in/mumbai/ganeshotsav-2025-maharashtra-govt-gears-up-for-grand-celebrations-awards-for-mandals-drone-shows-at-girgaon-chowpatty-announced</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Expert Panel To Study PoP Use For Ganesh Idols, Assures Minister Ashish Shelar</t>
+          <t>From 'jihadi gathering' to ‘no real brotherhood’: BJP on Uddhav-Raj Thackeray reunion</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/expert-panel-to-study-pop-use-for-ganesh-idols-assures-minister-ashish-shelar-9260345.html</t>
+          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Task force formed to set up AI university in Maharashtra, says IT Minister Ashish Shelar</t>
+          <t>BJP leader likens attacks on non-Marathi speakers to Pahalgam massacre</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
+          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares assaults on non-Marathi speakers in state to Pahalgam terror attack</t>
+          <t>BCCI announces Rajeev Shukla, Ashish Shelar as new representatives for ACC Board</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1084239/maharashtra-minister-compares-assaults-on-non-marathi-speakers-in-state-to-pahalgam-terror-attack</t>
+          <t>https://www.storyboard18.com/brand-makers/bcci-announces-rajeev-shukla-ashish-shelar-as-new-representatives-for-acc-board-58707.htm</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
+          <t>Rajeev Shukla, Ashish Shelar To Represent India In Asian Cricket Council</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
+          <t>https://www.news18.com/cricket/rajeev-shukla-ashish-shelar-to-represent-india-in-asian-cricket-council-9253383.html</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Forest department officials suddenly reached Shahrukh Khan's house 'Mannat', Maharashtra government got angry. ..?</t>
+          <t>Maharashtra minister condemns assault on Hindi-speaking people, draws parallel with Pahalgam attack</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.indiaherald.com/Breaking/Read/994828609/Forest-department-officials-suddenly-reached-Shahrukh-Khans-house-Mannat-Maharashtra-government-got-angry-</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-minister-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack/articleshow/122281220.cms</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+          <t>Fresh tussle between Shiv Sena and BJP over Marathi films</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/fresh-tussle-between-shiv-sena-and-bjp-over-marathi-films-10155696/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+          <t>Mumbai BJP unit likely to get new president ahead of BMC polls</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mumbai-bjp-unit-new-president-bmc-polls-10165826/</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Amit Satam Takes Charge as Mumbai BJP President Ahead of Crucial BMC Elections</t>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir's 'SUR Music' Label</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3601925-amit-satam-takes-charge-as-mumbai-bjp-president-ahead-of-crucial-bmc-elections</t>
+          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror: BJP’s Shelar says some leaders ...</t>
+          <t>Shelar orders swift action to curb bird menace near CSMIA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Agency News | ⚡Reema Lagoo’s Ex-Huband Vivek Lagoo No More</t>
+          <t>Nearly 60% of bakeries in Mumbai yet to switch to cleaner fuel</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/quickly/agency-news/reema-lagoo-s-ex-huband-vivek-lagoo-no-more-6939671.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/nearly-60-of-bakeries-in-mumbai-yet-to-switch-to-cleaner-fuel-10088723/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Maharashtra govt to grant Rs 25,000 each to 'bhajani mandals' for Ganesh festival</t>
+          <t>Raghuji Bhonsale’s legendary sword set to arrive in Mumbai tomorrow, ‘darshan’ ceremony to be held at PL Deshpande Maharashtra Kala Academy</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/maharashtra-govt-to-grant-rs-25000-each-to-bhajani-mandals-for-ganesh-festival-9690752</t>
+          <t>https://indianexpress.com/article/cities/mumbai/raghuji-bhonsales-legendary-sword-mumbai-10194874/</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Sword of Maratha glory returns after two centuries: Maharashtra minister Shelar brings home Raghuji ...</t>
+          <t>Maharashtra Cultural Minister Ashish Shelar inaugurates Kala Ghoda Arts Festival 2025</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/sword-of-maratha-glory-returns-after-two-centuries-maharashtra-brings-home-raghuji-bhosales-legendary-weapon-from-london-auction-135656002.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Minister Shelar inaugurates Gokhale bridge: After almost 2.5 years waiting, Andheri's Gokhale bridge second...</t>
+          <t>Maharashtra BJP Minister links Mira Road assault to Pahalgam attack</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Maharashtra To Extend Official Curriculum Support To Marathi Schools In US</t>
+          <t>BJP names three-term MLA Ameet Satam as Mumbai chief before BMC polls</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
+          <t>https://tripuratimes.com/ttimes/bjp-names-three-term-mla-ameet-satam-as-mumbai-chief-before-bmc-polls-30851.html/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Amid Language Row At Home, Maharashtra Govt To Provide Curriculum To Marathi Schools In US</t>
+          <t>Maharashtra's Ganesh Festival: Celebrating India's Valor</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/amid-language-row-at-home-maharashtra-govt-to-provide-curriculum-to-marathi-schools-in-us-ws-l-9462862.html</t>
+          <t>https://www.devdiscourse.com/article/entertainment/3548452-maharashtras-ganesh-festival-celebrating-indias-valor</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+          <t>PoP idol-making supports livelihood of Maharashtra artisans, experts to study issue: Shelar</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
+          <t>https://theprint.in/india/pop-idol-making-supports-livelihood-of-maharashtra-artisans-experts-to-study-issue-shelar/2544248/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>4 Marathi films selected for Cannes Film Festival: Minister</t>
+          <t>Mumbai News: BJP To Celebrate Maharashtra Day And Labour Day At 106 Locations Under Minister Ashish Shelars</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/entertainment/marathi/movies/news/4-marathi-films-selected-for-cannes-film-festival-minister/articleshow/120451522.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bjp-to-celebrate-maharashtra-day-and-labour-day-at-106-locations-under-minister-ashish-shelars-leadership</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>अमेरिकेतील मराठी शाळांना महाराष्ट्र सरकारतर्फे अभ्यासक्रम पुरवणार; आशिष शेलारांचे आश्वासन</t>
+          <t>Second Arm Of Andheris Gokhale Bridge Inaugurated, Minister Ashish Shelar Hails Fast-Track Completion As</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/international/bjp-minister-ashish-shelar-on-america-tour-said-maharashtra-government-will-provide-curriculum-to-marathi-schools-in-america-a-a719/</t>
+          <t>https://www.freepressjournal.in/mumbai/second-arm-of-andheris-gokhale-bridge-inaugurated-minister-ashish-shelar-hails-fast-track-completion-as-success-story-see-pics</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Ashish Shelar : पहलगाममध्ये धर्म विचारून हिंदूंना गोळ्या मारल्या अन् इथे निष्पाप हिंदूंना</t>
+          <t>Maharashtra Minister Ashish Shelar Criticises Desilting Works In Mumbai, Demands Accountability From</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Avinash Jadhav on Ashish Shelar : आशिष शेलारांकडून मनसेच्या मराठी भाषा आंदोलनाची पहलगाम हल्ल्याशी</t>
+          <t>Mumbai News: Minister Ashish Shelar Seeks Centre’s Help As Water Tanker Strike Looms Over CGWA License Row</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-seeks-centres-help-as-water-tanker-strike-looms-over-cgwa-license-row</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>मुंबई भाजपच्या अध्यक्षपदी आशिष शेलार कायम राहणार?</t>
+          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/will-ashish-shelar-continue-as-mumbai-bjp-president-a-a285-c941/</t>
+          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BMC Election : मनसैनिकांची तुलना पहलगामच्या दहशतवाद्यांशी, आशिष शेलारांचा तोल कसा सुटला? की</t>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
+          <t>https://www.thehawk.in/news/india/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>राज्यातील भजनी मंडळांना शासनाकडून २५ हजार</t>
+          <t>Mumbai To House New Cultural Centre And Museum Celebrating Maharashtra’s Heritage, Says Minister Ashish</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-announced-grant-of-rs-25000-for-1800-bhajani-mandals-across-maharashtra-for-ganesh-festival-zws-70-5324659/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-house-new-cultural-centre-and-museum-celebrating-maharashtras-heritage-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BJP : आशिष शेलारांच्या गाडीसमोर मोठा राडा, भाजप पदाधिकाऱ्यांमध्ये थेट हाणामारी</t>
+          <t>Concerns Of Residents Affected By Elphinstone Bridge Demolition Will Be Addressed, Assures Mumbai Suburban</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/dispute-between-bjp-party-workers-in-front-of-minister-ashish-shelar-car/articleshow/121829032.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/concerns-of-residents-affected-by-elphinstone-bridge-demolition-will-be-addressed-assures-mumbai-suburban-guardian-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ashish Shelar : अहो ‘बाता’शिष शेलार… मुंबईची तुंबई होताच ठाकरेंच्या सेनेकडून...</t>
+          <t>Maharashtra Minister Ashish Shelar Proposes Grand National Memorial For Veer Savarkar At Andaman’s Cellular</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-proposes-grand-national-memorial-for-veer-savarkar-at-andamans-cellular-jail</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Mumbai BEST Elections Result: मुंबई ही आमचीच...! बेस्टच्या निकालानंतर शेलारांनी BMC साठी शड्डू ठोकला, ठाकरे...</t>
+          <t>Maharashtra Forms Task Force To Establish Indias First Artificial Intelligence University, Says IT Minister</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-forms-task-force-to-establish-indias-first-artificial-intelligence-university-says-it-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>कोल्हापुरात जुन्या मराठी चित्रपटांचे मोफत प्रदर्शन; ॲड. आशिष शेलार</t>
+          <t>No New Road Works After May 20, Ensure Motorable Roads Before Monsoon: Ashish Shelar To BMC</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/ashish-shelar-announces-free-screening-of-old-marathi-films-in-kolhapur-news-amy-95-5196886/</t>
+          <t>https://www.freepressjournal.in/mumbai/no-new-road-works-after-may-20-ensure-motorable-roads-before-monsoon-ashish-shelar-to-bmc</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>मराठी चित्रपटांसाठी महाराष्ट्र सरकार थेट Netflix च्या अमेरिकेतील हेडक्वॉर्टर्समध्ये पोहोचलं; अमेरिका...</t>
+          <t>Mumbai News: PoP Ganesh Idol Makers Protest Bombay HC Ban; Minister Shelar Backs Artisans</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-pop-ganesh-idol-makers-protest-bombay-hc-ban-minister-shelar-backs-artisans</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>मराठी आंदोलनाची ‘पहलगाम’शी तुलना, आशीष शेलार यांच्या विधानामुळे वाद; विरोधकांचे टीकास्त्र</t>
+          <t>"Only Marathi Is Mandatory In Maharashtra Schools, Not Hindi": Minister</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-compared-marathi-movement-with-pahalgam-terrorist-attack-css-98-5209656/</t>
+          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meets Ashish Shelar : आशिष शेलारांच्या कार्यालयाच्या बाहेरूनच अमित ठाकरे म्हणाले,</t>
+          <t>Maharashtra To Extend Official Curriculum Support To Marathi Schools In US</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
+          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Ashish Shelar praises Raj Thackeray : राज ठाकरेंचा 'दानपट्टा' फिरणार? 'मनसे'च्या गुढीपाडवा मेळाव्यापूर्वीच भाजप मंत्री शेलारांनी गोंजारलं</t>
+          <t>Amid Language Row At Home, Maharashtra Govt To Provide Curriculum To Marathi Schools In US</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-minister-ashish-shelar-praises-raj-thackeray-at-marathi-film-event-mumbai-pp82</t>
+          <t>https://www.news18.com/india/amid-language-row-at-home-maharashtra-govt-to-provide-curriculum-to-marathi-schools-in-us-ws-l-9462862.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ashish Shelar : कांदिवलीत मंत्री आशिष शेलारांसमोर भाजपच्या दोन गटात राडा; नेमकं प्रकरण काय?</t>
+          <t>अमेरिकेतील मराठी शाळांना महाराष्ट्र सरकारतर्फे अभ्यासक्रम पुरवणार; आशिष शेलारांचे आश्वासन</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
+          <t>https://www.lokmat.com/international/bjp-minister-ashish-shelar-on-america-tour-said-maharashtra-government-will-provide-curriculum-to-marathi-schools-in-america-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>“राज्यात सक्ती फक्त मराठीची, हिंदीची नाही; चर्चा अवास्तव, अवाजवी, अतार्किक”: आशिष शेलार</t>
+          <t>Ashish Shelar : पहलगाममध्ये धर्म विचारून हिंदूंना गोळ्या मारल्या अन् इथे निष्पाप हिंदूंना</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-said-compulsion-in-the-state-is-only-marathi-not-hindi-and-the-discussion-is-unrealistic-unreasonable-illogical-a-a719/</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Bala Nandgaonkar:आजच्या तारखेला अख्ख्या भारतात आशिष शेलार साहेब एक नंबरचे वक्ते बाळा नांदगावकरांचा</t>
+          <t>Avinash Jadhav on Ashish Shelar : आशिष शेलारांकडून मनसेच्या मराठी भाषा आंदोलनाची पहलगाम हल्ल्याशी</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
+          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>मराठी माणसाने काळानुरुप नाट्यकलेत नवनवीन प्रयोग केले – ॲड. आशिष शेलार</t>
+          <t>मुंबई भाजपच्या अध्यक्षपदी आशिष शेलार कायम राहणार?</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-says-marathi-people-experimented-new-ways-of-performing-arts-mumbai-print-news-css-98-5158726/</t>
+          <t>https://www.lokmat.com/mumbai/will-ashish-shelar-continue-as-mumbai-bjp-president-a-a285-c941/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज्य शासना तर्फे गतवर्षापासून आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव होणार</t>
+          <t>BMC Election : मनसैनिकांची तुलना पहलगामच्या दहशतवाद्यांशी, आशिष शेलारांचा तोल कसा सुटला? की</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ashish-shelar-announces-international-marathi-film-festival/32779</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>शून्य + शून्य = भोपळा; आशिष शेलारांचा मनसे-उबाठावर घणाघात</t>
+          <t>राज्यातील भजनी मंडळांना शासनाकडून २५ हजार</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-bjp-mumbai-president-ashish-shelar-strongly-criticized-the-opposition-while-speaking-to-moderates-in-pune-after-the-best-election-results-a-a1008/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-announced-grant-of-rs-25000-for-1800-bhajani-mandals-across-maharashtra-for-ganesh-festival-zws-70-5324659/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>“मुंबईकर उद्धव ठाकरेंना त्यांची जागा दाखवतील, मविआच्या ५० जागाही येणार नाही”; भाजपाचा दावा</t>
+          <t>Ashish Shelar : अहो ‘बाता’शिष शेलार… मुंबईची तुंबई होताच ठाकरेंच्या सेनेकडून...</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-and-said-mahayuti-to-win-upcoming-mumbai-municipal-corporation-election-a-a719/</t>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांमधील असमानता दूर करण्यासाठी त्रिभाषा सूत्र स्वीकारले, मंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+          <t>Mumbai BEST Elections Result: मुंबई ही आमचीच...! बेस्टच्या निकालानंतर शेलारांनी BMC साठी शड्डू ठोकला, ठाकरे...</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-three-language-formula-ashish-shelar-on-third-language-debate-schools-policy-mumbai-print-news-vsd-99-5179405/</t>
+          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ चित्रपटासंदर्भात आशिष शेलार आक्रमक; सेन्सॉर बोर्डाचा उल्लेख केला, थेट फेरविचार करण्याचे आदेश..</t>
+          <t>कोल्हापुरात जुन्या मराठी चित्रपटांचे मोफत प्रदर्शन; ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-is-aggressive-regarding-the-film-khalid-ka-shivaji-mumbai-print-news-phm-00-5285093/</t>
+          <t>https://www.loksatta.com/kolhapur/ashish-shelar-announces-free-screening-of-old-marathi-films-in-kolhapur-news-amy-95-5196886/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+          <t>मराठी चित्रपटांसाठी महाराष्ट्र सरकार थेट Netflix च्या अमेरिकेतील हेडक्वॉर्टर्समध्ये पोहोचलं; अमेरिका...</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Ashish Shelar: रघुजी भोसलेंची तलवार परत मिळवण्यात यश | Marathi News</t>
+          <t>मराठी आंदोलनाची ‘पहलगाम’शी तुलना, आशीष शेलार यांच्या विधानामुळे वाद; विरोधकांचे टीकास्त्र</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ashish-shelar-success-in-regaining-raghuji-bhosle-s-sword-marathi-news-1043330.html</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-compared-marathi-movement-with-pahalgam-terrorist-attack-css-98-5209656/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मनसेच्या आंदोलनाची तुलना पहलगाम हल्ल्याशी; आशीष शेलारांचं मोठं विधान</t>
+          <t>Amit Thackeray Meets Ashish Shelar : आशिष शेलारांच्या कार्यालयाच्या बाहेरूनच अमित ठाकरे म्हणाले,</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>शेलारजी फार डिंग्या मारू नका, बेस्ट निवडणुकीतही तुम्ही तीर मारले नाहीत. तुम्हाला</t>
+          <t>मुंबई भाजपा पदाधिकाऱ्यांमध्ये राडा; आशिष शेलार कारमधून उतरताच दोन गटांत हाणामारी</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
+          <t>https://www.lokmat.com/mumbai/mumbai-bjp-office-bearers-clash-in-front-of-ashish-shelar-car-a-fight-broke-out-between-two-groups-at-kandivali-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>शिवाजी महाराजांच्या पराक्रमाची साक्ष असणारे किल्ले आमच्या ताब्यात द्या, राज्य</t>
+          <t>Ashish Shelar praises Raj Thackeray : राज ठाकरेंचा 'दानपट्टा' फिरणार? 'मनसे'च्या गुढीपाडवा मेळाव्यापूर्वीच भाजप मंत्री शेलारांनी गोंजारलं</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-demand-to-asi-central-government-to-handover-forts-to-maharashtra-govt-raigad-archaeological-survey-of-india-marathi-news-1351013</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-minister-ashish-shelar-praises-raj-thackeray-at-marathi-film-event-mumbai-pp82</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ashish Shelar : ठाकरे बंधूंच्या विजय मेळाव्यावर आशीष शेलार यांची खोचक टीका</t>
+          <t>Ashish Shelar : कांदिवलीत मंत्री आशिष शेलारांसमोर भाजपच्या दोन गटात राडा; नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>राज्य शासनातर्फे यंदा आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव, आशिष शेलार यांची घोषणा</t>
+          <t>“राज्यात सक्ती फक्त मराठीची, हिंदीची नाही; चर्चा अवास्तव, अवाजवी, अतार्किक”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/marathi-cinema/marathi-film-festival-in-2025-ashish-shelar-announced-rajya-shasan-marathi-movie-nomination-a-a998/</t>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-said-compulsion-in-the-state-is-only-marathi-not-hindi-and-the-discussion-is-unrealistic-unreasonable-illogical-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>“सार्वजनिक गणेशोत्सव आता ‘महाराष्ट्र राज्य महोत्सव’”; आशिष शेलार यांची विधानसभेत घोषणा</t>
+          <t>Bala Nandgaonkar:आजच्या तारखेला अख्ख्या भारतात आशिष शेलार साहेब एक नंबरचे वक्ते बाळा नांदगावकरांचा</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ganeshotsav-is-now-maharashtra-state-festival-bjp-minister-ashish-shelar-announcement-in-the-vidhan-sabha-a-a719/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>"राजकारणात फक्त आशिष शेलारांना ओळखते..."; ठाकरे बंधूंच्या मराठी मोर्चावर आशा भोसले काय म्हणाल्या?</t>
+          <t>मराठी माणसाने काळानुरुप नाट्यकलेत नवनवीन प्रयोग केले – ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/in-politics-i-only-know-ashish-shelar-what-did-singer-asha-bhosle-say-about-the-raj-and-uddhav-thackeray-brothers-marathi-morcha-a-a629/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-says-marathi-people-experimented-new-ways-of-performing-arts-mumbai-print-news-css-98-5158726/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>कान फिल्म फेस्टिव्हलमध्ये 'या' चार मराठी सिनेमांची झाली निवड, सांस्कृतिक मंत्री आशिष शेलार यांची घोषणा</t>
+          <t>‘खालिद का शिवाजी’ चित्रपटासंदर्भात आशिष शेलार आक्रमक; सेन्सॉर बोर्डाचा उल्लेख केला, थेट फेरविचार करण्याचे आदेश..</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/marathi-cinema/four-marathi-films-have-been-selected-for-the-cannes-film-festival-announced-by-cultural-minister-ashish-shelar-a-a998/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-is-aggressive-regarding-the-film-khalid-ka-shivaji-mumbai-print-news-phm-00-5285093/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>माहिती तंत्रज्ञान विभागातर्फे 4066 नवे आधार किट जिल्हाधिकाऱ्यांना देणार तुमच्या</t>
+          <t>Ashish Shelar : ठाकरे बंधूंच्या विजय मेळाव्यावर आशीष शेलार यांची खोचक टीका</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/4066-new-aadhaar-kits-will-be-given-to-district-collectors-by-information-technology-department-says-ashish-shelar-how-much-in-your-district-1341609</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>सांस्कृतिक मंत्री म्हणतात ” पोळा करा, शहरी नक्षलवाद संपवा”</t>
+          <t>शून्य + शून्य = भोपळा; आशिष शेलारांचा मनसे-उबाठावर घणाघात</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/wardha-to-end-urban-naxalism-traditional-festivals-like-bail-pola-must-be-celebrated-with-enthusiasm-adv-ashish-shelar-sud-02-5325172/</t>
+          <t>https://www.lokmat.com/pune/pune-news-bjp-mumbai-president-ashish-shelar-strongly-criticized-the-opposition-while-speaking-to-moderates-in-pune-after-the-best-election-results-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>राज ठाकरेंच्या ‘त्या’ टीकेला शेलारांचं खोचक प्रत्युत्तर; म्हणाले ज्यांना निवडून येता येत...</t>
+          <t>“मुंबईकर उद्धव ठाकरेंना त्यांची जागा दाखवतील, मविआच्या ५० जागाही येणार नाही”; भाजपाचा दावा</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-and-said-mahayuti-to-win-upcoming-mumbai-municipal-corporation-election-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रयत्न - आशिष शेलार</t>
+          <t>विद्यार्थ्यांमधील असमानता दूर करण्यासाठी त्रिभाषा सूत्र स्वीकारले, मंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/efforts-to-get-unesco-cultural-status-for-ganeshotsav-ashish-shelar-a-a727/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-three-language-formula-ashish-shelar-on-third-language-debate-schools-policy-mumbai-print-news-vsd-99-5179405/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ते मुंबईतल्या लँड स्कॅमचे…बड्या नेत्याचे उद्धव ठाकरेंवर खळबळजनक आरोप!</t>
+          <t>Ashish Shelar : राज्य शासना तर्फे गतवर्षापासून आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव होणार</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-said-uddhav-thackeray-is-baadshah-of-land-scam-amid-bmc-election-2025-1389756.html</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ashish-shelar-announces-international-marathi-film-festival/32779</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mumbai News : मुंबईत १९ इमारतींचा पुनर्विकास, एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी घरं मिळणार</t>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment-latest-marathi-news-pp0731</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ladki Bahin Movie : 'लाडकी बहीण' मोठ्या पडद्यावर झळकणार, चित्रपटात 'या' कलाकारांची लागली वर्णी</t>
+          <t>Ashish Shelar: रघुजी भोसलेंची तलवार परत मिळवण्यात यश | Marathi News</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/entertainment/ladki-bahin-movie-muhurat-cultural-minister-ashish-shelar-gives-clap-see-photos-list-of-actors-mukhyamantri-ladki-bahin-yojana-sm2000</t>
+          <t>https://lokmat.news18.com/videos/video/ashish-shelar-success-in-regaining-raghuji-bhosle-s-sword-marathi-news-1043330.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>धारावीची एक इंचही जागा अदानी यांना देणार नाही; शेलार यांनी स्पष्टच सांगितलं, नेमकं काय म्हणाले?</t>
+          <t>Ashish Shelar : मनसेच्या आंदोलनाची तुलना पहलगाम हल्ल्याशी; आशीष शेलारांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/adani-will-not-be-given-an-inch-of-space-in-dharavi-what-exactly-did-shelar-say-1370721.html</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Amit Thackeray : मनसे-भाजप जवळीक वाढतेय? सख्ख्या मित्रांमधला दुरावा मिटला, अमित ठाकरे शेलारांच्या भेटीला; म्हणाले, राज साहेबांनी...</t>
+          <t>शेलारजी फार डिंग्या मारू नका, बेस्ट निवडणुकीतही तुम्ही तीर मारले नाहीत. तुम्हाला</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/amit-thackeray-meets-ashish-shelar-amid-mns-shiv-sena-ubt-alliance-talks-on-raj-thackeray-uddhav-thackeray/articleshow/123466514.cms</t>
+          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>वाघनख्यानंतर आणखी एक ठेवा महाराष्ट्रात, नागपूरच्या रघुजीराजे भोसलेंची लंडनमधील</t>
+          <t>कान फिल्म फेस्टिव्हलमध्ये 'या' चार मराठी सिनेमांची झाली निवड, सांस्कृतिक मंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/four-marathi-films-have-been-selected-for-the-cannes-film-festival-announced-by-cultural-minister-ashish-shelar-a-a998/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ganeshutsav : गणेशोत्सवासंदर्भात सर्वात मोठी बातमी, राज्य सरकारची मोठी घोषणा</t>
+          <t>राज ठाकरेंच्या ‘त्या’ टीकेला शेलारांचं खोचक प्रत्युत्तर; म्हणाले ज्यांना निवडून येता येत...</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ganeshotsav-declared-maharashtra-official-festival-announces-ashish-shelar-mumbai-pune-latest-marathi-nck90</t>
+          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Maharaj: छत्रपती शिवाजी महाराजांच्या 'या' गडकिल्ल्यांना नामांकन; जागतिक वारसा यादीत स्थान मिळणार</t>
+          <t>सांस्कृतिक मंत्री म्हणतात ” पोळा करा, शहरी नक्षलवाद संपवा”</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/chhatrapati-shivaji-maharaj-12-forts-place-on-unesco-world-heritage-list-said-maharashtra-government-minister-ashish-shelar-marathi-news-795328.html</t>
+          <t>https://www.loksatta.com/nagpur/wardha-to-end-urban-naxalism-traditional-festivals-like-bail-pola-must-be-celebrated-with-enthusiasm-adv-ashish-shelar-sud-02-5325172/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Ashish Shelar News: निवडणुका होऊ नयेत म्हणून कुणाचे प्रयत्न सुरू आहेत?, शेलारांचा कुणावर निशाणा?</t>
+          <t>गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रयत्न - आशिष शेलार</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
+          <t>https://www.lokmat.com/pune/efforts-to-get-unesco-cultural-status-for-ganeshotsav-ashish-shelar-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Amit Thackeray-Ashish Shelar : गणेशोत्सवासाठी ‘मनविसे’ आक्रमक; अमित ठाकरेंनी थेट आशिष शेलारांना भेटून केली</t>
+          <t>ते मुंबईतल्या लँड स्कॅमचे…बड्या नेत्याचे उद्धव ठाकरेंवर खळबळजनक आरोप!</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/amit-thackeray-ashish-shelar-manvise-aggressive-for-ganeshotsav-amit-thackeray-directly-met-ashish-shelar-and-demanded-to-postpone-the-exams/</t>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-said-uddhav-thackeray-is-baadshah-of-land-scam-amid-bmc-election-2025-1389756.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>गणेशोउत्सवात मुंबईकरांना खड्डांचा त्रास होणार नाही, यासाठी प्रशासनाने सणापूर्वी खड्डे भरावे, पालकमंत्री आशिष शेलारांचे निर्देश</t>
+          <t>"निवडणुकीत हरणार म्हणून कुटुंब "तहात" जिंकण्याचा प्रयत्न"; भाजपाचा पलटवार</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/mumbaikars-do-not-face-problem-due-to-potholes-during-ganesh-chaturthi-should-fill-the-potholes-before-festival-says-minister-ashish-shelar-05-693364</t>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-over-raj-uddhav-thackeray-vijayi-melava-a-a597/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>यंदा दहिहंडी उत्सव साजरा करण्यासाठी पालिका आगळावेगळा उपक्रम राबविणार, मंत्री आशिष शेलारांची माहिती</t>
+          <t>“सार्वजनिक गणेशोत्सव आता ‘महाराष्ट्र राज्य महोत्सव’”; आशिष शेलार यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/this-year-the-municipality-will-implement-a-unique-initiative-to-celebrate-dahihandi-festival-according-to-minister-ashish-shelar-05-688129?utm_source=website&amp;utm_medium=related&amp;utm_campaign=relatedpost</t>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-is-now-maharashtra-state-festival-bjp-minister-ashish-shelar-announcement-in-the-vidhan-sabha-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार महाराष्ट्रात लवकरच येणार , सांस्कृतिक कार्यमंत्री आशिष शेलारांची माहिती</t>
+          <t>मराठी माणसांची तुलना पहलगाम अतिरेक्यांशी उद्धव ठाकरेंचा आशिष शेलार अन् निशिकांत</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/the-state-government-has-achieved-great-success-in-obtaining-the-historical-sword-of-the-brave-maratha-sardar-raghuji-bhosale-according-to-cultural-affairs-minister-ashish-shelar-05-675383</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Mumbai News: 'मुंबई में निर्दोष हिंदुओं को पहलगाम की तरह उनकी भाषा पूछकर पीटा गया', BJP नेता आशीष शेलार का चौंकाने वाला बयान</t>
+          <t>Top 80 News : टॉप 80 बातम्यांचा वेगवान आढावा : Maharashtra News</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>आम्ही तोडणारे नव्हे, तर जोडणारे- आशिष शेलार</t>
+          <t>ठाकरे गटाकडून मुंबईकरांशी एक लाख कोटींची बेईमानी, आशिष शेलार यांचा थेट आरोप</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
+          <t>https://www.lokmat.com/mumbai/ashish-shelar-directly-accuses-shiv-sena-ubt-of-dishonesty-worth-rs-1-lakh-crore-towards-mumbaikars-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>NDTV Emerging Business: मुंबईत AI विद्यापीठ स्थापण करणार, आशिष शेलारांनी दिली माहिती</t>
+          <t>गणेशोत्सव आता, महाराष्ट्र राज्य महोत्सव विधानसभेत घोषणा, आशिष शेलार म्हणाले</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
+          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : आशीष शेलार का ठाकरे ब्रदर्स पर हमला, कहा- सिर्फ घर बैठकर करते हैं राजनीति</t>
+          <t>हिंदी भाषा सक्ती प्रकरण: महाराष्ट्रात सक्ती फक्त मराठीची, हिंदीची नाही पण... : आशिष शेलार यांनी मांडली भूमिका</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
+          <t>https://www.etvbharat.com/mr/!state/only-marathi-is-compulsory-in-maharashtra-says-minister-ashish-shelar-on-hindi-language-controversy-maharashtra-news-mhs25062401471</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>लोकमान्य तिलक का गणपति उत्सव बना राज्य उत्सव, जानिए मंत्री आशीष शेलार ने क्या कहा</t>
+          <t>नालेसफाईच्या पाहणीवेळी तुम्ही कुठे होता? आशिष शेलार यांचा आदित्य ठाकरे यांना सवाल</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
+          <t>https://www.lokmat.com/mumbai/where-were-you-during-the-inspection-of-drain-cleaning-ashish-shelar-questions-aditya-thackeray-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>Ashish Shelar : मराठी कंटेंट क्रिएटर्ससाठी नेटफ्लिक्सने...; ओटीटी प्लॅटफॉर्मवर मराठी स्थान मिळण्यासाठी आशिष शेलार यांचा प्रयत्न</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
+          <t>https://zeenews.india.com/marathi/world/netflix-for-marathi-content-creators-ashish-shelar-efforts-to-get-marathi-a-place-on-ott-platforms/928660</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “तुम्हारे पाँव के नीचे कोई जमीन नही…”, आशिष शेलारांचा शेरोशायरीतून उद्धव ठाकरेंवर हल्लाबोल</t>
+          <t>धारावी पुनर्वसन: भाजपाचे आशिष शेलार अन् काँग्रेसच्या वर्षा गायकवाड यांच्यात ‘तू तू मै मै’</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mumbai-president-ashish-shelar-criticizes-uddhav-thackeray-and-mahavikas-aghadi-politics-gkt-96-4820917/</t>
+          <t>https://www.lokmat.com/mumbai/dharavi-rehabilitation-project-dispute-between-bjps-ashish-shelar-and-congresss-varsha-gaikwad-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ashish Shelar : माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला, आशिष शेलारांचे वक्तव्य</t>
+          <t>Video: मोठी बातमी! अमित ठाकरेंनी घेतली भाजपाच्या आशिष शेलारांची भेट; दोन दिवसांपूर्वीच राज ठाकरेंनी घेतली होती फडणवीसांची भेट</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
+          <t>https://www.loksatta.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-after-meeting-he-says-kvg-85-5325003/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के स्कूलों में हिंदी जरूरी? विवाद पर देवेंद्र फडणवीस का बड़ा फैसला, जानें क्या बोले आशीष शेलार</t>
+          <t>'पहलगामसारखं मुंबईत निष्पाप हिंदूंना भाषा विचारुन चोपलं', आशिष शेलार यांचं धक्कादायक वक्तव्य</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray &amp; Ashish Shelar: उद्धव ठाकरे हा मुंबईतील लँड स्कॅमचा बादशाह आशिष शेलारांनी दुसऱ्या</t>
+          <t>जास्त गर्दीच्या मेट्रो स्थानकांचा आपत्कालीन प्लॅन तयार करा; आशिष शेलारांचे MMRDAला निर्देश</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
+          <t>https://www.lokmat.com/mumbai/prepare-an-emergency-plan-for-overcrowded-metro-stations-ashish-shelar-directs-mmrda-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>सरकारच्या विभागांमधील रिक्त पदे नेमकी किती? मंत्री आशिष शेलार यांनी विधान परिषदेत दिली माहिती</t>
+          <t>Mumbai News : मुंबईत १९ इमारतींचा पुनर्विकास, एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी घरं मिळणार</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/information-technology-minister-ashish-shelar-announced-that-these-vacant-posts-will-be-filled-through-mahabharti-phm-00-5219670/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Nagpur Film City: नागपुरातील फिल्मसिटीची जागा ठरली! मुंबई, कोल्हापूरनंतर उपराजधानीत 128</t>
+          <t>Ladki Bahin Movie : 'लाडकी बहीण' मोठ्या पडद्यावर झळकणार, चित्रपटात 'या' कलाकारांची लागली वर्णी</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
+          <t>https://saamtv.esakal.com/entertainment/ladki-bahin-movie-muhurat-cultural-minister-ashish-shelar-gives-clap-see-photos-list-of-actors-mukhyamantri-ladki-bahin-yojana-sm2000</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’मुळे भावना दुखावतायत तर कान्सला का पाठवला? आशिष शेलार स्पष्टीकरण देत म्हणाले….</t>
+          <t>धारावीची एक इंचही जागा अदानी यांना देणार नाही; शेलार यांनी स्पष्टच सांगितलं, नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-explain-why-govt-sent-khalid-ka-shivaji-movie-to-cannes-film-festival-2025-asc-95-5290043/</t>
+          <t>https://www.tv9marathi.com/maharashtra/adani-will-not-be-given-an-inch-of-space-in-dharavi-what-exactly-did-shelar-say-1370721.html</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>मराठी चित्रपट योग्य दरात घेण्याची नेटफ्लिक्सला सूचना : ॲड. आशिष शेलार</t>
+          <t>वाघनख्यानंतर आणखी एक ठेवा महाराष्ट्रात, नागपूरच्या रघुजीराजे भोसलेंची लंडनमधील</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-state-film-awards-ashish-shelar-discusses-marathi-cinema-pricing-with-netflix-mumbai-print-news-rds-00-5283289/</t>
+          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
+          <t>Ganeshutsav : गणेशोत्सवासंदर्भात सर्वात मोठी बातमी, राज्य सरकारची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/ganeshotsav-declared-maharashtra-official-festival-announces-ashish-shelar-mumbai-pune-latest-marathi-nck90</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>धारावीतील एक इंचही जागा ‘अदानी’ला देणार नाही, मंत्री आशीष शेलार यांची ग्वाही</t>
+          <t>Chhatrapati Shivaji Maharaj: छत्रपती शिवाजी महाराजांच्या 'या' गडकिल्ल्यांना नामांकन; जागतिक वारसा यादीत स्थान मिळणार</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-assures-that-not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-mumbai-print-news-ssb-93-4964971/</t>
+          <t>https://www.navarashtra.com/maharashtra/chhatrapati-shivaji-maharaj-12-forts-place-on-unesco-world-heritage-list-said-maharashtra-government-minister-ashish-shelar-marathi-news-795328.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>“शहरी नक्षलवाद्यांचा डाव हाणून पाडू, गणेशोत्सव धुमधडाक्यात साजरा करू”: आशिष शेलार</t>
+          <t>Ashish Shelar News: निवडणुका होऊ नयेत म्हणून कुणाचे प्रयत्न सुरू आहेत?, शेलारांचा कुणावर निशाणा?</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-ashish-shelar-said-celebrate-ganeshotsav-on-big-scale-a-a719/</t>
+          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज ठाकरेंसोबतच्या मैत्रीचा प्रश्न, आशिष शेलारांनी दोन शब्दात संपवला विषय</t>
+          <t>गणेशोउत्सवात मुंबईकरांना खड्डांचा त्रास होणार नाही, यासाठी प्रशासनाने सणापूर्वी खड्डे भरावे, पालकमंत्री आशिष शेलारांचे निर्देश</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-speak-on-issue-of-mumbai-potholes-friendship-with-raj-thackeray-sanjay-raut-letter-india-pakistan-match-1476373.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/mumbaikars-do-not-face-problem-due-to-potholes-during-ganesh-chaturthi-should-fill-the-potholes-before-festival-says-minister-ashish-shelar-05-693364</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>'खालिद का शिवाजी' चित्रपटावरून आशिष शेलार आक्रमक; सेन्सॉर बोर्डाला धारेवर धरत घेतला मोठा निर्णय</t>
+          <t>यंदा दहिहंडी उत्सव साजरा करण्यासाठी पालिका आगळावेगळा उपक्रम राबविणार, मंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/this-year-the-municipality-will-implement-a-unique-initiative-to-celebrate-dahihandi-festival-according-to-minister-ashish-shelar-05-688129?utm_source=website&amp;utm_medium=related&amp;utm_campaign=relatedpost</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Raj Thackeray &amp; Ashish Shelar: आम्ही अन्नपाणी सोडलंय, आम्हाला खूप दु:ख झालंय आशिष शेलारांनी राज</t>
+          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार महाराष्ट्रात लवकरच येणार , सांस्कृतिक कार्यमंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/the-state-government-has-achieved-great-success-in-obtaining-the-historical-sword-of-the-brave-maratha-sardar-raghuji-bhosale-according-to-cultural-affairs-minister-ashish-shelar-05-675383</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>BJP : भाजपच्या दोन गटांमध्ये मुंबईत तुफान हाणामारी, आशिष शेलारांसमोरच कार्यकर्ते भिडले, Video</t>
+          <t>Mumbai News: 'मुंबई में निर्दोष हिंदुओं को पहलगाम की तरह उनकी भाषा पूछकर पीटा गया', BJP नेता आशीष शेलार का चौंकाने वाला बयान</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/bjp-supporters-fight-with-each-other-in-front-of-ashish-shelar-in-mumbai-watch-video-1414857.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>मुंबई महापालिकेचा महापौर महायुतीचा होणार संजय राऊत यांच्या बुद्धिमतेची चाचणी</t>
+          <t>आम्ही तोडणारे नव्हे, तर जोडणारे- आशिष शेलार</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>रवी परांजपे यांचा चित्रठेवा शासनाकडून जतन; सांस्कृतिकमंत्री आशिष शेलार यांच्या उपस्थितीत सामंजस्य करारावर स्वाक्षरी</t>
+          <t>NDTV Emerging Business: मुंबईत AI विद्यापीठ स्थापण करणार, आशिष शेलारांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/signing-of-mou-by-ashish-shelar-on-preservation-of-ravi-paranjpe-paintings-pune-print-news-amy-95-5319485/</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे यांच्या काळापेक्षा रस्ते कामाचा वेग अधिक; पालकमंत्री ऍड. आशिष शेलार यांचे मत</t>
+          <t>लोकमान्य तिलक का गणपति उत्सव बना राज्य उत्सव, जानिए मंत्री आशीष शेलार ने क्या कहा</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-slams-uddhav-thackeray-over-concrete-road-construction-mumbai-print-news-zws-70-5098492/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>आताची सर्वात मोठी बातमी! मनसे नेते अमित ठाकरे आशिष शेलार यांच्या भेटीला</t>
+          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
+          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>“पहलगाममध्ये धर्म विचारुन गोळ्या घातल्या अन् इथे भाषा विचारुन…”; आशिष शेलारांचा...</t>
+          <t>Ashish Shelar : माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला, आशिष शेलारांचे वक्तव्य</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-controversy-bjp-leader-aashish-shelar-target-thackeray-brothers-rally-1439702.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार दोन दिवसांआधी राज</t>
+          <t>महाराष्ट्र के स्कूलों में हिंदी जरूरी? विवाद पर देवेंद्र फडणवीस का बड़ा फैसला, जानें क्या बोले आशीष शेलार</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज ठाकरे-उद्धव ठाकरे युतीच्या चर्चे दरम्यान आशिष शेलारांचे मोठं वक्तव्य; म्हणाले, "आता वैयक्तिक संबंधही संपले"</t>
+          <t>Ashish Shelar : “तुम्हारे पाँव के नीचे कोई जमीन नही…”, आशिष शेलारांचा शेरोशायरीतून उद्धव ठाकरेंवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-says-his-personal-relationship-with-raj-thackeray-has-ended-amid-talks-of-mns-and-uddhav-thackerays-shiv-sena-alliance-as11</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mumbai-president-ashish-shelar-criticizes-uddhav-thackeray-and-mahavikas-aghadi-politics-gkt-96-4820917/</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>गणेशोत्सव आता, महाराष्ट्र राज्य महोत्सव विधानसभेत घोषणा, आशिष शेलार म्हणाले</t>
+          <t>Uddhav Thackeray &amp; Ashish Shelar: उद्धव ठाकरे हा मुंबईतील लँड स्कॅमचा बादशाह आशिष शेलारांनी दुसऱ्या</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>प्रस्तावित वांद्रे-कुर्ला मार्गिकेचे संरेखन रद्द का? आशिष शेलार यांचे ‘एमएमआरडीए’ला अवहाल देण्याचे आदेश</t>
+          <t>सरकारच्या विभागांमधील रिक्त पदे नेमकी किती? मंत्री आशिष शेलार यांनी विधान परिषदेत दिली माहिती</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-orders-mmrda-to-take-cognizance-of-the-proposed-bandra-kurla-corridor-mumbai-print-news-amy-95-5175404/</t>
+          <t>https://www.loksatta.com/mumbai/information-technology-minister-ashish-shelar-announced-that-these-vacant-posts-will-be-filled-through-mahabharti-phm-00-5219670/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>‘पुरातत्व’कडील गडकिल्ले राज्याकडे देण्याची विनंती; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे पत्र</t>
+          <t>Nagpur Film City: नागपुरातील फिल्मसिटीची जागा ठरली! मुंबई, कोल्हापूरनंतर उपराजधानीत 128</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-letter-to-union-minister-demanded-to-handed-over-forts-in-maharashtra-to-state-government-zws-70-4975719/</t>
+          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “राज ठाकरेंशी वैयक्तिक संबंध होते ते आता संपले…”, आशिष शेलार यांचं वक्तव्य</t>
+          <t>‘खालिद का शिवाजी’मुळे भावना दुखावतायत तर कान्सला का पाठवला? आशिष शेलार स्पष्टीकरण देत म्हणाले….</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-said-friendship-with-raj-thackeray-is-now-over-what-he-said-scj-81-5033142/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-explain-why-govt-sent-khalid-ka-shivaji-movie-to-cannes-film-festival-2025-asc-95-5290043/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>मुंबईत घरे देण्यासाठी आता थेट मुख्यमंत्र्यांनाच साकडे; संयुक्त बैठकीचे आशिष शेलार यांचे गिरणी कामगार एकजुटीला आश्वासन</t>
+          <t>मराठी चित्रपट योग्य दरात घेण्याची नेटफ्लिक्सला सूचना : ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-now-directly-appeals-to-chief-minister-devendra-fadnavis-to-provide-houses-to-mill-workers-in-mumbai-mumbai-print-news-phm-00-5061388/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-state-film-awards-ashish-shelar-discusses-marathi-cinema-pricing-with-netflix-mumbai-print-news-rds-00-5283289/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>खोक्याभाईचे काय घेऊन बसलात, विधानसभेत सगळे तेच भरलेत: राज ठाकरेंचा सरकारला टोला, भाजप नेते आशिष शेलारांनीही...</t>
+          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “निवडणुकीत हरणार म्हणून कुटुंब तहात…”, ठाकरे बंधूंच्या मेळाव्यानंतर भाजपाची पहिली प्रतिक्रिया; शेलार म्हणाले, “भाऊबंदकी…”</t>
+          <t>धारावीतील एक इंचही जागा ‘अदानी’ला देणार नाही, मंत्री आशीष शेलार यांची ग्वाही</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-on-mns-raj-thackeray-and-shivsena-ubt-uddhav-thackeray-victory-rally-in-mumbai-politics-gkt-96-5206150/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-assures-that-not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-mumbai-print-news-ssb-93-4964971/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>पारंपारिक गोंदण कलेचा समावेश कला अभ्यासक्रमात; सांस्कृतिक कार्य मंत्री ॲड आशिष शेलार यांच्या सूचना</t>
+          <t>“शहरी नक्षलवाद्यांचा डाव हाणून पाडू, गणेशोत्सव धुमधडाक्यात साजरा करू”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-adv-ashish-shelar-instructions-regarding-tattoo-art-courses-mumbai-print-news-amy-95-5196545/</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-ashish-shelar-said-celebrate-ganeshotsav-on-big-scale-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>“आशिष शेलार माझ्याव्यतिरिक्त कोणालाच छळत नाहीत”, देवेंद्र फडणवीसांचं वक्तव्य</t>
+          <t>'खालिद का शिवाजी' चित्रपटावरून आशिष शेलार आक्रमक; सेन्सॉर बोर्डाला धारेवर धरत घेतला मोठा निर्णय</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-says-ashish-shelar-not-bothering-anyone-except-me-asc-95-4973334/</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: " ...तर उध्दव ठाकरेंना 'बेईमान ऑफ द महाराष्ट्र' अवॉर्ड द्यावा लागेल!"; भाजप मंत्र्यांचं वादग्रस्त विधान</t>
+          <t>Raj Thackeray &amp; Ashish Shelar: आम्ही अन्नपाणी सोडलंय, आम्हाला खूप दु:ख झालंय आशिष शेलारांनी राज</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-controversial-remark-uddhav-thackeray-dishonest-of-maharashtra-award-dk88</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Ashish Shelar: “मित्र म्हणून तुम्हाला सल्ला देतो की…”, राज ठाकरेंनी निकालावर संशय घेताच भाजपाचा पलटवार</t>
+          <t>BJP : भाजपच्या दोन गटांमध्ये मुंबईत तुफान हाणामारी, आशिष शेलारांसमोरच कार्यकर्ते भिडले, Video</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-leader-ashish-shelar-slams-raj-thackeray-over-his-speech-alleges-his-fake-narrative-kvg-85-4859728/</t>
+          <t>https://news18marathi.com/mumbai/bjp-supporters-fight-with-each-other-in-front-of-ashish-shelar-in-mumbai-watch-video-1414857.html</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>मुंबईतच घरे हवीत… गिरणी कामगार पुन्हा आक्रमक…आशिष शेलार यांच्या वांद्रे कार्यालयावर २७ एप्रिल रोजी मोर्चा</t>
+          <t>Ashish Shelar : राज ठाकरेंसोबतच्या मैत्रीचा प्रश्न, आशिष शेलारांनी दोन शब्दात संपवला विषय</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-speak-on-issue-of-mumbai-potholes-friendship-with-raj-thackeray-sanjay-raut-letter-india-pakistan-match-1476373.html</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>गडकिल्ल्यांच्या संवर्धनासाठी शासन सक्षम: मंत्री आशिष शेलार यांचे राज ठाकरेंना उत्तर, म्हणाले - जागतिक वारशा...</t>
+          <t>रवी परांजपे यांचा चित्रठेवा शासनाकडून जतन; सांस्कृतिकमंत्री आशिष शेलार यांच्या उपस्थितीत सामंजस्य करारावर स्वाक्षरी</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
+          <t>https://www.loksatta.com/pune/signing-of-mou-by-ashish-shelar-on-preservation-of-ravi-paranjpe-paintings-pune-print-news-amy-95-5319485/</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>राज ठाकरे - आशिष शेलार यांच्या मैत्रीत दुरावा; शेलार म्हणाले, "माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला"</t>
+          <t>मुंबई महापालिकेचा महापौर महायुतीचा होणार संजय राऊत यांच्या बुद्धिमतेची चाचणी</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ashish-shelar-says-friendship-with-raj-thackeray-over-amid-mns-shiv-sena-ubt-alliance-maharashtra-news-mhs25042004504</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>प्रयोगात्मक कलांसाठी पु.ल. देशपांडे अकादमीमध्ये शाहीर साबळेच्या नावाने संशोधन केंद्र; सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची घोषणा</t>
+          <t>उद्धव ठाकरे यांच्या काळापेक्षा रस्ते कामाचा वेग अधिक; पालकमंत्री ऍड. आशिष शेलार यांचे मत</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announces-research-center-named-after-shahir-sable-at-p-l-deshpande-academy-mumbai-print-news-amy-95-5170476/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-slams-uddhav-thackeray-over-concrete-road-construction-mumbai-print-news-zws-70-5098492/</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>युनेस्कोच्या यादीत 12 किल्ले मोदी सरकारचे कान टोचणाऱ्या राज ठाकरेंना मंत्री</t>
+          <t>“पहलगाममध्ये धर्म विचारुन गोळ्या घातल्या अन् इथे भाषा विचारुन…”; आशिष शेलारांचा...</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-controversy-bjp-leader-aashish-shelar-target-thackeray-brothers-rally-1439702.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Video: मोठी बातमी! अमित ठाकरेंनी घेतली भाजपाच्या आशिष शेलारांची भेट; दोन दिवसांपूर्वीच राज ठाकरेंनी घेतली होती फडणवीसांची भेट</t>
+          <t>आताची सर्वात मोठी बातमी! मनसे नेते अमित ठाकरे आशिष शेलार यांच्या भेटीला</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-after-meeting-he-says-kvg-85-5325003/</t>
+          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>जिथं तुरुंगवास तिथंच सावरकरांचं भव्य स्मारक मंत्री आशिष शेलार यांची घोषणा,</t>
+          <t>Ashish Shelar : राज ठाकरे-उद्धव ठाकरे युतीच्या चर्चे दरम्यान आशिष शेलारांचे मोठं वक्तव्य; म्हणाले, "आता वैयक्तिक संबंधही संपले"</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-says-his-personal-relationship-with-raj-thackeray-has-ended-amid-talks-of-mns-and-uddhav-thackerays-shiv-sena-alliance-as11</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Ashish Shelar : रायगडच्या पालकमंत्री पदाचा तिढा अमित शाह नाहीतर यांच्या अखत्यारितला? आशिष शेलारांनी थेट नावच सांगितलं</t>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार दोन दिवसांआधी राज</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/raigad-guardian-minister-dispute-to-be-decided-by-devendra-fadnavis-says-ashish-shelar-as11</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>वांद्रे येथे राज्याचे नवीन महापुराभिलेख भवन, सांस्कृतिक कार्यमंत्री आशीष शेलार यांची घोषणा</t>
+          <t>‘पुरातत्व’कडील गडकिल्ले राज्याकडे देण्याची विनंती; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे पत्र</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-letter-to-union-minister-demanded-to-handed-over-forts-in-maharashtra-to-state-government-zws-70-4975719/</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>के. बी. भाभा रुग्णालयाच्या विस्तारित इमारतीचे लोकार्पण!</t>
+          <t>प्रस्तावित वांद्रे-कुर्ला मार्गिकेचे संरेखन रद्द का? आशिष शेलार यांचे ‘एमएमआरडीए’ला अवहाल देण्याचे आदेश</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-inaugurated-newly-expanded-khurshedji-behramji-bhabha-hospital-in-bandra-on-wednesday-mumbai-print-news-sud-02-4872371/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-orders-mmrda-to-take-cognizance-of-the-proposed-bandra-kurla-corridor-mumbai-print-news-amy-95-5175404/</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>मुंबई तुंबण्यावरून आशिष शेलार यांची ठाकरे गटावर टीका, वीस वर्षातील कामांची श्वेतपत्रिका काढण्याची पालिका आयुक्तांकडे मागणी</t>
+          <t>Ashish Shelar : “राज ठाकरेंशी वैयक्तिक संबंध होते ते आता संपले…”, आशिष शेलार यांचं वक्तव्य</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-alleged-uddhav-thackeray-group-has-been-dishonest-with-mumbaikars-on-wednesday-mumbai-print-news-sud-02-5119394/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-said-friendship-with-raj-thackeray-is-now-over-what-he-said-scj-81-5033142/</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार ताब्यात; १८ ऑगस्टला मुंबईत दाखल : आशिष शेलार</t>
+          <t>खोक्याभाईचे काय घेऊन बसलात, विधानसभेत सगळे तेच भरलेत: राज ठाकरेंचा सरकारला टोला, भाजप नेते आशिष शेलारांनीही...</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/in-mumbai-ashish-shelar-to-bring-maharashtra-auction-win-of-maratha-sword-on-august-18-mumbai-print-news-rds-00-5297158/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>मुंबई अध्यक्षपदावरून भाजपमध्ये तिढा; आशिष शेलारांकडे पद कायम राहणार?</t>
+          <t>Ashish Shelar : “निवडणुकीत हरणार म्हणून कुटुंब तहात…”, ठाकरे बंधूंच्या मेळाव्यानंतर भाजपाची पहिली प्रतिक्रिया; शेलार म्हणाले, “भाऊबंदकी…”</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-undecided-on-mumbai-president-ahead-of-elections-print-politics-news-ocd-94-5259220/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-on-mns-raj-thackeray-and-shivsena-ubt-uddhav-thackeray-victory-rally-in-mumbai-politics-gkt-96-5206150/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>“राज्य महोत्सव गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभाग वाढवावा”: आशिष शेलार</t>
+          <t>पारंपारिक गोंदण कलेचा समावेश कला अभ्यासक्रमात; सांस्कृतिक कार्य मंत्री ॲड आशिष शेलार यांच्या सूचना</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/every-government-department-should-increase-participation-in-the-state-festival-of-ganeshotsav-said-bjp-minister-ashish-shelar-a-a719/</t>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-adv-ashish-shelar-instructions-regarding-tattoo-art-courses-mumbai-print-news-amy-95-5196545/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>शेलार मामाला पोटदुखी सुरू झाली आहे, मनसे प्रवक्ता गजानन काळेंची पोस्ट चर्चेत</t>
+          <t>“आशिष शेलार माझ्याव्यतिरिक्त कोणालाच छळत नाहीत”, देवेंद्र फडणवीसांचं वक्तव्य</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/gajanan-kale-counterattacks-ashish-shelar-on-uddhav-thackeray-raj-thackeray-alliance-vsd-99-5206583/</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-says-ashish-shelar-not-bothering-anyone-except-me-asc-95-4973334/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मराठा सरदार रघुजीराजे भोसलेंची ऐतिहासिक तलवार १५ ऑगस्टच्या आधी महाराष्ट्रात आणणार, मंत्री आशिष शेलार यांची माहिती</t>
+          <t>Uddhav Thackeray: " ...तर उध्दव ठाकरेंना 'बेईमान ऑफ द महाराष्ट्र' अवॉर्ड द्यावा लागेल!"; भाजप मंत्र्यांचं वादग्रस्त विधान</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-sai-historic-sword-of-the-brave-maratha-sardar-raghuji-raje-bhosale-to-return-to-maharashtra-before-august-15-scj-81-5212150/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-controversial-remark-uddhav-thackeray-dishonest-of-maharashtra-award-dk88</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Asha Bhosle : राजकारणात मला फक्त आशिष शेलार माहिती; ठाकरे बंधूंवरील प्रश्नावर आशा भोसलेंचं उत्तर</t>
+          <t>Ashish Shelar: “मित्र म्हणून तुम्हाला सल्ला देतो की…”, राज ठाकरेंनी निकालावर संशय घेताच भाजपाचा पलटवार</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/famous-singer-asha-bhosle-comment-on-raj-uddhav-thackeray-morcha-in-mumbai-on-hindi-language-impose-912626.html</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-leader-ashish-shelar-slams-raj-thackeray-over-his-speech-alleges-his-fake-narrative-kvg-85-4859728/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>महाराष्ट्र क्वांटम विज्ञान व तंत्रज्ञानाचे आंतरराष्ट्रीय वर्ष साजरे करणार – मंत्री ॲड. आशिष शेलार</t>
+          <t>मुंबईतच घरे हवीत… गिरणी कामगार पुन्हा आक्रमक…आशिष शेलार यांच्या वांद्रे कार्यालयावर २७ एप्रिल रोजी मोर्चा</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/154669/</t>
+          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BJP Mumbai President :बीएमसी निवडणुकीआधी भाजपने भाकरी फिरवली, शेलारांना नारळ, मुंबईची धुरा कोणाकडे?</t>
+          <t>गडकिल्ल्यांच्या संवर्धनासाठी शासन सक्षम: मंत्री आशिष शेलार यांचे राज ठाकरेंना उत्तर, म्हणाले - जागतिक वारशा...</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>लोककलांना पुनरुज्जीवन करणे गरजेचे : ॲड. आशिष शेलार</t>
+          <t>राज ठाकरे - आशिष शेलार यांच्या मैत्रीत दुरावा; शेलार म्हणाले, "माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला"</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/in-thane-bjp-mla-ashish-shelar-says-need-to-revive-folk-arts-css-98-4953399/</t>
+          <t>https://www.etvbharat.com/mr/!state/ashish-shelar-says-friendship-with-raj-thackeray-over-amid-mns-shiv-sena-ubt-alliance-maharashtra-news-mhs25042004504</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>संगीत नाटकांसाठी रवींद्र नाट्य मंदिर २५ टक्के सवलतीत उपलब्ध होणार; ॲड.आशिष शेलार यांची घोषणा</t>
+          <t>प्रयोगात्मक कलांसाठी पु.ल. देशपांडे अकादमीमध्ये शाहीर साबळेच्या नावाने संशोधन केंद्र; सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announced-that-ravindra-natya-mandir-will-be-available-at-a-25-percent-discount-mumbai-print-news-phm-00-5232212/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announces-research-center-named-after-shahir-sable-at-p-l-deshpande-academy-mumbai-print-news-amy-95-5170476/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>“परिस्थितीच्या माऱ्याने दोघे एकत्र, आता नवा चित्रपट…”, आशिष शेलारांचा ठाकरे बंधूंना चिमटा; सिनेमाचं नावंही सांगितलं!</t>
+          <t>जिथं तुरुंगवास तिथंच सावरकरांचं भव्य स्मारक मंत्री आशिष शेलार यांची घोषणा,</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-slams-raj-and-uddhav-thackeray-mentions-zenda-and-yek-number-movie-asc-95-5217275/</t>
+          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>"मी फक्त आशिष शेलारांना ओळखते, बाकी कोणा राजकारण्याला ओळखत नाही", ठाकरे बंधूंच्या युतीवर आशा भोसलेंचं विधान</t>
+          <t>युनेस्कोच्या यादीत 12 किल्ले मोदी सरकारचे कान टोचणाऱ्या राज ठाकरेंना मंत्री</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
+          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>कातळशिल्पांचा ‘जागतिक वारसा स्थळा’च्या यादीत समावेशासाठी रोडमॅप तयार करा, मंत्री आशिष शेलार यांचे निर्देश</t>
+          <t>Ashish Shelar : रायगडच्या पालकमंत्री पदाचा तिढा अमित शाह नाहीतर यांच्या अखत्यारितला? आशिष शेलारांनी थेट नावच सांगितलं</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/prepare-a-roadmap-for-the-inclusion-of-rock-sculptures-in-the-world-heritage-site-list-directed-by-minister-ashish-shelar-scj-81-5114434/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/raigad-guardian-minister-dispute-to-be-decided-by-devendra-fadnavis-says-ashish-shelar-as11</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>महाराष्ट्राच्या राजकारणात उद्धव ठाकरेंची सर्वात मोठी बेईमानी; आशिष शेलार यांची जोरदार टीका</t>
+          <t>वांद्रे येथे राज्याचे नवीन महापुराभिलेख भवन, सांस्कृतिक कार्यमंत्री आशीष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-strongly-criticizes-uddhav-thackeray-over-tree-cutting-in-mumbai-zws-70-5151721/</t>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ganeshotsav State Festival : गणेशोत्सव आता 'राज्य उत्सव'... शेलारांची मोठी घोषणा, उत्सव निर्बंध मुक्त अन् 500 कोटींचा निधी</t>
+          <t>के. बी. भाभा रुग्णालयाच्या विस्तारित इमारतीचे लोकार्पण!</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-inaugurated-newly-expanded-khurshedji-behramji-bhabha-hospital-in-bandra-on-wednesday-mumbai-print-news-sud-02-4872371/</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>पैठणीचे व्हिक्टोरिया अल्बर्ट संग्रहालयामध्ये प्रदर्शन, सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची विनंती मान्य</t>
+          <t>मुंबई तुंबण्यावरून आशिष शेलार यांची ठाकरे गटावर टीका, वीस वर्षातील कामांची श्वेतपत्रिका काढण्याची पालिका आयुक्तांकडे मागणी</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-alleged-uddhav-thackeray-group-has-been-dishonest-with-mumbaikars-on-wednesday-mumbai-print-news-sud-02-5119394/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Ashish Shelar: ठाकरे बंधूंचा एकत्र मोर्चा; आशिष शेलार थेटच म्हणाले…</t>
+          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार ताब्यात; १८ ऑगस्टला मुंबईत दाखल : आशिष शेलार</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5187751/thackeray-brothers-raj-thackeray-and-uddhav-thackeray-protest-against-state-government-over-hindi-launguage-ashish-shelar-gave-a-reaction/</t>
+          <t>https://www.loksatta.com/mumbai/in-mumbai-ashish-shelar-to-bring-maharashtra-auction-win-of-maratha-sword-on-august-18-mumbai-print-news-rds-00-5297158/</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+          <t>मुंबई अध्यक्षपदावरून भाजपमध्ये तिढा; आशिष शेलारांकडे पद कायम राहणार?</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
+          <t>https://www.loksatta.com/politics/bjp-undecided-on-mumbai-president-ahead-of-elections-print-politics-news-ocd-94-5259220/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>"महाराष्ट्रद्वेष हाच भाजपाचा खरा डीएनए", शेलार व निशिकांत दुबेंच्या वक्तव्यावरून आदित्य ठाकरेंचा संताप</t>
+          <t>शेलार मामाला पोटदुखी सुरू झाली आहे, मनसे प्रवक्ता गजानन काळेंची पोस्ट चर्चेत</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/aditya-thackeray-says-hate-for-maharashtra-is-true-dna-of-bjp-over-nishikant-dubey-ashish-shelar-statement-asc-95-5211821/</t>
+          <t>https://www.loksatta.com/thane/gajanan-kale-counterattacks-ashish-shelar-on-uddhav-thackeray-raj-thackeray-alliance-vsd-99-5206583/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar : अमित ठाकरे घेणार शेलारांची भेट, कारण गुलदस्त्यात</t>
+          <t>Ashish Shelar : मराठा सरदार रघुजीराजे भोसलेंची ऐतिहासिक तलवार १५ ऑगस्टच्या आधी महाराष्ट्रात आणणार, मंत्री आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/amit-thackeray-meet-ashish-shelar-bjp-minister-mns-party-leader/914757/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-sai-historic-sword-of-the-brave-maratha-sardar-raghuji-raje-bhosale-to-return-to-maharashtra-before-august-15-scj-81-5212150/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ची स्तुती करणारे मंत्री शेलार आता कारवाई का करतायत? विरोधकांचा सरकारमधील लोकांवर संशय</t>
+          <t>“राज्य महोत्सव गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभाग वाढवावा”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/khalid-ka-shivaji-rohit-pawar-oppess-ashish-shelar-action-against-marathi-movie-asc-95-5289901/</t>
+          <t>https://www.lokmat.com/mumbai/every-government-department-should-increase-participation-in-the-state-festival-of-ganeshotsav-said-bjp-minister-ashish-shelar-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>आशिष शेलारांचा पर्यावरणवाद्यांवर बनावट हिंदू सणविरोधी असल्याचा ठपका, पर्यावरणवाद्यांकडूनही खरपूस समाचार</t>
+          <t>Asha Bhosle : राजकारणात मला फक्त आशिष शेलार माहिती; ठाकरे बंधूंवरील प्रश्नावर आशा भोसलेंचं उत्तर</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/cultural-minister-ashish-shelar-calls-environmentalists-anti-hindu-phm-00-5246668/</t>
+          <t>https://www.navarashtra.com/maharashtra/famous-singer-asha-bhosle-comment-on-raj-uddhav-thackeray-morcha-in-mumbai-on-hindi-language-impose-912626.html</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>राजकारणातले सच्चे मित्र दुरावले? आशिष शेलार आणि राज ठाकरेंमध्ये दुरावा?</t>
+          <t>लोककलांना पुनरुज्जीवन करणे गरजेचे : ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/ashish-shelar-still-upset-with-his-friens-mns-president-raj-thackeray/934652</t>
+          <t>https://www.loksatta.com/thane/in-thane-bjp-mla-ashish-shelar-says-need-to-revive-folk-arts-css-98-4953399/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>चित्रकार रवी परांजपे यांच्या कलाकृती मंत्री ॲड. आशिष शेलार यांच्या उपस्थितीत शासनाकडे सुपूर्द</t>
+          <t>राज ठाकरे आणि आशिष शेलारांच्या मैत्रीत मिठाचा खडा; म्हणाले, "मित्र होते, विषय आता संपला"</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176545/</t>
+          <t>https://www.lokmat.com/mumbai/speculations-of-reconciliation-between-mns-and-shiv-sena-ashish-shelar-said-friendship-with-raj-is-over-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>टीका करताना शेलारांचा तोल सुटला! मनसे कार्यकर्त्यांची पहलगामच्या दहशतवाद्यांशी तुलना; म्हणाले, त्यांनी...</t>
+          <t>“परिस्थितीच्या माऱ्याने दोघे एकत्र, आता नवा चित्रपट…”, आशिष शेलारांचा ठाकरे बंधूंना चिमटा; सिनेमाचं नावंही सांगितलं!</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/bjp-ashish-shelar-compare-raj-thackeray-mns-workers-with-pahalgam-terrorist-after-shivsena-victory-rally-vijayi-melava-in-mumbai-with-uddhav-thackeray/921560</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-slams-raj-and-uddhav-thackeray-mentions-zenda-and-yek-number-movie-asc-95-5217275/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुकीच्या तोंडावर भाजपमधील धुसफुस चव्हाट्यावर, आशीष शेलार यांच्यासमोरच हाणामारी, खडाजंगी</t>
+          <t>"राजकारणात फक्त आशिष शेलारांना ओळखते..."; ठाकरे बंधूंच्या मराठी मोर्चावर आशा भोसले काय म्हणाल्या?</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-workers-clashed-with-each-other-in-front-of-minister-ashish-shelar-in-kandivali-zws-70-5156138/</t>
+          <t>https://www.lokmat.com/filmy/in-politics-i-only-know-ashish-shelar-what-did-singer-asha-bhosle-say-about-the-raj-and-uddhav-thackeray-brothers-marathi-morcha-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ashish Shelar And Mungantiwar : मुनगंटीवार म्हणाले, मी देखील चुकून काही काळ, आशिष शेलारांनीच दिले उत्तर</t>
+          <t>"मी फक्त आशिष शेलारांना ओळखते, बाकी कोणा राजकारण्याला ओळखत नाही", ठाकरे बंधूंच्या युतीवर आशा भोसलेंचं विधान</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
+          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>गणेशोत्सवात यंदा सात दिवस रात्री उशिरापर्यंत ध्वनिक्षेपक? मंत्री शेलारांनी स्पष्टच सांगितले…!</t>
+          <t>कातळशिल्पांचा ‘जागतिक वारसा स्थळा’च्या यादीत समावेशासाठी रोडमॅप तयार करा, मंत्री आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-ashish-shelar-says-district-collectors-can-allow-loudspeaker-use-till-midnight-during-ganeshotsav-pune-print-news-rds-00-5320532/</t>
+          <t>https://www.loksatta.com/maharashtra/prepare-a-roadmap-for-the-inclusion-of-rock-sculptures-in-the-world-heritage-site-list-directed-by-minister-ashish-shelar-scj-81-5114434/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार</t>
+          <t>महाराष्ट्राच्या राजकारणात उद्धव ठाकरेंची सर्वात मोठी बेईमानी; आशिष शेलार यांची जोरदार टीका</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/publication-of-the-biography-book-manik-moti-based-on-the-veteran-singer-manik-verma-maharashtra-news-mhs25051306533</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-strongly-criticizes-uddhav-thackeray-over-tree-cutting-in-mumbai-zws-70-5151721/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Ganesh visarjan guidelines : उंच गणेशमूर्तींच्या विसर्जनाबाबत 30 तारखेपर्यंत भूमिका मांडणार</t>
+          <t>Ganeshotsav State Festival : गणेशोत्सव आता 'राज्य उत्सव'... शेलारांची मोठी घोषणा, उत्सव निर्बंध मुक्त अन् 500 कोटींचा निधी</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/tall-ganesh-idol-immersion-guidelines-2025-ab96</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>पवई व तुळशी तलावातील गाळ काढण्यासाठी तीन महिन्यांत कृती आराखडा तयार करा; मुंबई उपनगर पालकमंत्री आशिष शेलार यांचे आदेश</t>
+          <t>पैठणीचे व्हिक्टोरिया अल्बर्ट संग्रहालयामध्ये प्रदर्शन, सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची विनंती मान्य</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-suburban-guardian-minister-ashish-shelar-order-regarding-removal-of-silt-from-powai-and-tulsi-lakes-mumabi-print-news-amy-95-5183942/</t>
+          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>राज ठाकरेंशी संबधित ‘येक नंबर’ हिट की फ्लॉप? शेलारांची थेट विधीमंडळात माहिती, बजेट व बॉक्स ऑफिस कलेक्शनची तुलना करत म्हणाले…</t>
+          <t>Ashish Shelar: ठाकरे बंधूंचा एकत्र मोर्चा; आशिष शेलार थेटच म्हणाले…</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/raj-thackeray-yek-number-movie-box-office-collection-ashish-shelar-teases-at-assembly-monsoon-session-asc-95-5217195/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5187751/thackeray-brothers-raj-thackeray-and-uddhav-thackeray-protest-against-state-government-over-hindi-launguage-ashish-shelar-gave-a-reaction/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: मनसेकडून ठाकरे गटाला निमंत्रण दिल्यानं भाजप नाराज प्रतिसभागृहात सहभागी</t>
+          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>विमान सुरक्षेसाठी पक्ष्यांचा वावर कमी करण्याच्या नव्या संकल्पना शोधण्याचे मुंबई उपनगर पालकमंत्री ॲड आशिष शेलार यांचे निर्देश</t>
+          <t>"महाराष्ट्रद्वेष हाच भाजपाचा खरा डीएनए", शेलार व निशिकांत दुबेंच्या वक्तव्यावरून आदित्य ठाकरेंचा संताप</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-instructed-to-find-new-concepts-to-reduce-bird-strike-on-aircraft-zws-70-5186222/</t>
+          <t>https://www.loksatta.com/maharashtra/aditya-thackeray-says-hate-for-maharashtra-is-true-dna-of-bjp-over-nishikant-dubey-ashish-shelar-statement-asc-95-5211821/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>चित्रनगरीतील कामांची पाहणी मंत्री आशिष शेलार यांनी केली.</t>
+          <t>‘खालिद का शिवाजी’ची स्तुती करणारे मंत्री शेलार आता कारवाई का करतायत? विरोधकांचा सरकारमधील लोकांवर संशय</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-minister-ashish-shelar-inspected-ongoing-works-in-chitranagari-ocd-94-5192132/</t>
+          <t>https://www.loksatta.com/maharashtra/khalid-ka-shivaji-rohit-pawar-oppess-ashish-shelar-action-against-marathi-movie-asc-95-5289901/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>नालेसफाईच्या कामात यंदाही घोटाळा,उपनगर पालकमंत्री ॲड. आशिष शेलार यांचा आरोप</t>
+          <t>आशिष शेलारांचा पर्यावरणवाद्यांवर बनावट हिंदू सणविरोधी असल्याचा ठपका, पर्यावरणवाद्यांकडूनही खरपूस समाचार</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-bmc-administration-scam-has-been-revealed-in-drain-cleaning-work-this-year-as-well-mumbai-print-news-sud-02-5079088/</t>
+          <t>https://www.loksatta.com/nagpur/cultural-minister-ashish-shelar-calls-environmentalists-anti-hindu-phm-00-5246668/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>साताऱ्यातील ‘फाशीचा वड’ स्थळाच्या राज्य स्मारकासाठी प्रस्ताव पाठवावा, मंत्री आशिष शेलार यांची सूचना</t>
+          <t>चित्रकार रवी परांजपे यांच्या कलाकृती मंत्री ॲड. आशिष शेलार यांच्या उपस्थितीत शासनाकडे सुपूर्द</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-on-satara-s-fashicha-wad-state-memorial-proposal-css-98-5153794/</t>
+          <t>https://mahasamvad.in/176545/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Prakash Mahajan : ‘पाळीव प्राण्यापासून सर्वच अस्वस्थ अन् शोकाकूल’, शेलारांनी राज...</t>
+          <t>राजकारणातले सच्चे मित्र दुरावले? आशिष शेलार आणि राज ठाकरेंमध्ये दुरावा?</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ashish-shelar-mocks-mns-leader-prakash-mahajan-raj-thackeray-friendship-1389288.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/ashish-shelar-still-upset-with-his-friens-mns-president-raj-thackeray/934652</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>‘राज्य महोत्सव’ गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी - सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार</t>
+          <t>संगीत नाटकांसाठी रवींद्र नाट्य मंदिर २५ टक्के सवलतीत उपलब्ध होणार; ॲड.आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176672/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announced-that-ravindra-natya-mandir-will-be-available-at-a-25-percent-discount-mumbai-print-news-phm-00-5232212/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>गणेशोत्सव आंतरराष्ट्रीय पातळीवर पोहचविणार, सांस्कृतिक कार्यमंत्री आशिष शेलार यांची घोषणा</t>
+          <t>BJP Mumbai President :बीएमसी निवडणुकीआधी भाजपने भाकरी फिरवली, शेलारांना नारळ, मुंबईची धुरा कोणाकडे?</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announcement-in-assembly-session-ganeshotsav-international-level-publicity-asj-82-5238641/</t>
+          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाला राज्य महोत्सवाचा दर्जा, गणेशभक्तांमध्ये उत्साहाचे वातावरण</t>
+          <t>Ashish Shelar And Mungantiwar : मुनगंटीवार म्हणाले, मी देखील चुकून काही काळ, आशिष शेलारांनीच दिले उत्तर</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
+          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>पीओपी गणेश मूर्तींवर बंदीला काँग्रेस जबाबदार, सांस्कृतीक कार्य मंत्री आशिष शेलार यांचा आरोप</t>
+          <t>टीका करताना शेलारांचा तोल सुटला! मनसे कार्यकर्त्यांची पहलगामच्या दहशतवाद्यांशी तुलना; म्हणाले, त्यांनी...</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-alleged-congress-and-mahavikas-aghadi-for-conspired-to-ban-pop-ganesh-idols-sud-02-5242178/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/bjp-ashish-shelar-compare-raj-thackeray-mns-workers-with-pahalgam-terrorist-after-shivsena-victory-rally-vijayi-melava-in-mumbai-with-uddhav-thackeray/921560</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>महेश मांजरेकरांना व्ही. शांताराम जीवन गौरव पुरस्कार, तर विशेष योगदान पुरस्काराने होणार मुक्ता बर्वेचा सन्मान; आशिष शेलार यांची घोषणा</t>
+          <t>महापालिका निवडणुकीच्या तोंडावर भाजपमधील धुसफुस चव्हाट्यावर, आशीष शेलार यांच्यासमोरच हाणामारी, खडाजंगी</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/manoranjan/mahesh-manjrekar-shantaram-jeevan-gaurav-award-mukta-barve-to-be-honored-with-special-contribution-award-announced-by-ashish-shelar-scj-81-5026480/</t>
+          <t>https://www.loksatta.com/mumbai/bjp-workers-clashed-with-each-other-in-front-of-minister-ashish-shelar-in-kandivali-zws-70-5156138/</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरेंचा तो नेता भाजपाच्या दरबारात; चर्चांना उधाण, म्हणाला मी आमदार झाल्यापासून...</t>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार - MANIK MOTI BOOK LAUNCH</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/mumbai/shivsena-uddhav-thackeray-mla-mahesh-sawant-attends-janta-darbar-of-bjp-leader-ashish-shelar/930835</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/publication-of-the-biography-book-manik-moti-based-on-the-veteran-singer-manik-verma-maharashtra-news-mhs25051306533</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>मुंबईत भरणार देशातील पहिला ‘रेडिओ’ महोत्सव - आशिष शेलार यांची घोषणा; मराठी भाषा आणि कलाकारांसाठी नवे व्यासपीठ</t>
+          <t>गणेशोत्सवात यंदा सात दिवस रात्री उशिरापर्यंत ध्वनिक्षेपक? मंत्री शेलारांनी स्पष्टच सांगितले…!</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/17/maharashtra-radio-festival-for-the-first-time.html</t>
+          <t>https://www.loksatta.com/pune/pune-ashish-shelar-says-district-collectors-can-allow-loudspeaker-use-till-midnight-during-ganeshotsav-pune-print-news-rds-00-5320532/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BJP MNS Friendship: हिंदी सक्तीच्या निर्णयावरुन भाजप-मनसेची मैत्री तुटणार? राजकीय वॉर सुरु</t>
+          <t>Ganesh visarjan guidelines : उंच गणेशमूर्तींच्या विसर्जनाबाबत 30 तारखेपर्यंत भूमिका मांडणार</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/tall-ganesh-idol-immersion-guidelines-2025-ab96</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Mumbai News : मोठी बातमी! एल्फिन्स्टन पुलाच्या परिसरातील 19 इमारतींमधील सर्व रहिवाशांना त्याच ठिकाणी घरे मिळणार</t>
+          <t>राज ठाकरेंशी संबधित ‘येक नंबर’ हिट की फ्लॉप? शेलारांची थेट विधीमंडळात माहिती, बजेट व बॉक्स ऑफिस कलेक्शनची तुलना करत म्हणाले…</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment/articleshow/120695379.cms</t>
+          <t>https://www.loksatta.com/maharashtra/raj-thackeray-yek-number-movie-box-office-collection-ashish-shelar-teases-at-assembly-monsoon-session-asc-95-5217195/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Thackeray : ठाकरे पितापुत्र भाजपा नेत्यांच्या भेटीला, नेमकं कारण काय?</t>
+          <t>Maharashtra Politics: मनसेकडून ठाकरे गटाला निमंत्रण दिल्यानं भाजप नाराज प्रतिसभागृहात सहभागी</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/thackeray-father-and-son-meet-bjp-leaders-what-is-the-real-reason-281903/amp/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>मुंढेगाव चित्रनगरीविषयी अधिवेशनानंतर बैठक; आशिष शेलार यांचे अजित पवार गटाला आश्वासन</t>
+          <t>विमान सुरक्षेसाठी पक्ष्यांचा वावर कमी करण्याच्या नव्या संकल्पना शोधण्याचे मुंबई उपनगर पालकमंत्री ॲड आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/dadasaheb-phalke-film-city-to-come-up-at-igatpuri-near-nashik-cultural-development-vsd-99-5218532/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-instructed-to-find-new-concepts-to-reduce-bird-strike-on-aircraft-zws-70-5186222/</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>वांद्रे येथे पहिले बालकुमार साहित्य संमेलन, सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते १० फेब्रुवारीला संमेलनाचे उद्घाटन</t>
+          <t>मुंबईत घडतेय तरी काय? आता अमित ठाकरेंनी घेतली आशिष शेलारांची भेट; राजकीय वर्तुळात चर्चा</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/national-library-and-maharashtra-state-sahitya-sanskrit-mandal-organize-balakumar-sahitya-sammelan-on-february-10-mumbai-print-news-sud-02-4876644/</t>
+          <t>https://www.lokmat.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-know-about-what-is-exactly-the-reason-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाला राज्य महोत्सव दर्जाच्या निर्णयाचे स्वागत; गणेश मंडळाच्या पदाधिकाऱ्यांकडून आंनदोत्सव</t>
+          <t>चित्रनगरीतील कामांची पाहणी मंत्री आशिष शेलार यांनी केली.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ganesh-mandal-office-bearers-celebrate-with-joy-over-decision-to-grant-state-festival-status-to-ganeshotsav-pune-print-news-phm-00-5219942/</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-minister-ashish-shelar-inspected-ongoing-works-in-chitranagari-ocd-94-5192132/</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>राहुल गांधींच्या डोक्यातील चीप चोरीला गेली; मुख्यमंत्री देवेंद्र फडणवीस यांची बोचरी टीका</t>
+          <t>साताऱ्यातील ‘फाशीचा वड’ स्थळाच्या राज्य स्मारकासाठी प्रस्ताव पाठवावा, मंत्री आशिष शेलार यांची सूचना</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/chief-minister-devendra-fadnavis-criticizes-rahul-gandhi-mumbai-print-news-phm-00-5288682/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-on-satara-s-fashicha-wad-state-memorial-proposal-css-98-5153794/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी मिळणार घरे; मुख्यमंत्री फडणवीसांच्या बैठकीत निर्णय</t>
+          <t>गणेशोत्सव आंतरराष्ट्रीय पातळीवर पोहचविणार, सांस्कृतिक कार्यमंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mmrda-to-redevelop-19-buildings-near-elphinstone-bridge-a-a1001/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announcement-in-assembly-session-ganeshotsav-international-level-publicity-asj-82-5238641/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>महाराष्ट्र जिंकला, मराठी माणूस जिंकला, भाजप जिंकला: मंत्री आशिष शेलार</t>
+          <t>गणेशोत्सवाला राज्य महोत्सवाचा दर्जा, गणेशभक्तांमध्ये उत्साहाचे वातावरण</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-wins-marathi-people-win-bjp-wins-says-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy/articleshow-odudhrc</t>
+          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>आशिष शेलार यांना ‘नाफा’ मराठी चित्रपट महोत्सवाचे विशेष निमंत्रण !</t>
+          <t>‘राज्य महोत्सव’ गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी - सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
+          <t>https://mahasamvad.in/176672/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>आशिष शेलार यांचे आवाहन,“राज्य महोत्सवा” करिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी</t>
+          <t>पीओपी गणेश मूर्तींवर बंदीला काँग्रेस जबाबदार, सांस्कृतीक कार्य मंत्री आशिष शेलार यांचा आरोप</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
+          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-alleged-congress-and-mahavikas-aghadi-for-conspired-to-ban-pop-ganesh-idols-sud-02-5242178/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>“राज्य महोत्सव” गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी – सांस्कृतिक कार्य मंत्री आशिष शेलार</t>
+          <t>उद्धव ठाकरेंचा तो नेता भाजपाच्या दरबारात; चर्चांना उधाण, म्हणाला मी आमदार झाल्यापासून...</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
+          <t>https://zeenews.india.com/marathi/mumbai/shivsena-uddhav-thackeray-mla-mahesh-sawant-attends-janta-darbar-of-bjp-leader-ashish-shelar/930835</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Pune Ganesh Festival 2025 : पुण्यातील मंडळांनी लक्ष द्या! सांस्कृतिक मंत्र्याच्या अध्यक्षतेखाली बैठक, कोणते मोठे निर्णय झाले? जाणून घ्या...</t>
+          <t>मुंबईत भरणार देशातील पहिला ‘रेडिओ’ महोत्सव - आशिष शेलार यांची घोषणा; मराठी भाषा आणि कलाकारांसाठी नवे व्यासपीठ</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/17/maharashtra-radio-festival-for-the-first-time.html</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>आग्र्यावरून सुटकेचा दिवस ‘शिवचातुर्य दिन’ म्हणून साजरा होणार; मंत्री Ashish Shelar यांची घोषणा</t>
+          <t>BJP MNS Friendship: हिंदी सक्तीच्या निर्णयावरुन भाजप-मनसेची मैत्री तुटणार? राजकीय वॉर सुरु</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
+          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maharashtra: एमवीए के अंत को लेकर अपनी भविष्यवाणी पर आशीष शेलार बोले- सच साबित हुई, घोषणा की औपचारिकता बाकी</t>
+          <t>एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी मिळणार घरे; मुख्यमंत्री फडणवीसांच्या बैठकीत निर्णय</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-minister-ashish-shelar-says-my-prediction-about-mva-end-come-true-2025-02-14</t>
+          <t>https://www.lokmat.com/mumbai/mmrda-to-redevelop-19-buildings-near-elphinstone-bridge-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>'मुंबई में हिंदुओं को भाषा के कारण पीटा', BJP नेता आशीष शेलार ने पहलगाम हमले से की थप्‍पड़कांड की तुलना</t>
+          <t>महाराष्ट्र : आशीष शेलार का ठाकरे ब्रदर्स पर हमला, कहा- सिर्फ घर बैठकर करते हैं राजनीति</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>सैफ अली खान पर हमले के बाद मंत्री आशीष शेलार का बड़ा बयान, 'बॅालीवुड वालों डरना...'</t>
+          <t>महाराष्ट्र जिंकला, मराठी माणूस जिंकला, भाजप जिंकला: मंत्री आशिष शेलार</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
+          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-wins-marathi-people-win-bjp-wins-says-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy/articleshow-odudhrc</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार के 'मराठी और पहलगाम' वाले बयान पर भड़के संजय राउत, बोले- 'भाषा</t>
+          <t>आशिष शेलार यांना ‘नाफा’ मराठी चित्रपट महोत्सवाचे विशेष निमंत्रण !</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
+          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Maharashtra won, Marathi Manus won, BJP won in this fight, says BJP Mumbai chief Ashish Shelar slams MVA over three-language policy issue</t>
+          <t>आशिष शेलार यांचे आवाहन,“राज्य महोत्सवा” करिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
+          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Maharashtra: मुंबई में जलभराव पर सियासत तेज, मंत्री आशीष शेलार ने कर दी बड़ी मांग, उद्धव</t>
+          <t>“राज्य महोत्सव” गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी – सांस्कृतिक कार्य मंत्री आशिष शेलार</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
+          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में 'खालिद का शिवाजी' मूवी को बैन करने की मांग के बीच मंत्री आशीष शेलार का बड़ा बयान, जानें क्या कुछ कहा?</t>
+          <t>Pune Ganesh Festival 2025 : पुण्यातील मंडळांनी लक्ष द्या! सांस्कृतिक मंत्र्याच्या अध्यक्षतेखाली बैठक, कोणते मोठे निर्णय झाले? जाणून घ्या...</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
+          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>मुंबई: मंत्री की मौजूदगी में BJP कार्यकर्ताओं के दो गुटों में हिंसक झड़प, हिरासत में लिए गए देवांग दवे</t>
+          <t>आग्र्यावरून सुटकेचा दिवस ‘शिवचातुर्य दिन’ म्हणून साजरा होणार; मंत्री Ashish Shelar यांची घोषणा</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
+          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Maharashta: भाजपा नेता आशीष शेलार ने की हिंदी भाषी लोगों पर हमले की निंदा, पहलगाम आतंकी हमले से की तुलना</t>
+          <t>Maharashtra: एमवीए के अंत को लेकर अपनी भविष्यवाणी पर आशीष शेलार बोले- सच साबित हुई, घोषणा की औपचारिकता बाकी</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-2025-07-06</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-minister-ashish-shelar-says-my-prediction-about-mva-end-come-true-2025-02-14</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>‘इन गानों को नियमित रूप से बजाएं’, प्राइवेट रेडियो स्टेशनों से महाराष्ट्र के</t>
+          <t>'मुंबई में हिंदुओं को भाषा के कारण पीटा', BJP नेता आशीष शेलार ने पहलगाम हमले से की थप्‍पड़कांड की तुलना</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
+          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Marathi School in USA: अमेरिकतील मराठी शाळांना महाराष्ट्र शासन अभ्यासक्रम पुरवणार, आशिष शेलार यांचे आश्वासन</t>
+          <t>मंत्री आशीष शेलार के 'मराठी और पहलगाम' वाले बयान पर भड़के संजय राउत, बोले- 'भाषा</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BJP नेता आशीष शेलार का उद्धव ठाकरे पर गंभीर आरोप, 'मुंबई में जितने भी जमीन से जुड़े</t>
+          <t>Maharashtra won, Marathi Manus won, BJP won in this fight, says BJP Mumbai chief Ashish Shelar slams MVA over three-language policy issue</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>मुंबई की सड़कों के सारे गड्ढे भरेगी बीएमसी, आशीष शेलार का ऐलान</t>
+          <t>Maharashtra: मुंबई में जलभराव पर सियासत तेज, मंत्री आशीष शेलार ने कर दी बड़ी मांग, उद्धव</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
+          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>'पहलगाम की तरह महाराष्ट्र में भी...', MNS कार्यकर्ताओं की गुंडागर्दी पर महाराष्ट्र के मंत्री ने कसा तंज - Maharashtra Minister Ashish Shelar Compares Violence with Pahalgam Terror Attack amid Marathi Language Controv</t>
+          <t>महाराष्ट्र में 'खालिद का शिवाजी' मूवी को बैन करने की मांग के बीच मंत्री आशीष शेलार का बड़ा बयान, जानें क्या कुछ कहा?</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Maharashtra Language Row: Ashish Shelar के बयान से सियासी संग्राम, Aaditya Thackeray का पलटवार!</t>
+          <t>मुंबई: मंत्री की मौजूदगी में BJP कार्यकर्ताओं के दो गुटों में हिंसक झड़प, हिरासत में लिए गए देवांग दवे</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>राज-उद्धव ठाकरे के साथ आने पर BJP का बड़ा बयान- 'जब वह मुख्यमंत्री थे तो...'</t>
+          <t>‘इन गानों को नियमित रूप से बजाएं’, प्राइवेट रेडियो स्टेशनों से महाराष्ट्र के</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Maharashtra: IT विभाग में 1000 करोड़ के घोटाला का दावा, मंत्री आशीष शेलार का एक्शन, अफसर को</t>
+          <t>Maharashta: भाजपा नेता आशीष शेलार ने की हिंदी भाषी लोगों पर हमले की निंदा, पहलगाम आतंकी हमले से की तुलना</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
+          <t>https://www.amarujala.com/india-news/bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-2025-07-06</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदे के सम्मान को लेकर शरद पवार पर भड़की शिवसेना-यूबीटी तो BJP ने कसा तंज,</t>
+          <t>Marathi School in USA: अमेरिकतील मराठी शाळांना महाराष्ट्र शासन अभ्यासक्रम पुरवणार, आशिष शेलार यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
+          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Politics: 'राहुल गांधी के दिमाग की चिप चोरी और हार्ड डिस्क करप्ट हो गई', EC पर धांधली के आरोपों पर बोले फडणवीस</t>
+          <t>मुंबई की सड़कों के सारे गड्ढे भरेगी बीएमसी, आशीष शेलार का ऐलान</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/rahul-gandhi-election-commission-allegations-devendra-fadnavis-ashish-shelar-response-2025-08-07</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>इतिहास से छेड़छाड़ बर्दाश्त नहीं की जाएगी... विवादों में घिरी फिल्‍म 'खालिद का शिवाजी' पर मंत्री आशीष शेलार</t>
+          <t>BJP नेता आशीष शेलार का उद्धव ठाकरे पर गंभीर आरोप, 'मुंबई में जितने भी जमीन से जुड़े</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>‘हिंदुओं पर उनकी भाषा के कारण हमला…’, महाराष्ट्र सरकार के मंत्री ने मराठी विवाद को पहलगाम से जोड़ा</t>
+          <t>'पहलगाम की तरह महाराष्ट्र में भी...', MNS कार्यकर्ताओं की गुंडागर्दी पर महाराष्ट्र के मंत्री ने कसा तंज - Maharashtra Minister Ashish Shelar Compares Violence with Pahalgam Terror Attack amid Marathi Language Controv</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
+          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>रघुजी भोसले की पौराणिक तलवार लौटेगी भारत, आशीष शेलार ने जताई खुशी</t>
+          <t>Maharashtra Language Row: Ashish Shelar के बयान से सियासी संग्राम, Aaditya Thackeray का पलटवार!</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
+          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Cannes: कान फिल्म फेस्टिवल के लिए चयनित हुईं चार मराठी फिल्में, मंत्री आशीष शेलार ने दी सभी को बधाई</t>
+          <t>राज-उद्धव ठाकरे के साथ आने पर BJP का बड़ा बयान- 'जब वह मुख्यमंत्री थे तो...'</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>मुंबई में हिंदी भाषा के कारण पीटा… मंत्री आशीष सलार ने पहलगाम आतंकी हमले से की तुलना</t>
+          <t>रघुजी भोसले की पौराणिक तलवार लौटेगी भारत, आशीष शेलार ने जताई खुशी</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-hindi-speaker-attacks-bjp-ashish-shelar-condemns-violence-compares-to-pulwama-3376913.html</t>
+          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Asha Bhosle News: 'मी फक्त आशिष शेलारांना ओळखते..', ठाकरे बंधुंच्या मनोमिलनावर आशा भोसले काय म्हणाल्या?</t>
+          <t>एकनाथ शिंदे के सम्मान को लेकर शरद पवार पर भड़की शिवसेना-यूबीटी तो BJP ने कसा तंज,</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>भाषा विवाद पर महाराष्ट्र में तनाव, मंत्री आशीष शेलार ने की पहलगाम हमले से तुलना</t>
+          <t>Maharashtra: IT विभाग में 1000 करोड़ के घोटाला का दावा, मंत्री आशीष शेलार का एक्शन, अफसर को</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/maharashtra/ashish-shelar-compares-pahalgam-terror-attack-marathi-hindi-row-controversy/articleshow-ma03grc</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>मराठी पर बवाल जारी! रोहित पवार ने पंडित धीरेंद्र शास्त्री को दे दी चेतावनी- 'जहां</t>
+          <t>इतिहास से छेड़छाड़ बर्दाश्त नहीं की जाएगी... विवादों में घिरी फिल्‍म 'खालिद का शिवाजी' पर मंत्री आशीष शेलार</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
+          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>फडणवीस इफेक्ट या ठाकरे इम्पैक्ट? आशीष शेलार की जगह अमित साटम को मुंबई BJP की कमान के पीछे क्या</t>
+          <t>‘हिंदुओं पर उनकी भाषा के कारण हमला…’, महाराष्ट्र सरकार के मंत्री ने मराठी विवाद को पहलगाम से जोड़ा</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/amit-satam-mumbai-bjp-new-president-cm-devendra-fadnavish-ashish-shelar-civic-polls-ntcpbt-rpti-2318125-2025-08-25</t>
+          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>तणावाच्या परिस्थितीमुळे माहिती तंत्रज्ञान आणि सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचा दौरा रद्द</t>
+          <t>Cannes: कान फिल्म फेस्टिवल के लिए चयनित हुईं चार मराठी फिल्में, मंत्री आशीष शेलार ने दी सभी को बधाई</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165514/</t>
+          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>सर्वात मोठी बातमी ! गणेशोत्सव महाराष्ट्राचा महोत्सव म्हणून घोषित; आशिष शेलार यांची घोषणा</t>
+          <t>Asha Bhosle News: 'मी फक्त आशिष शेलारांना ओळखते..', ठाकरे बंधुंच्या मनोमिलनावर आशा भोसले काय म्हणाल्या?</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-declares-ganeshotsav-as-state-festival-bjp-leader-ashish-shalar-announcement-1442515.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>मुंबई भाजपा पदाधिकाऱ्यांमध्ये राडा; आशिष शेलार कारमधून उतरताच दोन गटांत हाणामारी</t>
+          <t>भाषा विवाद पर महाराष्ट्र में तनाव, मंत्री आशीष शेलार ने की पहलगाम हमले से तुलना</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mumbai-bjp-office-bearers-clash-in-front-of-ashish-shelar-car-a-fight-broke-out-between-two-groups-at-kandivali-a-a629/</t>
+          <t>https://hindi.asianetnews.com/state/maharashtra/ashish-shelar-compares-pahalgam-terror-attack-marathi-hindi-row-controversy/articleshow-ma03grc</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस से मिले राज ठाकरे, अब बेटे अमित ठाकरे की आशीष शेलार से मुलाकात, महाराष्ट्र में कुछ पक रहा है?</t>
+          <t>मराठी पर बवाल जारी! रोहित पवार ने पंडित धीरेंद्र शास्त्री को दे दी चेतावनी- 'जहां</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
+          <t>मुंबई में हिंदी भाषा के कारण पीटा… मंत्री आशीष सलार ने पहलगाम आतंकी हमले से की तुलना</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-hindi-speaker-attacks-bjp-ashish-shelar-condemns-violence-compares-to-pulwama-3376913.html</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार; दोन दिवसांआधी राज ठाकरेंनीही देवेंद्र फडणवीसांची घेतली होती भेट</t>
+          <t>तणावाच्या परिस्थितीमुळे माहिती तंत्रज्ञान आणि सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचा दौरा रद्द</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
+          <t>https://mahasamvad.in/165514/</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BJP on Raj Uddhav Alliance: ठाकरे बंधूंच्या एकत्र येण्याची पोस्ट अमित शाहांना टॅग केली, आशिष</t>
+          <t>सर्वात मोठी बातमी ! गणेशोत्सव महाराष्ट्राचा महोत्सव म्हणून घोषित; आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-declares-ganeshotsav-as-state-festival-bjp-leader-ashish-shalar-announcement-1442515.html</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Big announcement: मराठ्यांच्या पराक्रमाची साक्ष असलेली ऐतिहासिक तलवार लवकरच महाराष्ट्रात येणार</t>
+          <t>फडणवीस इफेक्ट या ठाकरे इम्पैक्ट? आशीष शेलार की जगह अमित साटम को मुंबई BJP की कमान के पीछे क्या</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/amit-satam-mumbai-bjp-new-president-cm-devendra-fadnavish-ashish-shelar-civic-polls-ntcpbt-rpti-2318125-2025-08-25</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Clerk-Typist Exam Result: लिपिक-टंकलेखक परीक्षेचा निकाल कधी लागणार? आशिष शेलारांनी दिली माहिती</t>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार; दोन दिवसांआधी राज ठाकरेंनीही देवेंद्र फडणवीसांची घेतली होती भेट</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>आपले सरकार सेवा केंद्रांच्या संख्येत वाढ – माहिती तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
+          <t>देवेंद्र फडणवीस से मिले राज ठाकरे, अब बेटे अमित ठाकरे की आशीष शेलार से मुलाकात, महाराष्ट्र में कुछ पक रहा है?</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160573/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>भजनी मंडळांना २५ हजारांचे अनुदान; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची माहिती</t>
+          <t>Big announcement: मराठ्यांच्या पराक्रमाची साक्ष असलेली ऐतिहासिक तलवार लवकरच महाराष्ट्रात येणार</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-bhajani-mandals-grant-25000-ashish-shelar</t>
+          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>स्थानीय राजनीति को इंटरनेशनल मुद्दों से नहीं जोड़ना चाहिए… संजय राउत के बयान पर बोले शरद पवार</t>
+          <t>Clerk-Typist Exam Result: लिपिक-टंकलेखक परीक्षेचा निकाल कधी लागणार? आशिष शेलारांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/maharashtra-bjp-leader-ashish-shelar-sharad-pawar-reaction-on-sanjay-raut-over-all-party-delegation-row-3297804.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Hindi Controversy: 'मराठी'वरुन दहशतवाद्यांशी तुलना, आशिष शेलारांच्या वक्तव्याचा मनसेकडून समाचार</t>
+          <t>भजनी मंडळांना २५ हजारांचे अनुदान; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-bhajani-mandals-grant-25000-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>शिवसेना UBT की हालत मुंबई की 'खतरनाक' और 'जर्जर' इमारतों जैसी, महाराष्ट्र के मंत्री आशीष शेलार ने कसा तंज</t>
+          <t>स्थानीय राजनीति को इंटरनेशनल मुद्दों से नहीं जोड़ना चाहिए… संजय राउत के बयान पर बोले शरद पवार</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
+          <t>https://www.tv9hindi.com/india/maharashtra-bjp-leader-ashish-shelar-sharad-pawar-reaction-on-sanjay-raut-over-all-party-delegation-row-3297804.html</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में कुछ होने वाला है बड़ा? पहले CM फडणवीस से मिले राज ठाकरे, अब बेटे ने BJP नेता से की मुलाकात</t>
+          <t>Hindi Controversy: 'मराठी'वरुन दहशतवाद्यांशी तुलना, आशिष शेलारांच्या वक्तव्याचा मनसेकडून समाचार</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/maharashtra-politics-amit-thackeray-met-minister-ashish-shelar-after-raj-thackeray-meeting-with-cm-fadnavis/2893316</t>
+          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>नागरिकांना डिजिटल सेवा देण्यासाठी शासन प्रयत्नशील – मंत्री ॲड.आशिष शेलार</t>
+          <t>शिवसेना UBT की हालत मुंबई की 'खतरनाक' और 'जर्जर' इमारतों जैसी, महाराष्ट्र के मंत्री आशीष शेलार ने कसा तंज</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159784/</t>
+          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>हिंदी भाषा सक्ती प्रकरण: महाराष्ट्रात सक्ती फक्त मराठीची, हिंदीची नाही पण... : आशिष शेलार यांनी मांडली भूमिका</t>
+          <t>नागरिकांना डिजिटल सेवा देण्यासाठी शासन प्रयत्नशील – मंत्री ॲड.आशिष शेलार</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/only-marathi-is-compulsory-in-maharashtra-says-minister-ashish-shelar-on-hindi-language-controversy-maharashtra-news-mhs25062401471</t>
+          <t>https://mahasamvad.in/159784/</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>मुंबईत उभारणार सांस्कृतिक केंद्र आणि वस्तुसंग्रहालय: आशिष शेलारांची घोषणा</t>
+          <t>महाराष्ट्र में कुछ होने वाला है बड़ा? पहले CM फडणवीस से मिले राज ठाकरे, अब बेटे ने BJP नेता से की मुलाकात</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-cultural-center-and-museum-to-be-set-up-in-bkc-mumbai-said-minister-ashish-shelar-in-assembly-budget-session-2025-maharashtra-news-mhs25031900644</t>
+          <t>https://zeenews.india.com/hindi/india/maharashtra-politics-amit-thackeray-met-minister-ashish-shelar-after-raj-thackeray-meeting-with-cm-fadnavis/2893316</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>NDTV Emerging Business Conclave : "उद्धवजींची अवस्था पाहता महायुतीचा विजय पक्का"; आशिष शेलारांचा निशाणा</t>
+          <t>आपले सरकार सेवा केंद्रांच्या संख्येत वाढ – माहिती तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
+          <t>https://mahasamvad.in/160573/</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Marathi Language Controversy : भाषा वादावर आशिष शेलारांचं मोठं विधान; मनसैनिकांची थेट पहलगाममधील दहशतवाद्यांशी तुलना</t>
+          <t>महाराष्ट्र में हिंदी को लेकर सियासी बवाल, उद्धव ठाकरे से जुड़े सवाल पर आशा भोसले</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
+          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Emerging Business Conclave : 'तुम्ही काय केलं, ठाकरे बंधूंना सवाल'; शेलारांनी 1995 पासून कामाचा पाढाच वाचला</t>
+          <t>NDTV Emerging Business Conclave : "उद्धवजींची अवस्था पाहता महायुतीचा विजय पक्का"; आशिष शेलारांचा निशाणा</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>महराष्ट्र में राजकीय उत्सव के रूप में मनाया जाएगा गणेशोत्सव, संस्कृति मंत्री आशीष शेलार ने विधानमंडल में किया ऐलान</t>
+          <t>Marathi Language Controversy : भाषा वादावर आशिष शेलारांचं मोठं विधान; मनसैनिकांची थेट पहलगाममधील दहशतवाद्यांशी तुलना</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
+          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>शिवसेना UBT के दो पूर्व पार्षद BJP में शामिल, मुंबई में उद्धव ठाकरे को फिर बड़ा झटका, शेलार ने छोड़े तीर</t>
+          <t>Emerging Business Conclave : 'तुम्ही काय केलं, ठाकरे बंधूंना सवाल'; शेलारांनी 1995 पासून कामाचा पाढाच वाचला</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Kishori Pednekar : ठाकरेंना ‘लँड माफिया’ म्हणताच पेडणेकरांकडून ‘झोलर’ची आठवण,...</t>
+          <t>महराष्ट्र में राजकीय उत्सव के रूप में मनाया जाएगा गणेशोत्सव, संस्कृति मंत्री आशीष शेलार ने विधानमंडल में किया ऐलान</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
+          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Ganeshotsav 2025: गणेशोत्सव महाराष्ट्र राज्याचा महोत्सव म्हणून घोषित; आशिष शेलार यांची विधानसभेत माहिती</t>
+          <t>Kishori Pednekar : ठाकरेंना ‘लँड माफिया’ म्हणताच पेडणेकरांकडून ‘झोलर’ची आठवण,...</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
+          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Ashish Shelar : गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा; आशिष शेलार यांचे अधिकाऱ्यांना निर्देश</t>
+          <t>Ganeshotsav 2025: गणेशोत्सव महाराष्ट्र राज्याचा महोत्सव म्हणून घोषित; आशिष शेलार यांची विधानसभेत माहिती</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Pen News : रायगडमध्ये पालकमंत्रिपद वादात, भाजपचे संपर्कमंत्री वेगात, मूर्तिकारांच्या प्रश्नाच्या निमित्ताने आशिष शेलार सक्रिय</t>
+          <t>Ashish Shelar : गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा; आशिष शेलार यांचे अधिकाऱ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>गणेशोत्सव को 'राज्य उत्सव' के रूप में मनाने की तैयारी - मंत्री एडवोकेट आशीष शेलार की घोषणा</t>
+          <t>शिवसेना UBT के दो पूर्व पार्षद BJP में शामिल, मुंबई में उद्धव ठाकरे को फिर बड़ा झटका, शेलार ने छोड़े तीर</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/festivals/preparations-to-celebrate-ganeshotsav-as-state-festival-announcement-by-minister-advocate-ashish-shelar-89618</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Ganeshotsav: गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रस्ताव सादर करणार; आशिष शेलार यांची माहिती</t>
+          <t>Pen News : रायगडमध्ये पालकमंत्रिपद वादात, भाजपचे संपर्कमंत्री वेगात, मूर्तिकारांच्या प्रश्नाच्या निमित्ताने आशिष शेलार सक्रिय</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/unesco-cultural-status-proposal-for-ganeshotsav-ashish-shelar-sb97</t>
+          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>'पहलगामसारखं मुंबईत निष्पाप हिंदूंना भाषा विचारुन चोपलं', आशिष शेलार यांचं धक्कादायक वक्तव्य</t>
+          <t>Ganeshotsav: गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रस्ताव सादर करणार; आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/unesco-cultural-status-proposal-for-ganeshotsav-ashish-shelar-sb97</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे हे मुंबईतील लँड स्कॅमचे बादशहा: त्यांच्या डोक्यात सतत स्कॅमचेच विचार येतात, भाजप नेते आशिष शेला...</t>
+          <t>गणेशोत्सव को 'राज्य उत्सव' के रूप में मनाने की तैयारी - मंत्री एडवोकेट आशीष शेलार की घोषणा</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/ashish-shelar-says-uddhav-thackeray-land-scam-king-in-mumbai-politics-134886158.html</t>
+          <t>https://www.mumbailive.com/hi/festivals/preparations-to-celebrate-ganeshotsav-as-state-festival-announcement-by-minister-advocate-ashish-shelar-89618</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ठाकरे बंधुमुळे भाजप अलर्ट मोडवर मुंबईच्या प्रत्येक वॉर्डमधील आढावा घेतला जाणार,</t>
+          <t>उद्धव ठाकरे हे मुंबईतील लँड स्कॅमचे बादशहा: त्यांच्या डोक्यात सतत स्कॅमचेच विचार येतात, भाजप नेते आशिष शेला...</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/ashish-shelar-says-uddhav-thackeray-land-scam-king-in-mumbai-politics-134886158.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>ठाकरेंना ज्यांनी धूळ चारली त्या जोडीला भाजपकडून मोठी जबाबदारी, आशिष शेलार यांची सर्वात मोठी घोषणा</t>
+          <t>मंत्री शेलार कल आयेंगे</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
+          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>निवडणुका आणि सत्तेसाठी पक्ष फोडता, भ्रष्टाचाऱ्यांना शुद्ध करून पक्षात घेता,</t>
+          <t>ठाकरेंना ज्यांनी धूळ चारली त्या जोडीला भाजपकडून मोठी जबाबदारी, आशिष शेलार यांची सर्वात मोठी घोषणा</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Mumbai Politics: आशिष शेलारांच्या वक्तव्यावर बाळा नांदगावकरांचे प्रत्युत्तर, म्हणाले...</t>
+          <t>निवडणुका आणि सत्तेसाठी पक्ष फोडता, भ्रष्टाचाऱ्यांना शुद्ध करून पक्षात घेता,</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/bala-nandgaonkar-hits-back-at-ashish-shelar-statement-mk94</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>Mumbai Politics: आशिष शेलारांच्या वक्तव्यावर बाळा नांदगावकरांचे प्रत्युत्तर, म्हणाले...</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://pudhari.news/maharashtra/mumbai/bala-nandgaonkar-hits-back-at-ashish-shelar-statement-mk94</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Asha Bhosle : ठाकरे बंधू एकत्र येणार? सवाल करताच आशा भोसले थेट म्हणाल्या, मला फक्त आशिष शेलार…</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>मराठी माणसांची तुलना पहलगाम अतिरेक्यांशी उद्धव ठाकरेंचा आशिष शेलार अन् निशिकांत</t>
+          <t>Asha Bhosle : ठाकरे बंधू एकत्र येणार? सवाल करताच आशा भोसले थेट म्हणाल्या, मला फक्त आशिष शेलार…</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
+          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>गणेशोत्सव 'महाराष्ट्र का राजकीय उत्सव' घोषित, मंत्री आशीष शेलार ने जताई खुशी</t>
+          <t>अमेरिकेतील ५० हून अधिक मराठी शाळांना महाराष्ट्र सरकारचा आधार; अभ्यासक्रम व परीक्षेत एकसंधतेचा मार्ग मोकळा</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-ganeshotsav-declared-state-festival-of-maharashtra-minister-ashish-shelar-expressed-happiness-news-hindi-1-735521-KKN.html</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>‘देवनार’च्या निविदेचे ४,५०० कोटी गेले कुठे? मंत्री आशिष शेलार यांचा आदित्य ठाकरेंना सवाल</t>
+          <t>गणेशोत्सवापूर्वी मुंबईतील सर्व खड्डे भरा: पालकमंत्री आशिष शेलार यांचे आदेश, मुंबई महापालिकेकडे आतापर्यंत 8 ...</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/where-did-the-4500-crores-of-the-deonar-tender-go-minister-ashish-shelar-questions-aaditya-thackeray-a-a719/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-potholes-ashish-shelar-ganesh-festival-deadline-135736371.html</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>मुंबईत भाजप पदाधिकारी एकमेकांना भिडले: मंत्री आशिष शेलारांच्या गाडीसमोरच झाला राडा, पक्षातील अंतर्गत वाद चव...</t>
+          <t>ठाकरे बंधुमुळे भाजप अलर्ट मोडवर मुंबईच्या प्रत्येक वॉर्डमधील आढावा घेतला जाणार,</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-infighting-ashish-shelar-kandivali-janupada-135227690.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Special Report Shelar Vs Thackeray | आशिष शेलारांचे उद्धव ठाकरेंवर गंभीर आरोप, सेनेकडून प्रत्युत्तर</t>
+          <t>पर्यावरण संवर्धनासाठी कमी कार्बन उत्सर्जनावर भर द्यावा - माहिती व तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/india-special-report-ashish-shelar-bjp-slams-on-uddhav-thackeray-shivsena-maharashtra-politics-abp-majha-1355752</t>
+          <t>https://mahasamvad.in/157961/</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Amit Thackeray-Ashish Shelar :अमित ठाकरे-आशिष शेलार भेट, राजकीय वर्तुळात चर्चांना उधाण</t>
+          <t>राजीव शुक्ला को BCCI ने दी बड़ी जिम्मेदारी, अब इस नए रोल में आएंगे नजर</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
+          <t>https://hindi.news24online.com/sports-news/rajeev-shukla-ashish-shellar-appointed-to-acc-board/1097176/</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>'स्कूलों में केवल मराठी अनिवार्य, हिंदी नहीं...', भाषा विवाद के बीच महाराष्ट्र के मंत्री का बड़ा बयान - only marathi is compulsory in schools not hindi maharashtra minister big statement amid language controversy</t>
+          <t>Aditya Thackeray On Ashish Shelar And Nishikant Dubey: ठाकरे बंधूंवर भाजपकडून हल्लाबोल आदित्य ठाकरेंनी आशिष</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-only-marathi-is-compulsory-in-schools-not-hindi-maharashtra-minister-big-statement-amid-language-controversy-40001615.html</t>
+          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>15 ऑगस्टच्या आधी सरदार रघुजी राजे भोसलेंची तलवार महाराष्ट्रात येणार, मंत्री शेलार</t>
+          <t>Shaktipeeth News: 'शक्तिपीठ महामार्गाबाबतचा अंतिम निर्णय...'; भाजपच्या बड्या नेत्याचं कोल्हापुरात मोठं विधान</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-statement-on-shaktipith-highway-final-decision-kolhapur-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Vijay Wadettiwar : महाराष्ट्राच्या राजकारणातून मोठी बातमी! वडेट्टीवारांच्या मनात चाललंय तरी काय? भाजप मंत्र्यासोबतच्या 'त्या' फोटोमुळे रंगली चर्चा</t>
+          <t>‘एमपीएससी’द्वारे विविध विभागातील रिक्त पदभरतीस गती देणार - माहिती व तंत्रज्ञान मंत्री ॲड.आशिष शेलार</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/chandrapur/congress-leader-vijay-wadettiwar-met-bjp-leader-and-minister-ashish-shelar-in-chandrapur-marathi-news/articleshow/119940732.cms</t>
+          <t>https://mahasamvad.in/158808/</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>'राज ठाकरे यांचा चित्रपटही लोकांनी स्वीकारला नाही...' मनसे अध्यक्षांबद्दल हे काय बोलून गेले आशिष शेलार?</t>
+          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते गायिका माणिक वर्मा यांच्या चरित्र ग्रंथाचे प्रकाशन</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/veteran-singer-manik-verma-lived-a-full-philosophical-life-adv-ashish-shelar-publication-of-the-book-manik-moti-written-by-shobha-bondre-mumbai-news-871060.html</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>धारावी पुनर्वसन: भाजपाचे आशिष शेलार अन् काँग्रेसच्या वर्षा गायकवाड यांच्यात ‘तू तू मै मै’</t>
+          <t>Ashish Shelar on Aaditya Thackeray | आदित्य ठाकरेंच्या होमपीचवर; आशिष शेलारांची तुफान बॅटिंग</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/dharavi-rehabilitation-project-dispute-between-bjps-ashish-shelar-and-congresss-varsha-gaikwad-a-a747/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-at-aaditya-thackeray-constituency-in-worli-maharashtra-politics-abp-majha-1361553</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाआधी मुंबईतील खड्ड्यांचं विघ्न दूर करा; पालकमंत्री आशिष शेलार यांचे निर्देश</t>
+          <t>गणेशोत्सव होगा महाराष्ट्र का महोत्सव</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
+          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Ashish Shelar On Raj Uddhav Thackeray: उद्धव ठाकरेंची टीका आशिष शेलारांच्या जिव्हारी विजयी मेळाव्यावरुन</t>
+          <t>'राज ठाकरे यांचा चित्रपटही लोकांनी स्वीकारला नाही...' मनसे अध्यक्षांबद्दल हे काय बोलून गेले आशिष शेलार?</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Ashish Shelar : बॉम्बे स्कॉटिशमध्ये शिकताना बॉम्बे नको मुंबई हे तुम्ही बोललात का? आशिष</t>
+          <t>मुंबईत भाजप पदाधिकारी एकमेकांना भिडले: मंत्री आशिष शेलारांच्या गाडीसमोरच झाला राडा, पक्षातील अंतर्गत वाद चव...</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-infighting-ashish-shelar-kandivali-janupada-135227690.html</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Ashish Shelar : आता कसा झेंडा घेऊ हाती? शेलारांनी ठाकरे बंधूंना डिवचलं अन्…</t>
+          <t>राज-उद्धव एकत्र येणार? आशा भोसलेंच्या उत्तरानं उंचावल्या सगळ्यांच्या भुवया, म्हणाल्या मी फक्त आशिष शेलार यांनाच...</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Ashish Shelar: आशिष शेलारांनी ठाकरे बंधूंच्या जखमेवर मीठ चोळलं, म्हणाले, बेस्ट पतपेढीच्या</t>
+          <t>सांस्कृतिक विभागाकडून मार्चपर्यंत राज्यात १२०० कार्यक्रम होणार; मंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
+          <t>https://www.lokmat.com/satara/cultural-department-to-hold-1200-programs-in-the-state-by-march-minister-ashish-shelar-announces-a-a829-c607/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>PoP Ganesh Idols | Ashish Shelar यांचा विरोधकांवर हल्लाबोल, मूर्तिकारांच्या पाठीशी BJP</t>
+          <t>Ashish Shelar On Raj Uddhav Thackeray: उद्धव ठाकरेंची टीका आशिष शेलारांच्या जिव्हारी विजयी मेळाव्यावरुन</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते 'लाडकी बहीण'चा मुहूर्त संपन्न!</t>
+          <t>Amit Thackeray-Ashish Shelar :अमित ठाकरे-आशिष शेलार भेट, राजकीय वर्तुळात चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>उबाठा सेना, राऊतांना तुकडे गँगची चिंता: भाजपच्या आशिष शेलार यांचा आरोप; महाराष्ट्र जनसुरक्षा विधेयकावरून सा...</t>
+          <t>Emerging Business Conclave : AI मुळे रोजगार कमी होतोय? आशिष शेलारांनी लोकांचा संभ्रम केला दूर</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-public-security-bill-opposition-shiv-sena-uddhav-sanjay-raut-ashish-shelar-attack-135430375.html</t>
+          <t>https://marathi.ndtv.com/maharashtra/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-ai-university-and-employment-shortage-9153869</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Ashish Shelar: "विभाग प्रमुखांनी 100 टक्के निधी..."; मंत्री आशीष शेलारांचे अधिकाऱ्यांना निर्देश</t>
+          <t>15 ऑगस्टच्या आधी सरदार रघुजी राजे भोसलेंची तलवार महाराष्ट्रात येणार, मंत्री शेलार</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai/minister-ashish-shelar-said-all-department-head-use-100-percent-fund-for-peoples-886116.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>जास्त गर्दीच्या मेट्रो स्थानकांचा आपत्कालीन प्लॅन तयार करा; आशिष शेलारांचे MMRDAला निर्देश</t>
+          <t>गणेशोत्सवाआधी मुंबईतील खड्ड्यांचं विघ्न दूर करा; पालकमंत्री आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/prepare-an-emergency-plan-for-overcrowded-metro-stations-ashish-shelar-directs-mmrda-a-a747/</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>गणेशोत्सव झाला महाराष्ट्र राज्य महोत्सव; सांस्कृतिक कार्यमंत्री आशिष शेलार यांची विधानसभेत घोषणा</t>
+          <t>Ashish Shelar : आता कसा झेंडा घेऊ हाती? शेलारांनी ठाकरे बंधूंना डिवचलं अन्…</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ganeshotsav-has-become-maharashtra-state-festival-cultural-affairs-minister-ashish-shelar-announced-in-the-legislative-assembly-a-a629/</t>
+          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Sanjay Raut : मनसे-शिवसेना युतीची चर्चा, शेलारांनी मैत्री संपवली, राऊतांचं मर्मावर बोट, मी आणि राज ठाकरे...</t>
+          <t>Ashish Shelar : बॉम्बे स्कॉटिशमध्ये शिकताना बॉम्बे नको मुंबई हे तुम्ही बोललात का? आशिष</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/sanjay-raut-talk-on-ashish-shelar-statement-about-friendship-with-raj-thackeray-news-in-marathi/articleshow/120507660.cms</t>
+          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meets Ashish Shelar: आशिष शेलारांची भेट घेत अमित ठाकरेंच्या विविध मागण्या मुंबईत आज</t>
+          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते 'लाडकी बहीण'चा मुहूर्त संपन्न!</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>भारतीय पुरातत्व विभागातील किल्ले देखभालीसाठी राज्याकडे द्या, मंत्री आशिष शेलार यांची केंद्राला विनंती</t>
+          <t>उबाठा सेना, राऊतांना तुकडे गँगची चिंता: भाजपच्या आशिष शेलार यांचा आरोप; महाराष्ट्र जनसुरक्षा विधेयकावरून सा...</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-public-security-bill-opposition-shiv-sena-uddhav-sanjay-raut-ashish-shelar-attack-135430375.html</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>“गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा”; आशिष शेलारांचे स्पष्ट निर्देश</t>
+          <t>Ashish Shelar: "विभाग प्रमुखांनी 100 टक्के निधी..."; मंत्री आशीष शेलारांचे अधिकाऱ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-minister-ashish-shelar-instruction-that-fill-all-the-potholes-on-mumbai-roads-completely-before-ganesh-chaturthi-2025-a-a719/</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/minister-ashish-shelar-said-all-department-head-use-100-percent-fund-for-peoples-886116.html</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar : 'गणेशोत्सवातील शाळा-कॉलेजच्या परीक्षा पुढे ढकला'; अमित ठाकरेंची मागणी</t>
+          <t>Ashish Shelar: आशिष शेलारांनी ठाकरे बंधूंच्या जखमेवर मीठ चोळलं, म्हणाले, बेस्ट पतपेढीच्या</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/mumbai/mumbai-amit-thackeray-meets-ashish-shelar-demands-ganesh-festival-exam-postponement/40235</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>मनोज जरांगेंच्या टोकदार भाषेवर मंत्री शेलार कडाडले; म्हणाले, 'मुंबईला या, बाप्पांचं दर्शन घ्या, पण...'</t>
+          <t>PoP Ganesh Idols | Ashish Shelar यांचा विरोधकांवर हल्लाबोल, मूर्तिकारांच्या पाठीशी BJP</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-reacts-over-manoj-jarange-patil-warns-mahayuti-government-due-to-maratha-reservation-as11</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>‘बीडीडी चाळीतील रहिवाशांना येत्या श्रावण महिन्याच्या आत मिळणार चाव्या’, आशिष शेलार यांचं आश्वासन</t>
+          <t>भारतीय पुरातत्व विभागातील किल्ले देखभालीसाठी राज्याकडे द्या, मंत्री आशिष शेलार यांची केंद्राला विनंती</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/residents-of-bdd-chawl-will-get-keys-within-the-coming-month-of-shravan-assures-ashish-shelar-a-a301/</t>
+          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Hindus in Pahalgam killed over religion, assaulted over language in Maha: Shelar | CM Fadnavis had also condemned the incident | Inshorts</t>
+          <t>गणेशोत्सव झाला महाराष्ट्र राज्य महोत्सव; सांस्कृतिक कार्यमंत्री आशिष शेलार यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://inshorts.com/en/news/hindus-in-pahalgam-killed-over-religion--over-language-in-maha--shelar-1751789540577</t>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-has-become-maharashtra-state-festival-cultural-affairs-minister-ashish-shelar-announced-in-the-legislative-assembly-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>अमित ठाकरेंची आशिष शेलारांसोबत बैठक; नेमकी काय चर्चा झाली? अमित ठाकरेंनी स्पष्टच सांगितलं</t>
+          <t>“गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा”; आशिष शेलारांचे स्पष्ट निर्देश</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/mns-chief-amit-thackeray-submits-memorandum-to-bjp-leader-ashish-shelar-political-news-bdk97</t>
+          <t>https://www.lokmat.com/mumbai/bjp-minister-ashish-shelar-instruction-that-fill-all-the-potholes-on-mumbai-roads-completely-before-ganesh-chaturthi-2025-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Ashish Shelar : दहावी, बारावीच्या निकालावर बैठक, संकेतस्थळ ‘क्रॅश’ होऊ नये : आशिष शेलार</t>
+          <t>Amit Thackeray Meets Ashish Shelar: आशिष शेलारांची भेट घेत अमित ठाकरेंच्या विविध मागण्या मुंबईत आज</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ashish-shelar-orders-increased-capacity-for-education-board-website-to-handle-exam-result-traffic-amp17</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>ॲड.आशिष शेलार यांच्या हस्ते मुंबई उपनगर जिल्हाधिकारी कार्यालयात ध्वजारोहण</t>
+          <t>‘बीडीडी चाळीतील रहिवाशांना येत्या श्रावण महिन्याच्या आत मिळणार चाव्या’, आशिष शेलार यांचं आश्वासन</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175532/</t>
+          <t>https://www.lokmat.com/mumbai/residents-of-bdd-chawl-will-get-keys-within-the-coming-month-of-shravan-assures-ashish-shelar-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>आशा भोसले, नात जनाई साई बाबांच्या दर्शनाला; मंत्री आशिष शेलार यांनीही घेतले शिर्डीतील समाधीचे दर्शन</t>
+          <t>पनवेल महानगरपालिकेच्या क्रिकेट प्रशिक्षण केंद्रातून गुणवत्ताधारक खेळाडू घडतील - मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
+          <t>https://mahasamvad.in/163660/</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार | Singer Manik Varma Autobiogrpahy Launched</t>
+          <t>अमित ठाकरेंची आशिष शेलारांसोबत बैठक; नेमकी काय चर्चा झाली? अमित ठाकरेंनी स्पष्टच सांगितलं</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/premier/advocate-ashish-shelar-praised-late-veteran-singer-manik-varma-on-book-launch-prorgram-of-her-autobiography-manik-moti-entertainment-news-kds07</t>
+          <t>https://saamtv.esakal.com/maharashtra/mns-chief-amit-thackeray-submits-memorandum-to-bjp-leader-ashish-shelar-political-news-bdk97</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील गणेशोत्सव राष्ट्रीय, आंतरराष्ट्रीय पातळीवर पोहचवणार, आशिष शेलार यांची घोषणा</t>
+          <t>मनोज जरांगेंच्या टोकदार भाषेवर मंत्री शेलार कडाडले; म्हणाले, 'मुंबईला या, बाप्पांचं दर्शन घ्या, पण...'</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/maharashtra-assembly-monsoon-session-2025-ashish-shelar-announces-that-maharashtras-ganeshotsav-will-be-taken-to-national-and-international-levels-a-a301/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-reacts-over-manoj-jarange-patil-warns-mahayuti-government-due-to-maratha-reservation-as11</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>गणेशोत्सव ‘राज्य महोत्सव’ म्हणून साजरा करणार शासनाची जोरदार तयारी ; मंत्री ॲड.आशिष शेलार यांची घोषणा</t>
+          <t>Ashish Shelar : दहावी, बारावीच्या निकालावर बैठक, संकेतस्थळ ‘क्रॅश’ होऊ नये : आशिष शेलार</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
+          <t>https://www.esakal.com/maharashtra/ashish-shelar-orders-increased-capacity-for-education-board-website-to-handle-exam-result-traffic-amp17</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Ashish Shelar: निवडणूक तोंडावर तरीही का बदलला मुंबई भाजप अध्यक्ष? आशिष शेलार यांनी सांगितली रणनीती</t>
+          <t>ॲड.आशिष शेलार यांच्या हस्ते मुंबई उपनगर जिल्हाधिकारी कार्यालयात ध्वजारोहण</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-changes-mumbai-president-ahead-of-elections-amit-satam-takes-charge-ashish-shelar-reveals-strategy-bbj88</t>
+          <t>https://mahasamvad.in/175532/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>राज ठाकरेंच्या मतचोरीच्या आरोपावर शेलारांचा हल्लाबोल: म्हणाले - अमितची मते सावंतांनी, देशपांडेंची मते आदित्...</t>
+          <t>आशा भोसले, नात जनाई साई बाबांच्या दर्शनाला; मंत्री आशिष शेलार यांनीही घेतले शिर्डीतील समाधीचे दर्शन</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/asish-shelar-criticizes-raj-uddhav-thackeray-best-election-135757049.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>मुंबईमधील चौकाला स्व. भापसे यांचे नाव दिल्याने झाला पाथर्डीचाही गौरव: मंत्री आशिष शेलार यांचे मत; माजी आ. स...</t>
+          <t>Amit Thackeray Meet Ashish Shelar : 'गणेशोत्सवातील शाळा-कॉलेजच्या परीक्षा पुढे ढकला'; अमित ठाकरेंची मागणी</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/pathardi-also-became-proud-by-naming-a-square-in-mumbai-after-the-late-baburao-bhapse-says-minister-ashish-shelar-former-mla-named-the-square-after-the-late-baburao-bhapse-135398508.html</t>
+          <t>https://www.jaimaharashtranews.com/mumbai/mumbai-amit-thackeray-meets-ashish-shelar-demands-ganesh-festival-exam-postponement/40235</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान उपक्रम केंद्र सुरू करणार, आशिष शेलार यांची घोषणा</t>
+          <t>सार्वजनिक गणेशोत्सव मंडळांसाठी आनंदवार्ता! मोठ्या गणेश मूर्तींच्या समुद्रात विसर्जनाचा मार्ग मोकळा होणार; मंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>ठाकरे बंधूंच्या प्रश्नावर आशा भोसलेंचं भुवया उंचावणारं विधान, मी कोणाला ओळखत नाही फक्त आशिष शेलारांना ओळखते</t>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार | Singer Manik Varma Autobiogrpahy Launched</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/asha-bhosle-statement-on-thackeray-brothers-coming-together-i-only-know-ashish-shelar-in-politics/918599</t>
+          <t>https://www.esakal.com/premier/advocate-ashish-shelar-praised-late-veteran-singer-manik-varma-on-book-launch-prorgram-of-her-autobiography-manik-moti-entertainment-news-kds07</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>एक पडदा सिनेमागृहाबाबत संयुक्त समिती करा – सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचे निर्देश</t>
+          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज, उद्या...</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174804/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>आपले सरकार सेवा केंद्रांची संख्या वाढविणे आणि सेवा दरवाढीबाबत माहिती तंत्रज्ञान मंत्री आशिष शेलार यांचे विधानसभेत निवेदन</t>
+          <t>महाराष्ट्रातील गणेशोत्सव राष्ट्रीय, आंतरराष्ट्रीय पातळीवर पोहचवणार, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160568/</t>
+          <t>https://www.lokmat.com/maharashtra/maharashtra-assembly-monsoon-session-2025-ashish-shelar-announces-that-maharashtras-ganeshotsav-will-be-taken-to-national-and-international-levels-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>सिनेमावर सेन्सॉर अथवा निर्बंध घालणार नाही: परिणय फुकेंच्या लक्षवेधी सूचनेवर सांस्कृतिक कार्य मंत्री आशिष शे...</t>
+          <t>गणेशोत्सव ‘राज्य महोत्सव’ म्हणून साजरा करणार शासनाची जोरदार तयारी ; मंत्री ॲड.आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/entertainment/marathi-cinema/news/maharashtra-film-policy-ashish-shelar-censorship-135409939.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Dahi Handi 2025: गोविंदांसाठी आनंदाची बातमी! यंदा दीड लाख गोविंदांना मिळणार विम्याचे कवच</t>
+          <t>Ashish Shelar: निवडणूक तोंडावर तरीही का बदलला मुंबई भाजप अध्यक्ष? आशिष शेलार यांनी सांगितली रणनीती</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-changes-mumbai-president-ahead-of-elections-amit-satam-takes-charge-ashish-shelar-reveals-strategy-bbj88</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ कान्स चित्रपट महोत्सवाच्या यादीतून बाहेर? चित्रपटातील ‘आक्षेपार्ह’ मजकुरावरून आशिष शेलार यांचे संकेत</t>
+          <t>मुंबईमधील चौकाला स्व. भापसे यांचे नाव दिल्याने झाला पाथर्डीचाही गौरव: मंत्री आशिष शेलार यांचे मत; माजी आ. स...</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/entertainment/khalid-ka-shivaji-excluded-from-cannes-film-festival-ashish-shelar-comments</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/pathardi-also-became-proud-by-naming-a-square-in-mumbai-after-the-late-baburao-bhapse-says-minister-ashish-shelar-former-mla-named-the-square-after-the-late-baburao-bhapse-135398508.html</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>ज्ञानेश्वर महाराजांचा जन्म सप्तशताब्दी सुवर्ण महोत्सव राज्यभर साजरा करणार: मंत्री आशिष शेलार यांची घोषणा, न...</t>
+          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान उपक्रम केंद्र सुरू करणार, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/the-golden-jubilee-of-the-birth-of-dnyaneshwar-maharaj-will-be-celebrated-across-the-state-minister-ashish-shelar-announced-mogra-phulla-program-will-be-held-during-narli-week-134770599.html</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Tuljabhavani Temple : धार्मिक भावना आणि परंपरेचा आदर करूनच तुळजाभवानी मंदिराचा जीर्णोद्धार; आशिष शेलारांची माहिती</t>
+          <t>राज ठाकरेंच्या मतचोरीच्या आरोपावर शेलारांचा हल्लाबोल: म्हणाले - अमितची मते सावंतांनी, देशपांडेंची मते आदित्...</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/asish-shelar-criticizes-raj-uddhav-thackeray-best-election-135757049.html</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Ashish Shelar: आनंदाची बातमी! चित्रीकरणासाठी नि:शुल्क परवानगी अन् चित्रपट निर्मिती स्थळांवर...; मंत्री आशिष शेलारांची मोठी घोषणा</t>
+          <t>आपले सरकार सेवा केंद्रांची संख्या वाढविणे आणि सेवा दरवाढीबाबत माहिती तंत्रज्ञान मंत्री आशिष शेलार यांचे विधानसभेत निवेदन</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/minister-ashish-shelar-announces-free-permission-for-filming-anywhere-in-mumbai-vru98</t>
+          <t>https://mahasamvad.in/160568/</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>हिंदूना मारत आहेत म्हणत मुंबईकर आशिष शेलारांची मनसैनिकांची थेट पहलगाम दहशतवाद्यांशी</t>
+          <t>ठाकरे बंधूंच्या प्रश्नावर आशा भोसलेंचं भुवया उंचावणारं विधान, मी कोणाला ओळखत नाही फक्त आशिष शेलारांना ओळखते</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/asha-bhosle-statement-on-thackeray-brothers-coming-together-i-only-know-ashish-shelar-in-politics/918599</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>रघुजी भोसले महाराजांची तलवार राज्य सरकारकडे; मंत्री शेलार यांनी लंडनच्या मध्यस्थाकडून घेतली ताब्यात</t>
+          <t>सिनेमावर सेन्सॉर अथवा निर्बंध घालणार नाही: परिणय फुकेंच्या लक्षवेधी सूचनेवर सांस्कृतिक कार्य मंत्री आशिष शे...</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/raghuji-bhosale-maharaj-sword-handover-to-maharashtra-government</t>
+          <t>https://divyamarathi.bhaskar.com/entertainment/marathi-cinema/news/maharashtra-film-policy-ashish-shelar-censorship-135409939.html</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>मंत्री आशिष शेलारांकडून नामदेव ढसाळ यांचा अवमान</t>
+          <t>ज्ञानेश्वर महाराजांचा जन्म सप्तशताब्दी सुवर्ण महोत्सव राज्यभर साजरा करणार: मंत्री आशिष शेलार यांची घोषणा, न...</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ashish-shelar-statement-on-namdev-dhasal</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/the-golden-jubilee-of-the-birth-of-dnyaneshwar-maharaj-will-be-celebrated-across-the-state-minister-ashish-shelar-announced-mogra-phulla-program-will-be-held-during-narli-week-134770599.html</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Mumbai : मराठी चित्रपट कट्टा सुरू, मंत्री आशिष शेलार यांच्या हस्ते लोकार्पण</t>
+          <t>‘खालिद का शिवाजी’ कान्स चित्रपट महोत्सवाच्या यादीतून बाहेर? चित्रपटातील ‘आक्षेपार्ह’ मजकुरावरून आशिष शेलार यांचे संकेत</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/mumbai/marathi-film-katta-was-launched-by-ashish-shelar/844408/</t>
+          <t>https://marathi.freepressjournal.in/entertainment/khalid-ka-shivaji-excluded-from-cannes-film-festival-ashish-shelar-comments</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Maharashtra Heritage News | कातळशिल्पांच्या वय निश्चितीसाठी तज्ज्ञांची समिती</t>
+          <t>Dahi Handi 2025: गोविंदांसाठी आनंदाची बातमी! यंदा दीड लाख गोविंदांना मिळणार विम्याचे कवच</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mumbai-rock-carvings-unesco-heritage-committee-ashish-shelar-maharashtra-archaeology-sp96</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Aaple Sarkar Seva Kendra: राज्यात 'आपले सरकार सेवा केंद्रां'ची संख्या वाढणार; आशिष शेलारांनी जाहीर केले 'हे' निकष</t>
+          <t>Tuljabhavani Temple : धार्मिक भावना आणि परंपरेचा आदर करूनच तुळजाभवानी मंदिराचा जीर्णोद्धार; आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/aple-sarkar-seva-kendra-center-increased-in-state-said-minister-ashish-shelar-825241.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>आपले सरकार सेवा केंद्रांची संख्या वाढवणार, 5000 पेक्षा कमी लोकसंख्येच्या गावात</t>
+          <t>Ashish Shelar: आनंदाची बातमी! चित्रीकरणासाठी नि:शुल्क परवानगी अन् चित्रपट निर्मिती स्थळांवर...; मंत्री आशिष शेलारांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-declare-aaple-sarkar-numbers-increased-in-maharashtra-and-also-rates-also-modified-marathi-news-1351214</t>
+          <t>https://www.esakal.com/mumbai/minister-ashish-shelar-announces-free-permission-for-filming-anywhere-in-mumbai-vru98</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Ashish Shelar : ठाकरेंच्या हाती सभेत दाखवण्यासाठी रुद्राक्षांची माळ, तोंडी औरंगजेबाचाच</t>
+          <t>रघुजी भोसले महाराजांची तलवार राज्य सरकारकडे; मंत्री शेलार यांनी लंडनच्या मध्यस्थाकडून घेतली ताब्यात</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-criticizes-uddhav-thackeray-wears-rudraksha-mala-to-his-rally-and-chants-aurangzeb-mantra-maharashtra-politics-marathi-news-1346679</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/raghuji-bhosale-maharaj-sword-handover-to-maharashtra-government</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>मुंबई उपनगर जिल्हाधिकारी कार्यालयात मंत्री ॲड.आशिष शेलार यांच्या हस्ते ध्वजारोहण; तिरंगा यात्रेचेही आयोजन</t>
+          <t>एक पडदा सिनेमागृहाबाबत संयुक्त समिती करा – सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
+          <t>https://mahasamvad.in/174804/</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Singer Asha Bhosle On Ashish Shelar: राज-उद्धव एकत्र येण्याबाबत प्रश्न, आशाताई म्हणाल्या, 'मला फक्त</t>
+          <t>हिंदूना मारत आहेत म्हणत मुंबईकर आशिष शेलारांची मनसैनिकांची थेट पहलगाम दहशतवाद्यांशी</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/singer-asha-bhosle-on-raj-thackrey-uddhav-thackrey-togater-she-says-i-only-know-ashish-shelar-i-don-t-know-any-other-politician-1366511</t>
+          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>नालेसफाईच्या पाहणीवेळी तुम्ही कुठे होता? आशिष शेलार यांचा आदित्य ठाकरे यांना सवाल</t>
+          <t>मंत्री आशिष शेलारांकडून नामदेव ढसाळ यांचा अवमान</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/where-were-you-during-the-inspection-of-drain-cleaning-ashish-shelar-questions-aditya-thackeray-a-a1001/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ashish-shelar-statement-on-namdev-dhasal</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Aditya Thackeray On Ashish Shelar And Nishikant Dubey: ठाकरे बंधूंवर भाजपकडून हल्लाबोल आदित्य ठाकरेंनी आशिष</t>
+          <t>Maharashtra Heritage News | कातळशिल्पांच्या वय निश्चितीसाठी तज्ज्ञांची समिती</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-rock-carvings-unesco-heritage-committee-ashish-shelar-maharashtra-archaeology-sp96</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Asha Bhosle News: आशा भोसले म्हणतात, “मला राजकारणातले फक्त आशिष शेलार माहिती आहेत”, ठाकरे बंधूंबाबतच्या प्रश्नावर दिलं उत्तर!</t>
+          <t>BJP Politics: भाजपची तिरपी चाल...;आशिष शेलारांना हटवून अमित साटम यांच्याकडे मुंबई शहर अध्यक्षपदाची सुत्रे</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/singer-asha-bhosle-reaction-on-raj-uddhav-thackeray-morcha-in-mumbai-pmw-88-5187805/</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/bjp-politics-amit-satam-appointed-as-mumbai-bjp-city-president-replacing-ashish-shelar-969778.html</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>छत्रपती शिवाजी महाराज यांच्या १२ गडकिल्ल्यांना नामांकन, जागतिक वारसा यादीत मिळणार स्थान; मंत्री आशिष शेलारांची माहिती</t>
+          <t>Aaple Sarkar Seva Kendra: राज्यात 'आपले सरकार सेवा केंद्रां'ची संख्या वाढणार; आशिष शेलारांनी जाहीर केले 'हे' निकष</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chhatrapati-shivaji-maharaj-fort-place-on-the-world-heritage-list-minister-ashish-shelar-said/articleshow/118510900.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/aple-sarkar-seva-kendra-center-increased-in-state-said-minister-ashish-shelar-825241.html</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>दरवर्षी २१ एप्रिल दरम्यान रंगणार आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची घोषणा!</t>
+          <t>'मुंबईतल्या सर्व लँड स्कॅमचे बादशाह उद्धव ठाकरे';आशिष शेलारांचा घणाघात</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
+          <t>https://www.jaimaharashtranews.com/latest-news/ashish-shelar-says-uddhav-thackeray-is-the-king-of-all-land-scams-in-mumbai-/35864</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Aasha Bhosle on Raj-Uddhav : राज-उद्धव युतीचा प्रश्न, आशाताई म्हणाल्या, मला फक्त आशिष शेलार माहिती</t>
+          <t>गणेशोत्सव - महाराष्ट्र राज्याचा महोत्सव!: मंत्री आशिष शेलार यांची घोषणा; गणेशोत्सवाच्या प्रचारासाठी सरकार क...</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-ganesh-festival-declared-maharashtra-state-festival-shelarnew-135414987.html</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Marathi Not Hindi: BJP Clarifies Language Policy in Maharashtra Schools</t>
+          <t>BJP on Raj Uddhav Alliance: ठाकरे बंधूंच्या एकत्र येण्याची पोस्ट अमित शाहांना टॅग केली, आशिष</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Mumbai Monsoon Mess: MVA Blames MahaYuti Govt, BJP Points to 25 Yrs of BMC Misrule</t>
+          <t>मुंबई उपनगर जिल्हाधिकारी कार्यालयात मंत्री ॲड.आशिष शेलार यांच्या हस्ते ध्वजारोहण; तिरंगा यात्रेचेही आयोजन</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Ganpati mandals get political colours ahead of civic polls</t>
+          <t>राज्य शासनातर्फे यंदा आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ganpati-mandals-and-the-politics-around-it-10211504/</t>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/marathi-film-festival-in-2025-ashish-shelar-announced-rajya-shasan-marathi-movie-nomination-a-a998/</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Live telecast of Ganeshotsav events: Minister | Mumbai News</t>
+          <t>Asha Bhosle News: आशा भोसले म्हणतात, “मला राजकारणातले फक्त आशिष शेलार माहिती आहेत”, ठाकरे बंधूंबाबतच्या प्रश्नावर दिलं उत्तर!</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/live-telecast-of-ganeshotsav-events-minister/articleshow/122770675.cms</t>
+          <t>https://www.loksatta.com/maharashtra/singer-asha-bhosle-reaction-on-raj-uddhav-thackeray-morcha-in-mumbai-pmw-88-5187805/</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
+          <t>दरवर्षी २१ एप्रिल दरम्यान रंगणार आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची घोषणा!</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Shiv Sena UBT exodus continues, BJP gains two more corporators</t>
+          <t>मध्यस्थ उभा केला न् लिलाव जिंकला; मराठा सरदार रघुजी भोसलेंची ऐतिहासिक तलवार सरकारच्या ताब्यात</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Maharashtra govt to grant ₹25,000 each to 1,800 bhajani mandals for Ganesh festival</t>
+          <t>Aasha Bhosle on Raj-Uddhav : राज-उद्धव युतीचा प्रश्न, आशाताई म्हणाल्या, मला फक्त आशिष शेलार माहिती</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-grant-25000-each-to-1800-bhajani-mandals-for-ganesh-festival/articleshow/123453964.cms</t>
+          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>‘Insult to people’s mandate’: Devendra Fadnavis slams Rahul Gandhi’s voter fraud allegations as ‘baseless’</t>
+          <t>Mumbai Monsoon Mess: MVA Blames MahaYuti Govt, BJP Points to 25 Yrs of BMC Misrule</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/devendra-fadnavis-slams-rahul-gandhi-voter-fraud-allegations-10177483/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Maharashtra BJP leader flays attack on Hindi-speaking people, cites Pahalgam parallel</t>
+          <t>Ganpati mandals get political colours ahead of civic polls</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-bjp-leader-attack-on-hindi-speaking-people-pahalgam-parallel-195564</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ganpati-mandals-and-the-politics-around-it-10211504/</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Maharashtra govt declares ‘Sarvajanik Ganeshotsav’ as state festival; says it will ‘bear expenses for grand celebrations’</t>
+          <t>Maharashtra parties try to woo Ganpati devotees with free travel | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-declares-sarvajanik-ganeshotsav-as-state-festival-10118535/</t>
+          <t>https://www.hindustantimes.com/india-news/maharashtra-parties-try-to-woo-ganpati-devotees-with-free-travel-101756094947074.html</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Major fire at mall in Mumbai's Bandra; firefighting on after 18 hours</t>
+          <t>Shiv Sena UBT exodus continues, BJP gains two more corporators</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Apr/29/major-fire-at-mall-in-mumbais-bandra-firefighting-on-after-18-hours</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Pune Declares 10-Day Dry Spell</t>
+          <t>243 roads dug up in H West ward, many utilities damaged | Mumbai news</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/243-roads-dug-up-in-h-west-ward-many-utilities-damaged-101738523195660.html</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Minister links Mira Road assault to Pahalgam attack</t>
+          <t>‘Insult to people’s mandate’: Devendra Fadnavis slams Rahul Gandhi’s voter fraud allegations as ‘baseless’</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
+          <t>https://indianexpress.com/article/cities/mumbai/devendra-fadnavis-slams-rahul-gandhi-voter-fraud-allegations-10177483/</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP's Ashish Shelar Slams Raj, Uddhav's Joint Rally as Misleading</t>
+          <t>Maharashtra govt to grant ₹25,000 each to 1,800 bhajani mandals for Ganesh festival</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-grant-25000-each-to-1800-bhajani-mandals-for-ganesh-festival/articleshow/123453964.cms</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Talk of Thackeray cousins reunion 'rattles' Eknath Shinde; BJP says 'wait and watch'</t>
+          <t>BJP's Nishikant Dubey dares Uddhav, Raj Thackeray to visit north India, Tamil Nadu | Reactions so far</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Apr/20/talk-of-thackeray-cousins-reunion-rattles-eknath-shinde-bjp-says-wait-and-watch</t>
+          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Ex-CJI Chandrachud’s call for inclusion spurs immediate government action</t>
+          <t>Maharashtra BJP leader flays attack on Hindi-speaking people, cites Pahalgam parallel</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/ex-cji-chandrachuds-call-for-inclusion-spurs-immediate-government-action/article69972187.ece</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-bjp-leader-attack-on-hindi-speaking-people-pahalgam-parallel-195564</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Thackeray Reunion Fallout: BJP Targets Uddhav, Spares Raj</t>
+          <t>Mumbai To Get Rid of Flood-Like Situations? New Plan Announced After 180 mm Rainfall Chaos</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Primary education should be in mother tongue, says RSS</t>
+          <t>Pune Declares 10-Day Dry Spell</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/primary-education-should-be-in-mother-tongue-says-rss/article69785053.ece</t>
+          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Desperate bid to control BMC &amp; loot Mumbai: BJP</t>
+          <t>MNS Chief Raj Thackeray Questions Maharashtra Poll Results, Raises Doubts Over Ajit Pawars Sudden Rise In</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mns-chief-raj-thackeray-questions-maharashtra-poll-results-raises-doubts-over-ajit-pawars-sudden-rise-in-assembly-elections</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>'India's Got Latent' row: Maharashtra government orders inquiry into Ranveer Allahbadia controversy | Latest News India - Hindustan Times</t>
+          <t>Mumbai BJP Leadership Shake-Up: Pravin Darekar And Amit Satam In Contention For City President Post Ahead Of</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-leadership-shake-up-pravin-darekar-and-amit-satam-in-contention-for-city-president-post-ahead-of-bmc-elections</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Khamenei says won't surrender, warns US of 'irreparable damage' if it intervenes - India Today</t>
+          <t>Mumbai: Sanjay Gandhi National Park To Introduce Leopard Safari For Visitors Soon, Says Ashish Shelar</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/world/video/khamenei-says-wont-surrender-warns-us-of-irreparable-damage-if-it-intervenes-2742623-2025-06-18</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-sanjay-gandhi-national-park-to-introduce-leopard-safari-for-visitors-soon-says-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>PM Modi-Trump meet among most successful bilateral talks, says US political expert - India Today</t>
+          <t>Dharavi Redevelopment Project: Not an Inch Of Land Given To Adani, Asserts Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/video/pm-modi-trump-meet-among-most-successful-bilateral-talks-us-political-expert-2687329-2025-03-01</t>
+          <t>https://www.freepressjournal.in/mumbai/dharavi-redevelopment-project-not-an-inch-of-land-given-to-adani-asserts-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Final decision on three-language formula after talks with stakeholders: Maharashtra CM Fadnavis</t>
+          <t>Maharashtra Politics: BJP's Ashish Shelar Slams Raj, Uddhav's Joint Rally as Misleading</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jun/24/final-decision-on-three-language-formula-after-talks-with-stakeholders-maharashtra-cm-fadnavis</t>
+          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Ranveer Allahbadia Controversy News Highlights: Ranveer Allahbadia's Mumbai flat found locked; cops summon him again</t>
+          <t>Talk of Thackeray cousins reunion 'rattles' Eknath Shinde; BJP says 'wait and watch'</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/ranveer-allahbadia-controversy-live-updates-youtuber-samay-raina-indias-got-mumbai-police-ashish-chanchlani-apoorva-11739266598623.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/20/talk-of-thackeray-cousins-reunion-rattles-eknath-shinde-bjp-says-wait-and-watch</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Kajol Gets Emotional While Receiving Late Raj Kapoor Life Gaurav Award: "Today I Feel..."</t>
+          <t>Ex-CJI Chandrachud’s call for inclusion spurs immediate government action</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/actress-kajol-received-maharashtra-state-film-award-which-was-held-in-mumbai-in-presence-of-cm-devedra-fadnavis</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/ex-cji-chandrachuds-call-for-inclusion-spurs-immediate-government-action/article69972187.ece</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Asaduddin Owaisi slams Pakistan's fakery with fake Chinese military drill photo - India Today</t>
+          <t>Desperate bid to control BMC &amp; loot Mumbai: BJP</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/video/asaduddin-owaisi-slams-pakistans-fakery-with-fake-chinese-military-drill-photo-2731277-2025-05-27</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>India Highlights News Updates: Government appoints former cabinet secretary Rajiv Gauba as full-time memb...</t>
+          <t>Thackeray Reunion Fallout: BJP Targets Uddhav, Spares Raj</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Maharashtra: NCP-SCP MLA Rohit Pawar hit back at BJP MP Nishikant Dubey for comparing opposition parties to terrorists</t>
+          <t>'Washing powder' formula again? Uddhav Thackeray asks, 'did the Pahalgam terrorists join BJP?’ amid Hindi</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452</t>
+          <t>https://timesofindia.indiatimes.com/india/washing-powder-formula-again-uddhav-thackeray-asks-did-the-pahalgam-terrorists-join-bjp-amid-hindi-vs-marathi-row/articleshow/122297598.cms</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>England New Captain CONFIRMED? ECB Director Rob Key Gives BOLD Statement For The Captaincy Hunt</t>
+          <t>'India's Got Latent' row: Maharashtra government orders inquiry into Ranveer Allahbadia controversy | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>https://news24online.com/sports/england-new-captain-confirmed-ecb-director-rob-key-gives-bold-statement-for-the-captaincy-hunt/496413/</t>
+          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Maharashtra CM Fadnavis Mocks Uddhav’s Rally Speech As Rudali, BJP Hits Out At Thackeray Cousins Over</t>
+          <t>Video: PM pauses Delhi victory speech to check on unwell BJP worker in audience - India Today</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-cm-fadnavis-mocks-uddhavs-rally-speech-as-rudali-bjp-hits-out-at-thackeray-cousins-over-political-reunion</t>
+          <t>https://www.indiatoday.in/elections/assembly/video/video-pm-pauses-delhi-victory-speech-to-check-on-unwell-bjp-worker-in-audience-2676959-2025-02-08</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>MNS Chief Raj Thackeray Questions Maharashtra Poll Results, Raises Doubts Over Ajit Pawars Sudden Rise In</t>
+          <t>Final decision on three-language formula after talks with stakeholders: Maharashtra CM Fadnavis</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mns-chief-raj-thackeray-questions-maharashtra-poll-results-raises-doubts-over-ajit-pawars-sudden-rise-in-assembly-elections</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jun/24/final-decision-on-three-language-formula-after-talks-with-stakeholders-maharashtra-cm-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>मुंबई बीजेपी को मिला नया अध्यक्ष, अमीत साटम के सामने बीएमसी है चुनौती</t>
+          <t>Ranveer Allahbadia Controversy News Highlights: Ranveer Allahbadia's Mumbai flat found locked; cops summon him again</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/mumbai-bjp-new-president-appointed-three-time-mla-ameet-satam-bmc-elections-big-challenge/4109409/</t>
+          <t>https://www.livemint.com/news/ranveer-allahbadia-controversy-live-updates-youtuber-samay-raina-indias-got-mumbai-police-ashish-chanchlani-apoorva-11739266598623.html</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>बीजेपी ने तैनात की नई 'मिसाइल': तीन बार MLA रहे अमित साटम को बनाया मुंबई भाजपा का अध्यक्ष</t>
+          <t>PM Modi to speak in Lok Sabha tomorrow at 5 pm - India Today</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/hi/!bharat/ahead-of-bmc-polls-mla-ameet-satam-named-new-mumbai-bjp-chief-hindi-news-hin25082501591</t>
+          <t>https://www.indiatoday.in/india/video/pm-modi-to-speak-in-lok-sabha-tomorrow-at-5-pm-2673866-2025-02-03</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>महाराष्ट्र विधानसभा परिसर में भिड़े विधायक जितेंद्र आव्हाड और गोपीचंद पडलकर के समर्थक, गाड़ी टच होने पर हुआ था विवाद</t>
+          <t>Kajol Gets Emotional While Receiving Late Raj Kapoor Life Gaurav Award: "Today I Feel..."</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/a-scuffle-broke-out-between-bjp-mla-gopichand-padalkar-and-ncp-jitendra-awhad-ntc-rpti-2289942-2025-07-17</t>
+          <t>https://english.lokshahi.com/latest-news/actress-kajol-received-maharashtra-state-film-award-which-was-held-in-mumbai-in-presence-of-cm-devedra-fadnavis</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>देश संक्षेप: गणेशोत्सव महाराष्ट्र का राज्य उत्सव घोषित</t>
+          <t>India Highlights News Updates: Government appoints former cabinet secretary Rajiv Gauba as full-time memb...</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/ncr/new-delhi/story-maharashtra-officially-declares-ganeshotsav-as-state-festival-cultural-heritage-emphasized-201752157149955.html</t>
+          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Ganeshotsav now Maharashtra State Festival: गणेशोत्सव बना महाराष्ट्र का राजकीय त्योहार, अब होगा राज्योत्सव</t>
+          <t>Asaduddin Owaisi slams Pakistan's fakery with fake Chinese military drill photo - India Today</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/maharashtra-declares-ganeshotsav-as-state-festival-hindi/</t>
+          <t>https://www.indiatoday.in/india/video/asaduddin-owaisi-slams-pakistans-fakery-with-fake-chinese-military-drill-photo-2731277-2025-05-27</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>फडणवीस सरकार का बड़ा फैसला, गणेशोत्सव को घोषित किया महाराष्ट्र का 'राज्य महोत्सव'</t>
+          <t>Maharashtra: NCP-SCP MLA Rohit Pawar hit back at BJP MP Nishikant Dubey for comparing opposition parties to terrorists</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/devendra-fadnavis-govt-declare-ganesh-festival-as-maharashtra-state-festival-2025-07-10-1148320</t>
+          <t>https://aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452/</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>मुंबई में विधायक अमीत साटम संभालेंगे बीजेपी की कमान, देवेंद्र फडणवीस ने नए अध्यक्ष के तौर पर नाम का किया ऐलान</t>
+          <t>England New Captain CONFIRMED? ECB Director Rob Key Gives BOLD Statement For The Captaincy Hunt</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-andheri-west-mla-ameet-satam-appointed-mumbai-bjp-chief-ahead-of-bmc-polls-know-all/articleshow/123499476.cms</t>
+          <t>https://news24online.com/sports/england-new-captain-confirmed-ecb-director-rob-key-gives-bold-statement-for-the-captaincy-hunt/496413/</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>‘गणपति उत्सव’ बना महाराष्ट्र का राज्य उत्सव, कार्यक्रम का खर्च उठाएगी फडणवीस सरकार</t>
+          <t>Maharashtra CM Fadnavis Mocks Uddhav’s Rally Speech As Rudali, BJP Hits Out At Thackeray Cousins Over</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/ganpati-festival-becomes-maharashtra-state-festival-fadnavis-government-will-bear-expenses-of-program/4040819/</t>
-        </is>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>Ganeshotsav 2025: गणेशोत्सव में भाग लेगी महाराष्ट्र सरकार, राज्य उत्सव मनाने के लिए किया गया ये ऐलान</t>
-        </is>
-      </c>
-      <c r="B615" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-devendra-fadnavis-govt-also-participates-in-ganeshotsav-2025-made-a-big-announcement/articleshow/122785708.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
-        </is>
-      </c>
-      <c r="B616" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>सावरकर के गीत 'अनादि मैं, अनंत मैं' को प्रेरणा गीत का पुरस्कार, महाराष्ट्र सरकार का बड़ा ऐलान</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/savarkar-song-anadi-me-anant-me-gets-inspirational-song-award-maharashtra-government-makes-a-big-announcement-ntc-dskc-2176549-2025-02-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>निकाय चुनाव से पहले आशीष शेलार की हुई छुट्टी, अमित साटम को मिली मुंबई बीजेपी की कमान</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
-        <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-removed-post-before-civic-elections-amit-satam-given-command-mumbai-bjp-1329777.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>मनपा चुनाव से पहले बीजेपी का मास्टरस्ट्रोक, अमित साटम बने मुंबई अध्यक्ष</t>
-        </is>
-      </c>
-      <c r="B619" t="inlineStr">
-        <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bjp-masterstroke-before-municipal-elections-amit-satam-becomes-mumbai-president-1330683.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>मुंबई भाजपा अध्यक्ष की हुई नियुक्ति, भगवा दल ने इस चेहरे पर जताया भरोसा; कितनी बड़ी जिम्मेदारी</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t>https://mpbreakingnews.in/national/mla-ameet-satnam-named-mumbai-bjp-chief-ahead-of-civic-body-polls-big-decesion-55-807941</t>
-        </is>
-      </c>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>महाराष्ट्र सरकार ने गणेशोत्सव को राज्य उत्सव घोषित किया |</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
-        <is>
-          <t>https://hindicurrentaffairs.adda247.com/maharashtra-government-declares-ganeshotsav-as-state-festival/</t>
-        </is>
-      </c>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>'राहुल गांधी के दिमाग की चिप चोरी और हार्ड डिस्क करप्ट हो गई', EC पर वोट चोरी के आरोपों पर बोले सीएम फडणवीस</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>https://lalluram.com/rahul-gandhis-brain-chip-stolen-and-hard-disk-corrupted/</t>
-        </is>
-      </c>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>Mumbai: मुंबई भाजपा अध्यक्ष के तौर पर अमित साटम का चयन</t>
-        </is>
-      </c>
-      <c r="B623" t="inlineStr">
-        <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-amit-satam-selected-as-mumbai-bjp-president-mumbai--4230449</t>
-        </is>
-      </c>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>Maharashtra में गणेशोत्सव को मिला ‘राज्य महोत्सव’ का दर्जा… फडणवीस सरकार का बड़ा फैसला</t>
-        </is>
-      </c>
-      <c r="B624" t="inlineStr">
-        <is>
-          <t>https://dainiksaveratimes.com/big-1/ganeshotsav-gets-status-state-festival-in-maharashtra-fadnavis-government/</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>Ganeshotsav 2025: महाराष्ट्र का 'राज्य उत्सव' बना गणेशोत्सव, अब सरकार उठाएगी जश्न का पूरा खर्च</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>https://hindi.latestly.com/lifestyle/festivals-events/ganeshotsav-now-maharashtras-official-state-festival-govt-to-fund-celebrations-2689983.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>जय शाह की जगह देवजीत सैकिया बने BCCI सचिव, प्रभतेज सिंह भाटिया कोषाध्यक्ष नियुक्त</t>
-        </is>
-      </c>
-      <c r="B626" t="inlineStr">
-        <is>
-          <t>https://bharat24live.com/news/devajit-saikia-replaces-jay-shah-as-bcci-secretary</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
-        </is>
-      </c>
-      <c r="B627" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-cm-fadnavis-mocks-uddhavs-rally-speech-as-rudali-bjp-hits-out-at-thackeray-cousins-over-political-reunion</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B614"/>
+  <dimension ref="A1:B653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,36 +467,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar</t>
+          <t>BCCI Vice-President Rajeev Shukla, Former Treasurer Ashish Shelar To Represent India In Asian Cricke..</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
+          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCCI Vice-President Rajeev Shukla, Former Treasurer Ashish Shelar To Represent India In Asian Cricke..</t>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://sports.ndtv.com/cricket/bcci-vice-president-rajeev-shukla-former-treasurer-ashish-shelar-to-represent-india-in-asian-cricket-council-7871715</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
@@ -587,36 +587,36 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Air safety: As bird hits rise, Maharashtra minister Ashish Shelar chairs high level meeting to find soluti</t>
+          <t>"What's The Difference?" BJP Leader's Religion-Language Remark Amid Slapgate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
+          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>"What's The Difference?" BJP Leader's Religion-Language Remark Amid Slapgate</t>
+          <t>Shiv Sena (UBT)’s condition in Mumbai is dangerous and dilapidated, says BJP MLA Ashish Shelar; welcomes</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/bjp-leader-ashish-shelar-compares-marathi-slapgate-with-pahalgam-terror-attack-8832513</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT)’s condition in Mumbai is dangerous and dilapidated, says BJP MLA Ashish Shelar; welcomes</t>
+          <t>Air safety: As bird hits rise, Maharashtra minister Ashish Shelar chairs high level meeting to find soluti</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shiv-sena-ubts-condition-in-mumbai-is-dangerous-and-dilapidated-says-bjp-mla-ashish-shelar-welcomes-former-corporators-who-join-party-ahead-of-bmc-polls/articleshow/122007760.cms</t>
+          <t>https://m.economictimes.com/industry/transportation/airlines-/-aviation/air-safety-as-bird-hits-rise-maharashtra-minister-ashish-shelar-chairs-high-level-meeting-to-find-solutions/articleshow/122090829.cms</t>
         </is>
       </c>
     </row>
@@ -647,24 +647,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>POP idol ban lifted: Will continue to raise issues while upholding devotion, sustainability, says Ashish Shelar</t>
+          <t>Minister Ashish Shelar slams BJP MP over remarks against Marathi people</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/pop-idol-ban-lifted-will-continue-to-raise-issues-while-upholding-devotion-sustainability-says-ashish-shelar-10057291/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/ashish-shelar-slams-bjp-mp-marathi-10112152/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Minister Ashish Shelar slams BJP MP over remarks against Marathi people</t>
+          <t>POP idol ban lifted: Will continue to raise issues while upholding devotion, sustainability, says Ashish Shelar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/ashish-shelar-slams-bjp-mp-marathi-10112152/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/pop-idol-ban-lifted-will-continue-to-raise-issues-while-upholding-devotion-sustainability-says-ashish-shelar-10057291/</t>
         </is>
       </c>
     </row>
@@ -683,132 +683,132 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>No need to question capabilities of Marathi speakers: BJP minister Ashish Shelar after Nishikant Dubey remarks</t>
+          <t>Mahayuti, BJP disown Jharkhand MP remarks on Marathi manoos</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Loudspeakers may be used till midnight on 7 days: Ashish Shelar</t>
+          <t>Mumbai: Play Marathi devotional songs on private radio stations, says Ashish Shelar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Shelar likens attacks on non-Marathi speakers in Mumbai to Pahalgam attack</t>
+          <t>No need to question capabilities of Marathi speakers: BJP minister Ashish Shelar after Nishikant Dubey remarks</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-attack-non-marathi-speakers-mumbai-pahalgam-massacre-10109991/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/no-need-to-question-capabilities-of-marathi-speakers-bjp-minister-ashish-shelar-after-nishikant-dubey-remarks-23583611</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Shelar-led delegation off to Paris to obtain UNESCO heritage status for 12 forts of Shivaji</t>
+          <t>Shelar likens attacks on non-Marathi speakers in Mumbai to Pahalgam attack</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/shelar-led-delegation-off-to-paris-to-obtain-unesco-heritage-status-for-12-forts-of-shivaji/article69255530.ece</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ashish-shelar-attack-non-marathi-speakers-mumbai-pahalgam-massacre-10109991/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>"Hindi Not Compulsory": Maharashtra Minister Amid Language Row</t>
+          <t>Loudspeakers may be used till midnight on 7 days: Ashish Shelar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/loudspeakers-may-be-used-till-midnight-on-7-days-ashish-shelar/articleshow/123418400.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mahayuti, BJP disown Jharkhand MP remarks on Marathi manoos</t>
+          <t>Shelar-led delegation off to Paris to obtain UNESCO heritage status for 12 forts of Shivaji</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/mahayuti-bjp-disown-jharkhand-mp-remarks-on-marathi-manoos-101751916221541.html</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/shelar-led-delegation-off-to-paris-to-obtain-unesco-heritage-status-for-12-forts-of-shivaji/article69255530.ece</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Have urged Netflix to provide space for Marathi content on platform: Shelar</t>
+          <t>"Hindi Not Compulsory": Maharashtra Minister Amid Language Row</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
+          <t>https://www.ndtv.com/india-news/hindi-not-compulsory-maharashtra-minister-amid-language-row-8742058</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mumbai: Play Marathi devotional songs on private radio stations, says Ashish Shelar</t>
+          <t>Have urged Netflix to provide space for Marathi content on platform: Shelar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-play-marathi-devotional-songs-on-private-radio-stations-says-ashish-shelar-23548694</t>
+          <t>https://www.msn.com/en-in/news/techandscience/have-urged-netflix-to-provide-space-for-marathi-content-on-platform-shelar/ar-AA1JJjMy</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>New Roles For Rajeev Shukla, Ashish Shelar In Asian Cricket Council As BCCI Expands Its Influence</t>
+          <t>Over 50 Marathi schools in US to get support from Maharashtra government</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
+          <t>https://www.indiatoday.in/education-today/news/story/over-50-marathi-schools-in-us-to-get-support-from-maharashtra-government-2761714-2025-07-26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BJP's Ashish Shelar dismisses Thackeray rally as political gimmick on Marathi language</t>
+          <t>New Roles For Rajeev Shukla, Ashish Shelar In Asian Cricket Council As BCCI Expands Its Influence</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
+          <t>https://www.republicworld.com/sports/cricket/new-roles-for-rajeev-shukla-ashish-shelar-in-asian-cricket-council-as-bcci-expands-its-influence</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror</t>
+          <t>BJP's Ashish Shelar dismisses Thackeray rally as political gimmick on Marathi language</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-minister-bjp-leader-ashish-shelar-compares-attacks-hindi-speakers-pahalgam-terror-2751745-2025-07-07</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bjps-ashish-shelar-dismisses-thackeray-rally-as-political-gimmick-on-marathi-language-23583412</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Over 50 Marathi schools in US to get support from Maharashtra government</t>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/over-50-marathi-schools-in-us-to-get-support-from-maharashtra-government-2761714-2025-07-26</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-minister-bjp-leader-ashish-shelar-compares-attacks-hindi-speakers-pahalgam-terror-2751745-2025-07-07</t>
         </is>
       </c>
     </row>
@@ -863,216 +863,216 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Inquiry must be conducted in rat extermination drive: Ashish Shelar</t>
+          <t>'Even a dog becomes a lion in its own house': Marathi row spills beyond Maharashtra; BJP minister Ashish</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maharashtra govt will not impose censorship on films: Ashish Shelar</t>
+          <t>Inquiry must be conducted in rat extermination drive: Ashish Shelar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-will-not-impose-censorship-on-films-ashish-shelar-10116698/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/inquiry-must-be-conducted-in-rat-extermination-drive-ashish-shelar-101750878303200.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Maharashtra govt to develop cyber security policy, IT minister Ashish Shelar announces taskforce</t>
+          <t>Maharashtra govt will not impose censorship on films: Ashish Shelar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-cyber-security-policy-it-minister-ashish-shelar-9784459/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-will-not-impose-censorship-on-films-ashish-shelar-10116698/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCCI Names Rajeev Shukla, Ashish Shelar As Representatives For ACC Board</t>
+          <t>Maharashtra govt to develop cyber security policy, IT minister Ashish Shelar announces taskforce</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-cyber-security-policy-it-minister-ashish-shelar-9784459/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ashish Shelar Reviews Mumbai Covid-19 Preparedness Amid New Case Spike</t>
+          <t>BCCI Names Rajeev Shukla, Ashish Shelar As Representatives For ACC Board</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
+          <t>https://www.bwmarketingworld.com/article/bcci-names-rajeev-shukla-ashish-shelar-as-representatives-for-acc-board-550285</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashish Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
+          <t>Ashish Shelar Reviews Mumbai Covid-19 Preparedness Amid New Case Spike</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-minister-ashish-shelar-chairs-meeting-to-discuss-covid-19-situation-3568037</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>How was ‘Khalid Ka Shivaji’ sent to Cannes Film Festival, asks Maharashtra cultural minister Shelar</t>
+          <t>Ashish Shelar slams Thackeray brothers joint rally as ‘Vague and Politically Motivated'</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
+          <t>https://daijiworld.com/news/newsDisplay?newsID=1285504</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>'Even a dog becomes a lion in its own house': Marathi row spills beyond Maharashtra; BJP minister Ashish</t>
+          <t>Ahead of BMC polls, BJP asks review reports from party members | Mumbai news</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-mps-enter-bihar-up-dare-to-thackerays-triggers-row/articleshow/122304841.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/ahead-of-bmc-polls-bjp-asks-review-reports-from-party-members-101751138056408.html</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ashish Shelar slams Thackeray brothers joint rally as ‘Vague and Politically Motivated'</t>
+          <t>Attacks on Hindi-speaking people: BJP leader draws Pahalgam parallel to target Thackeray cousins</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://daijiworld.com/news/newsDisplay?newsID=1285504</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/attacks-on-hindi-speaking-people-bjp-leader-draws-pahalgam-parallel-to-target-thackeray-cousins/article69782349.ece</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ahead of BMC polls, BJP asks review reports from party members | Mumbai news</t>
+          <t>Leopard safari to begin soon at Sanjay Gandhi National Park: Ashish Shelar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/ahead-of-bmc-polls-bjp-asks-review-reports-from-party-members-101751138056408.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-ashish-shelar-9810427/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Attacks on Hindi-speaking people: BJP leader draws Pahalgam parallel to target Thackeray cousins</t>
+          <t>Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/attacks-on-hindi-speaking-people-bjp-leader-draws-pahalgam-parallel-to-target-thackeray-cousins/article69782349.ece</t>
+          <t>http://www.msn.com/en-in/news/India/shelar-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra/ar-AA1L1WDR?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Leopard safari to begin soon at Sanjay Gandhi National Park: Ashish Shelar</t>
+          <t>Asha Bhosle's Cryptic Comment Add Twist to Thackeray Reunion Speculation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/leopard-safari-to-begin-soon-at-sanjay-gandhi-national-park-ashish-shelar-9810427/</t>
+          <t>https://english.lokshahi.com/top-stories/asha-bhosles-cryptic-comment-add-twist-to-thackeray-reunion-speculation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maharashtra minister's shocker! BJP's Ashish Shelar compares MNS assault over language with Pahalgam terror attack</t>
+          <t>No land in Dharavi has been given to Adani, Ashish Shelar</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/india/maharashtra-ministers-shocker-bjps-ashish-shelar-compares-mns-assault-over-language-with-pahalgam-terror-attack-11751802600494.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/no-land-in-dharavi-has-been-given-to-adani-ashish-shelar-9899366/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Asha Bhosle's Cryptic Comment Add Twist to Thackeray Reunion Speculation</t>
+          <t>Complete all dug up roads in Mumbai by May 31: Ashish Shelar to BMC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/top-stories/asha-bhosles-cryptic-comment-add-twist-to-thackeray-reunion-speculation</t>
+          <t>https://indianexpress.com/article/cities/mumbai/shelar-directs-bmc-to-stop-road-concretisation-works-from-today-10016418/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>No land in Dharavi has been given to Adani, Ashish Shelar</t>
+          <t>Ashish Shelar urges all departments to amplify Ganeshotsav celebrations in Maharashtra</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/no-land-in-dharavi-has-been-given-to-adani-ashish-shelar-9899366/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-chaturthi-2025-maharashtra-minister-ashish-shelar-directs-officials-to-scale-up-festivities-23590689</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Complete all dug up roads in Mumbai by May 31: Ashish Shelar to BMC</t>
+          <t>AI audit found irregularities in drain cleaning works in Mumbai: Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/shelar-directs-bmc-to-stop-road-concretisation-works-from-today-10016418/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI audit found irregularities in drain cleaning works in Mumbai: Maharashtra Minister Ashish Shelar</t>
+          <t>Marathi Cinema At Cannes Film Festival: 4 Movies Selected, Confirms Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-monsoon-ai-audit-found-irregularities-in-drain-cleaning-works-in-mumbai-says-maharashtra-minister-ashish-shelar-23538866</t>
+          <t>https://www.timesnownews.com/entertainment-news/bollywood/marathi-cinema-at-cannes-film-festival-4-movies-selected-confirms-maharashtra-minister-ashish-shelar-article-151459918</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marathi Cinema At Cannes Film Festival: 4 Movies Selected, Confirms Maharashtra Minister Ashish Shelar</t>
+          <t>Maharashtra minister's shocker! BJP's Ashish Shelar compares MNS assault over language with Pahalgam terror attack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/entertainment-news/bollywood/marathi-cinema-at-cannes-film-festival-4-movies-selected-confirms-maharashtra-minister-ashish-shelar-article-151459918</t>
+          <t>https://www.livemint.com/news/india/maharashtra-ministers-shocker-bjps-ashish-shelar-compares-mns-assault-over-language-with-pahalgam-terror-attack-11751802600494.html</t>
         </is>
       </c>
     </row>
@@ -1115,24 +1115,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Maharashtra Cultural Affairs Ministry to probe obscenity plaints against entertainment programmes</t>
+          <t>Ashish Shelar lauds Pune’s startup culture</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra-cultural-affairs-ministry-to-probe-obscenity-plaints-against-entertainment-programmes/article69220801.ece</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ashish Shelar lauds Pune’s startup culture</t>
+          <t>Maharashtra Cultural Affairs Ministry to probe obscenity plaints against entertainment programmes</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/ashish-shelar-lauds-punes-startup-culture/articleshow/120174945.cms</t>
+          <t>https://www.thehindu.com/news/national/maharashtra-cultural-affairs-ministry-to-probe-obscenity-plaints-against-entertainment-programmes/article69220801.ece</t>
         </is>
       </c>
     </row>
@@ -1151,996 +1151,996 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>State’s AI policy to be released in April: Shelar</t>
+          <t>BJP’s Ashish Shelar Likens MNS' Marathi Assaults To Pahalgam Attack: ‘What’s The Difference?'</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
+          <t>https://www.news18.com/politics/ashish-shelar-compares-mns-assault-over-marathi-with-pahalgam-attack-whats-the-difference-9424380.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BJP’s Ashish Shelar Likens MNS' Marathi Assaults To Pahalgam Attack: ‘What’s The Difference?'</t>
+          <t>Rajeev Shukla, Ashish Shelar named BCCI’s representatives on ACC board</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/ashish-shelar-compares-mns-assault-over-marathi-with-pahalgam-attack-whats-the-difference-9424380.html</t>
+          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sinhagad Fort Restoration Plan: Development Meeting Scheduled Within 15 Days</t>
+          <t>Ashish Shelar Slams Shiv Sena (UBT) Faction for "Fake Drama" and Political Theatrics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.thebridgechronicle.com/news/sinhagad-fort-restoration-plan-development-meeting-scheduled-within-15-days</t>
+          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shelar named BCCI’s representatives on ACC board</t>
+          <t>Sinhagad Fort Restoration Plan: Development Meeting Scheduled Within 15 Days</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/sports/cricket/rajeev-shukla-ashish-shelar-named-bcci-s-representatives-on-acc-board-2025-03-07-979613</t>
+          <t>https://www.thebridgechronicle.com/news/sinhagad-fort-restoration-plan-development-meeting-scheduled-within-15-days</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ashish Shelar Slams Shiv Sena (UBT) Faction for "Fake Drama" and Political Theatrics</t>
+          <t>Raghuji Bhonsale’s legendary sword set to arrive in Mumbai tomorrow, ‘darshan’ ceremony to be held at PL Deshpande Maharashtra Kala Academy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://punemirror.com/politics/ashish-shelar-slams-shiv-sena-ubt-faction-for-fake-drama-and-political-theatrics/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/raghuji-bhonsales-legendary-sword-mumbai-10194874/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BJP pans UBT over Deonar dump remarks</t>
+          <t>Maharashtra: BJP's Shelar Condemns Attacks on Hindi Speakers, Cites Pahalgam Parallel</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP's Shelar Condemns Attacks on Hindi Speakers, Cites Pahalgam Parallel</t>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-3617851</t>
+          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+          <t>BJP pans UBT over Deonar dump remarks</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/news/national/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar-982160</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-pans-ubt-over-deonar-dump-remarks/articleshow/121193802.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marathi Not Hindi: BJP Clarifies Language Policy in Maharashtra Schools</t>
+          <t>State’s AI policy to be released in April: Shelar</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/states-ai-policy-to-be-released-in-april-shelar/articleshow/119268347.cms</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Days after Raj met CM Fadnavis, his son meets Shelar; sets tongues wagging</t>
+          <t>Marathi Not Hindi: BJP Clarifies Language Policy in Maharashtra Schools</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/days-after-raj-met-cm-fadnavis-his-son-meets-shelar-sets-tongues-wagging-10207422/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-clarifies-bjp-minister-shelar-3599253</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mumbai: MNS protests alleged ill-treatment to Marathi speakers over non-veg food; Ashish Shelar issues warning</t>
+          <t>Days after Raj met CM Fadnavis, his son meets Shelar; sets tongues wagging</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
+          <t>https://indianexpress.com/article/cities/mumbai/days-after-raj-met-cm-fadnavis-his-son-meets-shelar-sets-tongues-wagging-10207422/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Shelar-led delegation in Paris to secure UNESCO Heritage status for 12 Shivaji forts</t>
+          <t>Culture minister Ashish Shelar seeks MoU between state archives of Maharashtra and Gujarat</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tech experts will study use of PoP in Ganesh idols: Minister Ashish Shelar</t>
+          <t>Mumbai: MNS protests alleged ill-treatment to Marathi speakers over non-veg food; Ashish Shelar issues warning</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-mns-protests-alleged-ill-treatment-to-marathi-speakers-over-non-veg-food-ashish-shelar-issues-warning-23522029</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maharashtra govt to support Marathi schools in US with official curriculum</t>
+          <t>Shelar-led delegation in Paris to secure UNESCO Heritage status for 12 Shivaji forts</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelarled-delegation-in-paris-to-secure-unesco-heritage-status-for-12-shivaji-forts-101740338138681.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>'Sarvajanik Ganehotsav' announced as ‘State Festival of Maharashtra', confirms Ashish Shelar</t>
+          <t>Maharashtra govt to support Marathi schools in US with official curriculum</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/sarvajanik-ganehotsav-announced-as-state-festival-of-maharashtra-confirms-ashish-shelar-11752164479346.html</t>
+          <t>https://www.indiatvnews.com/education/news/maharashtra-govt-to-support-marathi-schools-in-us-with-official-curriculum-2025-07-25-1000528</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Highlight power of Operation Sindoor during Ganeshotsav: Ashish Shelar tells organisers</t>
+          <t>Tech experts will study use of PoP in Ganesh idols: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/tech-experts-will-study-use-of-pop-in-ganesh-idols-minister/articleshow/118901970.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Maharashtra to unveil AI policy by April; Ashish Shelar warns against over-reliance</t>
+          <t>'Sarvajanik Ganehotsav' announced as ‘State Festival of Maharashtra', confirms Ashish Shelar</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
+          <t>https://www.livemint.com/news/sarvajanik-ganehotsav-announced-as-state-festival-of-maharashtra-confirms-ashish-shelar-11752164479346.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maharashtra minister addresses AI concerns, assures policy will complement, not replace, education</t>
+          <t>Highlight power of Operation Sindoor during Ganeshotsav: Ashish Shelar tells organisers</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/highlight-power-of-operation-sindoor-during-ganeshotsav-ashish-shelar-tells-organisers-23590466</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maharashtra govt to set up research centre for experimental arts in Mumbai, name it after Shahir Sable: M</t>
+          <t>Maharashtra to unveil AI policy by April; Ashish Shelar warns against over-reliance</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-unveil-ai-policy-by-april-ashish-shelar-warns-against-over-reliance-23503365</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>'Where did Pahalgam attackers go?': Aaditya Thackeray's 'poison' reply to Maharashtra minister's remark amid Marathi row | Latest News India - Hindustan Times</t>
+          <t>Maharashtra govt to set up research centre for experimental arts in Mumbai, name it after Shahir Sable: M</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-set-up-research-centre-for-experimental-arts-in-mumbai-name-it-after-shahir-sable-minister-ashish-shelar/articleshow/121957407.cms</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Allahbadia remarks: Maharashtra minister Ashish Shelar asks cultural affairs department to probe obscene programmes</t>
+          <t>Mumbai BJP unit likely to get new president ahead of BMC polls</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
+          <t>https://indianexpress.com/article/cities/mumbai/mumbai-bjp-unit-new-president-bmc-polls-10165826/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Renovated Ravindra Natya Mandir in Mumbai to be reopened on February 28: Ashish Shelar</t>
+          <t>'Where did Pahalgam attackers go?': Aaditya Thackeray's 'poison' reply to Maharashtra minister's remark amid Marathi row | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/renovated-ravindra-natya-mandir-reopening-mumbai-9843008/</t>
+          <t>https://www.hindustantimes.com/india-news/where-did-pahalgam-attackers-go-aaditya-thackerays-poison-reply-to-maharashtra-ministers-remark-amid-marathi-row-101751825235843.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Not an inch of Dharavi will be given to Adani, says Maharashtra minister Ashish Shelar</t>
+          <t>Maharashtra minister addresses AI concerns, assures policy will complement, not replace, education</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
+          <t>https://cio.economictimes.indiatimes.com/news/artificial-intelligence/maharashtra-minister-addresses-ai-concerns-assures-policy-will-complement-not-replace-education/119286707</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BJP demands 'white paper' from BMC on monsoon related spending</t>
+          <t>Renovated Ravindra Natya Mandir in Mumbai to be reopened on February 28: Ashish Shelar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
+          <t>https://indianexpress.com/article/cities/mumbai/renovated-ravindra-natya-mandir-reopening-mumbai-9843008/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>74 roads in H West ward will be completed by May 31: Ashish Shelar</t>
+          <t>Allahbadia remarks: Maharashtra minister Ashish Shelar asks cultural affairs department to probe obscene programmes</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/allahbadia-remarks-maharashtra-minister-ashish-shelar-asks-cultural-affairs-department-to-probe-obscene-programmes-3406629</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ashish Shelar chairs Covid-19 review meet; suggests masks, re-vaccination for high-risk individuals</t>
+          <t>BJP demands 'white paper' from BMC on monsoon related spending</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/bmc-vows-to-finish-monsoon-readiness-in-8-days-bjp-shiv-sena-slams-aditya-uddhav-for-looting-rs-1-lakh-crore-23554178</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>‘We take full responsibility for Mumbai’s roads’: Shelar after visiting eastern suburbs</t>
+          <t>Not an inch of Dharavi will be given to Adani, says Maharashtra minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/not-an-inch-of-dharavi-will-be-given-to-adani-says-shelar/articleshow/119315346.cms</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Warring BJP factions clash in Kandivali public meeting</t>
+          <t>Firebrand legislator and Fadnavis confidante Ameet Satam made BJP’s Mumbai chief ahead of BMC polls</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/firebrand-legislator-and-fadnavis-confidante-ameet-satam-made-bjps-mumbai-chiefahead-of-bmc-polls-3696247</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maharashtra govt to crack down on lane-cutting, draw up integrated traffic management plan for Mumbai: Su</t>
+          <t>74 roads in H West ward will be completed by May 31: Ashish Shelar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/74-roads-in-h-west-ward-will-be-completed-by-may-31-ashish-shelar-101744053976416.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Expert committee set up to look into 'tamasha' artistes' problems: Shelar</t>
+          <t>Warring BJP factions clash in Kandivali public meeting</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/warring-bjp-factions-clash-in-kandivali-public-meeting-101749838974947.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maharashtra Cabinet Minister Ashish Shelar to be the Chief Guest of e4m IDMA 2025</t>
+          <t>Ashish Shelar chairs Covid-19 review meet; suggests masks, re-vaccination for high-risk individuals</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-chairs-covid-19-review-meet-suggests-masks-re-vaccination-for-high-risk-individuals-23557776</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
+          <t>‘We take full responsibility for Mumbai’s roads’: Shelar after visiting eastern suburbs</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/we-take-full-responsibility-for-mumbai-s-roads-shelar-after-visiting-eastern-suburbs-101747854531966.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BJP politician calls Uddhav Thackeray badshah of land scams in Mumbai</t>
+          <t>Maharashtra govt to crack down on lane-cutting, draw up integrated traffic management plan for Mumbai: Su</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-to-crack-down-on-lane-cutting-draw-up-integrated-traffic-management-plan-for-mumbai-suburban-guardian-minister-ashish-shelar/articleshow/122394082.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Asha Bhosle, Minister Ashish Shelar visit RD Burman's residence to celebrate singer's 86th birth anniversary</t>
+          <t>Maharashtra Cabinet Minister Ashish Shelar to be the Chief Guest of e4m IDMA 2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
+          <t>https://www.exchange4media.com/marketing-news/ashish-shelar-to-be-the-chief-guest-of-idma-2025-145447.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Maharashtra minister Ashish Shelar urges transfer of Shivaji’s forts under ASI to state govt</t>
+          <t>Expert committee set up to look into 'tamasha' artistes' problems: Shelar</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/expert-committee-set-up-to-look-into-tamasha-artistes-problems-shelar-3482754</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>No Dharavi land being handed over to Adani: Shelar</t>
+          <t>18.08.2025 : CM Devendra Fadnavis and Cultural Affairs Minister Ashish Shelar meets Governor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/18-08-2025-cm-devendra-fadnavis-and-cultural-affairs-minister-ashish-shelar-meets-governor/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Maharashtra cultural centre and museum to come up at BKC</t>
+          <t>BJP politician calls Uddhav Thackeray badshah of land scams in Mumbai</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-politician-calls-uddhav-thackeray-badshah-of-land-scams-in-mumbai/articleshow/120528864.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>"Maharashtra won, Marathi Manus won, BJP won in this fight", says BJP Mumbai chief Ashish Shelar as Mahayuti slams MVA over three-language policy issue</t>
+          <t>Asha Bhosle, Minister Ashish Shelar visit RD Burman's residence to celebrate singer's 86th birth anniversary</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/asha-bhosle-minister-ashish-selar-visit-rd-burmans-residence-to-celebrate-singers-85th-birth-anniversary20250627132848</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BJP’s Shelar, not Sena neta, is advisor for Maha tech hub</t>
+          <t>Maharashtra minister Ashish Shelar urges transfer of Shivaji’s forts under ASI to state govt</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
+          <t>https://www.theweek.in/news/india/2025/03/25/maharashtra-minister-ashish-shelar-urges-transfer-of-shivajis-forts-under-asi-to-state-govt.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maha minister Shelar pays tribute</t>
+          <t>No Dharavi land being handed over to Adani: Shelar</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/no-dharavi-land-being-handed-over-to-adani-shelar-101742584118783.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mumbai Looted Of Rs 1 Lakh Crore Under Uddhav Thackeray's Watch, Alleges BJP’s Ashish Shelar</t>
+          <t>Maharashtra cultural centre and museum to come up at BKC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.news18.com/cities/shiv-sena-ubt-looted-mumbai-of-rs-1-lakh-crore-alleges-bjps-ashish-shelar-9358239.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cultural-centre-and-museum-to-come-up-at-bkc/articleshow/119168717.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Don’t question capabilities of Marathi speakers: BJP minister Shelar after Dubey remarks</t>
+          <t>"Maharashtra won, Marathi Manus won, BJP won in this fight", says BJP Mumbai chief Ashish Shelar as Mahayuti slams MVA over three-language policy issue</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/dont-question-capabilities-of-marathi-speakers-bjp-minister-shelar-after-dubey-remarks/2682767/</t>
+          <t>https://www.aninews.in/news/national/politics/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy-issue20250630150117/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ashish Shelar praises Mukta Arts Marathi Productions and Subhash Ghai for backing regional cinema</t>
+          <t>BJP’s Shelar, not Sena neta, is advisor for Maha tech hub</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjps-shelar-not-sena-neta-is-advisor-for-maha-tech-hub/articleshow/118256727.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>"Police working meticulously, truth will be out soon": Maharashtra Minister Ashish Shelar on Saif Ali Khan attack case</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maha minister Shelar pays tribute</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
+          <t>https://www.business-standard.com/india-news/veteran-actor-vivek-lagoo-passes-away-maha-minister-shelar-pays-tribute-125061901458_1.html</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Rajiv Shukla, Ashish Shelar To Represent BCCI On ACC Board</t>
+          <t>State grants ‘Maharashtra State Festival’ status to Ganeshotsav, promises funds</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/state-grants-maharashtra-state-festival-status-to-ganeshotsav-promises-funds/articleshow/122373114.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Culture minister Ashish Shelar seeks MoU between state archives of Maharashtra and Gujarat</t>
+          <t>Maharashtra govt orders cultural dept probe, ‘absconding’ Ranveer Allahbadia to face cops today? All you</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/culture-minister-ashish-shelar-seeks-mou-between-state-archives-of-maharashtra-and-gujarat-23573707</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-govt-orders-cultural-dept-probe-absconding-ranveer-allahbadia-to-face-cops-today-all-you-need-to-know/articleshow/118267899.cms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ashish Shelar demands report from MMRDA; slams ‘deception’ behind axed Bandra-Kurla rail route</t>
+          <t>Mumbai Looted Of Rs 1 Lakh Crore Under Uddhav Thackeray's Watch, Alleges BJP’s Ashish Shelar</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
+          <t>https://www.news18.com/cities/shiv-sena-ubt-looted-mumbai-of-rs-1-lakh-crore-alleges-bjps-ashish-shelar-9358239.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maharashtra Spearheading India’s First AI University Says Maharashtra IT Minister Ashish Shelar</t>
+          <t>Don’t question capabilities of Marathi speakers: BJP minister Shelar after Dubey remarks</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
+          <t>https://theprint.in/india/dont-question-capabilities-of-marathi-speakers-bjp-minister-shelar-after-dubey-remarks/2682767/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Minister Shelar criticises UBT over education policy, says Cong started Hindi mandate &amp; Thackeray continu</t>
+          <t>Ashish Shelar praises Mukta Arts Marathi Productions and Subhash Ghai for backing regional cinema</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
+          <t>https://www.indiablooms.com/showbiz/ashish-shelar-praises-mukta-arts-marathi-productions-and-subhash-ghai-for-backing-regional-cinema/details</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Prepare monsoon contingency plan for Mumbai Metro stations: Ashish Shelar to officials</t>
+          <t>Shelar orders swift action to curb bird menace near CSMIA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Science and Innovation Activity centres to be set up across Maharashtra</t>
+          <t>"Police working meticulously, truth will be out soon": Maharashtra Minister Ashish Shelar on Saif Ali Khan attack case</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/science-and-innovation-activity-centres-to-be-set-up-across-maharashtra-10133570/</t>
+          <t>https://aninews.in/news/national/general-news/police-working-meticulously-truth-will-be-out-soon-maharashtra-minister-ashish-shelar-on-saif-ali-khan-attack-case20250118134629/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>‘Celebrate Ganeshotsav Like Never Before’: Shelar Blames Urban Naxals For Attack On Hindu Fests</t>
+          <t>Rajiv Shukla, Ashish Shelar To Represent BCCI On ACC Board</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/celebrate-ganeshotsav-like-never-before-shelar-blames-urban-naxals-for-attacks-on-hindu-fests-ws-kl-9452155.html</t>
+          <t>https://www.etvbharat.com/en/!sports/rajiv-shukla-ashish-shelar-to-represent-bcci-on-acc-board-enn25030706251</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mannat inspection: Maharashtra govt fumes at forest department officials for visiting SRK residence</t>
+          <t>Ashish Shelar demands report from MMRDA; slams ‘deception’ behind axed Bandra-Kurla rail route</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/shelar-slams-deception-behind-axed-bandra-kurla-rail-route-23574631</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Only Marathi is mandatory in Maharashtra, and not Hindi: Mumbai BJP chief Ashish Shelar</t>
+          <t>Maharashtra Spearheading India’s First AI University Says Maharashtra IT Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
+          <t>https://www.businesstoday.in/bt-tv/video/maharashtra-spearheading-indias-first-ai-university-says-maharashtra-it-minister-ashish-shelar-464333-2025-02-12</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Plot in Marol transforms into urban forest, mercury drops</t>
+          <t>Minister Shelar criticises UBT over education policy, says Cong started Hindi mandate &amp; Thackeray continu</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/minister-shelar-criticises-ubt-over-education-policy-says-cong-started-hindi-mandate-thackeray-continued-with-it/articleshow/122135473.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Video | BJP Minister Condemns MNS Attacks, Compares Them To Pahalgam Shooting Over Religious Identity</t>
+          <t>Prepare monsoon contingency plan for Mumbai Metro stations: Ashish Shelar to officials</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-prepare-monsoon-contingency-plan-for-mumbai-metro-stations-ashish-shelar-to-officials-23557472</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UBT looted Mumbai to the tune of ₹1 lakh crore, alleges BJP’s Ashish Shelar</t>
+          <t>‘Celebrate Ganeshotsav Like Never Before’: Shelar Blames Urban Naxals For Attack On Hindu Fests</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
+          <t>https://www.news18.com/india/celebrate-ganeshotsav-like-never-before-shelar-blames-urban-naxals-for-attacks-on-hindu-fests-ws-kl-9452155.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Prize money, production grants and daily allowance hiked for Maharashtra State Drama Competition: Ashish Shelar</t>
+          <t>Mannat inspection: Maharashtra govt fumes at forest department officials for visiting SRK residence</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
+          <t>https://www.indiatvnews.com/entertainment/news/mannat-inspection-maharashtra-govt-fumes-at-forest-department-officials-for-visiting-srk-residence-2025-06-22-995738</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Will Raj Thackeray Join Mahayuti Ahead Of Civic Polls? His Meeting With Mumbai BJP Chief Sparks Buzz</t>
+          <t>Only Marathi is mandatory in Maharashtra, and not Hindi: Mumbai BJP chief Ashish Shelar</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/brihanmumbai-municipal-corporation-bmc-elections-mumbai-mns-raj-thackeray-bjp-ashish-shelar-mahayuti-shiv-sena-eknath-shinde-9181677.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/only-marathi-is-mandatory-in-maharashtra-and-not-hindi-mumbai-bjp-chief-ashish-shelar-23577062</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+          <t>Video | BJP Minister Condemns MNS Attacks, Compares Them To Pahalgam Shooting Over Religious Identity</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+          <t>https://www.ndtv.com/video/bjp-minister-condemns-mns-attacks-compares-them-to-pahalgam-shooting-over-religious-identity-962094</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Khalid Ka Shivaji to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
+          <t>Plot in Marol transforms into urban forest, mercury drops</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/plot-in-marol-transforms-into-urban-forest-mercury-drops-101747076665898.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Maharashtra government forms panel for Artificial Intelligence policy</t>
+          <t>Science and Innovation Activity centres to be set up across Maharashtra</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
+          <t>https://indianexpress.com/article/cities/mumbai/science-and-innovation-activity-centres-to-be-set-up-across-maharashtra-10133570/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+          <t>UBT looted Mumbai to the tune of ₹1 lakh crore, alleges BJP’s Ashish Shelar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event20250806055507</t>
+          <t>https://www.cnbctv18.com/india/politics/ubt-looted-mumbai-to-the-tune-of-rs-1-lakh-crore-alleges-bjp-ashish-shelar-19612583.htm</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Satam Appointed As Mumbai BJP Chief Ahead Of Crucial BMC Polls</t>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/satam-appointed-as-mumbai-bjp-chief-ahead-of-crucial-bmc-polls-1899682</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Maharashtra govt will make arrangements for immersion of large Ganesh idols: Ashish Shelar on PoP use</t>
+          <t>Khalid Ka Shivaji to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
+          <t>https://www.moneycontrol.com/entertainment/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-article-13427385.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>AID strongly advocates GCC Policy: Ashish Kale</t>
+          <t>Maharashtra government forms panel for Artificial Intelligence policy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-forms-panel-for-artificial-intelligence-policy-3360405</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4 Marathi films selected for 2025 Cannes Film Festival reveals Maharashtra cultural affairs minister...</t>
+          <t>Satam Appointed As Mumbai BJP Chief Ahead Of Crucial BMC Polls</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
+          <t>https://www.deccanchronicle.com/nation/satam-appointed-as-mumbai-bjp-chief-ahead-of-crucial-bmc-polls-1899682</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
+          <t>AID strongly advocates GCC Policy: Ashish Kale</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/21/aid-strongly-advocates-gcc-policy-ashish-kale-.html</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sword of Raghuji-1 Bhonsale to be brought to India on Aug 18</t>
+          <t>BJP's Ameet Satam named Mumbai party chief to counter Thackerays in civic polls</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
+          <t>https://www.indiatoday.in/india/story/bjp-leader-ameet-satam-appointed-party-chief-in-mumbai-to-counter-thackerays-in-the-upcoming-civic-polls-2776671-2025-08-25</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Maharashtra to launch India’s first AI University</t>
+          <t>Maharashtra govt will make arrangements for immersion of large Ganesh idols: Ashish Shelar on PoP use</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-to-launch-indias-first-ai-university-9797631/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganeshotsav-2025-maharashtra-govt-will-make-arrangements-for-immersion-of-large-ganesh-idols-says-ashish-shelar-on-pop-use-23563896</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AI in education: Maharashtra to launch new AI policy in April, says IT Minister</t>
+          <t>4 Marathi films selected for 2025 Cannes Film Festival reveals Maharashtra cultural affairs minister...</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
+          <t>https://www.moneycontrol.com/entertainment/4-marathi-films-selected-for-2025-cannes-film-festival-reveals-maharashtra-cultural-affairs-minister-ashish-shelar-article-12998891.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Reema Lagoos Ex-Husband And Veteran Actor Vivek Lagoo Dies, Last Rites To Be Held Today; Maharashtra Minister Ashish Shelar Pays Tribute</t>
+          <t>Cabinet Minister Shelar Calls for Innovators as Lions Clubs Highlight Rs. 500 Cr Annual Community Investment</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
+          <t>https://m.thewire.in/article/ptiprnews/cabinet-minister-shelar-calls-for-innovators-as-lions-clubs-highlight-rs-500-cr-annual-community-investment</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar pays tribute to Savarkar at Andaman's Cellular Jail</t>
+          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
+          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
+          <t>Sword of Raghuji-1 Bhonsale to be brought to India on Aug 18</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
+          <t>https://www.thehitavada.com/Encyc/2025/8/12/sword-of-raghuji-1-bhonsale-to-be-brought-to-india-on-aug-18.html</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>News On Click</t>
+          <t>AI in education: Maharashtra to launch new AI policy in April, says IT Minister</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/ai-in-education-maharashtra-to-launch-new-ai-policy-in-april-says-it-minister</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>23rd Pune International Film Festival begins with a grand opening</t>
+          <t>Maharashtra to launch India’s first AI University</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/pune/23rd-pune-international-film-festival-begins-with-a-grand-opening-9835047/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-to-launch-indias-first-ai-university-9797631/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ganeshotsav to Get Status of Maharashtra’s ‘State Festival’</t>
+          <t>‘Khalid Ka Shivaji’ to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/current-affairs/ganeshotsav-to-get-status-of-maharashtras-state-festival-1890637</t>
+          <t>https://www.dtnext.in/entertainment/cinema/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-842675</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar calls for urgent desilting plan for key lakes in Mumbai</t>
+          <t>Maharashtra Minister Ashish Shelar pays tribute to Savarkar at Andaman's Cellular Jail</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
+          <t>https://www.mid-day.com/news/india-news/article/maharashtra-minister-ashish-shelar-pays-tribute-to-savarkar-at-andamans-cellular-jail-23545285</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Minister Shelar warns of ‘urban naxal’ threat</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
+          <t>https://www.aninews.in/news/entertainment/bollywood/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute20250619234252/</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Maharashtra govt to form panel to study issues faced by single-screen cinemas</t>
+          <t>Ganeshotsav to Get Status of Maharashtra’s ‘State Festival’</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-panel-to-study-issues-faced-by-single-screen-cinemas-10176447/</t>
+          <t>https://www.deccanchronicle.com/nation/current-affairs/ganeshotsav-to-get-status-of-maharashtras-state-festival-1890637</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>‘Khalid Ka Shivaji’ to be removed from Cannes Festival listings on 'objectionable' content: Shelar</t>
+          <t>News On Click</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.dtnext.in/entertainment/cinema/khalid-ka-shivaji-to-be-removed-from-cannes-festival-listings-on-objectionable-content-shelar-842675</t>
+          <t>https://globalprimenews.com/2025/05/12/acharya-shri-mahashramanji-garden-in-marol-sagbagh-will-set-an-example-towards-mumbais-beautification-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Maharashtra govt taking balanced approach to pigeon feeding issue: Minister Shelar</t>
+          <t>Maharashtra Minister Ashish Shelar calls for urgent desilting plan for key lakes in Mumbai</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
+          <t>https://www.mid-day.com/news/india-news/article/mumbai-suburban-guardian-minister-ashish-shelar-calls-for-urgent-desilting-of-key-lakes-23578487</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Shiv Sena (UBT) MP Sanjay Raut slams BJP Minister Ashish Shelar for comparing Hindi-Marathi row to Pahalgam attack</t>
+          <t>Minister Shelar warns of ‘urban naxal’ threat</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/shiv-sena-ubt-mp-sanjay-raut-slams-bjp-minister-ashish-shelar-for-comparing-hindi-marathi-row-to-pahalgam-attack20250707113350</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/minister-shelar-warns-of-urban-naxal-threat/articleshow/118097121.cms</t>
         </is>
       </c>
     </row>
@@ -2159,5640 +2159,6108 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Advantage Vidarbha 2025 to be inaugurated today</t>
+          <t>Maharashtra govt taking balanced approach to pigeon feeding issue: Minister Shelar</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
+          <t>https://health.economictimes.indiatimes.com/news/policy/maharashtra-balances-pigeon-feeding-practices-amid-health-concerns-minister-shelar/123210870</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>State forms district-level panels to remove encroachments on forts</t>
+          <t>Advantage Vidarbha 2025 to be inaugurated today</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/7/Advantage-Vidarbha-2025-to-be-inaugurated-today.html</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BMC told to finish all roadworks in Mumbai suburbs by May 31, says minister</t>
+          <t>State forms district-level panels to remove encroachments on forts</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/state-forms-district-level-panels-to-remove-encroachments-on-forts-101737304913578.html</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>India’s Got Latent row: Maharashtra govt orders inquiry into controversy involving Ranveer Allahbadia, Samay Raina</t>
+          <t>BMC told to finish all roadworks in Mumbai suburbs by May 31, says minister</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bmc-told-to-finish-all-roadworks-in-mumbai-suburbs-by-may-31-says-minister-101744197242653.html</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray's Shiv Sena (UBT) failed to improve Mumbai's stormwater drain system despite Rs 1 lakh crore spending: BJP</t>
+          <t>India’s Got Latent row: Maharashtra govt orders inquiry into controversy involving Ranveer Allahbadia, Samay Raina</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
+          <t>https://www.businesstoday.in/india/story/indias-got-latent-row-maharashtra-govt-orders-inquiry-into-controversy-involving-ranveer-allahbadia-samay-raina-464749-2025-02-14</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Film City in Ramtek inches closer to reality</t>
+          <t>Sena UBT’s condition akin to ‘dangerous’, ‘dilapidated’ buildings of Mumbai: Shelar</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
+          <t>https://theprint.in/india/sena-ubts-condition-akin-to-dangerous-dilapidated-buildings-of-mumbai-shelar/2666348/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Shelar invokes Pahalgam: ‘Here, Hindus attacked over language’</t>
+          <t>Uddhav Thackeray's Shiv Sena (UBT) failed to improve Mumbai's stormwater drain system despite Rs 1 lakh crore spending: BJP</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-rains-uddhav-thackerays-shiv-sena-ubt-failed-to-improve-mumbais-stormwater-drain-system-despite-rs-1-lakh-crore-spending-says-bjp-23553883</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Not all road works in Mumbai will be completed before May 31 monsoon deadline: Maharashtra Minister Ashish Shelar</t>
+          <t>Prize money, production grants and daily allowance hiked for Maharashtra State Drama Competition: Ashish Shelar</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/prize-money-production-grants-and-daily-allowance-hiked-for-maharashtra-state-drama-competition-says-cultural-minister-ashish-shelar-23590531</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>All govt departments, implementing agencies must ensure 100 per cent fund utilisation: Shelar</t>
+          <t>Not all road works in Mumbai will be completed before May 31 monsoon deadline: Maharashtra Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/road-concretisation-in-mumbai-not-all-road-works-will-be-completed-before-may-31-monsoon-deadline-says-maharashtra-minister-ashish-shelar-23547168</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Maharashtra minister Shelar asks govt departments to step up Ganeshotsav participation; Rs 10 crore for cultural events</t>
+          <t>Film City in Ramtek inches closer to reality</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-minister-shelar-asks-govt-departments-to-step-up-ganeshotsav-participation-rs-10-crore-for-cultural-events-10205121/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/film-city-in-ramtek-inches-closer-to-reality/articleshow/118285166.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Submit action plan within 3 months to desilt three lakes in Mumbai: Shelar</t>
+          <t>Maharashtra govt to form panel to study issues faced by single-screen cinemas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/submit-action-plan-within-3-months-to-desilt-three-lakes-in-mumbai-shelar-10088728/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-panel-to-study-issues-faced-by-single-screen-cinemas-10176447/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shellar appointed as reps to ACC board</t>
+          <t>Maharashtra minister Shelar asks govt departments to step up Ganeshotsav participation; Rs 10 crore for cultural events</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-minister-shelar-asks-govt-departments-to-step-up-ganeshotsav-participation-rs-10-crore-for-cultural-events-10205121/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Maharashtra orders inquiry by cultural dept officials into Ranveer Allahbadia controversy</t>
+          <t>All govt departments, implementing agencies must ensure 100 per cent fund utilisation: Shelar</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Feb/15/maharashtra-orders-inquiry-by-cultural-dept-officials-into-ranveer-allahbadia-controversy</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-development-all-govt-departments-implementing-agencies-must-ensure-100-per-cent-utilisation-of-funds-says-ashish-shelar-23557098</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Shelar &amp; Cong MP get into spat over Dharavi master plan</t>
+          <t>Shelar invokes Pahalgam: ‘Here, Hindus attacked over language’</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-invokes-pahalgam-here-hindus-attacked-over-language/articleshow/122284105.cms</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Veer Savarkar’s iconic song ‘Anadi Me Anant Me...’ to be honoured with award named after Sambhaji Maharaj: Minister</t>
+          <t>Submit action plan within 3 months to desilt three lakes in Mumbai: Shelar</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/veer-savarkars-iconic-song-anadi-me-anant-me-to-be-honoured-with-award-named-after-sambhaji-maharaj-minister-3421353</t>
+          <t>https://indianexpress.com/article/cities/mumbai/submit-action-plan-within-3-months-to-desilt-three-lakes-in-mumbai-shelar-10088728/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FTII and Maharashtra Film, Stage &amp; Cultural Development Corporation Ltd. sign MoU to expand film and media training in Maharashtra</t>
+          <t>CM Fadnavis to be guardian minister of Gadchiroli; Dhananjay Munde not in list</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
+          <t>https://www.deccanherald.com/india/maharashtra/cm-fadnavis-to-be-guardian-minister-of-gadchiroli-dhananjay-munde-not-in-list-3362163</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Give Custodianship Of Historic Forts To Maharashtra Government: Minister Ashish Shelar To Centre</t>
+          <t>Rajeev Shukla, Ashish Shellar appointed as reps to ACC board</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/hand-over-custodianship-of-historic-forts-to-maharashtra-government-minister-ashish-shelar-to-centre-9274572.html</t>
+          <t>https://www.exchange4media.com/media-others-news/rajeev-shukla-ashish-shellar-appointed-as-reps-to-acc-board-141565.html</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Maharashtra to get India's first AI university led by industry experts</t>
+          <t>Maharashtra orders inquiry by cultural dept officials into Ranveer Allahbadia controversy</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/education-today/news/story/ai-education-indias-first-ai-university-to-set-up-in-maharashtra-2673858-2025-02-03</t>
+          <t>https://www.newindianexpress.com/nation/2025/Feb/15/maharashtra-orders-inquiry-by-cultural-dept-officials-into-ranveer-allahbadia-controversy</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mumbai's Sanjay Gandhi National Park To Introduce 'Leopard Safari' For Visitors Soon</t>
+          <t>Shelar &amp; Cong MP get into spat over Dharavi master plan</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/sanjay-gandhi-national-park-in-mumbai-to-introduce-leopard-safari-for-visitors-soon-ashish-shelar-9209891.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/shelar-cong-mp-get-into-spat-over-dharavi-master-plan/articleshow/121656799.cms</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>New Mumbai BJP chief Ameet Satam is 3-time MLA with corporate background, Thackeray critic</t>
+          <t>Veer Savarkar’s iconic song ‘Anadi Me Anant Me...’ to be honoured with award named after Sambhaji Maharaj: Minister</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/new-mumbai-bjp-chief-ameet-satam-is-3-time-mla-with-corporate-background-thackeray-critic/2728464/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/veer-savarkars-iconic-song-anadi-me-anant-me-to-be-honoured-with-award-named-after-sambhaji-maharaj-minister-3421353</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Maharashtra government aims to make forts encroachment-free by May 31</t>
+          <t>FTII and Maharashtra Film, Stage &amp; Cultural Development Corporation Ltd. sign MoU to expand film and media training in Maharashtra</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
+          <t>https://www.pib.gov.in/PressReleasePage.aspx?PRID=2146456</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Maharashtra govt forms 16-member panel to draft first-ever AI policy</t>
+          <t>Give Custodianship Of Historic Forts To Maharashtra Government: Minister Ashish Shelar To Centre</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-16-member-panel-draft-ai-policy-9784605/</t>
+          <t>https://www.news18.com/india/hand-over-custodianship-of-historic-forts-to-maharashtra-government-minister-ashish-shelar-to-centre-9274572.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Maharashtra: Honorarium of Aadhaar centre operators raised; 12.8 cr Aadhaar registrations recorded till date</t>
+          <t>Mumbai's Sanjay Gandhi National Park To Introduce 'Leopard Safari' For Visitors Soon</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-aadhaar-centre-operators-honorarium-raised-registrations-recorded-9952118/</t>
+          <t>https://www.news18.com/india/sanjay-gandhi-national-park-in-mumbai-to-introduce-leopard-safari-for-visitors-soon-ashish-shelar-9209891.html</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Mumbai rains: Sena (UBT), contractors misappropriated funds meant for drainage system, claims Shelar</t>
+          <t>Maharashtra to get India's first AI university led by industry experts</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/mumbai-rains-sena-ubt-contractors-misappropriated-funds-meant-for-drainage-system-claims-shelar/2637642/</t>
+          <t>https://www.indiatoday.in/education-today/news/story/ai-education-indias-first-ai-university-to-set-up-in-maharashtra-2673858-2025-02-03</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Maharashtra to Establish India’s First Artificial Intelligence University</t>
+          <t>Maharashtra Declares Ganeshotsav As State Festival</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
+          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Roads in Mumbai will be pothole-free before Ganesh festival: BJP ministers</t>
+          <t>Ameet Satam Appointed BJP Mumbai Chief Ahead Of Polls</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Roads-in-Mumbai-will-be-pothole-free-before-Ganesh-festival--BJP-ministers/2846226</t>
+          <t>https://www.bwpeople.in/article/ameet-satam-appointed-bjp-mumbai-chief-ahead-of-polls-568808</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Play Marathi devotional songs on private radio stations: Shelar</t>
+          <t>Maharashtra govt forms 16-member panel to draft first-ever AI policy</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/play-marathi-devotional-songs-on-private-radio-stations-shelar/2576362</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-16-member-panel-draft-ai-policy-9784605/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Maharashtra to have India's first AI university, says minister</t>
+          <t>Maharashtra government aims to make forts encroachment-free by May 31</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-government-aims-to-make-forts-encroachment-free-by-may-31-3365169</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Maharashtra Declares Ganeshotsav As State Festival</t>
+          <t>Maharashtra to Establish India’s First Artificial Intelligence University</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/maharashtra-declares-ganeshotsav-as-state-festival-8854969</t>
+          <t>https://digitallearning.eletsonline.com/2025/02/maharashtra-to-establish-indias-first-artificial-intelligence-university/</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Major fire at mall in Mumbai's Bandra; firefighting on after 18 hours</t>
+          <t>Maharashtra to have India's first AI university, says minister</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Apr/29/major-fire-at-mall-in-mumbais-bandra-firefighting-on-after-18-hours</t>
+          <t>https://bestcolleges.indiatoday.in/news-detail/maharashtra-to-have-indias-first-ai-university-says-minister</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Culture Minister Ashish Shelar Praises Mukta Arts Productions, Subhash Ghai For Backing Regional Cinema</t>
+          <t>Mumbai rains: Sena (UBT), contractors misappropriated funds meant for drainage system, claims Shelar</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
+          <t>https://theprint.in/india/mumbai-rains-sena-ubt-contractors-misappropriated-funds-meant-for-drainage-system-claims-shelar/2637642/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray, Rohit Pawar Hit Back After BJP Minister’s ‘Terrorist’ Remark</t>
+          <t>Major fire at mall in Mumbai's Bandra; firefighting on after 18 hours</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/uddhav-thackeray-rohit-pawar-hit-back-after-bjp-ministers-terrorist-remark-1503454822.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/29/major-fire-at-mall-in-mumbais-bandra-firefighting-on-after-18-hours</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Highlight power of Operation Sindoor during Ganesh festival: Shelar tells organisers</t>
+          <t>Culture Minister Ashish Shelar Praises Mukta Arts Productions, Subhash Ghai For Backing Regional Cinema</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/highlight-power-of-operation-sindoor-during-ganesh-festival-shelar-tells-organisers/2841354</t>
+          <t>https://www.filmibeat.com/bollywood/news/2025/culture-minister-ashish-shelar-praises-mukta-arts-productions-subhash-ghai-for-backing-regional-cin-461737.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Maharashtra to establish country's first Artificial Intelligence university</t>
+          <t>Maharashtra: Honorarium of Aadhaar centre operators raised; 12.8 cr Aadhaar registrations recorded till date</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-aadhaar-centre-operators-honorarium-raised-registrations-recorded-9952118/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Maharashtra seeks custodianship of ASI-protected forts for better conservation</t>
+          <t>Uddhav Thackeray, Rohit Pawar Hit Back After BJP Minister’s ‘Terrorist’ Remark</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-seeks-custodianship-of-asi-protected-forts-for-better-conservation/article69373142.ece</t>
+          <t>https://www.thestatesman.com/india/uddhav-thackeray-rohit-pawar-hit-back-after-bjp-ministers-terrorist-remark-1503454822.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Shelar criticises desilting works in Mumbai, demands accountability from contractors</t>
+          <t>Maharashtra seeks custodianship of ASI-protected forts for better conservation</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors/2619256/</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/maharashtra-seeks-custodianship-of-asi-protected-forts-for-better-conservation/article69373142.ece</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Good News For Marathi Filmmakers: Maharashtra Govt Plans Revival Of Single-Screen Cinemas</t>
+          <t>Maharashtra to establish country's first Artificial Intelligence university</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/good-news-for-marathi-filmmakers-maharashtra-govt-plans-revival-of-single-screen-cinemas-ws-l-9492408.html</t>
+          <t>https://www.hindustantimes.com/education/news/maharashtra-to-establish-countrys-first-artificial-intelligence-university-101738556429585.html</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares assaults on non-Marathi speakers in state to Pahalgam terror attack</t>
+          <t>Ameet Satam appointed BJP Mumbai Chief</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://scroll.in/latest/1084239/maharashtra-minister-compares-assaults-on-non-marathi-speakers-in-state-to-pahalgam-terror-attack</t>
+          <t>https://www.exchange4media.com/industry-briefing-news/ameet-satam-appointed-bjp-mumbai-chief-146770.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Maharashtra to Set up The India First Artificial Intelligence University Details Here</t>
+          <t>Shelar criticises desilting works in Mumbai, demands accountability from contractors</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.jagranjosh.com/news/maharashtra-to-set-up-the-india-first-artificial-intelligence-university-details-here-175203</t>
+          <t>https://theprint.in/india/shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors/2619256/</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Task force formed to set up AI university in Maharashtra, says IT Minister Ashish Shelar</t>
+          <t>Who Is Ameet Satam? Three-Term MLA Picked As BJP's Mumbai Chief Ahead Of BMC Polls</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
+          <t>https://www.news18.com/politics/ameet-satam-mumbai-bjp-chief-andheri-west-mla-bmc-polls-ws-l-9526976.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Residents of BDD chawls in Worli will get homes before July: Maharashtra minister</t>
+          <t>Good News For Marathi Filmmakers: Maharashtra Govt Plans Revival Of Single-Screen Cinemas</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
+          <t>https://www.news18.com/india/good-news-for-marathi-filmmakers-maharashtra-govt-plans-revival-of-single-screen-cinemas-ws-l-9492408.html</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Expert Panel To Study PoP Use For Ganesh Idols, Assures Minister Ashish Shelar</t>
+          <t>Maharashtra minister compares assaults on non-Marathi speakers in state to Pahalgam terror attack</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/expert-panel-to-study-pop-use-for-ganesh-idols-assures-minister-ashish-shelar-9260345.html</t>
+          <t>https://scroll.in/latest/1084239/maharashtra-minister-compares-assaults-on-non-marathi-speakers-in-state-to-pahalgam-terror-attack</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Film City to come up near Khindsi lake in Ramtek</t>
+          <t>Play Marathi devotional songs on private radio stations: Shelar</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
+          <t>https://theprint.in/india/play-marathi-devotional-songs-on-private-radio-stations-shelar/2633618/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Maharashtra Govt Selects Savarkar's Composition For Its 1st Sambhaji Maharaj Song Award</t>
+          <t>Maharashtra to Set up The India First Artificial Intelligence University Details Here</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/maharashtra-government-selects-savarkar-composition-for-its-1st-sambhaji-maharaj-song-award-enn25022600100</t>
+          <t>https://www.jagranjosh.com/news/maharashtra-to-set-up-the-india-first-artificial-intelligence-university-details-here-175203</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Maharashtra govt arranges buses, special trains for people travelling to celebrate Ganesh Utsav</t>
+          <t>Task force formed to set up AI university in Maharashtra, says IT Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609/</t>
+          <t>https://news.careers360.com/task-force-formed-set-up-artificial-intelligence-varsity-in-maharashtra-information-technology-minister</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NIAT Students Shine at Mumbai Tech Week, Earning Recognition from Industry Leaders and IT Minister</t>
+          <t>Residents of BDD chawls in Worli will get homes before July: Maharashtra minister</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
+          <t>https://realty.economictimes.indiatimes.com/news/residential/worli-residents-to-receive-new-homes-before-july-promises-maharashtra-minister/121512751</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Maharashtra govt declares Ganesh festival as Rajya Mahotsav'; launches portal</t>
+          <t>Expert Panel To Study PoP Use For Ganesh Idols, Assures Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
+          <t>https://www.news18.com/india/expert-panel-to-study-pop-use-for-ganesh-idols-assures-minister-ashish-shelar-9260345.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>BCCI issues update on appointment to ACC's Board of Directors</t>
+          <t>Film City to come up near Khindsi lake in Ramtek</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
+          <t>https://www.thehitavada.com/Encyc/2025/2/16/Film-City-to-come-up-near-Khindsi-lake-in-Ramtek.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
+          <t>Maharashtra Govt Selects Savarkar's Composition For Its 1st Sambhaji Maharaj Song Award</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
+          <t>https://www.etvbharat.com/en/!state/maharashtra-government-selects-savarkar-composition-for-its-1st-sambhaji-maharaj-song-award-enn25022600100</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BCCI appoints Jay Shah and Ashish Shelar's successor ahead of Champions Trophy 2025</t>
+          <t>Highlight power of Operation Sindoor during Ganesh festival: Shelar tells organisers</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
+          <t>https://theprint.in/india/highlight-power-of-operation-sindoor-during-ganesh-festival-shelar-tells-organisers/2725508/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mumbai BJP Chief Ashish Shelar Slams Uddhav &amp; Raj Thackeray For Pushing Personal Agendas Under Marathi Pride</t>
+          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-chief-ashish-shelar-slams-uddhav-raj-thackeray-for-pushing-personal-agendas-under-marathi-pride-video</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Maharashtra News: Minister Ashish Shelar Accuses Opposition Of Urban Naxalite Agenda To Curtail Ganeshotsav</t>
+          <t>Maharashtra govt arranges buses, special trains for people travelling to celebrate Ganesh Utsav</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-minister-ashish-shelar-accuses-opposition-of-urban-naxalite-agenda-to-curtail-ganeshotsav-traditions</t>
+          <t>https://www.aninews.in/news/national/general-news/maharashtra-govt-arranges-buses-special-trains-for-people-travelling-to-celebrate-ganesh-utsav20250823230609</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Urges Netflix To Promote Marathi Content On OTT Platform</t>
+          <t>NIAT Students Shine at Mumbai Tech Week, Earning Recognition from Industry Leaders and IT Minister</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-urges-netflix-to-promote-marathi-content-on-ott-platform</t>
+          <t>https://www.aninews.in/news/business/niat-students-shine-at-mumbai-tech-week-earning-recognition-from-industry-leaders-and-it-minister20250308101754/</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Targets Uddhav Thackeray, Raj Thackeray Over Hindi Row; Says Marathi</t>
+          <t>Ganeshotsav Gets Maharashtra's State Festival Status, Plans International Outreach</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-targets-uddhav-thackeray-raj-thackeray-over-hindi-row-says-marathi-mandatory-hindi-optional-video</t>
+          <t>https://www.mumbailive.com/en/civic/ganeshotsav-gets-maharashtra's-state-festival-status-plans-international-outreach-89276</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ashish Shelar Slams Uddhav-Raj Thackeray Rally As Irrelevant, Accuses Duo Of Distorting Facts</t>
+          <t>Maharashtra govt declares Ganesh festival as Rajya Mahotsav'; launches portal</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ganesh-festival-2025-maharashtra-declares-ganesh-festival-as-rajya-mahotsav-launches-portal-23590809</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
+          <t>BCCI issues update on appointment to ACC's Board of Directors</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://www.aninews.in/news/sports/cricket/bcci-issues-update-on-appointment-to-accs-board-of-directors20250307230901</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>No New Restrictions On Political Portrayals In Films, Says Minister Ashish Shelar During Council Debate</t>
+          <t>Mumbai Buzz: Top Headlines &amp; Latest News from the City That Never Sleeps</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-new-restrictions-on-political-portrayals-in-films-says-minister-ashish-shelar-during-council-debate</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/photo/in-photos-mumbai-suburban-guardian-minister-inspects-new-towers-for-worli-bdd-chawl-residents-105634</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Mumbai Minister Ashish Shelar Gives 72-Hour Deadline To Fix Potholes Ahead Of Ganeshotsav 2025</t>
+          <t>BCCI appoints Jay Shah and Ashish Shelar's successor ahead of Champions Trophy 2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-ashish-shelar-gives-72-hour-deadline-to-fix-potholes-ahead-of-ganeshotsav-2025</t>
+          <t>https://thesportstak.com/cricket/story/bcci-appoints-jay-shah-and-ashish-shelars-successor-ahead-of-champions-trophy-2025-3155457-2025-01-12</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>No One Should Hurt Sentiments..: Maha Minister Ashish Shelar On Row Over Viral Ganeshotsav Reel By Content</t>
+          <t>Mumbai BJP Chief Ashish Shelar Slams Uddhav &amp; Raj Thackeray For Pushing Personal Agendas Under Marathi Pride</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-one-should-hurt-sentiments-maha-minister-ashish-shelar-on-row-over-viral-ganeshotsav-reel-by-content-creator-atharva-sudame</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-chief-ashish-shelar-slams-uddhav-raj-thackeray-for-pushing-personal-agendas-under-marathi-pride-video</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Mumbai Rains: Minister Ashish Shelar Meets BMC Chief Bhushan Gagrani, Demands White Paper On ₹1 Lakh Crore</t>
+          <t>Maharashtra News: Minister Ashish Shelar Accuses Opposition Of Urban Naxalite Agenda To Curtail Ganeshotsav</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-minister-ashish-shelar-meets-bmc-chief-bhushan-gagrani-demands-white-paper-on-1-lakh-crore-flood-control-spending-over-past-20-years</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-minister-ashish-shelar-accuses-opposition-of-urban-naxalite-agenda-to-curtail-ganeshotsav-traditions</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ashish Shelar Addresses Media on Hindi as Third Language in Schools #Gallery</t>
+          <t>Maharashtra Minister Ashish Shelar Urges Netflix To Promote Marathi Content On OTT Platform</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6712027</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-urges-netflix-to-promote-marathi-content-on-ott-platform</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Maharashtra govt to assist Marathi schools in USA: Support promised with curriculum and recommendations to ...</t>
+          <t>Maharashtra Minister Ashish Shelar Targets Uddhav Thackeray, Raj Thackeray Over Hindi Row; Says Marathi</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/50-marathi-teaching-schools-in-america-support-promised-with-curriculum-and-recommendations-to-over-50-schools-teaching-nearly-300-students-135526242.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-targets-uddhav-thackeray-raj-thackeray-over-hindi-row-says-marathi-mandatory-hindi-optional-video</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Maharashtra: Ganeshotsav Declared State Festival; Ashish Shelar Alleges Conspiracy Against Hindu Traditions</t>
+          <t>Ashish Shelar Slams Uddhav-Raj Thackeray Rally As Irrelevant, Accuses Duo Of Distorting Facts</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-ganeshotsav-declared-state-festival-ashish-shelar-alleges-conspiracy-against-hindu-traditions</t>
+          <t>https://news.abplive.com/news/india/ashish-shelar-slams-uddhav-raj-thackeray-rally-as-irrelevant-accuses-duo-of-distorting-facts-1785696</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ashish Shelar inaugurates Art Show by IAS Officers Nidhi Choudhari &amp; Rajanvir Singh Kapur</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra Minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://culturecrossroads.ca/posts/ashish-shelar-inaugurates-art-show-by-ias-officers-nidhi-choudhari-rajanvir-singh-kapur/</t>
+          <t>https://www.lokmattimes.com/entertainment/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ashish Shelar Directs BMC To Deploy 1,000 Volunteers With 1916 Helpline For Dahi Handi Safety</t>
+          <t>No New Restrictions On Political Portrayals In Films, Says Minister Ashish Shelar During Council Debate</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-bmc-to-deploy-1000-volunteers-with-1916-helpline-for-dahi-handi-safety</t>
+          <t>https://www.freepressjournal.in/mumbai/no-new-restrictions-on-political-portrayals-in-films-says-minister-ashish-shelar-during-council-debate</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed As Mumbai BJP President Ahead Of BMC Polls; CM Devendra Fadnavis, Ashish Shelar Extend</t>
+          <t>Mumbai Minister Ashish Shelar Gives 72-Hour Deadline To Fix Potholes Ahead Of Ganeshotsav 2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-minister-ashish-shelar-gives-72-hour-deadline-to-fix-potholes-ahead-of-ganeshotsav-2025</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Historic Sword Of Maratha Sardar Raghuji Bhosale To Return To Maharashtra By July-End, Says Minister Ashish</t>
+          <t>Mumbai Rains: Minister Ashish Shelar Meets BMC Chief Bhushan Gagrani, Demands White Paper On ₹1 Lakh Crore</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-maratha-sardar-raghuji-bhosale-to-return-to-maharashtra-by-july-end-says-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-rains-minister-ashish-shelar-meets-bmc-chief-bhushan-gagrani-demands-white-paper-on-1-lakh-crore-flood-control-spending-over-past-20-years</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir’s ‘SUR Music’ Label</t>
+          <t>Ashish Shelar Addresses Media on Hindi as Third Language in Schools #Gallery</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
+          <t>https://www.socialnews.xyz/?p=6712027</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Calls For Action To Boost Marathi Films &amp; Save Single-Screen Cinemas</t>
+          <t>Maharashtra govt to assist Marathi schools in USA: Support promised with curriculum and recommendations to ...</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-calls-for-action-to-boost-marathi-films-save-single-screen-cinemas</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/50-marathi-teaching-schools-in-america-support-promised-with-curriculum-and-recommendations-to-over-50-schools-teaching-nearly-300-students-135526242.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Read Finally Gokhale Bridge Andheri Poora Ready Hua, Finally Ready, Guardian Minister Ashish Shelar Ke Hathon Open Kiya Gaya</t>
+          <t>Maharashtra: Ganeshotsav Declared State Festival; Ashish Shelar Alleges Conspiracy Against Hindu Traditions</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-ganeshotsav-declared-state-festival-ashish-shelar-alleges-conspiracy-against-hindu-traditions</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Ashish Shelar Slams Thackeray Rally As Theatrical, Draws Pahalgam Parallel; Kishori</t>
+          <t>Mumbai Politics: Two Ex-UBT Corporators Join BJP; Shelar Declares Party Now Largest In Civic Body Ahead Of BMC</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ashish-shelar-slams-thackeray-rally-as-theatrical-draws-pahalgam-parallel-kishori-pednekar-hits-back</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-two-ex-ubt-corporators-join-bjp-shelar-declares-party-now-largest-in-civic-body-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Mumbai Politics: Two Ex-UBT Corporators Join BJP; Shelar Declares Party Now Largest In Civic Body Ahead Of BMC</t>
+          <t>Ashish Shelar inaugurates Art Show by IAS Officers Nidhi Choudhari &amp; Rajanvir Singh Kapur</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-politics-two-ex-ubt-corporators-join-bjp-shelar-declares-party-now-largest-in-civic-body-ahead-of-bmc-polls</t>
+          <t>https://culturecrossroads.ca/posts/ashish-shelar-inaugurates-art-show-by-ias-officers-nidhi-choudhari-rajanvir-singh-kapur/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Mumbai: Siddhivinayak Temple Trust Felicitates Ashish Shelar For Declaring Ganeshotsav As State Festival</t>
+          <t>Ashish Shelar Directs BMC To Deploy 1,000 Volunteers With 1916 Helpline For Dahi Handi Safety</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-siddhivinayak-temple-trust-felicitates-ashish-shelar-for-declaring-ganeshotsav-as-state-festival</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-bmc-to-deploy-1000-volunteers-with-1916-helpline-for-dahi-handi-safety</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Maharashtra: Gondan Kala To Enter Maharashtras Art Curriculum, Says Minister Ashish Shelar</t>
+          <t>Maharashtra Minister Ashish Shelar Proposes Grand National Memorial For Veer Savarkar At Andaman’s Cellular</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-gondan-kala-to-enter-maharashtras-art-curriculum-says-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-proposes-grand-national-memorial-for-veer-savarkar-at-andamans-cellular-jail</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Mumbai News: Relief For 86 Stalled SRA Projects As Residents Allowed To Appoint New Developers; Ashish Shelar</t>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead Of BMC Polls; CM Devendra Fadnavis, Ashish Shelar Extend</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-relief-for-86-stalled-sra-projects-as-residents-allowed-to-appoint-new-developers-ashish-shelar-reviews-progress</t>
+          <t>https://www.freepressjournal.in/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Mumbai News: Minister Ashish Shelar Directs BMC To Submit 3-Month Action Plan For Desilting Powai, Tulsi And</t>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir’s ‘SUR Music’ Label</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-directs-bmc-to-submit-3-month-action-plan-for-desilting-powai-tulsi-and-vihar-lakes</t>
+          <t>https://indiaeducationdiary.in/hariharan-pt-hariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mahavirs-sur-music-label/</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP Leader Sudhir Mungantiwar Slams Ministers’ Absenteeism, Pushes For Ban On Alcohol At</t>
+          <t>VIDEO: Uddhav Thackerays Party Failed To improve Mumbais Stormwater Drain System Despite ₹1 Lakh Crore</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-leader-sudhir-mungantiwar-slams-ministers-absenteeism-pushes-for-ban-on-alcohol-at-heritage-forts</t>
+          <t>https://www.freepressjournal.in/mumbai/video-uddhav-thackerays-party-failed-to-improve-mumbais-stormwater-drain-system-despite-1-lakh-crore-spend-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Maharashtra News: Shiv Sena (UBT) Chief Uddhav Thackeray Slams CM Devendra Fadnavis Over Rudali Remark,</t>
+          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shiv-sena-ubt-chief-uddhav-thackeray-slams-cm-devendra-fadnavis-over-rudali-remark-defends-marathi-identity-video</t>
+          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Pune: Maharashtra Declares Ganesh Festival as ‘State Festival,’ Plans Global Promotion: Ashish Shelar</t>
+          <t>Historic Sword Of Maratha Sardar Raghuji Bhosale To Return To Maharashtra By July-End, Says Minister Ashish</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
+          <t>https://www.freepressjournal.in/mumbai/historic-sword-of-maratha-sardar-raghuji-bhosale-to-return-to-maharashtra-by-july-end-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Hindi Not Mandatory in Maharashtra Schools, Marathi Remains Only Compulsory Language: Ashish Shelar</t>
+          <t>Maharashtra Minister Ashish Shelar Calls For Action To Boost Marathi Films &amp; Save Single-Screen Cinemas</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/hindi-not-mandatory-in-maharashtra-schools-marathi-remains-only-compulsory-language-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-calls-for-action-to-boost-marathi-films-save-single-screen-cinemas</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>POP idol ban lifted: A triumph for artisans, says Maha Minister Ashish Shelar</t>
+          <t>Read Finally Gokhale Bridge Andheri Poora Ready Hua, Finally Ready, Guardian Minister Ashish Shelar Ke Hathon Open Kiya Gaya - Gallinews India</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/pop-idol-ban-lifted-a-triumph-for-artisans-says-maha-minister-ashish-shelar</t>
+          <t>https://gallinews.com/finally-gokhale-bridge-andheri-poora-ready-hua-finally-ready-guardian-minister-ashish-shelar-ke-hathon-open-kiya-gaya/</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Maharashtra News: Shivchaturya Din Celebrated With Agra-To-Rajgad Cycle Yatra Flagged Off By Ashish Shelar</t>
+          <t>Maharashtra Politics: Ashish Shelar Slams Thackeray Rally As Theatrical, Draws Pahalgam Parallel; Kishori</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shivchaturya-din-celebrated-with-agra-to-rajgad-cycle-yatra-flagged-off-by-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ashish-shelar-slams-thackeray-rally-as-theatrical-draws-pahalgam-parallel-kishori-pednekar-hits-back</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Mahesh Kale’s ‘Abhangwari’ Unveiled by Ashish Shelar on Ashadi Ekadashi!</t>
+          <t>Mumbai: Siddhivinayak Temple Trust Felicitates Ashish Shelar For Declaring Ganeshotsav As State Festival</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-siddhivinayak-temple-trust-felicitates-ashish-shelar-for-declaring-ganeshotsav-as-state-festival</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror: BJP’s Shelar says some leaders ...</t>
+          <t>Maharashtra News: Shivchaturya Din Celebrated With Agra-To-Rajgad Cycle Yatra Flagged Off By Ashish Shelar</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shivchaturya-din-celebrated-with-agra-to-rajgad-cycle-yatra-flagged-off-by-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CM Fadnavis unveils emblem for Ganeshotsav to be celebrated as Rajya Mahotsav</t>
+          <t>Maharashtra: Gondan Kala To Enter Maharashtras Art Curriculum, Says Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/08/19/cm-fadnavis-unveils-emblem-for-ganeshotsav-to-be-celebrated-as-rajya-mahotsav/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-gondan-kala-to-enter-maharashtras-art-curriculum-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Ganeshotsav declared as ‘State Festival of Maharashtra’: Cultural Affairs Minister Ashish Shelar announces ...</t>
+          <t>Mumbai News: Relief For 86 Stalled SRA Projects As Residents Allowed To Appoint New Developers; Ashish Shelar</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-relief-for-86-stalled-sra-projects-as-residents-allowed-to-appoint-new-developers-ashish-shelar-reviews-progress</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Veteran actor Vivek Lagoo passes away, Maharashtra minister Ashish Shelar pays tribute</t>
+          <t>Maharashtra: BJP Leader Sudhir Mungantiwar Slams Ministers’ Absenteeism, Pushes For Ban On Alcohol At</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-leader-sudhir-mungantiwar-slams-ministers-absenteeism-pushes-for-ban-on-alcohol-at-heritage-forts</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Cultural Minister Ashish Shelar Gives Muhurat Clap for a Marathi Film ‘Ladki Bahin’!</t>
+          <t>Mumbai News: Minister Ashish Shelar Directs BMC To Submit 3-Month Action Plan For Desilting Powai, Tulsi And</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-directs-bmc-to-submit-3-month-action-plan-for-desilting-powai-tulsi-and-vihar-lakes</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Rajeev Shukla Replaces Jay Shah in ACC Leadership</t>
+          <t>No New Road Works After May 20, Ensure Motorable Roads Before Monsoon: Ashish Shelar To BMC</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
+          <t>https://www.freepressjournal.in/mumbai/no-new-road-works-after-may-20-ensure-motorable-roads-before-monsoon-ashish-shelar-to-bmc</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Minister Shelar inaugurates Gokhale bridge: After almost 2.5 years waiting, Andheri's Gokhale bridge second...</t>
+          <t>Pune: Maharashtra Declares Ganesh Festival as ‘State Festival,’ Plans Global Promotion: Ashish Shelar</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
+          <t>https://www.punekarnews.in/pune-maharashtra-declares-ganesh-festival-as-state-festival-plans-global-promotion-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>मुंबई में 2.5 लाख चूहों को मारने का दावा, जांच के आदेश, क्या है पूरा सच? आशिष शेलार</t>
+          <t>Hindi Not Mandatory in Maharashtra Schools, Marathi Remains Only Compulsory Language: Ashish Shelar</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
+          <t>https://www.freepressjournal.in/mumbai/hindi-not-mandatory-in-maharashtra-schools-marathi-remains-only-compulsory-language-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>गणेशोत्सव को मिला `राज्य महोत्सव` का दर्जा, सांस्कृतिक कार्य मंत्री आशिष शेलार ने किया बड़ा ऐलान</t>
+          <t>Mahesh Kale’s ‘Abhangwari’ Unveiled by Ashish Shelar on Ashadi Ekadashi!</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
+          <t>https://www.cinebuster.in/mahesh-kales-abhangwari-unveiled-by-ashish-shelar-on-ashadi-ekadashi/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा, मंत्री आशिष शेलार ने किया ऐलान</t>
+          <t>POP idol ban lifted: A triumph for artisans, says Maha Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/maharashtra-ganesh-utsav-latest-news-ashish-shelar-new-announcement/1248697/</t>
+          <t>https://www.thehawk.in/news/india/pop-idol-ban-lifted-a-triumph-for-artisans-says-maha-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+          <t>Maharashtra minister compares attacks on Hindi speakers to Pahalgam terror: BJP’s Shelar says some leaders ...</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+          <t>https://www.bhaskarenglish.in/national/news/maharashtra-minister-attacks-hindi-speakers-pahalgam-terror-bjp-asish-shelar-hindus-athawale-strict-action-mns-workers-135391577.html</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Hindi-Marathi Row: मराठी लोगों पर निशिकांत दुबे के बयान से भाजपा का किनारा, फडणवीस के मंत्री ने दी सख्त हिदायत</t>
+          <t>Ganeshotsav declared as ‘State Festival of Maharashtra’: Cultural Affairs Minister Ashish Shelar announces ...</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/ganeshotsav-declared-as-state-festival-of-maharashtra-cultural-affairs-minister-ashish-shelar-announces-in-assembly-highlights-lokmanya-tilaks-legacy-pop-idol-clearance-135417383.html</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>'शिवतीर्थ' पहुंचकर राज ठाकरे से मिले मुंबई बीजेपी अध्यक्ष, बीएमसी चुनावों में किससे हिसाब बराबर करेगी मनसे?</t>
+          <t>Cultural Minister Ashish Shelar Gives Muhurat Clap for a Marathi Film ‘Ladki Bahin’!</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
+          <t>https://www.cinebuster.in/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-marathi-film-ladki-bahin/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Maharashtra: मंत्री आशीष शेलार का बड़ा बयान- 'महाराष्ट्र में केवल मराठी अनिवार्य, हिंदी नहीं'</t>
+          <t>Veteran actor Vivek Lagoo passes away, Maharashtra minister Ashish Shelar pays tribute</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
+          <t>https://english.publictv.in/veteran-actor-vivek-lagoo-passes-away-maharashtra-minister-ashish-shelar-pays-tribute/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>`मुंबई हमारी है` बीजेपी नेता आशिष शेलार के दावे पर सुषमा अंधारे ने दिया करारा जवाब</t>
+          <t>Rajeev Shukla Replaces Jay Shah in ACC Leadership</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
+          <t>https://currentaffairs.adda247.com/rajeev-shukla-replaces-jay-shah-in-acc-leadership/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>अमित साटम को मुंबई BJP का अध्यक्ष नियुक्त किया गया</t>
+          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/amit-satam-appointed-as-mumbai-bjp-president-89721</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>राज ठाकरे के बयान पर आशीष शेलार बोले, 'पहलगाम में धर्म पूछकर मारा जाता है, यहां</t>
+          <t>Minister Shelar inaugurates Gokhale bridge: After almost 2.5 years waiting, Andheri's Gokhale bridge second...</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-inaugurates-gokhale-bridge-135011244.html</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के गणेशोत्सव को मिलेगा वैश्विक दर्जा, मंत्री आशीष शेलार ने की खास घोषणा</t>
+          <t>मुंबई में 2.5 लाख चूहों को मारने का दावा, जांच के आदेश, क्या है पूरा सच? आशिष शेलार</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-municipal-corporation-claim-of-killing-2-5-lakh-rats-investigation-ordered-ashish-shelar-raised-questions-ann-2968811</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Maharashtra: निशिकांत दुबे के बयान पर बीजेपी ने बनाई दूरी! आशीष शेलार बोले- 'मराठी व्यक्ति</t>
+          <t>गणेशोत्सव को मिला `राज्य महोत्सव` का दर्जा, सांस्कृतिक कार्य मंत्री आशिष शेलार ने किया बड़ा ऐलान</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-got-the-status-of-state-festival-cultural-affairs-minister-ashish-shelar-made-a-big-announcement-11272</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>सैफ अली खान पर हमले के बाद मंत्री आशीष शेलार का बड़ा बयान, 'बॅालीवुड वालों डरना...'</t>
+          <t>महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा, मंत्री आशिष शेलार ने किया ऐलान</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/bjp-leader-ashish-shelar-on-saif-ali-khan-news-and-mumbai-law-and-order-2864718</t>
+          <t>https://hindi.news24online.com/state/mumbai/maharashtra-ganesh-utsav-latest-news-ashish-shelar-new-announcement/1248697/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>आशीष शेलार की जगह कौन होगा मुंबई BJP का अगला अध्यक्ष? रेस में ये नाम सबसे आगे</t>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BJP सांसद निशिकांत दुबे के पटककर मारने वाले बयान पर उद्धव ठाकरे बोले, 'ऐसे कई लकड़बग्घे...'</t>
+          <t>Hindi-Marathi Row: मराठी लोगों पर निशिकांत दुबे के बयान से भाजपा का किनारा, फडणवीस के मंत्री ने दी सख्त हिदायत</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
+          <t>https://www.amarujala.com/india-news/hindi-marathi-row-bjp-sidelines-nishikant-dubey-statement-on-marathi-people-fadnavis-minister-ashish-shelar-gives-strict-instructions-2025-07-07</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>बीजेपी नेता आशीष शेलार के बयान से मची सियासी हलचल, बोले- 'राज ठाकरे और मैं...'</t>
+          <t>'शिवतीर्थ' पहुंचकर राज ठाकरे से मिले मुंबई बीजेपी अध्यक्ष, बीएमसी चुनावों में किससे हिसाब बराबर करेगी मनसे?</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/mumbai-politics-ashish-shelar-meets-raj-thackeray-at-shivtirth-dadar-know-mns-bmc-election-2025-strategy/articleshow/117125108.cms</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>शाहरुख खान के घर 'मन्नत' अचानक पहुंचे वन विभाग के अधिकारी, भड़की महाराष्ट्र सरकार</t>
+          <t>Maharashtra: मंत्री आशीष शेलार का बड़ा बयान- 'महाराष्ट्र में केवल मराठी अनिवार्य, हिंदी नहीं'</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
+          <t>https://www.abplive.com/states/maharashtra/minister-ashish-shelar-said-only-marathi-is-compulsory-in-maharashtra-not-hindi-ann-2967582</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले BJP का बड़ा फैसला, इस नेता को बनाया मुंबई का पार्टी अध्यक्ष</t>
+          <t>`मुंबई हमारी है` बीजेपी नेता आशिष शेलार के दावे पर सुषमा अंधारे ने दिया करारा जवाब</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/sushma-andhare-gave-a-befitting-reply-to-bjp-leader-ashish-shelar-s-claim-that-mumbai-is-ours-11248</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Saif Ali Khan attack case: Ashish Shelar dares Uddhav Thackeray to confront Mamata Banerjee over Bangladesh infiltration</t>
+          <t>राज ठाकरे के बयान पर आशीष शेलार बोले, 'पहलगाम में धर्म पूछकर मारा जाता है, यहां</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-slams-raj-thackeray-over-language-politics-third-language-marathi-violence-ann-2974821</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : आशीष शेलार ने सांस्कृतिक पुरस्कारों का किया ऐलान</t>
+          <t>महाराष्ट्र के गणेशोत्सव को मिलेगा वैश्विक दर्जा, मंत्री आशीष शेलार ने की खास घोषणा</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
+          <t>https://hindi.mid-day.com/news/india-news/article/ganeshotsav-will-get-global-status-minister-ashish-shelar-made-a-special-announcement-11243</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>4,066 new Aadhaar kits to be distributed to collector's office across Maharashtra: Minister Ashish Shelar</t>
+          <t>Maharashtra: निशिकांत दुबे के बयान पर बीजेपी ने बनाई दूरी! आशीष शेलार बोले- 'मराठी व्यक्ति</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
+          <t>https://www.abplive.com/states/maharashtra/bjp-ashish-shellar-reacted-on-nishikant-dubey-marathi-hindi-dispute-in-monsoon-legislative-session-ann-2975538</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>MLA: File report in 7 days on status of H-West rd works, finish them by May 31</t>
+          <t>आशीष शेलार की जगह कौन होगा मुंबई BJP का अगला अध्यक्ष? रेस में ये नाम सबसे आगे</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/who-will-new-mumbai-bjp-president-pravin-darekar-prasad-lad-and-ameet-satam-after-ashish-shelar-ann-2925629</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Worli BDD Chawl redevelopment residents will get their new homes before 'Shravan': Maharashtra Minister</t>
+          <t>Saif Ali Khan attack case: Ashish Shelar dares Uddhav Thackeray to confront Mamata Banerjee over Bangladesh infiltration</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-dares-uddhav-to-confront-mamata-banerjee-on-infiltration-of-bangladeshis-23468336</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार ने गणेशोत्सव गीत और पोर्टल का किया शुभारंभ, नागरिकों से भागीदारी की अपील</t>
+          <t>BJP सांसद निशिकांत दुबे के पटककर मारने वाले बयान पर उद्धव ठाकरे बोले, 'ऐसे कई लकड़बग्घे...'</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/minister-ashish-shelar-launched-ganeshotsav-song-and-portal-appealed-to-citizens-for-participation-1328512.html</t>
+          <t>https://www.abplive.com/states/maharashtra/uddhav-thackeray-and-aditya-thackeray-slam-nishikant-dubey-marathi-hindi-dispute-call-him-hyena-ann-2975341</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ऐतिहासिक धरोहरें होंगी सुरक्षित, मंत्री शेलार का ऐलान-दस्तावेजों के संरक्षण को सरकार देगी मदद</t>
+          <t>बीजेपी नेता आशीष शेलार के बयान से मची सियासी हलचल, बोले- 'राज ठाकरे और मैं...'</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/maharashtra-historical-heritage-will-be-protected-minister-shelar-announced-government-will-help-in-preservation-of-documents-1324840.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-bjp-on-raj-thackeray-said-we-are-no-more-friend-mumbai-maharashtra-ann-2928862</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>दुनिया में होगी महाराष्ट्र के गणेशोत्सव की धूम, आशीष शेलार कहा इसे बनाएंगे वर्ल्ड क्लास</t>
+          <t>शाहरुख खान के घर 'मन्नत' अचानक पहुंचे वन विभाग के अधिकारी, भड़की महाराष्ट्र सरकार</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/maharashtras-ganeshotsav-will-become-world-class-1325768.html</t>
+          <t>https://www.abplive.com/states/maharashtra/forest-department-officials-reached-shah-rukh-khan-house-mannat-maharashtra-government-angry-ann-2966647</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>मुंबई भाजपा अध्यक्ष पद पर अमित साटम की नियुक्ति, फडणवीस और शेलार ने दी बधाई</t>
+          <t>BMC चुनाव से पहले BJP का बड़ा फैसला, इस नेता को बनाया मुंबई का पार्टी अध्यक्ष</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/bjp-mumbai-amit-satam-ashish-shelar-devendra-fadnavis-54-807644</t>
+          <t>https://www.abplive.com/states/maharashtra/mumbai-gets-new-bjp-chief-ameet-satam-before-bmc-election-2025-ann-3001053</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Maharashtras First International Marathi Film Festival, Chitrapataka, Begins April 21; Cultural Affairs</t>
+          <t>महाराष्ट्र : आशीष शेलार ने सांस्कृतिक पुरस्कारों का किया ऐलान</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtras-first-international-marathi-film-festival-chitrapataka-begins-april-21-cultural-affairs-minister-ashish-shelar-reveals-emblem</t>
+          <t>https://www.deshbandhu.co.in/maharashtra-ashish-shelar-announced-cultural-awards-549740-1</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Visits Cellular Jail, Seeks Support For Veer Savarkar Memorial In Andaman</t>
+          <t>4,066 new Aadhaar kits to be distributed to collector's office across Maharashtra: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-visits-cellular-jail-seeks-support-for-veer-savarkar-memorial-in-andaman-islands</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/4066-new-aadhaar-kits-to-be-distributed-to-collectors-across-maharashtra-minister-ashish-shelar-23474937</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Mumbai News: Displaced Residents Near Elphinstone Bridge To Get Redeveloped Homes At Same Location, Announces</t>
+          <t>मंत्री आशीष शेलार ने गणेशोत्सव गीत और पोर्टल का किया शुभारंभ, नागरिकों से भागीदारी की अपील</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-displaced-residents-near-elphinstone-bridge-to-get-redeveloped-homes-at-same-location-announces-minister-ashish-shelar-video</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/minister-ashish-shelar-launched-ganeshotsav-song-and-portal-appealed-to-citizens-for-participation-1328512.html</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>VIDEO: Uddhav Thackerays Party Failed To improve Mumbais Stormwater Drain System Despite ₹1 Lakh Crore</t>
+          <t>ऐतिहासिक धरोहरें होंगी सुरक्षित, मंत्री शेलार का ऐलान-दस्तावेजों के संरक्षण को सरकार देगी मदद</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-uddhav-thackerays-party-failed-to-improve-mumbais-stormwater-drain-system-despite-1-lakh-crore-spend-says-minister-ashish-shelar</t>
+          <t>https://navbharatlive.com/maharashtra/maharashtra-historical-heritage-will-be-protected-minister-shelar-announced-government-will-help-in-preservation-of-documents-1324840.html</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Mumbai: Iconic Sword of Raghuji Bhonsle Arrives from London; Bike Rally Cancelled Due to Rains, Grand...</t>
+          <t>दुनिया में होगी महाराष्ट्र के गणेशोत्सव की धूम, आशीष शेलार कहा इसे बनाएंगे वर्ल्ड क्लास</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-iconic-sword-of-raghuji-bhonsle-arrives-from-london-bike-rally-cancelled-due-to-rains-grand-inauguration-tonight-a525/</t>
+          <t>https://navbharatlive.com/maharashtra/pune/maharashtras-ganeshotsav-will-become-world-class-1325768.html</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Vikram Gaikwad Death: Maharashtra Deputy CM Eknath Shinde, Ashish Shelar Express Condolences</t>
+          <t>मुंबई भाजपा अध्यक्ष पद पर अमित साटम की नियुक्ति, फडणवीस और शेलार ने दी बधाई</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/national-award-winning-makeup-artist-vikram-gaikwad-passes-away-in-mumbai-maharashtra-deputy-cm-eknath-shinde-expresses-condolences</t>
+          <t>https://mpbreakingnews.in/maharashtra/bjp-mumbai-amit-satam-ashish-shelar-devendra-fadnavis-54-807644</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Ganeshotsav 2025: Maharashtra Govt Gears Up For Grand Celebrations; Awards For Mandals, Drone Shows At Girgaon</t>
+          <t>महाराष्ट्र में पूर्व प्रधानमंत्री अटल बिहारी वाजपेयी के नाम से दिया विशेष भाषा शिखर सम्मान, मंत्री आशीष शेलार ने किया ऐलान</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ganeshotsav-2025-maharashtra-govt-gears-up-for-grand-celebrations-awards-for-mandals-drone-shows-at-girgaon-chowpatty-announced</t>
+          <t>https://navbharatlive.com/maharashtra/distribution-of-prestigious-awards-of-maharashtra-state-hindi-sahitya-academy-1158303.html</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>From 'jihadi gathering' to ‘no real brotherhood’: BJP on Uddhav-Raj Thackeray reunion</t>
+          <t>Maharashtras First International Marathi Film Festival, Chitrapataka, Begins April 21; Cultural Affairs</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtras-first-international-marathi-film-festival-chitrapataka-begins-april-21-cultural-affairs-minister-ashish-shelar-reveals-emblem</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>BJP leader likens attacks on non-Marathi speakers to Pahalgam massacre</t>
+          <t>Maharashtra Minister Ashish Shelar Visits Cellular Jail, Seeks Support For Veer Savarkar Memorial In Andaman</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-visits-cellular-jail-seeks-support-for-veer-savarkar-memorial-in-andaman-islands</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BCCI announces Rajeev Shukla, Ashish Shelar as new representatives for ACC Board</t>
+          <t>Mumbai News: Displaced Residents Near Elphinstone Bridge To Get Redeveloped Homes At Same Location, Announces</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://www.storyboard18.com/brand-makers/bcci-announces-rajeev-shukla-ashish-shelar-as-new-representatives-for-acc-board-58707.htm</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-displaced-residents-near-elphinstone-bridge-to-get-redeveloped-homes-at-same-location-announces-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Rajeev Shukla, Ashish Shelar To Represent India In Asian Cricket Council</t>
+          <t>Vikram Gaikwad Death: Maharashtra Deputy CM Eknath Shinde, Ashish Shelar Express Condolences</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://www.news18.com/cricket/rajeev-shukla-ashish-shelar-to-represent-india-in-asian-cricket-council-9253383.html</t>
+          <t>https://www.freepressjournal.in/mumbai/national-award-winning-makeup-artist-vikram-gaikwad-passes-away-in-mumbai-maharashtra-deputy-cm-eknath-shinde-expresses-condolences</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Maharashtra minister condemns assault on Hindi-speaking people, draws parallel with Pahalgam attack</t>
+          <t>Ganeshotsav 2025: Maharashtra Govt Gears Up For Grand Celebrations; Awards For Mandals, Drone Shows At Girgaon</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-minister-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack/articleshow/122281220.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/ganeshotsav-2025-maharashtra-govt-gears-up-for-grand-celebrations-awards-for-mandals-drone-shows-at-girgaon-chowpatty-announced</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Fresh tussle between Shiv Sena and BJP over Marathi films</t>
+          <t>BJP leader likens attacks on non-Marathi speakers to Pahalgam massacre</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/fresh-tussle-between-shiv-sena-and-bjp-over-marathi-films-10155696/</t>
+          <t>https://www.tribuneindia.com/news/india/bjp-leader-likens-attacks-on-non-marathi-speakers-to-pahalgam-massacre/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Mumbai BJP unit likely to get new president ahead of BMC polls</t>
+          <t>MLA: File report in 7 days on status of H-West rd works, finish them by May 31</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/mumbai-bjp-unit-new-president-bmc-polls-10165826/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mla-file-report-in-7-days-on-status-of-h-west-rd-works-finish-them-by-may-31/articleshow/120072611.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir's 'SUR Music' Label</t>
+          <t>BCCI announces Rajeev Shukla, Ashish Shelar as new representatives for ACC Board</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
+          <t>https://www.storyboard18.com/brand-makers/bcci-announces-rajeev-shukla-ashish-shelar-as-new-representatives-for-acc-board-58707.htm</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Shelar orders swift action to curb bird menace near CSMIA</t>
+          <t>Rajeev Shukla, Ashish Shelar To Represent India In Asian Cricket Council</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-orders-swift-action-to-curb-bird-menace-near-csmia-101750878843102.html</t>
+          <t>https://www.news18.com/cricket/rajeev-shukla-ashish-shelar-to-represent-india-in-asian-cricket-council-9253383.html</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Nearly 60% of bakeries in Mumbai yet to switch to cleaner fuel</t>
+          <t>Maharashtra minister condemns assault on Hindi-speaking people, draws parallel with Pahalgam attack</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/nearly-60-of-bakeries-in-mumbai-yet-to-switch-to-cleaner-fuel-10088723/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/maharashtra-minister-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack/articleshow/122281220.cms</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Raghuji Bhonsale’s legendary sword set to arrive in Mumbai tomorrow, ‘darshan’ ceremony to be held at PL Deshpande Maharashtra Kala Academy</t>
+          <t>Hariharan Pt.Hariprasad Chaurasia, Ashish Shelar and Javed Ali Unite for Global Launch of Rajeev Mahavir's 'SUR Music' Label</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/raghuji-bhonsales-legendary-sword-mumbai-10194874/</t>
+          <t>https://www.indianewscalling.com/news/172161-hariharan-pthariprasad-chaurasia-ashish-shelar-and-javed-ali-unite-for-global-launch-of-rajeev-mah.aspx</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Maharashtra Cultural Minister Ashish Shelar inaugurates Kala Ghoda Arts Festival 2025</t>
+          <t>How was ‘Khalid Ka Shivaji’ sent to Cannes Film Festival, asks Maharashtra cultural minister Shelar</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/articleshow/123172379.cms</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Minister links Mira Road assault to Pahalgam attack</t>
+          <t>16,343 malnourished children in Mumbai suburb: Survey</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
+          <t>https://www.thehindu.com/sci-tech/health/16343-malnourished-children-in-mumbai-suburb-survey/article69412453.ece</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>BJP names three-term MLA Ameet Satam as Mumbai chief before BMC polls</t>
+          <t>Reema Lagoos Ex-Husband And Veteran Actor Vivek Lagoo Dies, Last Rites To Be Held Today; Maharashtra Minister Ashish Shelar Pays Tribute</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://tripuratimes.com/ttimes/bjp-names-three-term-mla-ameet-satam-as-mumbai-chief-before-bmc-polls-30851.html/</t>
+          <t>https://zeenews.india.com/people/reema-lagoos-ex-husband-and-veteran-actor-vivek-lagoo-dies-last-rites-to-be-held-today-maharashtra-minister-ashish-shelar-pays-tribute-2918710.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Maharashtra's Ganesh Festival: Celebrating India's Valor</t>
+          <t>It's a Public Appeasement Campaign: BJP on Thackerays Reunion</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3548452-maharashtras-ganesh-festival-celebrating-indias-valor</t>
+          <t>https://www.deccanchronicle.com/nation/politics/its-a-public-appeasement-campaign-bjp-on-thackerays-reunion-1889545</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PoP idol-making supports livelihood of Maharashtra artisans, experts to study issue: Shelar</t>
+          <t>BJP likely to appoint new Mumbai chief ahead of BMC polls</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/pop-idol-making-supports-livelihood-of-maharashtra-artisans-experts-to-study-issue-shelar/2544248/</t>
+          <t>https://www.moneycontrol.com/news/india/bjp-likely-to-appoint-new-mumbai-chief-ahead-of-bmc-polls-13375950.html</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Mumbai News: BJP To Celebrate Maharashtra Day And Labour Day At 106 Locations Under Minister Ashish Shelars</t>
+          <t>How was ‘Khalid Ka Shivaji’ sent to Cannes Film Festival, asks Maharashtra cultural minister Shelar</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bjp-to-celebrate-maharashtra-day-and-labour-day-at-106-locations-under-minister-ashish-shelars-leadership</t>
+          <t>http://www.msn.com/en-in/entertainment/bollywood/how-was-khalid-ka-shivaji-sent-to-cannes-film-festival-asks-maharashtra-cultural-minister-shelar/ar-AA1K6y4Q?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Second Arm Of Andheris Gokhale Bridge Inaugurated, Minister Ashish Shelar Hails Fast-Track Completion As</t>
+          <t>Barely 10% nullah desilting work completed in 35 days: Shelar</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/second-arm-of-andheris-gokhale-bridge-inaugurated-minister-ashish-shelar-hails-fast-track-completion-as-success-story-see-pics</t>
+          <t>https://indianexpress.com/article/cities/mumbai/barely-10-nullah-desilting-work-completed-in-35-days-shelar-9991132/</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Criticises Desilting Works In Mumbai, Demands Accountability From</t>
+          <t>BJP's Nishikant Dubey dares Uddhav, Raj Thackeray to visit north India, Tamil Nadu | Reactions so far</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors</t>
+          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Mumbai News: Minister Ashish Shelar Seeks Centre’s Help As Water Tanker Strike Looms Over CGWA License Row</t>
+          <t>New Mumbai BJP chief Ameet Satam is 3-time MLA with corporate background, Thackeray critic</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-seeks-centres-help-as-water-tanker-strike-looms-over-cgwa-license-row</t>
+          <t>https://theprint.in/politics/new-mumbai-bjp-chief-ameet-satam-is-3-time-mla-with-corporate-background-thackeray-critic/2728464/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ashish Shelar hails 60 years of Marathi film awards at Diamond Jubilee event</t>
+          <t>Amit Satam Takes Charge as Mumbai BJP President Ahead of Crucial BMC Elections</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://thenewsmill.com/2025/08/ashish-shelar-hails-60-years-of-marathi-film-awards-at-diamond-jubilee-event/</t>
+          <t>https://www.devdiscourse.com/article/politics/3601925-amit-satam-takes-charge-as-mumbai-bjp-president-ahead-of-crucial-bmc-elections</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
+          <t>Worli BDD Chawl redevelopment residents will get their new homes before 'Shravan': Maharashtra Minister</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-suburban-guardian-minister-says-worli-bdd-chawl-redevelopment-residents-will-get-their-homes-before-shravan-23554712</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Mumbai To House New Cultural Centre And Museum Celebrating Maharashtra’s Heritage, Says Minister Ashish</t>
+          <t>Mumbai To Get Rid of Flood-Like Situations? New Plan Announced After 180 mm Rainfall Chaos</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-to-house-new-cultural-centre-and-museum-celebrating-maharashtras-heritage-says-minister-ashish-shelar</t>
+          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Concerns Of Residents Affected By Elphinstone Bridge Demolition Will Be Addressed, Assures Mumbai Suburban</t>
+          <t>Maharashtra govt declares ‘Sarvajanik Ganeshotsav’ as state festival; says it will ‘bear expenses for grand celebrations’</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/concerns-of-residents-affected-by-elphinstone-bridge-demolition-will-be-addressed-assures-mumbai-suburban-guardian-minister-ashish-shelar</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-govt-declares-sarvajanik-ganeshotsav-as-state-festival-10118535/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Maharashtra Minister Ashish Shelar Proposes Grand National Memorial For Veer Savarkar At Andaman’s Cellular</t>
+          <t>Dahi Handi on August 16: Maharashtra govt has a unique gift for 1.5 lakh Govindas</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-proposes-grand-national-memorial-for-veer-savarkar-at-andamans-cellular-jail</t>
+          <t>https://www.cnbctv18.com/travel/culture/dahi-handi-on-august-16-maharashtra-govt-has-a-unique-gift-for-1-5-lakh-govindas-19639524.htm</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Maharashtra Forms Task Force To Establish Indias First Artificial Intelligence University, Says IT Minister</t>
+          <t>Forest department officials suddenly reached Shahrukh Khan's house 'Mannat', Maharashtra government got angry. ..?</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-forms-task-force-to-establish-indias-first-artificial-intelligence-university-says-it-minister-ashish-shelar</t>
+          <t>https://www.indiaherald.com/Breaking/Read/994828609/Forest-department-officials-suddenly-reached-Shahrukh-Khans-house-Mannat-Maharashtra-government-got-angry-</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>No New Road Works After May 20, Ensure Motorable Roads Before Monsoon: Ashish Shelar To BMC</t>
+          <t>Second Arm Of Andheris Gokhale Bridge Inaugurated, Minister Ashish Shelar Hails Fast-Track Completion As</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/no-new-road-works-after-may-20-ensure-motorable-roads-before-monsoon-ashish-shelar-to-bmc</t>
+          <t>https://www.freepressjournal.in/mumbai/second-arm-of-andheris-gokhale-bridge-inaugurated-minister-ashish-shelar-hails-fast-track-completion-as-success-story-see-pics</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Mumbai News: PoP Ganesh Idol Makers Protest Bombay HC Ban; Minister Shelar Backs Artisans</t>
+          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-pop-ganesh-idol-makers-protest-bombay-hc-ban-minister-shelar-backs-artisans</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>"Only Marathi Is Mandatory In Maharashtra Schools, Not Hindi": Minister</t>
+          <t>Marathi mandatory in Maharashtra, not Hindi: Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
+          <t>https://www.thehawk.in/news/india/marathi-mandatory-in-maharashtra-not-hindi-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Maharashtra To Extend Official Curriculum Support To Marathi Schools In US</t>
+          <t>Sword of Maratha glory returns after two centuries: Maharashtra minister Shelar brings home Raghuji ...</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/sword-of-maratha-glory-returns-after-two-centuries-maharashtra-brings-home-raghuji-bhosales-legendary-weapon-from-london-auction-135656002.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Amid Language Row At Home, Maharashtra Govt To Provide Curriculum To Marathi Schools In US</t>
+          <t>Minister Shelar sets-up 52-foot Kashi Vishwanath Temple replica in Mumbai: Pays grand tribute to social ref...</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.news18.com/india/amid-language-row-at-home-maharashtra-govt-to-provide-curriculum-to-marathi-schools-in-us-ws-l-9462862.html</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/bandra-ganeshotsav-mandal-kashi-vishwanath-temple-replica-celebrates-ahilyabai-holkar-300-birth-anniversary-rajya-mahotsav-135765190.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>अमेरिकेतील मराठी शाळांना महाराष्ट्र सरकारतर्फे अभ्यासक्रम पुरवणार; आशिष शेलारांचे आश्वासन</t>
+          <t>"Only Marathi Is Mandatory In Maharashtra Schools, Not Hindi": Minister</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/international/bjp-minister-ashish-shelar-on-america-tour-said-maharashtra-government-will-provide-curriculum-to-marathi-schools-in-america-a-a719/</t>
+          <t>https://www.ndtv.com/india-news/only-marathi-is-mandatory-in-maharashtra-schools-not-hindi-minister-ashish-shelar-8742499</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ashish Shelar : पहलगाममध्ये धर्म विचारून हिंदूंना गोळ्या मारल्या अन् इथे निष्पाप हिंदूंना</t>
+          <t>Maharashtra To Extend Official Curriculum Support To Marathi Schools In US</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
+          <t>https://www.ndtv.com/education/maharashtra-to-extend-official-curriculum-support-to-marathi-schools-in-us-8948091</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Avinash Jadhav on Ashish Shelar : आशिष शेलारांकडून मनसेच्या मराठी भाषा आंदोलनाची पहलगाम हल्ल्याशी</t>
+          <t>Amid Language Row At Home, Maharashtra Govt To Provide Curriculum To Marathi Schools In US</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
+          <t>https://www.news18.com/india/amid-language-row-at-home-maharashtra-govt-to-provide-curriculum-to-marathi-schools-in-us-ws-l-9462862.html</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>मुंबई भाजपच्या अध्यक्षपदी आशिष शेलार कायम राहणार?</t>
+          <t>अमेरिकेतील मराठी शाळांना महाराष्ट्र सरकारतर्फे अभ्यासक्रम पुरवणार; आशिष शेलारांचे आश्वासन</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/will-ashish-shelar-continue-as-mumbai-bjp-president-a-a285-c941/</t>
+          <t>https://www.lokmat.com/international/bjp-minister-ashish-shelar-on-america-tour-said-maharashtra-government-will-provide-curriculum-to-marathi-schools-in-america-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>BMC Election : मनसैनिकांची तुलना पहलगामच्या दहशतवाद्यांशी, आशिष शेलारांचा तोल कसा सुटला? की</t>
+          <t>Ashish Shelar : पहलगाममध्ये धर्म विचारून हिंदूंना गोळ्या मारल्या अन् इथे निष्पाप हिंदूंना</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-compares-mns-marathi-language-andolan-to-pahalgam-terrorist-attack-maharashtra-politics-marathi-news-1368452</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>राज्यातील भजनी मंडळांना शासनाकडून २५ हजार</t>
+          <t>Avinash Jadhav on Ashish Shelar : आशिष शेलारांकडून मनसेच्या मराठी भाषा आंदोलनाची पहलगाम हल्ल्याशी</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-announced-grant-of-rs-25000-for-1800-bhajani-mandals-across-maharashtra-for-ganesh-festival-zws-70-5324659/</t>
+          <t>https://marathi.abplive.com/news/politics/avinash-jadhav-on-ashish-shelar-compares-mns-marathi-language-movement-to-pahalgam-terror-attack-maharashtra-politics-marathi-news-1368295</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Ashish Shelar : अहो ‘बाता’शिष शेलार… मुंबईची तुंबई होताच ठाकरेंच्या सेनेकडून...</t>
+          <t>मुंबई भाजपच्या अध्यक्षपदी आशिष शेलार कायम राहणार?</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
+          <t>https://www.lokmat.com/mumbai/will-ashish-shelar-continue-as-mumbai-bjp-president-a-a285-c941/</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Mumbai BEST Elections Result: मुंबई ही आमचीच...! बेस्टच्या निकालानंतर शेलारांनी BMC साठी शड्डू ठोकला, ठाकरे...</t>
+          <t>BMC Election : मनसैनिकांची तुलना पहलगामच्या दहशतवाद्यांशी, आशिष शेलारांचा तोल कसा सुटला? की</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-ashish-shelar-statement-on-raj-thackeray-mns-comparison-to-pahalgam-terrorist-maharashtra-marathi-news-1368362</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>कोल्हापुरात जुन्या मराठी चित्रपटांचे मोफत प्रदर्शन; ॲड. आशिष शेलार</t>
+          <t>राज्यातील भजनी मंडळांना शासनाकडून २५ हजार</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/ashish-shelar-announces-free-screening-of-old-marathi-films-in-kolhapur-news-amy-95-5196886/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-announced-grant-of-rs-25000-for-1800-bhajani-mandals-across-maharashtra-for-ganesh-festival-zws-70-5324659/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>मराठी चित्रपटांसाठी महाराष्ट्र सरकार थेट Netflix च्या अमेरिकेतील हेडक्वॉर्टर्समध्ये पोहोचलं; अमेरिका...</t>
+          <t>Ashish Shelar : अहो ‘बाता’शिष शेलार… मुंबईची तुंबई होताच ठाकरेंच्या सेनेकडून...</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
+          <t>https://www.tv9marathi.com/videos/uddhav-thackeray-shiv-sena-protested-sarcastic-banner-against-bjp-ashish-shelar-in-mumbai-bandra-area-1413171.html</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>मराठी आंदोलनाची ‘पहलगाम’शी तुलना, आशीष शेलार यांच्या विधानामुळे वाद; विरोधकांचे टीकास्त्र</t>
+          <t>Mumbai BEST Elections Result: मुंबई ही आमचीच...! बेस्टच्या निकालानंतर शेलारांनी BMC साठी शड्डू ठोकला, ठाकरे...</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-compared-marathi-movement-with-pahalgam-terrorist-attack-css-98-5209656/</t>
+          <t>https://news18marathi.com/maharashtra/mumbai-best-elections-result-bjp-leader-ashish-shelar-first-reaction-challenge-to-uddhav-thackeray-and-raj-thackeray-bmc-elections-1462147.html</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meets Ashish Shelar : आशिष शेलारांच्या कार्यालयाच्या बाहेरूनच अमित ठाकरे म्हणाले,</t>
+          <t>निवडणुका आणि सत्तेसाठी पक्ष फोडता, भ्रष्टाचाऱ्यांना शुद्ध करून पक्षात घेता,</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>मुंबई भाजपा पदाधिकाऱ्यांमध्ये राडा; आशिष शेलार कारमधून उतरताच दोन गटांत हाणामारी</t>
+          <t>Ashish Shelar: रघुजी भोसलेंची तलवार परत मिळवण्यात यश | Marathi News</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mumbai-bjp-office-bearers-clash-in-front-of-ashish-shelar-car-a-fight-broke-out-between-two-groups-at-kandivali-a-a629/</t>
+          <t>https://lokmat.news18.com/videos/video/ashish-shelar-success-in-regaining-raghuji-bhosle-s-sword-marathi-news-1043330.html</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ashish Shelar praises Raj Thackeray : राज ठाकरेंचा 'दानपट्टा' फिरणार? 'मनसे'च्या गुढीपाडवा मेळाव्यापूर्वीच भाजप मंत्री शेलारांनी गोंजारलं</t>
+          <t>कोल्हापुरात जुन्या मराठी चित्रपटांचे मोफत प्रदर्शन; ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-minister-ashish-shelar-praises-raj-thackeray-at-marathi-film-event-mumbai-pp82</t>
+          <t>https://www.loksatta.com/kolhapur/ashish-shelar-announces-free-screening-of-old-marathi-films-in-kolhapur-news-amy-95-5196886/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Ashish Shelar : कांदिवलीत मंत्री आशिष शेलारांसमोर भाजपच्या दोन गटात राडा; नेमकं प्रकरण काय?</t>
+          <t>मराठी आंदोलनाची ‘पहलगाम’शी तुलना, आशीष शेलार यांच्या विधानामुळे वाद; विरोधकांचे टीकास्त्र</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-compared-marathi-movement-with-pahalgam-terrorist-attack-css-98-5209656/</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>“राज्यात सक्ती फक्त मराठीची, हिंदीची नाही; चर्चा अवास्तव, अवाजवी, अतार्किक”: आशिष शेलार</t>
+          <t>मराठी चित्रपटांसाठी महाराष्ट्र सरकार थेट Netflix च्या अमेरिकेतील हेडक्वॉर्टर्समध्ये पोहोचलं; अमेरिका...</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-said-compulsion-in-the-state-is-only-marathi-not-hindi-and-the-discussion-is-unrealistic-unreasonable-illogical-a-a719/</t>
+          <t>https://zeenews.india.com/marathi/entertainment/ashish-shelar-talks-about-demand-raised-for-marathi-movie-during-visit-to-netflix-office-in-usa-los-angeles/930085</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Bala Nandgaonkar:आजच्या तारखेला अख्ख्या भारतात आशिष शेलार साहेब एक नंबरचे वक्ते बाळा नांदगावकरांचा</t>
+          <t>Amit Thackeray Meets Ashish Shelar : आशिष शेलारांच्या कार्यालयाच्या बाहेरूनच अमित ठाकरे म्हणाले,</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-statement-after-meeting-ashish-shelar-says-citizens-gave-power-in-nashik-now-give-opportunity-in-mumbai-maharashtra-politics-marathi-news-1379236</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>मराठी माणसाने काळानुरुप नाट्यकलेत नवनवीन प्रयोग केले – ॲड. आशिष शेलार</t>
+          <t>मुंबई भाजपा पदाधिकाऱ्यांमध्ये राडा; आशिष शेलार कारमधून उतरताच दोन गटांत हाणामारी</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-says-marathi-people-experimented-new-ways-of-performing-arts-mumbai-print-news-css-98-5158726/</t>
+          <t>https://www.lokmat.com/mumbai/mumbai-bjp-office-bearers-clash-in-front-of-ashish-shelar-car-a-fight-broke-out-between-two-groups-at-kandivali-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ चित्रपटासंदर्भात आशिष शेलार आक्रमक; सेन्सॉर बोर्डाचा उल्लेख केला, थेट फेरविचार करण्याचे आदेश..</t>
+          <t>Arun Gawli : डॉन अरुण गवळींची कन्या भाजपच्या वाटेवर? महापालिका निवडणुकीत मोठी घडामोड,</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-is-aggressive-regarding-the-film-khalid-ka-shivaji-mumbai-print-news-phm-00-5285093/</t>
+          <t>https://marathi.abplive.com/news/mumbai/geeta-gawli-meet-ashish-shelar-mumbai-gangster-arun-gawli-daughter-daughter-bjp-meeting-bmc-election-marathi-news-1364407</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Ashish Shelar : ठाकरे बंधूंच्या विजय मेळाव्यावर आशीष शेलार यांची खोचक टीका</t>
+          <t>Ashish Shelar praises Raj Thackeray : राज ठाकरेंचा 'दानपट्टा' फिरणार? 'मनसे'च्या गुढीपाडवा मेळाव्यापूर्वीच भाजप मंत्री शेलारांनी गोंजारलं</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-minister-ashish-shelar-praises-raj-thackeray-at-marathi-film-event-mumbai-pp82</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>शून्य + शून्य = भोपळा; आशिष शेलारांचा मनसे-उबाठावर घणाघात</t>
+          <t>‘खालिद का शिवाजी’ चित्रपटासंदर्भात आशिष शेलार आक्रमक; सेन्सॉर बोर्डाचा उल्लेख केला, थेट फेरविचार करण्याचे आदेश..</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/pune-news-bjp-mumbai-president-ashish-shelar-strongly-criticized-the-opposition-while-speaking-to-moderates-in-pune-after-the-best-election-results-a-a1008/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-is-aggressive-regarding-the-film-khalid-ka-shivaji-mumbai-print-news-phm-00-5285093/</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>“मुंबईकर उद्धव ठाकरेंना त्यांची जागा दाखवतील, मविआच्या ५० जागाही येणार नाही”; भाजपाचा दावा</t>
+          <t>Ashish Shelar : कांदिवलीत मंत्री आशिष शेलारांसमोर भाजपच्या दोन गटात राडा; नेमकं प्रकरण काय?</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-and-said-mahayuti-to-win-upcoming-mumbai-municipal-corporation-election-a-a719/</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-fight-between-bjp-workers-in-kandivali-news-in-marathi/892529/</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>विद्यार्थ्यांमधील असमानता दूर करण्यासाठी त्रिभाषा सूत्र स्वीकारले, मंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+          <t>“राज्यात सक्ती फक्त मराठीची, हिंदीची नाही; चर्चा अवास्तव, अवाजवी, अतार्किक”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-three-language-formula-ashish-shelar-on-third-language-debate-schools-policy-mumbai-print-news-vsd-99-5179405/</t>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-said-compulsion-in-the-state-is-only-marathi-not-hindi-and-the-discussion-is-unrealistic-unreasonable-illogical-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज्य शासना तर्फे गतवर्षापासून आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव होणार</t>
+          <t>Bala Nandgaonkar:आजच्या तारखेला अख्ख्या भारतात आशिष शेलार साहेब एक नंबरचे वक्ते बाळा नांदगावकरांचा</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ashish-shelar-announces-international-marathi-film-festival/32779</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bala-nandgaonkar-take-jibe-on-ashish-shelar-says-he-is-number-one-speaker-in-the-whole-of-india-marathi-news-update-1368253</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+          <t>शून्य + शून्य = भोपळा; आशिष शेलारांचा मनसे-उबाठावर घणाघात</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+          <t>https://www.lokmat.com/pune/pune-news-bjp-mumbai-president-ashish-shelar-strongly-criticized-the-opposition-while-speaking-to-moderates-in-pune-after-the-best-election-results-a-a1008/</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ashish Shelar: रघुजी भोसलेंची तलवार परत मिळवण्यात यश | Marathi News</t>
+          <t>Ashish Shelar : ठाकरे बंधूंच्या विजय मेळाव्यावर आशीष शेलार यांची खोचक टीका</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ashish-shelar-success-in-regaining-raghuji-bhosle-s-sword-marathi-news-1043330.html</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-slams-mns-shivsena-vijay-mela-1436197.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मनसेच्या आंदोलनाची तुलना पहलगाम हल्ल्याशी; आशीष शेलारांचं मोठं विधान</t>
+          <t>Ashish Shelar : राज ठाकरे यांच्या ‘हिंदी’ विरोधानंतर आशिष शेलार आक्रमक; म्हणाले, जरा...</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ashish-shelar-slams-mns-raj-thackeray-on-hindi-language-compulsory-in-maharashtra-school-curriculum-1386802.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>शेलारजी फार डिंग्या मारू नका, बेस्ट निवडणुकीतही तुम्ही तीर मारले नाहीत. तुम्हाला</t>
+          <t>‘धारावीतील १ इंचही जागा अदानीला देणार नाही ’</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
+          <t>https://www.lokmat.com/mumbai/not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-says-ashish-shelar-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>कान फिल्म फेस्टिव्हलमध्ये 'या' चार मराठी सिनेमांची झाली निवड, सांस्कृतिक मंत्री आशिष शेलार यांची घोषणा</t>
+          <t>राज्य शासनातर्फे यंदा आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/marathi-cinema/four-marathi-films-have-been-selected-for-the-cannes-film-festival-announced-by-cultural-minister-ashish-shelar-a-a998/</t>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/marathi-film-festival-in-2025-ashish-shelar-announced-rajya-shasan-marathi-movie-nomination-a-a998/</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>राज ठाकरेंच्या ‘त्या’ टीकेला शेलारांचं खोचक प्रत्युत्तर; म्हणाले ज्यांना निवडून येता येत...</t>
+          <t>Ashish Shelar : राज्य शासना तर्फे गतवर्षापासून आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव होणार</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/ashish-shelar-announces-international-marathi-film-festival/32779</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>सांस्कृतिक मंत्री म्हणतात ” पोळा करा, शहरी नक्षलवाद संपवा”</t>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/wardha-to-end-urban-naxalism-traditional-festivals-like-bail-pola-must-be-celebrated-with-enthusiasm-adv-ashish-shelar-sud-02-5325172/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रयत्न - आशिष शेलार</t>
+          <t>आगामी महापौर भाजपाचा होण्यासाठी कार्यकर्त्यानी सज्ज राहा- आशिष शेलार</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/efforts-to-get-unesco-cultural-status-for-ganeshotsav-ashish-shelar-a-a727/</t>
+          <t>https://www.lokmat.com/mumbai/workers-should-be-ready-to-become-the-next-mayor-of-bjp-ashish-shelar-a-a840-c1012/</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ते मुंबईतल्या लँड स्कॅमचे…बड्या नेत्याचे उद्धव ठाकरेंवर खळबळजनक आरोप!</t>
+          <t>Ashish Shelar : मनसेच्या आंदोलनाची तुलना पहलगाम हल्ल्याशी; आशीष शेलारांचं मोठं विधान</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-said-uddhav-thackeray-is-baadshah-of-land-scam-amid-bmc-election-2025-1389756.html</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-compares-mumbai-mns-violence-to-pahalgam-attack-1439617.html</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>"निवडणुकीत हरणार म्हणून कुटुंब "तहात" जिंकण्याचा प्रयत्न"; भाजपाचा पलटवार</t>
+          <t>कान फिल्म फेस्टिव्हलमध्ये 'या' चार मराठी सिनेमांची झाली निवड, सांस्कृतिक मंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-over-raj-uddhav-thackeray-vijayi-melava-a-a597/</t>
+          <t>https://www.lokmat.com/filmy/marathi-cinema/four-marathi-films-have-been-selected-for-the-cannes-film-festival-announced-by-cultural-minister-ashish-shelar-a-a998/</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>“सार्वजनिक गणेशोत्सव आता ‘महाराष्ट्र राज्य महोत्सव’”; आशिष शेलार यांची विधानसभेत घोषणा</t>
+          <t>राज ठाकरेंच्या ‘त्या’ टीकेला शेलारांचं खोचक प्रत्युत्तर; म्हणाले ज्यांना निवडून येता येत...</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ganeshotsav-is-now-maharashtra-state-festival-bjp-minister-ashish-shelar-announcement-in-the-vidhan-sabha-a-a719/</t>
+          <t>https://www.tv9marathi.com/maharashtra/ashish-shelar-response-to-raj-thackeray-criticism-1371675.html</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>मराठी माणसांची तुलना पहलगाम अतिरेक्यांशी उद्धव ठाकरेंचा आशिष शेलार अन् निशिकांत</t>
+          <t>सांस्कृतिक मंत्री म्हणतात ” पोळा करा, शहरी नक्षलवाद संपवा”</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
+          <t>https://www.loksatta.com/nagpur/wardha-to-end-urban-naxalism-traditional-festivals-like-bail-pola-must-be-celebrated-with-enthusiasm-adv-ashish-shelar-sud-02-5325172/</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Top 80 News : टॉप 80 बातम्यांचा वेगवान आढावा : Maharashtra News</t>
+          <t>ते मुंबईतल्या लँड स्कॅमचे…बड्या नेत्याचे उद्धव ठाकरेंवर खळबळजनक आरोप!</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-said-uddhav-thackeray-is-baadshah-of-land-scam-amid-bmc-election-2025-1389756.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ठाकरे गटाकडून मुंबईकरांशी एक लाख कोटींची बेईमानी, आशिष शेलार यांचा थेट आरोप</t>
+          <t>गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रयत्न - आशिष शेलार</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ashish-shelar-directly-accuses-shiv-sena-ubt-of-dishonesty-worth-rs-1-lakh-crore-towards-mumbaikars-a-a301/</t>
+          <t>https://www.lokmat.com/pune/efforts-to-get-unesco-cultural-status-for-ganeshotsav-ashish-shelar-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>गणेशोत्सव आता, महाराष्ट्र राज्य महोत्सव विधानसभेत घोषणा, आशिष शेलार म्हणाले</t>
+          <t>“सार्वजनिक गणेशोत्सव आता ‘महाराष्ट्र राज्य महोत्सव’”; आशिष शेलार यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-is-now-maharashtra-state-festival-bjp-minister-ashish-shelar-announcement-in-the-vidhan-sabha-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>हिंदी भाषा सक्ती प्रकरण: महाराष्ट्रात सक्ती फक्त मराठीची, हिंदीची नाही पण... : आशिष शेलार यांनी मांडली भूमिका</t>
+          <t>Top 80 News : टॉप 80 बातम्यांचा वेगवान आढावा : Maharashtra News</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/only-marathi-is-compulsory-in-maharashtra-says-minister-ashish-shelar-on-hindi-language-controversy-maharashtra-news-mhs25062401471</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-top-80-news-maharashtra-politics-udpate-ashish-shelar-raj-thackeray-1355421</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>नालेसफाईच्या पाहणीवेळी तुम्ही कुठे होता? आशिष शेलार यांचा आदित्य ठाकरे यांना सवाल</t>
+          <t>मराठी माणसांची तुलना पहलगाम अतिरेक्यांशी उद्धव ठाकरेंचा आशिष शेलार अन् निशिकांत</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/where-were-you-during-the-inspection-of-drain-cleaning-ashish-shelar-questions-aditya-thackeray-a-a1001/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-react-on-bjp-nishikant-dubey-ashish-shelar-statement-on-marathi-hindi-dispute-raj-thackeray-mns-pahalgam-1368495</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मराठी कंटेंट क्रिएटर्ससाठी नेटफ्लिक्सने...; ओटीटी प्लॅटफॉर्मवर मराठी स्थान मिळण्यासाठी आशिष शेलार यांचा प्रयत्न</t>
+          <t>ठाकरे गटाकडून मुंबईकरांशी एक लाख कोटींची बेईमानी, आशिष शेलार यांचा थेट आरोप</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/world/netflix-for-marathi-content-creators-ashish-shelar-efforts-to-get-marathi-a-place-on-ott-platforms/928660</t>
+          <t>https://www.lokmat.com/mumbai/ashish-shelar-directly-accuses-shiv-sena-ubt-of-dishonesty-worth-rs-1-lakh-crore-towards-mumbaikars-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>धारावी पुनर्वसन: भाजपाचे आशिष शेलार अन् काँग्रेसच्या वर्षा गायकवाड यांच्यात ‘तू तू मै मै’</t>
+          <t>"राज ठाकरेंकडे किती वेळा भीक मागितली की उमदेवार..."; मनसे नेत्याचा आशिष शेलारांवर पलटवार</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/dharavi-rehabilitation-project-dispute-between-bjps-ashish-shelar-and-congresss-varsha-gaikwad-a-a747/</t>
+          <t>https://www.lokmat.com/mumbai/sandeep-deshpande-asked-ashish-shelar-how-many-times-you-begged-raj-thackeray-not-to-field-an-mns-candidate-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Video: मोठी बातमी! अमित ठाकरेंनी घेतली भाजपाच्या आशिष शेलारांची भेट; दोन दिवसांपूर्वीच राज ठाकरेंनी घेतली होती फडणवीसांची भेट</t>
+          <t>गणेशोत्सव आता, महाराष्ट्र राज्य महोत्सव विधानसभेत घोषणा, आशिष शेलार म्हणाले</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-after-meeting-he-says-kvg-85-5325003/</t>
+          <t>https://marathi.abplive.com/news/mumbai/ganeshotsav-now-maharashtra-state-festival-announcement-in-the-legislative-assembly-by-ashish-shelar-said-operation-sindoor-1369092</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>'पहलगामसारखं मुंबईत निष्पाप हिंदूंना भाषा विचारुन चोपलं', आशिष शेलार यांचं धक्कादायक वक्तव्य</t>
+          <t>हिंदी भाषा सक्ती प्रकरण: महाराष्ट्रात सक्ती फक्त मराठीची, हिंदीची नाही पण... : आशिष शेलार यांनी मांडली भूमिका</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
+          <t>https://www.etvbharat.com/mr/!state/only-marathi-is-compulsory-in-maharashtra-says-minister-ashish-shelar-on-hindi-language-controversy-maharashtra-news-mhs25062401471</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>जास्त गर्दीच्या मेट्रो स्थानकांचा आपत्कालीन प्लॅन तयार करा; आशिष शेलारांचे MMRDAला निर्देश</t>
+          <t>"निवडणुकीत हरणार म्हणून कुटुंब "तहात" जिंकण्याचा प्रयत्न"; भाजपाचा पलटवार</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/prepare-an-emergency-plan-for-overcrowded-metro-stations-ashish-shelar-directs-mmrda-a-a747/</t>
+          <t>https://www.lokmat.com/mumbai/bjp-ashish-shelar-slams-uddhav-thackeray-over-raj-uddhav-thackeray-vijayi-melava-a-a597/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Mumbai News : मुंबईत १९ इमारतींचा पुनर्विकास, एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी घरं मिळणार</t>
+          <t>नालेसफाईच्या पाहणीवेळी तुम्ही कुठे होता? आशिष शेलार यांचा आदित्य ठाकरे यांना सवाल</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment-latest-marathi-news-pp0731</t>
+          <t>https://www.lokmat.com/mumbai/where-were-you-during-the-inspection-of-drain-cleaning-ashish-shelar-questions-aditya-thackeray-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ladki Bahin Movie : 'लाडकी बहीण' मोठ्या पडद्यावर झळकणार, चित्रपटात 'या' कलाकारांची लागली वर्णी</t>
+          <t>Devendra Fadanvis : फडणवीसांची फटकेबाजी; सांगितले लहानपणीचे रेडिओचे किस्से Special Report</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/entertainment/ladki-bahin-movie-muhurat-cultural-minister-ashish-shelar-gives-clap-see-photos-list-of-actors-mukhyamantri-ladki-bahin-yojana-sm2000</t>
+          <t>https://marathi.abplive.com/tv-show/special-report/devendra-fadanvis-asha-bhosale-ashish-shelar-radio-mhotsav-special-report-marathi-news-abp-majha-1365435</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>धारावीची एक इंचही जागा अदानी यांना देणार नाही; शेलार यांनी स्पष्टच सांगितलं, नेमकं काय म्हणाले?</t>
+          <t>Ashish Shelar : मराठी कंटेंट क्रिएटर्ससाठी नेटफ्लिक्सने...; ओटीटी प्लॅटफॉर्मवर मराठी स्थान मिळण्यासाठी आशिष शेलार यांचा प्रयत्न</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/adani-will-not-be-given-an-inch-of-space-in-dharavi-what-exactly-did-shelar-say-1370721.html</t>
+          <t>https://zeenews.india.com/marathi/world/netflix-for-marathi-content-creators-ashish-shelar-efforts-to-get-marathi-a-place-on-ott-platforms/928660</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>वाघनख्यानंतर आणखी एक ठेवा महाराष्ट्रात, नागपूरच्या रघुजीराजे भोसलेंची लंडनमधील</t>
+          <t>Video: मोठी बातमी! अमित ठाकरेंनी घेतली भाजपाच्या आशिष शेलारांची भेट; दोन दिवसांपूर्वीच राज ठाकरेंनी घेतली होती फडणवीसांची भेट</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
+          <t>https://www.loksatta.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-after-meeting-he-says-kvg-85-5325003/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ganeshutsav : गणेशोत्सवासंदर्भात सर्वात मोठी बातमी, राज्य सरकारची मोठी घोषणा</t>
+          <t>'पहलगामसारखं मुंबईत निष्पाप हिंदूंना भाषा विचारुन चोपलं', आशिष शेलार यांचं धक्कादायक वक्तव्य</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ganeshotsav-declared-maharashtra-official-festival-announces-ashish-shelar-mumbai-pune-latest-marathi-nck90</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/mns-leader-ashish-shelar-compare-mns-party-workers-action-like-pahalgam-attack/articleshow/122281333.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Chhatrapati Shivaji Maharaj: छत्रपती शिवाजी महाराजांच्या 'या' गडकिल्ल्यांना नामांकन; जागतिक वारसा यादीत स्थान मिळणार</t>
+          <t>शेलारजी फार डिंग्या मारू नका, बेस्ट निवडणुकीतही तुम्ही तीर मारले नाहीत. तुम्हाला</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/chhatrapati-shivaji-maharaj-12-forts-place-on-unesco-world-heritage-list-said-maharashtra-government-minister-ashish-shelar-marathi-news-795328.html</t>
+          <t>https://marathi.abplive.com/news/mumbai/sushma-andhare-scathing-criticism-of-ashish-shelar-for-criticizing-best-patpedhi-elections-marathi-news-update-1378655</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ashish Shelar News: निवडणुका होऊ नयेत म्हणून कुणाचे प्रयत्न सुरू आहेत?, शेलारांचा कुणावर निशाणा?</t>
+          <t>Mumbai News : मुंबईत १९ इमारतींचा पुनर्विकास, एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी घरं मिळणार</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>गणेशोउत्सवात मुंबईकरांना खड्डांचा त्रास होणार नाही, यासाठी प्रशासनाने सणापूर्वी खड्डे भरावे, पालकमंत्री आशिष शेलारांचे निर्देश</t>
+          <t>Ladki Bahin Movie : 'लाडकी बहीण' मोठ्या पडद्यावर झळकणार, चित्रपटात 'या' कलाकारांची लागली वर्णी</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/mumbaikars-do-not-face-problem-due-to-potholes-during-ganesh-chaturthi-should-fill-the-potholes-before-festival-says-minister-ashish-shelar-05-693364</t>
+          <t>https://saamtv.esakal.com/entertainment/ladki-bahin-movie-muhurat-cultural-minister-ashish-shelar-gives-clap-see-photos-list-of-actors-mukhyamantri-ladki-bahin-yojana-sm2000</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>यंदा दहिहंडी उत्सव साजरा करण्यासाठी पालिका आगळावेगळा उपक्रम राबविणार, मंत्री आशिष शेलारांची माहिती</t>
+          <t>Ashish Shelar On Raj Thackeray: राज ठाकरे- आशिष शेलारांच्या मैत्रिमध्ये दरार? कारण काय?</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/this-year-the-municipality-will-implement-a-unique-initiative-to-celebrate-dahihandi-festival-according-to-minister-ashish-shelar-05-688129?utm_source=website&amp;utm_medium=related&amp;utm_campaign=relatedpost</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ashish-shelar-on-raj-thackeray-crack-in-raj-thackeray-ashish-shelar-s-friendship-what-is-the-reason-1040910.html</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार महाराष्ट्रात लवकरच येणार , सांस्कृतिक कार्यमंत्री आशिष शेलारांची माहिती</t>
+          <t>धारावीची एक इंचही जागा अदानी यांना देणार नाही; शेलार यांनी स्पष्टच सांगितलं, नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/the-state-government-has-achieved-great-success-in-obtaining-the-historical-sword-of-the-brave-maratha-sardar-raghuji-bhosale-according-to-cultural-affairs-minister-ashish-shelar-05-675383</t>
+          <t>https://www.tv9marathi.com/maharashtra/adani-will-not-be-given-an-inch-of-space-in-dharavi-what-exactly-did-shelar-say-1370721.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Mumbai News: 'मुंबई में निर्दोष हिंदुओं को पहलगाम की तरह उनकी भाषा पूछकर पीटा गया', BJP नेता आशीष शेलार का चौंकाने वाला बयान</t>
+          <t>वाघनख्यानंतर आणखी एक ठेवा महाराष्ट्रात, नागपूरच्या रघुजीराजे भोसलेंची लंडनमधील</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
+          <t>https://marathi.abplive.com/news/nagpur/london-musium-transfer-historic-sword-of-raghuji-raje-bhonsle-nagpur-to-maharashtra-ashish-shelar-marathi-news-1376449</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>आम्ही तोडणारे नव्हे, तर जोडणारे- आशिष शेलार</t>
+          <t>Chhatrapati Shivaji Maharaj: छत्रपती शिवाजी महाराजांच्या 'या' गडकिल्ल्यांना नामांकन; जागतिक वारसा यादीत स्थान मिळणार</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
+          <t>https://www.navarashtra.com/maharashtra/chhatrapati-shivaji-maharaj-12-forts-place-on-unesco-world-heritage-list-said-maharashtra-government-minister-ashish-shelar-marathi-news-795328.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>NDTV Emerging Business: मुंबईत AI विद्यापीठ स्थापण करणार, आशिष शेलारांनी दिली माहिती</t>
+          <t>Ashish Shelar News: निवडणुका होऊ नयेत म्हणून कुणाचे प्रयत्न सुरू आहेत?, शेलारांचा कुणावर निशाणा?</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
+          <t>https://marathi.timesnownews.com/videos/ashish-shelar-has-criticized-uddhav-thackeray-for-not-wanting-elections-in-mumbai-video-152208993</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>लोकमान्य तिलक का गणपति उत्सव बना राज्य उत्सव, जानिए मंत्री आशीष शेलार ने क्या कहा</t>
+          <t>गणेशोउत्सवात मुंबईकरांना खड्डांचा त्रास होणार नाही, यासाठी प्रशासनाने सणापूर्वी खड्डे भरावे, पालकमंत्री आशिष शेलारांचे निर्देश</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/mumbaikars-do-not-face-problem-due-to-potholes-during-ganesh-chaturthi-should-fill-the-potholes-before-festival-says-minister-ashish-shelar-05-693364</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
+          <t>यंदा दहिहंडी उत्सव साजरा करण्यासाठी पालिका आगळावेगळा उपक्रम राबविणार, मंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/this-year-the-municipality-will-implement-a-unique-initiative-to-celebrate-dahihandi-festival-according-to-minister-ashish-shelar-05-688129?utm_source=website&amp;utm_medium=related&amp;utm_campaign=relatedpost</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ashish Shelar : माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला, आशिष शेलारांचे वक्तव्य</t>
+          <t>Mumbai News: 'मुंबई में निर्दोष हिंदुओं को पहलगाम की तरह उनकी भाषा पूछकर पीटा गया', BJP नेता आशीष शेलार का चौंकाने वाला बयान</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-leader-ashish-shelar-compare-mumbai-and-mira-road-assault-action-by-mns-party-workers-like-pahalgam-attack/articleshow/122281582.cms</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के स्कूलों में हिंदी जरूरी? विवाद पर देवेंद्र फडणवीस का बड़ा फैसला, जानें क्या बोले आशीष शेलार</t>
+          <t>आम्ही तोडणारे नव्हे, तर जोडणारे- आशिष शेलार</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-statement-regarding-gokhale-bridge-traffic-mumbai-print-news-amy-95-5083205/</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “तुम्हारे पाँव के नीचे कोई जमीन नही…”, आशिष शेलारांचा शेरोशायरीतून उद्धव ठाकरेंवर हल्लाबोल</t>
+          <t>NDTV Emerging Business: मुंबईत AI विद्यापीठ स्थापण करणार, आशिष शेलारांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mumbai-president-ashish-shelar-criticizes-uddhav-thackeray-and-mahavikas-aghadi-politics-gkt-96-4820917/</t>
+          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-minister-ashish-shelar-on-ai-university-9154007</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray &amp; Ashish Shelar: उद्धव ठाकरे हा मुंबईतील लँड स्कॅमचा बादशाह आशिष शेलारांनी दुसऱ्या</t>
+          <t>पालकमंत्री ऍड आशिष शेलार यांनी घेतला आपात्कालीन व्यवस्थापनाचा आढावा</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
+          <t>https://www.loksatta.com/mumbai/guardian-minister-adv-ashish-shelar-reviewed-emergency-management-mumbai-print-news-amy-95-5313321/</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>सरकारच्या विभागांमधील रिक्त पदे नेमकी किती? मंत्री आशिष शेलार यांनी विधान परिषदेत दिली माहिती</t>
+          <t>लोकमान्य तिलक का गणपति उत्सव बना राज्य उत्सव, जानिए मंत्री आशीष शेलार ने क्या कहा</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/information-technology-minister-ashish-shelar-announced-that-these-vacant-posts-will-be-filled-through-mahabharti-phm-00-5219670/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/lokmanya-tilaks-ganpati-festival-became-the-state-festival-of-maharashtra-minister-ashish-shelar-said-it-is-the-cultural-identity-of-maharashtra/articleshow/122380535.cms</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Nagpur Film City: नागपुरातील फिल्मसिटीची जागा ठरली! मुंबई, कोल्हापूरनंतर उपराजधानीत 128</t>
+          <t>Ashish Shelar : माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला, आशिष शेलारांचे वक्तव्य</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
+          <t>https://marathi.abplive.com/news/mumbai/ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-shiv-sena-mns-alliance-no-more-personal-friendship-bmc-mumbai-election-marathi-news-1355377</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’मुळे भावना दुखावतायत तर कान्सला का पाठवला? आशिष शेलार स्पष्टीकरण देत म्हणाले….</t>
+          <t>Ashish Shelar : “तुम्हारे पाँव के नीचे कोई जमीन नही…”, आशिष शेलारांचा शेरोशायरीतून उद्धव ठाकरेंवर हल्लाबोल</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-explain-why-govt-sent-khalid-ka-shivaji-movie-to-cannes-film-festival-2025-asc-95-5290043/</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mumbai-president-ashish-shelar-criticizes-uddhav-thackeray-and-mahavikas-aghadi-politics-gkt-96-4820917/</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>मराठी चित्रपट योग्य दरात घेण्याची नेटफ्लिक्सला सूचना : ॲड. आशिष शेलार</t>
+          <t>Uddhav Thackeray &amp; Ashish Shelar: उद्धव ठाकरे हा मुंबईतील लँड स्कॅमचा बादशाह आशिष शेलारांनी दुसऱ्या</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-state-film-awards-ashish-shelar-discusses-marathi-cinema-pricing-with-netflix-mumbai-print-news-rds-00-5283289/</t>
+          <t>https://marathi.abplive.com/news/politics/uddhav-thackeray-is-king-of-land-scam-in-mumbai-big-statement-by-bjp-leader-ashish-shelar-at-mumbai-1355652</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
+          <t>मराठी चित्रपट योग्य दरात घेण्याची नेटफ्लिक्सला सूचना : ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-state-film-awards-ashish-shelar-discusses-marathi-cinema-pricing-with-netflix-mumbai-print-news-rds-00-5283289/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>धारावीतील एक इंचही जागा ‘अदानी’ला देणार नाही, मंत्री आशीष शेलार यांची ग्वाही</t>
+          <t>सरकारच्या विभागांमधील रिक्त पदे नेमकी किती? मंत्री आशिष शेलार यांनी विधान परिषदेत दिली माहिती</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-assures-that-not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-mumbai-print-news-ssb-93-4964971/</t>
+          <t>https://www.loksatta.com/mumbai/information-technology-minister-ashish-shelar-announced-that-these-vacant-posts-will-be-filled-through-mahabharti-phm-00-5219670/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>“शहरी नक्षलवाद्यांचा डाव हाणून पाडू, गणेशोत्सव धुमधडाक्यात साजरा करू”: आशिष शेलार</t>
+          <t>Nagpur Film City: नागपुरातील फिल्मसिटीची जागा ठरली! मुंबई, कोल्हापूरनंतर उपराजधानीत 128</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-ashish-shelar-said-celebrate-ganeshotsav-on-big-scale-a-a719/</t>
+          <t>https://marathi.abplive.com/news/nagpur-film-city-news-update-the-place-of-film-city-has-been-decided-after-mumbai-kolhapur-128-acres-of-land-has-been-fixed-in-ramtek-information-from-minister-ashish-shelar-maharashtra-marathi-news-1344434</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>'खालिद का शिवाजी' चित्रपटावरून आशिष शेलार आक्रमक; सेन्सॉर बोर्डाला धारेवर धरत घेतला मोठा निर्णय</t>
+          <t>‘खालिद का शिवाजी’मुळे भावना दुखावतायत तर कान्सला का पाठवला? आशिष शेलार स्पष्टीकरण देत म्हणाले….</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-explain-why-govt-sent-khalid-ka-shivaji-movie-to-cannes-film-festival-2025-asc-95-5290043/</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Raj Thackeray &amp; Ashish Shelar: आम्ही अन्नपाणी सोडलंय, आम्हाला खूप दु:ख झालंय आशिष शेलारांनी राज</t>
+          <t>Maharashtra Live Updates: ज्येष्ठ वकील गुणरत्न सदावर्ते यांनी केली राज ठाकरेंविरोधात तक्रार दाखल</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-march-2025-shivsena-bjp-congress-devendra-fadnavis-raj-thackeray-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>BJP : भाजपच्या दोन गटांमध्ये मुंबईत तुफान हाणामारी, आशिष शेलारांसमोरच कार्यकर्ते भिडले, Video</t>
+          <t>“शहरी नक्षलवाद्यांचा डाव हाणून पाडू, गणेशोत्सव धुमधडाक्यात साजरा करू”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/bjp-supporters-fight-with-each-other-in-front-of-ashish-shelar-in-mumbai-watch-video-1414857.html</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-ashish-shelar-said-celebrate-ganeshotsav-on-big-scale-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज ठाकरेंसोबतच्या मैत्रीचा प्रश्न, आशिष शेलारांनी दोन शब्दात संपवला विषय</t>
+          <t>धारावीतील एक इंचही जागा ‘अदानी’ला देणार नाही, मंत्री आशीष शेलार यांची ग्वाही</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-speak-on-issue-of-mumbai-potholes-friendship-with-raj-thackeray-sanjay-raut-letter-india-pakistan-match-1476373.html</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-assures-that-not-even-an-inch-of-land-in-dharavi-will-be-given-to-adani-mumbai-print-news-ssb-93-4964971/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>रवी परांजपे यांचा चित्रठेवा शासनाकडून जतन; सांस्कृतिकमंत्री आशिष शेलार यांच्या उपस्थितीत सामंजस्य करारावर स्वाक्षरी</t>
+          <t>'खालिद का शिवाजी' चित्रपटावरून आशिष शेलार आक्रमक; सेन्सॉर बोर्डाला धारेवर धरत घेतला मोठा निर्णय</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/signing-of-mou-by-ashish-shelar-on-preservation-of-ravi-paranjpe-paintings-pune-print-news-amy-95-5319485/</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-on-khalid-ka-shivaji-marathi-film-controversy-censor-board-reconsideration-1451530.html</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>मुंबई महापालिकेचा महापौर महायुतीचा होणार संजय राऊत यांच्या बुद्धिमतेची चाचणी</t>
+          <t>Raj Thackeray &amp; Ashish Shelar: आम्ही अन्नपाणी सोडलंय, आम्हाला खूप दु:ख झालंय आशिष शेलारांनी राज</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
+          <t>https://marathi.abplive.com/news/politics/mns-leader-prakash-mahajan-taunts-bjp-ashish-shelar-over-breaking-friendship-ties-with-raj-thackeray-1355491</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे यांच्या काळापेक्षा रस्ते कामाचा वेग अधिक; पालकमंत्री ऍड. आशिष शेलार यांचे मत</t>
+          <t>BJP : भाजपच्या दोन गटांमध्ये मुंबईत तुफान हाणामारी, आशिष शेलारांसमोरच कार्यकर्ते भिडले, Video</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-slams-uddhav-thackeray-over-concrete-road-construction-mumbai-print-news-zws-70-5098492/</t>
+          <t>https://news18marathi.com/mumbai/bjp-supporters-fight-with-each-other-in-front-of-ashish-shelar-in-mumbai-watch-video-1414857.html</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>“पहलगाममध्ये धर्म विचारुन गोळ्या घातल्या अन् इथे भाषा विचारुन…”; आशिष शेलारांचा...</t>
+          <t>Ashish Shelar : राज ठाकरेंसोबतच्या मैत्रीचा प्रश्न, आशिष शेलारांनी दोन शब्दात संपवला विषय</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-controversy-bjp-leader-aashish-shelar-target-thackeray-brothers-rally-1439702.html</t>
+          <t>https://www.tv9marathi.com/politics/bjp-leader-ashish-shelar-speak-on-issue-of-mumbai-potholes-friendship-with-raj-thackeray-sanjay-raut-letter-india-pakistan-match-1476373.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>आताची सर्वात मोठी बातमी! मनसे नेते अमित ठाकरे आशिष शेलार यांच्या भेटीला</t>
+          <t>मुंबई महापालिकेचा महापौर महायुतीचा होणार संजय राऊत यांच्या बुद्धिमतेची चाचणी</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ashish-shelar-says-the-mayor-of-mumbai-municipal-corporation-will-be-from-the-mahayuti-sanjay-raut-intelligence-will-have-to-be-tested-in-the-third-grade-1366697</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Ashish Shelar : राज ठाकरे-उद्धव ठाकरे युतीच्या चर्चे दरम्यान आशिष शेलारांचे मोठं वक्तव्य; म्हणाले, "आता वैयक्तिक संबंधही संपले"</t>
+          <t>रवी परांजपे यांचा चित्रठेवा शासनाकडून जतन; सांस्कृतिकमंत्री आशिष शेलार यांच्या उपस्थितीत सामंजस्य करारावर स्वाक्षरी</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-says-his-personal-relationship-with-raj-thackeray-has-ended-amid-talks-of-mns-and-uddhav-thackerays-shiv-sena-alliance-as11</t>
+          <t>https://www.loksatta.com/pune/signing-of-mou-by-ashish-shelar-on-preservation-of-ravi-paranjpe-paintings-pune-print-news-amy-95-5319485/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार दोन दिवसांआधी राज</t>
+          <t>उद्धव ठाकरे यांच्या काळापेक्षा रस्ते कामाचा वेग अधिक; पालकमंत्री ऍड. आशिष शेलार यांचे मत</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-slams-uddhav-thackeray-over-concrete-road-construction-mumbai-print-news-zws-70-5098492/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>‘पुरातत्व’कडील गडकिल्ले राज्याकडे देण्याची विनंती; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे पत्र</t>
+          <t>आताची सर्वात मोठी बातमी! मनसे नेते अमित ठाकरे आशिष शेलार यांच्या भेटीला</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-letter-to-union-minister-demanded-to-handed-over-forts-in-maharashtra-to-state-government-zws-70-4975719/</t>
+          <t>https://news18marathi.com/mumbai/maharashtra-politics-mns-leader-amit-thackeray-meet-ashish-shelar-in-bandra-ws-l-1464242.html</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>प्रस्तावित वांद्रे-कुर्ला मार्गिकेचे संरेखन रद्द का? आशिष शेलार यांचे ‘एमएमआरडीए’ला अवहाल देण्याचे आदेश</t>
+          <t>“पहलगाममध्ये धर्म विचारुन गोळ्या घातल्या अन् इथे भाषा विचारुन…”; आशिष शेलारांचा...</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-orders-mmrda-to-take-cognizance-of-the-proposed-bandra-kurla-corridor-mumbai-print-news-amy-95-5175404/</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-hindi-controversy-bjp-leader-aashish-shelar-target-thackeray-brothers-rally-1439702.html</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “राज ठाकरेंशी वैयक्तिक संबंध होते ते आता संपले…”, आशिष शेलार यांचं वक्तव्य</t>
+          <t>Ashish Shelar : राज ठाकरे-उद्धव ठाकरे युतीच्या चर्चे दरम्यान आशिष शेलारांचे मोठं वक्तव्य; म्हणाले, "आता वैयक्तिक संबंधही संपले"</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-said-friendship-with-raj-thackeray-is-now-over-what-he-said-scj-81-5033142/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-says-his-personal-relationship-with-raj-thackeray-has-ended-amid-talks-of-mns-and-uddhav-thackerays-shiv-sena-alliance-as11</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>खोक्याभाईचे काय घेऊन बसलात, विधानसभेत सगळे तेच भरलेत: राज ठाकरेंचा सरकारला टोला, भाजप नेते आशिष शेलारांनीही...</t>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार दोन दिवसांआधी राज</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meet-ashish-shelar-will-meet-mns-leader-amit-thackeray-and-minister-ashish-shelar-raj-thackeray-devendra-fadnavis-1379187</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ashish Shelar : “निवडणुकीत हरणार म्हणून कुटुंब तहात…”, ठाकरे बंधूंच्या मेळाव्यानंतर भाजपाची पहिली प्रतिक्रिया; शेलार म्हणाले, “भाऊबंदकी…”</t>
+          <t>‘पुरातत्व’कडील गडकिल्ले राज्याकडे देण्याची विनंती; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे पत्र</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-on-mns-raj-thackeray-and-shivsena-ubt-uddhav-thackeray-victory-rally-in-mumbai-politics-gkt-96-5206150/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-letter-to-union-minister-demanded-to-handed-over-forts-in-maharashtra-to-state-government-zws-70-4975719/</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>पारंपारिक गोंदण कलेचा समावेश कला अभ्यासक्रमात; सांस्कृतिक कार्य मंत्री ॲड आशिष शेलार यांच्या सूचना</t>
+          <t>प्रस्तावित वांद्रे-कुर्ला मार्गिकेचे संरेखन रद्द का? आशिष शेलार यांचे ‘एमएमआरडीए’ला अवहाल देण्याचे आदेश</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-adv-ashish-shelar-instructions-regarding-tattoo-art-courses-mumbai-print-news-amy-95-5196545/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-orders-mmrda-to-take-cognizance-of-the-proposed-bandra-kurla-corridor-mumbai-print-news-amy-95-5175404/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>“आशिष शेलार माझ्याव्यतिरिक्त कोणालाच छळत नाहीत”, देवेंद्र फडणवीसांचं वक्तव्य</t>
+          <t>Ashish Shelar : “राज ठाकरेंशी वैयक्तिक संबंध होते ते आता संपले…”, आशिष शेलार यांचं वक्तव्य</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-says-ashish-shelar-not-bothering-anyone-except-me-asc-95-4973334/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-said-friendship-with-raj-thackeray-is-now-over-what-he-said-scj-81-5033142/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Uddhav Thackeray: " ...तर उध्दव ठाकरेंना 'बेईमान ऑफ द महाराष्ट्र' अवॉर्ड द्यावा लागेल!"; भाजप मंत्र्यांचं वादग्रस्त विधान</t>
+          <t>खोक्याभाईचे काय घेऊन बसलात, विधानसभेत सगळे तेच भरलेत: राज ठाकरेंचा सरकारला टोला, भाजप नेते आशिष शेलारांनीही...</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-controversial-remark-uddhav-thackeray-dishonest-of-maharashtra-award-dk88</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/raj-thackeray-criticize-mahayuti-government-on-khokya-bhai-ashish-shelar-answered-this-criticism-134695078.html</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ashish Shelar: “मित्र म्हणून तुम्हाला सल्ला देतो की…”, राज ठाकरेंनी निकालावर संशय घेताच भाजपाचा पलटवार</t>
+          <t>“आशिष शेलार माझ्याव्यतिरिक्त कोणालाच छळत नाहीत”, देवेंद्र फडणवीसांचं वक्तव्य</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-leader-ashish-shelar-slams-raj-thackeray-over-his-speech-alleges-his-fake-narrative-kvg-85-4859728/</t>
+          <t>https://www.loksatta.com/mumbai/devendra-fadnavis-says-ashish-shelar-not-bothering-anyone-except-me-asc-95-4973334/</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>मुंबईतच घरे हवीत… गिरणी कामगार पुन्हा आक्रमक…आशिष शेलार यांच्या वांद्रे कार्यालयावर २७ एप्रिल रोजी मोर्चा</t>
+          <t>Ashish Shelar : “निवडणुकीत हरणार म्हणून कुटुंब तहात…”, ठाकरे बंधूंच्या मेळाव्यानंतर भाजपाची पहिली प्रतिक्रिया; शेलार म्हणाले, “भाऊबंदकी…”</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-on-mns-raj-thackeray-and-shivsena-ubt-uddhav-thackeray-victory-rally-in-mumbai-politics-gkt-96-5206150/</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>गडकिल्ल्यांच्या संवर्धनासाठी शासन सक्षम: मंत्री आशिष शेलार यांचे राज ठाकरेंना उत्तर, म्हणाले - जागतिक वारशा...</t>
+          <t>पारंपारिक गोंदण कलेचा समावेश कला अभ्यासक्रमात; सांस्कृतिक कार्य मंत्री ॲड आशिष शेलार यांच्या सूचना</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-adv-ashish-shelar-instructions-regarding-tattoo-art-courses-mumbai-print-news-amy-95-5196545/</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>राज ठाकरे - आशिष शेलार यांच्या मैत्रीत दुरावा; शेलार म्हणाले, "माझ्या दृष्टीने वैयक्तिक मित्र वैगेरे विषय संपला"</t>
+          <t>Uddhav Thackeray: " ...तर उध्दव ठाकरेंना 'बेईमान ऑफ द महाराष्ट्र' अवॉर्ड द्यावा लागेल!"; भाजप मंत्र्यांचं वादग्रस्त विधान</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/ashish-shelar-says-friendship-with-raj-thackeray-over-amid-mns-shiv-sena-ubt-alliance-maharashtra-news-mhs25042004504</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-controversial-remark-uddhav-thackeray-dishonest-of-maharashtra-award-dk88</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>प्रयोगात्मक कलांसाठी पु.ल. देशपांडे अकादमीमध्ये शाहीर साबळेच्या नावाने संशोधन केंद्र; सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची घोषणा</t>
+          <t>Ashish Shelar: “मित्र म्हणून तुम्हाला सल्ला देतो की…”, राज ठाकरेंनी निकालावर संशय घेताच भाजपाचा पलटवार</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announces-research-center-named-after-shahir-sable-at-p-l-deshpande-academy-mumbai-print-news-amy-95-5170476/</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-leader-ashish-shelar-slams-raj-thackeray-over-his-speech-alleges-his-fake-narrative-kvg-85-4859728/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>जिथं तुरुंगवास तिथंच सावरकरांचं भव्य स्मारक मंत्री आशिष शेलार यांची घोषणा,</t>
+          <t>मुंबईतच घरे हवीत… गिरणी कामगार पुन्हा आक्रमक…आशिष शेलार यांच्या वांद्रे कार्यालयावर २७ एप्रिल रोजी मोर्चा</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
+          <t>https://www.loksatta.com/mumbai/want-houses-mumbai-mill-workers-are-aggressive-again-march-on-ashish-shelars-bandra-office-on-april-27-mumbai-print-news-sud-02-5029634/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>युनेस्कोच्या यादीत 12 किल्ले मोदी सरकारचे कान टोचणाऱ्या राज ठाकरेंना मंत्री</t>
+          <t>गडकिल्ल्यांच्या संवर्धनासाठी शासन सक्षम: मंत्री आशिष शेलार यांचे राज ठाकरेंना उत्तर, म्हणाले - जागतिक वारशा...</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/maharashtra-forts-unesco-heritage-raj-thackeray-ashish-shelar-135431706.html</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ashish Shelar : रायगडच्या पालकमंत्री पदाचा तिढा अमित शाह नाहीतर यांच्या अखत्यारितला? आशिष शेलारांनी थेट नावच सांगितलं</t>
+          <t>धारावी पुनर्वसन: भाजपाचे आशिष शेलार अन् काँग्रेसच्या वर्षा गायकवाड यांच्यात ‘तू तू मै मै’</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/raigad-guardian-minister-dispute-to-be-decided-by-devendra-fadnavis-says-ashish-shelar-as11</t>
+          <t>https://www.lokmat.com/mumbai/dharavi-rehabilitation-project-dispute-between-bjps-ashish-shelar-and-congresss-varsha-gaikwad-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>वांद्रे येथे राज्याचे नवीन महापुराभिलेख भवन, सांस्कृतिक कार्यमंत्री आशीष शेलार यांची घोषणा</t>
+          <t>प्रयोगात्मक कलांसाठी पु.ल. देशपांडे अकादमीमध्ये शाहीर साबळेच्या नावाने संशोधन केंद्र; सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announces-research-center-named-after-shahir-sable-at-p-l-deshpande-academy-mumbai-print-news-amy-95-5170476/</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>के. बी. भाभा रुग्णालयाच्या विस्तारित इमारतीचे लोकार्पण!</t>
+          <t>जिथं तुरुंगवास तिथंच सावरकरांचं भव्य स्मारक मंत्री आशिष शेलार यांची घोषणा,</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-inaugurated-newly-expanded-khurshedji-behramji-bhabha-hospital-in-bandra-on-wednesday-mumbai-print-news-sud-02-4872371/</t>
+          <t>https://marathi.abplive.com/news/india/veer-savarkar-grand-memorial-will-be-built-wherever-he-was-imprisoned-minister-ashish-shelar-announces-visit-to-andaman-jail-1359450</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>मुंबई तुंबण्यावरून आशिष शेलार यांची ठाकरे गटावर टीका, वीस वर्षातील कामांची श्वेतपत्रिका काढण्याची पालिका आयुक्तांकडे मागणी</t>
+          <t>लोककलांना पुनरुज्जीवन करणे गरजेचे : ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-alleged-uddhav-thackeray-group-has-been-dishonest-with-mumbaikars-on-wednesday-mumbai-print-news-sud-02-5119394/</t>
+          <t>https://www.loksatta.com/thane/in-thane-bjp-mla-ashish-shelar-says-need-to-revive-folk-arts-css-98-4953399/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार ताब्यात; १८ ऑगस्टला मुंबईत दाखल : आशिष शेलार</t>
+          <t>युनेस्कोच्या यादीत 12 किल्ले मोदी सरकारचे कान टोचणाऱ्या राज ठाकरेंना मंत्री</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/in-mumbai-ashish-shelar-to-bring-maharashtra-auction-win-of-maratha-sword-on-august-18-mumbai-print-news-rds-00-5297158/</t>
+          <t>https://marathi.abplive.com/news/politics/shivaji-maharaj-12-forts-on-unesco-list-minister-ashish-shelar-reply-to-raj-thackeray-who-poked-the-ears-of-modi-government-1369497</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>मुंबई अध्यक्षपदावरून भाजपमध्ये तिढा; आशिष शेलारांकडे पद कायम राहणार?</t>
+          <t>Ashish Shelar : रायगडच्या पालकमंत्री पदाचा तिढा अमित शाह नाहीतर यांच्या अखत्यारितला? आशिष शेलारांनी थेट नावच सांगितलं</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/bjp-undecided-on-mumbai-president-ahead-of-elections-print-politics-news-ocd-94-5259220/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/raigad-guardian-minister-dispute-to-be-decided-by-devendra-fadnavis-says-ashish-shelar-as11</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>शेलार मामाला पोटदुखी सुरू झाली आहे, मनसे प्रवक्ता गजानन काळेंची पोस्ट चर्चेत</t>
+          <t>के. बी. भाभा रुग्णालयाच्या विस्तारित इमारतीचे लोकार्पण!</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/gajanan-kale-counterattacks-ashish-shelar-on-uddhav-thackeray-raj-thackeray-alliance-vsd-99-5206583/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-inaugurated-newly-expanded-khurshedji-behramji-bhabha-hospital-in-bandra-on-wednesday-mumbai-print-news-sud-02-4872371/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मराठा सरदार रघुजीराजे भोसलेंची ऐतिहासिक तलवार १५ ऑगस्टच्या आधी महाराष्ट्रात आणणार, मंत्री आशिष शेलार यांची माहिती</t>
+          <t>वांद्रे येथे राज्याचे नवीन महापुराभिलेख भवन, सांस्कृतिक कार्यमंत्री आशीष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-sai-historic-sword-of-the-brave-maratha-sardar-raghuji-raje-bhosale-to-return-to-maharashtra-before-august-15-scj-81-5212150/</t>
+          <t>https://www.loksatta.com/mumbai/cultural-affairs-minister-ashish-shelar-announced-new-mahapurabhilekha-bhavan-in-bandra-east-mumbai-print-news-sud-02-4964714/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>“राज्य महोत्सव गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभाग वाढवावा”: आशिष शेलार</t>
+          <t>शूर मराठा सरदार रघुजी भोसले यांची ऐतिहासिक तलवार ताब्यात; १८ ऑगस्टला मुंबईत दाखल : आशिष शेलार</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/every-government-department-should-increase-participation-in-the-state-festival-of-ganeshotsav-said-bjp-minister-ashish-shelar-a-a719/</t>
+          <t>https://www.loksatta.com/mumbai/in-mumbai-ashish-shelar-to-bring-maharashtra-auction-win-of-maratha-sword-on-august-18-mumbai-print-news-rds-00-5297158/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Asha Bhosle : राजकारणात मला फक्त आशिष शेलार माहिती; ठाकरे बंधूंवरील प्रश्नावर आशा भोसलेंचं उत्तर</t>
+          <t>मुंबई तुंबण्यावरून आशिष शेलार यांची ठाकरे गटावर टीका, वीस वर्षातील कामांची श्वेतपत्रिका काढण्याची पालिका आयुक्तांकडे मागणी</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/famous-singer-asha-bhosle-comment-on-raj-uddhav-thackeray-morcha-in-mumbai-on-hindi-language-impose-912626.html</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-alleged-uddhav-thackeray-group-has-been-dishonest-with-mumbaikars-on-wednesday-mumbai-print-news-sud-02-5119394/</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>लोककलांना पुनरुज्जीवन करणे गरजेचे : ॲड. आशिष शेलार</t>
+          <t>शेलार मामाला पोटदुखी सुरू झाली आहे, मनसे प्रवक्ता गजानन काळेंची पोस्ट चर्चेत</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/in-thane-bjp-mla-ashish-shelar-says-need-to-revive-folk-arts-css-98-4953399/</t>
+          <t>https://www.loksatta.com/thane/gajanan-kale-counterattacks-ashish-shelar-on-uddhav-thackeray-raj-thackeray-alliance-vsd-99-5206583/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>राज ठाकरे आणि आशिष शेलारांच्या मैत्रीत मिठाचा खडा; म्हणाले, "मित्र होते, विषय आता संपला"</t>
+          <t>Ashish Shelar : मराठा सरदार रघुजीराजे भोसलेंची ऐतिहासिक तलवार १५ ऑगस्टच्या आधी महाराष्ट्रात आणणार, मंत्री आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/speculations-of-reconciliation-between-mns-and-shiv-sena-ashish-shelar-said-friendship-with-raj-is-over-a-a1001/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-sai-historic-sword-of-the-brave-maratha-sardar-raghuji-raje-bhosale-to-return-to-maharashtra-before-august-15-scj-81-5212150/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>“परिस्थितीच्या माऱ्याने दोघे एकत्र, आता नवा चित्रपट…”, आशिष शेलारांचा ठाकरे बंधूंना चिमटा; सिनेमाचं नावंही सांगितलं!</t>
+          <t>“राज्य महोत्सव गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभाग वाढवावा”: आशिष शेलार</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-slams-raj-and-uddhav-thackeray-mentions-zenda-and-yek-number-movie-asc-95-5217275/</t>
+          <t>https://www.lokmat.com/mumbai/every-government-department-should-increase-participation-in-the-state-festival-of-ganeshotsav-said-bjp-minister-ashish-shelar-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>"राजकारणात फक्त आशिष शेलारांना ओळखते..."; ठाकरे बंधूंच्या मराठी मोर्चावर आशा भोसले काय म्हणाल्या?</t>
+          <t>Asha Bhosle : राजकारणात मला फक्त आशिष शेलार माहिती; ठाकरे बंधूंवरील प्रश्नावर आशा भोसलेंचं उत्तर</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/in-politics-i-only-know-ashish-shelar-what-did-singer-asha-bhosle-say-about-the-raj-and-uddhav-thackeray-brothers-marathi-morcha-a-a629/</t>
+          <t>https://www.navarashtra.com/maharashtra/famous-singer-asha-bhosle-comment-on-raj-uddhav-thackeray-morcha-in-mumbai-on-hindi-language-impose-912626.html</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>"मी फक्त आशिष शेलारांना ओळखते, बाकी कोणा राजकारण्याला ओळखत नाही", ठाकरे बंधूंच्या युतीवर आशा भोसलेंचं विधान</t>
+          <t>मुंबई अध्यक्षपदावरून भाजपमध्ये तिढा; आशिष शेलारांकडे पद कायम राहणार?</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/i-only-know-ashish-shelar-i-dont-know-any-other-politician-asha-bhosles-statement-on-the-uddhav-thackeray-and-raj-thackeray-alliance-mumbai-maharashtra-news-mhs25062702929</t>
+          <t>https://www.loksatta.com/politics/bjp-undecided-on-mumbai-president-ahead-of-elections-print-politics-news-ocd-94-5259220/</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>कातळशिल्पांचा ‘जागतिक वारसा स्थळा’च्या यादीत समावेशासाठी रोडमॅप तयार करा, मंत्री आशिष शेलार यांचे निर्देश</t>
+          <t>राज ठाकरे आणि आशिष शेलारांच्या मैत्रीत मिठाचा खडा; म्हणाले, "मित्र होते, विषय आता संपला"</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/prepare-a-roadmap-for-the-inclusion-of-rock-sculptures-in-the-world-heritage-site-list-directed-by-minister-ashish-shelar-scj-81-5114434/</t>
+          <t>https://www.lokmat.com/mumbai/speculations-of-reconciliation-between-mns-and-shiv-sena-ashish-shelar-said-friendship-with-raj-is-over-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>महाराष्ट्राच्या राजकारणात उद्धव ठाकरेंची सर्वात मोठी बेईमानी; आशिष शेलार यांची जोरदार टीका</t>
+          <t>संगीत नाटकांसाठी रवींद्र नाट्य मंदिर २५ टक्के सवलतीत उपलब्ध होणार; ॲड.आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashish-shelar-strongly-criticizes-uddhav-thackeray-over-tree-cutting-in-mumbai-zws-70-5151721/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announced-that-ravindra-natya-mandir-will-be-available-at-a-25-percent-discount-mumbai-print-news-phm-00-5232212/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Ganeshotsav State Festival : गणेशोत्सव आता 'राज्य उत्सव'... शेलारांची मोठी घोषणा, उत्सव निर्बंध मुक्त अन् 500 कोटींचा निधी</t>
+          <t>“परिस्थितीच्या माऱ्याने दोघे एकत्र, आता नवा चित्रपट…”, आशिष शेलारांचा ठाकरे बंधूंना चिमटा; सिनेमाचं नावंही सांगितलं!</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-slams-raj-and-uddhav-thackeray-mentions-zenda-and-yek-number-movie-asc-95-5217275/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>पैठणीचे व्हिक्टोरिया अल्बर्ट संग्रहालयामध्ये प्रदर्शन, सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची विनंती मान्य</t>
+          <t>"राजकारणात फक्त आशिष शेलारांना ओळखते..."; ठाकरे बंधूंच्या मराठी मोर्चावर आशा भोसले काय म्हणाल्या?</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
+          <t>https://www.lokmat.com/filmy/in-politics-i-only-know-ashish-shelar-what-did-singer-asha-bhosle-say-about-the-raj-and-uddhav-thackeray-brothers-marathi-morcha-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Ashish Shelar: ठाकरे बंधूंचा एकत्र मोर्चा; आशिष शेलार थेटच म्हणाले…</t>
+          <t>कातळशिल्पांचा ‘जागतिक वारसा स्थळा’च्या यादीत समावेशासाठी रोडमॅप तयार करा, मंत्री आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5187751/thackeray-brothers-raj-thackeray-and-uddhav-thackeray-protest-against-state-government-over-hindi-launguage-ashish-shelar-gave-a-reaction/</t>
+          <t>https://www.loksatta.com/maharashtra/prepare-a-roadmap-for-the-inclusion-of-rock-sculptures-in-the-world-heritage-site-list-directed-by-minister-ashish-shelar-scj-81-5114434/</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
+          <t>Ganeshotsav State Festival : गणेशोत्सव आता 'राज्य उत्सव'... शेलारांची मोठी घोषणा, उत्सव निर्बंध मुक्त अन् 500 कोटींचा निधी</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-government-declare-ganeshotsav-state-festival-ashish-shelar-big-announcement-8853468</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>"महाराष्ट्रद्वेष हाच भाजपाचा खरा डीएनए", शेलार व निशिकांत दुबेंच्या वक्तव्यावरून आदित्य ठाकरेंचा संताप</t>
+          <t>महाराष्ट्राच्या राजकारणात उद्धव ठाकरेंची सर्वात मोठी बेईमानी; आशिष शेलार यांची जोरदार टीका</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/aditya-thackeray-says-hate-for-maharashtra-is-true-dna-of-bjp-over-nishikant-dubey-ashish-shelar-statement-asc-95-5211821/</t>
+          <t>https://www.loksatta.com/maharashtra/ashish-shelar-strongly-criticizes-uddhav-thackeray-over-tree-cutting-in-mumbai-zws-70-5151721/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ची स्तुती करणारे मंत्री शेलार आता कारवाई का करतायत? विरोधकांचा सरकारमधील लोकांवर संशय</t>
+          <t>पैठणीचे व्हिक्टोरिया अल्बर्ट संग्रहालयामध्ये प्रदर्शन, सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार यांची विनंती मान्य</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/khalid-ka-shivaji-rohit-pawar-oppess-ashish-shelar-action-against-marathi-movie-asc-95-5289901/</t>
+          <t>https://www.loksatta.com/mumbai/paithani-saree-exhibition-victoria-albert-museum-aashish-shelar-mumbai-print-news-css-98-5299768/</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>आशिष शेलारांचा पर्यावरणवाद्यांवर बनावट हिंदू सणविरोधी असल्याचा ठपका, पर्यावरणवाद्यांकडूनही खरपूस समाचार</t>
+          <t>Ashish Shelar: ठाकरे बंधूंचा एकत्र मोर्चा; आशिष शेलार थेटच म्हणाले…</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/cultural-minister-ashish-shelar-calls-environmentalists-anti-hindu-phm-00-5246668/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5187751/thackeray-brothers-raj-thackeray-and-uddhav-thackeray-protest-against-state-government-over-hindi-launguage-ashish-shelar-gave-a-reaction/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>चित्रकार रवी परांजपे यांच्या कलाकृती मंत्री ॲड. आशिष शेलार यांच्या उपस्थितीत शासनाकडे सुपूर्द</t>
+          <t>धार्मिक भावना आणि परंपरेचा आदर करूनच कुलस्वामिनी तुळजाभवानी मंदिर जीर्णोद्धाराचे काम; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176545/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelars-statement-regarding-the-renovation-work-of-kulswamini-tuljabhawani-temple-mumbai-print-news-amy-95-5313829/</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>राजकारणातले सच्चे मित्र दुरावले? आशिष शेलार आणि राज ठाकरेंमध्ये दुरावा?</t>
+          <t>प्रस्तावित वांद्रे – कुर्ला रेल्वे मार्गिकेचे संरेखन रद्द का केले? अहवाल सादर करण्याचे आशिष शेलार यांचे एमएमआरडीएला आदेश</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/ashish-shelar-still-upset-with-his-friens-mns-president-raj-thackeray/934652</t>
+          <t>https://www.loksatta.com/mumbai/bandra-kurla-railway-alignment-cancelled-controversy-ashish-shelar-orders-report-to-mmrda-mumbai-print-news-vsd-99-5174076/</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>संगीत नाटकांसाठी रवींद्र नाट्य मंदिर २५ टक्के सवलतीत उपलब्ध होणार; ॲड.आशिष शेलार यांची घोषणा</t>
+          <t>"महाराष्ट्रद्वेष हाच भाजपाचा खरा डीएनए", शेलार व निशिकांत दुबेंच्या वक्तव्यावरून आदित्य ठाकरेंचा संताप</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announced-that-ravindra-natya-mandir-will-be-available-at-a-25-percent-discount-mumbai-print-news-phm-00-5232212/</t>
+          <t>https://www.loksatta.com/maharashtra/aditya-thackeray-says-hate-for-maharashtra-is-true-dna-of-bjp-over-nishikant-dubey-ashish-shelar-statement-asc-95-5211821/</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>BJP Mumbai President :बीएमसी निवडणुकीआधी भाजपने भाकरी फिरवली, शेलारांना नारळ, मुंबईची धुरा कोणाकडे?</t>
+          <t>‘खालिद का शिवाजी’ची स्तुती करणारे मंत्री शेलार आता कारवाई का करतायत? विरोधकांचा सरकारमधील लोकांवर संशय</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
+          <t>https://www.loksatta.com/maharashtra/khalid-ka-shivaji-rohit-pawar-oppess-ashish-shelar-action-against-marathi-movie-asc-95-5289901/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Ashish Shelar And Mungantiwar : मुनगंटीवार म्हणाले, मी देखील चुकून काही काळ, आशिष शेलारांनीच दिले उत्तर</t>
+          <t>आशिष शेलारांचा पर्यावरणवाद्यांवर बनावट हिंदू सणविरोधी असल्याचा ठपका, पर्यावरणवाद्यांकडूनही खरपूस समाचार</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
+          <t>https://www.loksatta.com/nagpur/cultural-minister-ashish-shelar-calls-environmentalists-anti-hindu-phm-00-5246668/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>टीका करताना शेलारांचा तोल सुटला! मनसे कार्यकर्त्यांची पहलगामच्या दहशतवाद्यांशी तुलना; म्हणाले, त्यांनी...</t>
+          <t>राजकारणातले सच्चे मित्र दुरावले? आशिष शेलार आणि राज ठाकरेंमध्ये दुरावा?</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/bjp-ashish-shelar-compare-raj-thackeray-mns-workers-with-pahalgam-terrorist-after-shivsena-victory-rally-vijayi-melava-in-mumbai-with-uddhav-thackeray/921560</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/ashish-shelar-still-upset-with-his-friens-mns-president-raj-thackeray/934652</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुकीच्या तोंडावर भाजपमधील धुसफुस चव्हाट्यावर, आशीष शेलार यांच्यासमोरच हाणामारी, खडाजंगी</t>
+          <t>BJP Mumbai President :बीएमसी निवडणुकीआधी भाजपने भाकरी फिरवली, शेलारांना नारळ, मुंबईची धुरा कोणाकडे?</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-workers-clashed-with-each-other-in-front-of-minister-ashish-shelar-in-kandivali-zws-70-5156138/</t>
+          <t>https://news18marathi.com/maharashtra/bjp-announce-amit-satam-as-party-mumbai-president-insted-of-ashish-shelar-1465757.html</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार - MANIK MOTI BOOK LAUNCH</t>
+          <t>Ashish Shelar And Mungantiwar : मुनगंटीवार म्हणाले, मी देखील चुकून काही काळ, आशिष शेलारांनीच दिले उत्तर</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/publication-of-the-biography-book-manik-moti-based-on-the-veteran-singer-manik-verma-maharashtra-news-mhs25051306533</t>
+          <t>https://www.mymahanagar.com/maharashtra/former-minister-sudhir-mungantiwar-said-i-was-a-minister-by-mistake-while-minister-ashish-shelar-said-you-are-our-leader-in-marathi/859112/</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>गणेशोत्सवात यंदा सात दिवस रात्री उशिरापर्यंत ध्वनिक्षेपक? मंत्री शेलारांनी स्पष्टच सांगितले…!</t>
+          <t>महापालिका निवडणुकीच्या तोंडावर भाजपमधील धुसफुस चव्हाट्यावर, आशीष शेलार यांच्यासमोरच हाणामारी, खडाजंगी</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/pune-ashish-shelar-says-district-collectors-can-allow-loudspeaker-use-till-midnight-during-ganeshotsav-pune-print-news-rds-00-5320532/</t>
+          <t>https://www.loksatta.com/mumbai/bjp-workers-clashed-with-each-other-in-front-of-minister-ashish-shelar-in-kandivali-zws-70-5156138/</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Ganesh visarjan guidelines : उंच गणेशमूर्तींच्या विसर्जनाबाबत 30 तारखेपर्यंत भूमिका मांडणार</t>
+          <t>महिनाभरात चार हजार खड्डे; गणेशोत्सवापूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे बुजवा – ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/tall-ganesh-idol-immersion-guidelines-2025-ab96</t>
+          <t>https://www.loksatta.com/mumbai/four-thousand-potholes-on-mumbai-roads-in-a-month-mumbai-print-news-phm-00-5324291/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>राज ठाकरेंशी संबधित ‘येक नंबर’ हिट की फ्लॉप? शेलारांची थेट विधीमंडळात माहिती, बजेट व बॉक्स ऑफिस कलेक्शनची तुलना करत म्हणाले…</t>
+          <t>चित्रकार रवी परांजपे यांच्या कलाकृती मंत्री ॲड. आशिष शेलार यांच्या उपस्थितीत शासनाकडे सुपूर्द</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/raj-thackeray-yek-number-movie-box-office-collection-ashish-shelar-teases-at-assembly-monsoon-session-asc-95-5217195/</t>
+          <t>https://mahasamvad.in/176545/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: मनसेकडून ठाकरे गटाला निमंत्रण दिल्यानं भाजप नाराज प्रतिसभागृहात सहभागी</t>
+          <t>टीका करताना शेलारांचा तोल सुटला! मनसे कार्यकर्त्यांची पहलगामच्या दहशतवाद्यांशी तुलना; म्हणाले, त्यांनी...</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/bjp-ashish-shelar-compare-raj-thackeray-mns-workers-with-pahalgam-terrorist-after-shivsena-victory-rally-vijayi-melava-in-mumbai-with-uddhav-thackeray/921560</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>विमान सुरक्षेसाठी पक्ष्यांचा वावर कमी करण्याच्या नव्या संकल्पना शोधण्याचे मुंबई उपनगर पालकमंत्री ॲड आशिष शेलार यांचे निर्देश</t>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार - MANIK MOTI BOOK LAUNCH</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-instructed-to-find-new-concepts-to-reduce-bird-strike-on-aircraft-zws-70-5186222/</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/publication-of-the-biography-book-manik-moti-based-on-the-veteran-singer-manik-verma-maharashtra-news-mhs25051306533</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>मुंबईत घडतेय तरी काय? आता अमित ठाकरेंनी घेतली आशिष शेलारांची भेट; राजकीय वर्तुळात चर्चा</t>
+          <t>गणेशोत्सवात यंदा सात दिवस रात्री उशिरापर्यंत ध्वनिक्षेपक? मंत्री शेलारांनी स्पष्टच सांगितले…!</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mns-leader-amit-raj-thackeray-meets-bjp-minister-ashish-shelar-know-about-what-is-exactly-the-reason-a-a719/</t>
+          <t>https://www.loksatta.com/pune/pune-ashish-shelar-says-district-collectors-can-allow-loudspeaker-use-till-midnight-during-ganeshotsav-pune-print-news-rds-00-5320532/</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>चित्रनगरीतील कामांची पाहणी मंत्री आशिष शेलार यांनी केली.</t>
+          <t>Ganesh visarjan guidelines : उंच गणेशमूर्तींच्या विसर्जनाबाबत 30 तारखेपर्यंत भूमिका मांडणार</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/kolhapur-minister-ashish-shelar-inspected-ongoing-works-in-chitranagari-ocd-94-5192132/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/tall-ganesh-idol-immersion-guidelines-2025-ab96</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>साताऱ्यातील ‘फाशीचा वड’ स्थळाच्या राज्य स्मारकासाठी प्रस्ताव पाठवावा, मंत्री आशिष शेलार यांची सूचना</t>
+          <t>राज ठाकरेंशी संबधित ‘येक नंबर’ हिट की फ्लॉप? शेलारांची थेट विधीमंडळात माहिती, बजेट व बॉक्स ऑफिस कलेक्शनची तुलना करत म्हणाले…</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-on-satara-s-fashicha-wad-state-memorial-proposal-css-98-5153794/</t>
+          <t>https://www.loksatta.com/maharashtra/raj-thackeray-yek-number-movie-box-office-collection-ashish-shelar-teases-at-assembly-monsoon-session-asc-95-5217195/</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>गणेशोत्सव आंतरराष्ट्रीय पातळीवर पोहचविणार, सांस्कृतिक कार्यमंत्री आशिष शेलार यांची घोषणा</t>
+          <t>Maharashtra Politics: मनसेकडून ठाकरे गटाला निमंत्रण दिल्यानं भाजप नाराज प्रतिसभागृहात सहभागी</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-announcement-in-assembly-session-ganeshotsav-international-level-publicity-asj-82-5238641/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-mns-holds-municipal-hall-in-mumbai-bjp-refuses-to-participate-in-the-program-mumbai-municipal-corporation-1356260</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाला राज्य महोत्सवाचा दर्जा, गणेशभक्तांमध्ये उत्साहाचे वातावरण</t>
+          <t>विमान सुरक्षेसाठी पक्ष्यांचा वावर कमी करण्याच्या नव्या संकल्पना शोधण्याचे मुंबई उपनगर पालकमंत्री ॲड आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
+          <t>https://www.loksatta.com/mumbai/minister-ashish-shelar-instructed-to-find-new-concepts-to-reduce-bird-strike-on-aircraft-zws-70-5186222/</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>‘राज्य महोत्सव’ गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी - सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार</t>
+          <t>चित्रनगरीतील कामांची पाहणी मंत्री आशिष शेलार यांनी केली.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/176672/</t>
+          <t>https://www.loksatta.com/maharashtra/kolhapur-minister-ashish-shelar-inspected-ongoing-works-in-chitranagari-ocd-94-5192132/</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>पीओपी गणेश मूर्तींवर बंदीला काँग्रेस जबाबदार, सांस्कृतीक कार्य मंत्री आशिष शेलार यांचा आरोप</t>
+          <t>Ashish Shelar:”मुंबईची तुंबई करण्याचं पाप…”;आशिष शेलार यांची आदित्य ठाकरेंवर टीका</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-alleged-congress-and-mahavikas-aghadi-for-conspired-to-ban-pop-ganesh-idols-sud-02-5242178/</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5115217/bjp-leader-ashish-shelar-criticised-on-mla-aaditya-thackeray/</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरेंचा तो नेता भाजपाच्या दरबारात; चर्चांना उधाण, म्हणाला मी आमदार झाल्यापासून...</t>
+          <t>साताऱ्यातील ‘फाशीचा वड’ स्थळाच्या राज्य स्मारकासाठी प्रस्ताव पाठवावा, मंत्री आशिष शेलार यांची सूचना</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/mumbai/shivsena-uddhav-thackeray-mla-mahesh-sawant-attends-janta-darbar-of-bjp-leader-ashish-shelar/930835</t>
+          <t>https://www.loksatta.com/maharashtra/minister-ashish-shelar-on-satara-s-fashicha-wad-state-memorial-proposal-css-98-5153794/</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>मुंबईत भरणार देशातील पहिला ‘रेडिओ’ महोत्सव - आशिष शेलार यांची घोषणा; मराठी भाषा आणि कलाकारांसाठी नवे व्यासपीठ</t>
+          <t>मुंबई महापालिकेत ठाकरे बंधूंना टक्कर देणार भाजपाचे 'जय-वीरू'; आशिष शेलारांनी डिवचलं, म्हणाले... Mumbai Marathi News | BJP's Ashish Shelar criticizes Uddhav Thackeray and Raj Thackeray over BEST Kamgar Patpedhi elec</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/17/maharashtra-radio-festival-for-the-first-time.html</t>
+          <t>https://www.lokmat.com/shorts/mumbai/bjp-s-jai-veeru-to-challenge-thackeray-brothers-in-mumbai-municipal-elections/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>BJP MNS Friendship: हिंदी सक्तीच्या निर्णयावरुन भाजप-मनसेची मैत्री तुटणार? राजकीय वॉर सुरु</t>
+          <t>गणेशोत्सव आंतरराष्ट्रीय पातळीवर पोहचविणार, सांस्कृतिक कार्यमंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
+          <t>https://www.loksatta.com/mumbai/ashish-shelar-announcement-in-assembly-session-ganeshotsav-international-level-publicity-asj-82-5238641/</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>एल्फिन्स्टन पुलाच्या परिसरातील रहिवाशांना त्याच ठिकाणी मिळणार घरे; मुख्यमंत्री फडणवीसांच्या बैठकीत निर्णय</t>
+          <t>गणेशोत्सवाला राज्य महोत्सवाचा दर्जा, गणेशभक्तांमध्ये उत्साहाचे वातावरण</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/mmrda-to-redevelop-19-buildings-near-elphinstone-bridge-a-a1001/</t>
+          <t>https://www.loksatta.com/mumbai/bjp-leader-ashish-shelar-announced-ganeshotsav-as-maharashtras-official-festival-symbolizing-unity-harmony-sud-02-5219549/</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>महाराष्ट्र : आशीष शेलार का ठाकरे ब्रदर्स पर हमला, कहा- सिर्फ घर बैठकर करते हैं राजनीति</t>
+          <t>‘राज्य महोत्सव’ गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी - सांस्कृतिक कार्य मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
+          <t>https://mahasamvad.in/176672/</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>महाराष्ट्र जिंकला, मराठी माणूस जिंकला, भाजप जिंकला: मंत्री आशिष शेलार</t>
+          <t>उद्धव ठाकरेंचा तो नेता भाजपाच्या दरबारात; चर्चांना उधाण, म्हणाला मी आमदार झाल्यापासून...</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/maharashtra-wins-marathi-people-win-bjp-wins-says-mumbai-chief-ashish-shelar-as-mahayuti-slams-mva-over-three-language-policy/articleshow-odudhrc</t>
+          <t>https://zeenews.india.com/marathi/mumbai/shivsena-uddhav-thackeray-mla-mahesh-sawant-attends-janta-darbar-of-bjp-leader-ashish-shelar/930835</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>आशिष शेलार यांना ‘नाफा’ मराठी चित्रपट महोत्सवाचे विशेष निमंत्रण !</t>
+          <t>मुंबईत भरणार देशातील पहिला ‘रेडिओ’ महोत्सव - आशिष शेलार यांची घोषणा; मराठी भाषा आणि कलाकारांसाठी नवे व्यासपीठ</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/17/maharashtra-radio-festival-for-the-first-time.html</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>आशिष शेलार यांचे आवाहन,“राज्य महोत्सवा” करिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी</t>
+          <t>Ashish Shelar: पीओपीमुर्तीवरील बंदी उठली, आता मोठ्या गणेशमुर्ती विसर्जनाबाबतही घेणार निर्णय; आशिष शेलार काय म्हणाले?</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
+          <t>https://www.esakal.com/mumbai/ashish-shelar-says-after-ban-on-pop-idols-was-lifted-now-government-will-take-decision-on-ganeshotsav-visarjan-mvk02</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>“राज्य महोत्सव” गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी – सांस्कृतिक कार्य मंत्री आशिष शेलार</t>
+          <t>BJP MNS Friendship: हिंदी सक्तीच्या निर्णयावरुन भाजप-मनसेची मैत्री तुटणार? राजकीय वॉर सुरु</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
+          <t>https://civicmirror.in/maharashtra/bjp-mns-friendship-will-break-due-to-hindi-mandatory-decision-politics-war-maharashtra-politics/</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Pune Ganesh Festival 2025 : पुण्यातील मंडळांनी लक्ष द्या! सांस्कृतिक मंत्र्याच्या अध्यक्षतेखाली बैठक, कोणते मोठे निर्णय झाले? जाणून घ्या...</t>
+          <t>Mumbai News : मोठी बातमी! एल्फिन्स्टन पुलाच्या परिसरातील 19 इमारतींमधील सर्व रहिवाशांना त्याच ठिकाणी घरे मिळणार</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maharashtra-government-gives-big-relief-to-19-buildings-people-who-affected-in-elphinstone-bridge-redevelopment/articleshow/120695379.cms</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>आग्र्यावरून सुटकेचा दिवस ‘शिवचातुर्य दिन’ म्हणून साजरा होणार; मंत्री Ashish Shelar यांची घोषणा</t>
+          <t>महाराष्ट्र : आशीष शेलार का ठाकरे ब्रदर्स पर हमला, कहा- सिर्फ घर बैठकर करते हैं राजनीति</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-maharashtra-ashish-shelar-attacks-thackeray-brothers-says-they-only-do-politics-sitting-at-home-news-hindi-1-746796-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Maharashtra: एमवीए के अंत को लेकर अपनी भविष्यवाणी पर आशीष शेलार बोले- सच साबित हुई, घोषणा की औपचारिकता बाकी</t>
+          <t>आशिष शेलार यांना ‘नाफा’ मराठी चित्रपट महोत्सवाचे विशेष निमंत्रण !</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/maharashtra-minister-ashish-shelar-says-my-prediction-about-mva-end-come-true-2025-02-14</t>
+          <t>https://lokmanthan.com/ashish-shelar-receives-special-invitation-to-nafa-marathi-film-festival/</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>'मुंबई में हिंदुओं को भाषा के कारण पीटा', BJP नेता आशीष शेलार ने पहलगाम हमले से की थप्‍पड़कांड की तुलना</t>
+          <t>आशिष शेलार यांचे आवाहन,“राज्य महोत्सवा” करिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
+          <t>https://www.marathiebatmya.com/political/ashish-shelars-appeal-every-department-increase-participation-in-festival/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>मंत्री आशीष शेलार के 'मराठी और पहलगाम' वाले बयान पर भड़के संजय राउत, बोले- 'भाषा</t>
+          <t>“राज्य महोत्सव” गणेशोत्सवाकरिता प्रत्येक शासकीय विभागाने सहभागीता वाढवावी – सांस्कृतिक कार्य मंत्री आशिष शेलार</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
+          <t>https://civicmirror.in/maharashtra/every-government-department-should-increase-participation-in-the-state-festival-ganeshotsav-cultural-affairs-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Maharashtra won, Marathi Manus won, BJP won in this fight, says BJP Mumbai chief Ashish Shelar slams MVA over three-language policy issue</t>
+          <t>Pune Ganesh Festival 2025 : पुण्यातील मंडळांनी लक्ष द्या! सांस्कृतिक मंत्र्याच्या अध्यक्षतेखाली बैठक, कोणते मोठे निर्णय झाले? जाणून घ्या...</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
+          <t>https://www.dainikprabhat.com/pay-attention-to-the-mandals-in-pune-meeting-chaired-by-the-minister-of-culture-what-major-decisions-were-made-find-out/</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Maharashtra: मुंबई में जलभराव पर सियासत तेज, मंत्री आशीष शेलार ने कर दी बड़ी मांग, उद्धव</t>
+          <t>आग्र्यावरून सुटकेचा दिवस ‘शिवचातुर्य दिन’ म्हणून साजरा होणार; मंत्री Ashish Shelar यांची घोषणा</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
+          <t>https://www.marathi.hindusthanpost.com/social/the-day-of-liberation-from-agra-will-be-celebrated-as-shiva-chaturya-day-announcement-by-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में 'खालिद का शिवाजी' मूवी को बैन करने की मांग के बीच मंत्री आशीष शेलार का बड़ा बयान, जानें क्या कुछ कहा?</t>
+          <t>Maharashtra: एमवीए के अंत को लेकर अपनी भविष्यवाणी पर आशीष शेलार बोले- सच साबित हुई, घोषणा की औपचारिकता बाकी</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
+          <t>https://www.amarujala.com/india-news/maharashtra-minister-ashish-shelar-says-my-prediction-about-mva-end-come-true-2025-02-14</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>मुंबई: मंत्री की मौजूदगी में BJP कार्यकर्ताओं के दो गुटों में हिंसक झड़प, हिरासत में लिए गए देवांग दवे</t>
+          <t>'मुंबई में हिंदुओं को भाषा के कारण पीटा', BJP नेता आशीष शेलार ने पहलगाम हमले से की थप्‍पड़कांड की तुलना</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
+          <t>https://ndtv.in/india/bjp-leader-ashish-shelar-compared-the-slapping-incident-with-pahalgam-attack-8832138</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>‘इन गानों को नियमित रूप से बजाएं’, प्राइवेट रेडियो स्टेशनों से महाराष्ट्र के</t>
+          <t>मंत्री आशीष शेलार के 'मराठी और पहलगाम' वाले बयान पर भड़के संजय राउत, बोले- 'भाषा</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
+          <t>https://www.abplive.com/states/maharashtra/sanjay-raut-shiv-sena-ubt-angry-on-ashish-shelar-for-comparing-marathi-dispute-with-pahalgam-terror-attack-2975138</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Maharashta: भाजपा नेता आशीष शेलार ने की हिंदी भाषी लोगों पर हमले की निंदा, पहलगाम आतंकी हमले से की तुलना</t>
+          <t>Work collectively to take Ganesh festival to global stage: Ashish Shelar - Hindustan Times</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-2025-07-06</t>
+          <t>https://www.hindustantimes.com/cities/pune-news/work-collectively-to-take-ganesh-festival-to-global-stage-ashish-shelar-101755717340688.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Marathi School in USA: अमेरिकतील मराठी शाळांना महाराष्ट्र शासन अभ्यासक्रम पुरवणार, आशिष शेलार यांचे आश्वासन</t>
+          <t>Maharashtra: मुंबई में जलभराव पर सियासत तेज, मंत्री आशीष शेलार ने कर दी बड़ी मांग, उद्धव</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
+          <t>https://www.abplive.com/states/mumbai-monsoon-waterlogging-minister-ashish-shelar-demand-white-paper-from-uddhav-thackeray-over-infrastructure-projects-delay-ann-2952350</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>मुंबई की सड़कों के सारे गड्ढे भरेगी बीएमसी, आशीष शेलार का ऐलान</t>
+          <t>Maharashtra won, Marathi Manus won, BJP won in this fight, says BJP Mumbai chief Ashish Shelar slams MVA over three-language policy issue</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-won-marathi-manus-won-bjp-won-in-this-fight-says-bjp-mumbai-chief-ashish-shelar-slams-mva-over-three-language-policy-issue-23582399</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BJP नेता आशीष शेलार का उद्धव ठाकरे पर गंभीर आरोप, 'मुंबई में जितने भी जमीन से जुड़े</t>
+          <t>मुंबई: मंत्री की मौजूदगी में BJP कार्यकर्ताओं के दो गुटों में हिंसक झड़प, हिरासत में लिए गए देवांग दवे</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-workers-clash-in-front-of-minister-ashish-shelar-in-kandivali-devang-dave-infighting-lclk-strc-2263251-2025-06-13</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>'पहलगाम की तरह महाराष्ट्र में भी...', MNS कार्यकर्ताओं की गुंडागर्दी पर महाराष्ट्र के मंत्री ने कसा तंज - Maharashtra Minister Ashish Shelar Compares Violence with Pahalgam Terror Attack amid Marathi Language Controv</t>
+          <t>महाराष्ट्र में 'खालिद का शिवाजी' मूवी को बैन करने की मांग के बीच मंत्री आशीष शेलार का बड़ा बयान, जानें क्या कुछ कहा?</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-minister-ashish-shelar-said-khalid-ka-shivaji-film-should-be-re-examined-sent-letter-to-central-government-amid-ban-demand-know-all/articleshow/123167844.cms</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Maharashtra Language Row: Ashish Shelar के बयान से सियासी संग्राम, Aaditya Thackeray का पलटवार!</t>
+          <t>‘इन गानों को नियमित रूप से बजाएं’, प्राइवेट रेडियो स्टेशनों से महाराष्ट्र के</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-minister-ashish-shelar-appeal-to-private-radio-stations-for-play-marathi-emotional-and-devotional-songs-regularly-2948512</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>राज-उद्धव ठाकरे के साथ आने पर BJP का बड़ा बयान- 'जब वह मुख्यमंत्री थे तो...'</t>
+          <t>Maharashta: भाजपा नेता आशीष शेलार ने की हिंदी भाषी लोगों पर हमले की निंदा, पहलगाम आतंकी हमले से की तुलना</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
+          <t>https://www.amarujala.com/india-news/bjp-leader-condemns-assault-on-hindi-speaking-people-draws-parallel-with-pahalgam-attack-2025-07-06</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>रघुजी भोसले की पौराणिक तलवार लौटेगी भारत, आशीष शेलार ने जताई खुशी</t>
+          <t>Marathi School in USA: अमेरिकतील मराठी शाळांना महाराष्ट्र शासन अभ्यासक्रम पुरवणार, आशिष शेलार यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
+          <t>https://marathi.ndtv.com/cities/maharashtra-government-will-provide-syllabus-to-marathi-schools-in-america-assures-ashish-shelar-8946300</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>एकनाथ शिंदे के सम्मान को लेकर शरद पवार पर भड़की शिवसेना-यूबीटी तो BJP ने कसा तंज,</t>
+          <t>मुंबई की सड़कों के सारे गड्ढे भरेगी बीएमसी, आशीष शेलार का ऐलान</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
+          <t>https://hindi.mid-day.com/mumbai/mumbai-news/article/bmc-will-fill-all-the-potholes-on-mumbai-roads-ashish-shelar-announced-11278</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Maharashtra: IT विभाग में 1000 करोड़ के घोटाला का दावा, मंत्री आशीष शेलार का एक्शन, अफसर को</t>
+          <t>'पहलगाम की तरह महाराष्ट्र में भी...', MNS कार्यकर्ताओं की गुंडागर्दी पर महाराष्ट्र के मंत्री ने कसा तंज - Maharashtra Minister Ashish Shelar Compares Violence with Pahalgam Terror Attack amid Marathi Language Controv</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
+          <t>https://www.jagran.com/news/national-maharashtra-minister-ashish-shelar-compares-violence-with-pahalgam-terror-attack-amid-marathi-language-controversy-23976944.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>इतिहास से छेड़छाड़ बर्दाश्त नहीं की जाएगी... विवादों में घिरी फिल्‍म 'खालिद का शिवाजी' पर मंत्री आशीष शेलार</t>
+          <t>हाथ मलते रह जाएंगे उद्धव ठाकरे? कई नेता बीजेपी और एकनाथ शिंदे के संपर्क में, आशीष शेलार ने किया बड़ा दावा</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
+          <t>https://www.indiatv.in/maharashtra/will-uddhav-thackeray-be-left-rubbing-his-hands-many-leaders-are-in-touch-with-bjp-and-eknath-shinde-ashish-shelar-made-a-big-claim-2025-02-15-1113497</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>‘हिंदुओं पर उनकी भाषा के कारण हमला…’, महाराष्ट्र सरकार के मंत्री ने मराठी विवाद को पहलगाम से जोड़ा</t>
+          <t>Maharashtra Language Row: Ashish Shelar के बयान से सियासी संग्राम, Aaditya Thackeray का पलटवार!</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
+          <t>https://www.abplive.com/videos/news/maharashtra-language-row-ashish-shelar-s-pahalgam-attack-comparison-sparks-political-firestorm-with-aaditya-thackeray-s-retort-2975019</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Cannes: कान फिल्म फेस्टिवल के लिए चयनित हुईं चार मराठी फिल्में, मंत्री आशीष शेलार ने दी सभी को बधाई</t>
+          <t>राज-उद्धव ठाकरे के साथ आने पर BJP का बड़ा बयान- 'जब वह मुख्यमंत्री थे तो...'</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-bjp-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-together-ann-2969595</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Asha Bhosle News: 'मी फक्त आशिष शेलारांना ओळखते..', ठाकरे बंधुंच्या मनोमिलनावर आशा भोसले काय म्हणाल्या?</t>
+          <t>इतिहास से छेड़छाड़ बर्दाश्त नहीं की जाएगी... विवादों में घिरी फिल्‍म 'खालिद का शिवाजी' पर मंत्री आशीष शेलार</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
+          <t>https://ndtv.in/india/film-khalid-ka-shivaji-surrounded-by-controversies-minister-ashish-shelar-big-statement-many-organizations-demanded-ban-9042401</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>भाषा विवाद पर महाराष्ट्र में तनाव, मंत्री आशीष शेलार ने की पहलगाम हमले से तुलना</t>
+          <t>Maharashtra: IT विभाग में 1000 करोड़ के घोटाला का दावा, मंत्री आशीष शेलार का एक्शन, अफसर को</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://hindi.asianetnews.com/state/maharashtra/ashish-shelar-compares-pahalgam-terror-attack-marathi-hindi-row-controversy/articleshow-ma03grc</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-it-department-section-officer-mukesh-somkuwar-1000-crore-scandal-suspended-by-minister-ashish-shelar-ann-3000145</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>मराठी पर बवाल जारी! रोहित पवार ने पंडित धीरेंद्र शास्त्री को दे दी चेतावनी- 'जहां</t>
+          <t>‘हिंदुओं पर उनकी भाषा के कारण हमला…’, महाराष्ट्र सरकार के मंत्री ने मराठी विवाद को पहलगाम से जोड़ा</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
+          <t>https://www.jansatta.com/national/maharashtra-government-minister-linked-marathi-non-marathi-language-dispute-to-pahalgam-attack-hindus-attacked-because-of-their-language/4034283/</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>मुंबई में हिंदी भाषा के कारण पीटा… मंत्री आशीष सलार ने पहलगाम आतंकी हमले से की तुलना</t>
+          <t>रघुजी भोसले की पौराणिक तलवार लौटेगी भारत, आशीष शेलार ने जताई खुशी</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-hindi-speaker-attacks-bjp-ashish-shelar-condemns-violence-compares-to-pulwama-3376913.html</t>
+          <t>https://ndtv.in/india/raghuji-bhosales-legendary-sword-will-return-to-india-ashish-shelar-expressed-happiness-9065700</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>तणावाच्या परिस्थितीमुळे माहिती तंत्रज्ञान आणि सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचा दौरा रद्द</t>
+          <t>BJP नेता आशीष शेलार का उद्धव ठाकरे पर गंभीर आरोप, 'मुंबई में जितने भी जमीन से जुड़े</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/165514/</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-mumbai-bjp-attacked-uddhav-thackeray-bmc-elections-2025-ann-2930287</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>सर्वात मोठी बातमी ! गणेशोत्सव महाराष्ट्राचा महोत्सव म्हणून घोषित; आशिष शेलार यांची घोषणा</t>
+          <t>Cannes: कान फिल्म फेस्टिवल के लिए चयनित हुईं चार मराठी फिल्में, मंत्री आशीष शेलार ने दी सभी को बधाई</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/maharashtra-declares-ganeshotsav-as-state-festival-bjp-leader-ashish-shalar-announcement-1442515.html</t>
+          <t>https://www.amarujala.com/entertainment/four-marathi-movies-selected-for-cannes-film-festival-cultural-minister-ashish-shelar-congratulates-them-2025-04-20</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>फडणवीस इफेक्ट या ठाकरे इम्पैक्ट? आशीष शेलार की जगह अमित साटम को मुंबई BJP की कमान के पीछे क्या</t>
+          <t>Asha Bhosle News: 'मी फक्त आशिष शेलारांना ओळखते..', ठाकरे बंधुंच्या मनोमिलनावर आशा भोसले काय म्हणाल्या?</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/amit-satam-mumbai-bjp-new-president-cm-devendra-fadnavish-ashish-shelar-civic-polls-ntcpbt-rpti-2318125-2025-08-25</t>
+          <t>https://marathi.ndtv.com/maharashtra/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-i-only-know-ashish-shelar-8789401</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार; दोन दिवसांआधी राज ठाकरेंनीही देवेंद्र फडणवीसांची घेतली होती भेट</t>
+          <t>एकनाथ शिंदे के सम्मान को लेकर शरद पवार पर भड़की शिवसेना-यूबीटी तो BJP ने कसा तंज,</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-reaction-on-shiv-sena-ubt-got-angry-on-sharad-pawar-honor-of-eknath-shinde-mva-end-2883978</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>देवेंद्र फडणवीस से मिले राज ठाकरे, अब बेटे अमित ठाकरे की आशीष शेलार से मुलाकात, महाराष्ट्र में कुछ पक रहा है?</t>
+          <t>भाषा विवाद पर महाराष्ट्र में तनाव, मंत्री आशीष शेलार ने की पहलगाम हमले से तुलना</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
+          <t>https://hindi.asianetnews.com/state/maharashtra/ashish-shelar-compares-pahalgam-terror-attack-marathi-hindi-row-controversy/articleshow-ma03grc</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Big announcement: मराठ्यांच्या पराक्रमाची साक्ष असलेली ऐतिहासिक तलवार लवकरच महाराष्ट्रात येणार</t>
+          <t>मराठी पर बवाल जारी! रोहित पवार ने पंडित धीरेंद्र शास्त्री को दे दी चेतावनी- 'जहां</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
+          <t>https://www.abplive.com/states/maharashtra/rohit-pawar-reacted-on-nishikhant-dubeys-dhirendra-shastri-and-ashish-shelar-statement-ann-2975099</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Clerk-Typist Exam Result: लिपिक-टंकलेखक परीक्षेचा निकाल कधी लागणार? आशिष शेलारांनी दिली माहिती</t>
+          <t>मुंबई में हिंदी भाषा के कारण पीटा… मंत्री आशीष सलार ने पहलगाम आतंकी हमले से की तुलना</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-hindi-speaker-attacks-bjp-ashish-shelar-condemns-violence-compares-to-pulwama-3376913.html</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>भजनी मंडळांना २५ हजारांचे अनुदान; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची माहिती</t>
+          <t>तणावाच्या परिस्थितीमुळे माहिती तंत्रज्ञान आणि सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचा दौरा रद्द</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-bhajani-mandals-grant-25000-ashish-shelar</t>
+          <t>https://mahasamvad.in/165514/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>स्थानीय राजनीति को इंटरनेशनल मुद्दों से नहीं जोड़ना चाहिए… संजय राउत के बयान पर बोले शरद पवार</t>
+          <t>सर्वात मोठी बातमी ! गणेशोत्सव महाराष्ट्राचा महोत्सव म्हणून घोषित; आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/maharashtra-bjp-leader-ashish-shelar-sharad-pawar-reaction-on-sanjay-raut-over-all-party-delegation-row-3297804.html</t>
+          <t>https://www.tv9marathi.com/maharashtra/maharashtra-declares-ganeshotsav-as-state-festival-bjp-leader-ashish-shalar-announcement-1442515.html</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Hindi Controversy: 'मराठी'वरुन दहशतवाद्यांशी तुलना, आशिष शेलारांच्या वक्तव्याचा मनसेकडून समाचार</t>
+          <t>फडणवीस इफेक्ट या ठाकरे इम्पैक्ट? आशीष शेलार की जगह अमित साटम को मुंबई BJP की कमान के पीछे क्या</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/amit-satam-mumbai-bjp-new-president-cm-devendra-fadnavish-ashish-shelar-civic-polls-ntcpbt-rpti-2318125-2025-08-25</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>शिवसेना UBT की हालत मुंबई की 'खतरनाक' और 'जर्जर' इमारतों जैसी, महाराष्ट्र के मंत्री आशीष शेलार ने कसा तंज</t>
+          <t>Amit Thackeray Meet Ashish Shelar मोठी बातमी: अमित ठाकरे आशिष शेलारांना भेटणार; दोन दिवसांआधी राज ठाकरेंनीही देवेंद्र फडणवीसांची घेतली होती भेट</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
+          <t>https://www.msn.com/mr-in/news/other/amit-thackeray-meet-ashish-shelar-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AD%E0%A5%87%E0%A4%9F%E0%A4%A3-%E0%A4%B0-%E0%A4%A6-%E0%A4%A8-%E0%A4%A6-%E0%A4%B5%E0%A4%B8-%E0%A4%82%E0%A4%86%E0%A4%A7-%E0%A4%B0-%E0%A4%9C-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%82%E0%A4%A8-%E0%A4%B9-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A-%E0%A4%98%E0%A5%87%E0%A4%A4%E0%A4%B2-%E0%A4%B9-%E0%A4%A4-%E0%A4%AD%E0%A5%87%E0%A4%9F/ar-AA1L3MvM</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>नागरिकांना डिजिटल सेवा देण्यासाठी शासन प्रयत्नशील – मंत्री ॲड.आशिष शेलार</t>
+          <t>देवेंद्र फडणवीस से मिले राज ठाकरे, अब बेटे अमित ठाकरे की आशीष शेलार से मुलाकात, महाराष्ट्र में कुछ पक रहा है?</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/159784/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/amit-thackeray-meets-ashish-shelar-after-father-raj-thackeray-and-devendra-fadnavis-meeting-something-happing-in-maharashtra/articleshow/123467261.cms</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में कुछ होने वाला है बड़ा? पहले CM फडणवीस से मिले राज ठाकरे, अब बेटे ने BJP नेता से की मुलाकात</t>
+          <t>BJP on Raj Uddhav Alliance: ठाकरे बंधूंच्या एकत्र येण्याची पोस्ट अमित शाहांना टॅग केली, आशिष</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/maharashtra-politics-amit-thackeray-met-minister-ashish-shelar-after-raj-thackeray-meeting-with-cm-fadnavis/2893316</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>आपले सरकार सेवा केंद्रांच्या संख्येत वाढ – माहिती तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
+          <t>Big announcement: मराठ्यांच्या पराक्रमाची साक्ष असलेली ऐतिहासिक तलवार लवकरच महाराष्ट्रात येणार</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160573/</t>
+          <t>https://marathi.ndtv.com/politics/ashish-shelar-information-that-the-historical-sword-of-the-bhosale-family-of-nagpur-which-is-in-london-will-come-to-india-8839059</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में हिंदी को लेकर सियासी बवाल, उद्धव ठाकरे से जुड़े सवाल पर आशा भोसले</t>
+          <t>Clerk-Typist Exam Result: लिपिक-टंकलेखक परीक्षेचा निकाल कधी लागणार? आशिष शेलारांनी दिली माहिती</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
+          <t>https://marathi.ndtv.com/maharashtra/clerk-typist-post-exam-result-declared-after-high-court-decision-ashish-shelar-information-8863601</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>NDTV Emerging Business Conclave : "उद्धवजींची अवस्था पाहता महायुतीचा विजय पक्का"; आशिष शेलारांचा निशाणा</t>
+          <t>भजनी मंडळांना २५ हजारांचे अनुदान; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/ndtv-emerging-business-conclave-ashish-shelar-bmc-election-uddhav-thackeray-9154153</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-bhajani-mandals-grant-25000-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Marathi Language Controversy : भाषा वादावर आशिष शेलारांचं मोठं विधान; मनसैनिकांची थेट पहलगाममधील दहशतवाद्यांशी तुलना</t>
+          <t>शिवसेना UBT की हालत मुंबई की 'खतरनाक' और 'जर्जर' इमारतों जैसी, महाराष्ट्र के मंत्री आशीष शेलार ने कसा तंज</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
+          <t>https://www.indiatv.in/maharashtra/shiv-sena-ubt-s-condition-is-like-dangerous-and-dilapidated-buildings-of-mumbai-bjp-leader-ashish-shelar-taunts-2025-06-22-1144340</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Emerging Business Conclave : 'तुम्ही काय केलं, ठाकरे बंधूंना सवाल'; शेलारांनी 1995 पासून कामाचा पाढाच वाचला</t>
+          <t>'युनेस्को' यादीतील प्रत्येक किल्ल्यासाठी समिती; सांस्कृतिक कार्य मंत्री आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-thackeray-brothers-9154326</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/unesco-shivaji-forts-committee-announced-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>महराष्ट्र में राजकीय उत्सव के रूप में मनाया जाएगा गणेशोत्सव, संस्कृति मंत्री आशीष शेलार ने विधानमंडल में किया ऐलान</t>
+          <t>नागरिकांना डिजिटल सेवा देण्यासाठी शासन प्रयत्नशील – मंत्री ॲड.आशिष शेलार</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
+          <t>https://mahasamvad.in/159784/</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Kishori Pednekar : ठाकरेंना ‘लँड माफिया’ म्हणताच पेडणेकरांकडून ‘झोलर’ची आठवण,...</t>
+          <t>महाराष्ट्र में कुछ होने वाला है बड़ा? पहले CM फडणवीस से मिले राज ठाकरे, अब बेटे ने BJP नेता से की मुलाकात</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
+          <t>https://zeenews.india.com/hindi/india/maharashtra-politics-amit-thackeray-met-minister-ashish-shelar-after-raj-thackeray-meeting-with-cm-fadnavis/2893316</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Ganeshotsav 2025: गणेशोत्सव महाराष्ट्र राज्याचा महोत्सव म्हणून घोषित; आशिष शेलार यांची विधानसभेत माहिती</t>
+          <t>Hindi Controversy: 'मराठी'वरुन दहशतवाद्यांशी तुलना, आशिष शेलारांच्या वक्तव्याचा मनसेकडून समाचार</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
+          <t>https://marathi.ndtv.com/maharashtra/mns-leaders-reply-ashish-shelar-on-marathi-hindi-language-row-compare-pahalgam-terrorist-8832571</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Ashish Shelar : गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा; आशिष शेलार यांचे अधिकाऱ्यांना निर्देश</t>
+          <t>आपले सरकार सेवा केंद्रांच्या संख्येत वाढ – माहिती तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
+          <t>https://mahasamvad.in/160573/</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>शिवसेना UBT के दो पूर्व पार्षद BJP में शामिल, मुंबई में उद्धव ठाकरे को फिर बड़ा झटका, शेलार ने छोड़े तीर</t>
+          <t>Mumbai BJP chief News: मुंबई BJP को मिल गया नया चीफ, जानें कौन हैं अमीत साटम?</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-ameet-satam-anheri-mla-is-mumbai-bjp-chief-took-place-of-ashish-shelar-know-detail-story-9547057.html</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Pen News : रायगडमध्ये पालकमंत्रिपद वादात, भाजपचे संपर्कमंत्री वेगात, मूर्तिकारांच्या प्रश्नाच्या निमित्ताने आशिष शेलार सक्रिय</t>
+          <t>महाराष्ट्र में हिंदी को लेकर सियासी बवाल, उद्धव ठाकरे से जुड़े सवाल पर आशा भोसले</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
+          <t>https://www.abplive.com/states/maharashtra/hindi-controvery-in-maharashtra-asha-bhosle-on-uddhav-thackeray-shiv-sena-ubt-devendra-fadnavis-2969826</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Ganeshotsav: गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रस्ताव सादर करणार; आशिष शेलार यांची माहिती</t>
+          <t>मुंबईत उभारणार सांस्कृतिक केंद्र आणि वस्तुसंग्रहालय: आशिष शेलारांची घोषणा</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/unesco-cultural-status-proposal-for-ganeshotsav-ashish-shelar-sb97</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-cultural-center-and-museum-to-be-set-up-in-bkc-mumbai-said-minister-ashish-shelar-in-assembly-budget-session-2025-maharashtra-news-mhs25031900644</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>गणेशोत्सव को 'राज्य उत्सव' के रूप में मनाने की तैयारी - मंत्री एडवोकेट आशीष शेलार की घोषणा</t>
+          <t>Marathi Language Controversy : भाषा वादावर आशिष शेलारांचं मोठं विधान; मनसैनिकांची थेट पहलगाममधील दहशतवाद्यांशी तुलना</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/festivals/preparations-to-celebrate-ganeshotsav-as-state-festival-announcement-by-minister-advocate-ashish-shelar-89618</t>
+          <t>https://marathi.ndtv.com/maharashtra/marathi-language-controversy-ashish-shelar-compares-mns-to-pahalgam-terrorists-8831964</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे हे मुंबईतील लँड स्कॅमचे बादशहा: त्यांच्या डोक्यात सतत स्कॅमचेच विचार येतात, भाजप नेते आशिष शेला...</t>
+          <t>Kishori Pednekar : ठाकरेंना ‘लँड माफिया’ म्हणताच पेडणेकरांकडून ‘झोलर’ची आठवण,...</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/ashish-shelar-says-uddhav-thackeray-land-scam-king-in-mumbai-politics-134886158.html</t>
+          <t>https://www.tv9marathi.com/videos/kishori-pednekar-reply-to-bjp-ashish-shelar-his-criticism-on-thackeray-is-the-king-of-all-land-scam-in-mumbai-1390050.html</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>मंत्री शेलार कल आयेंगे</t>
+          <t>Ganeshotsav 2025: गणेशोत्सव महाराष्ट्र राज्याचा महोत्सव म्हणून घोषित; आशिष शेलार यांची विधानसभेत माहिती</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ashish-shelar-announces-sarvajanik-ganeshotsav-will-henceforth-be-celebrated-as-state-festival/articleshow/122376656.cms</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>ठाकरेंना ज्यांनी धूळ चारली त्या जोडीला भाजपकडून मोठी जबाबदारी, आशिष शेलार यांची सर्वात मोठी घोषणा</t>
+          <t>Ashish Shelar : गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा; आशिष शेलार यांचे अधिकाऱ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/ashish-shelar-instructs-officials-to-completely-fill-all-potholes-on-mumbai-roads-before-ganesh-chaturthi/914692/</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>निवडणुका आणि सत्तेसाठी पक्ष फोडता, भ्रष्टाचाऱ्यांना शुद्ध करून पक्षात घेता,</t>
+          <t>Pen News : रायगडमध्ये पालकमंत्रिपद वादात, भाजपचे संपर्कमंत्री वेगात, मूर्तिकारांच्या प्रश्नाच्या निमित्ताने आशिष शेलार सक्रिय</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/mns-leader-gajanan-kale-response-to-ashish-shelar-after-criticizing-raj-thackeray-uddhav-thackeray-victory-rally-maharashtra-politics-marathi-news-1368104</t>
+          <t>https://www.mymahanagar.com/mahamumbai/raigarh/pen-news-ashish-shelar-active-in-raigad-on-the-issue-of-sculptors-dispute-over-guardian-minister-post-in-raigad-in-shiv-sena-and-ncp-raigad-politics/860489/</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Mumbai Politics: आशिष शेलारांच्या वक्तव्यावर बाळा नांदगावकरांचे प्रत्युत्तर, म्हणाले...</t>
+          <t>गणेशोत्सव को 'राज्य उत्सव' के रूप में मनाने की तैयारी - मंत्री एडवोकेट आशीष शेलार की घोषणा</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/bala-nandgaonkar-hits-back-at-ashish-shelar-statement-mk94</t>
+          <t>https://www.mumbailive.com/hi/festivals/preparations-to-celebrate-ganeshotsav-as-state-festival-announcement-by-minister-advocate-ashish-shelar-89618</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
+          <t>Ganeshotsav: गणेशोत्सवाला युनेस्कोचा सांस्कृतिक दर्जा मिळविण्यासाठी प्रस्ताव सादर करणार; आशिष शेलार यांची माहिती</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
+          <t>https://pudhari.news/maharashtra/pune/unesco-cultural-status-proposal-for-ganeshotsav-ashish-shelar-sb97</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Asha Bhosle : ठाकरे बंधू एकत्र येणार? सवाल करताच आशा भोसले थेट म्हणाल्या, मला फक्त आशिष शेलार…</t>
+          <t>मंत्री शेलार कल आयेंगे</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
+          <t>https://mandalnews.com/amravati/minister-shelar-will-come-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>अमेरिकेतील ५० हून अधिक मराठी शाळांना महाराष्ट्र सरकारचा आधार; अभ्यासक्रम व परीक्षेत एकसंधतेचा मार्ग मोकळा</t>
+          <t>उद्धव ठाकरे हे मुंबईतील लँड स्कॅमचे बादशहा: त्यांच्या डोक्यात सतत स्कॅमचेच विचार येतात, भाजप नेते आशिष शेला...</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/ashish-shelar-says-uddhav-thackeray-land-scam-king-in-mumbai-politics-134886158.html</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>गणेशोत्सवापूर्वी मुंबईतील सर्व खड्डे भरा: पालकमंत्री आशिष शेलार यांचे आदेश, मुंबई महापालिकेकडे आतापर्यंत 8 ...</t>
+          <t>Maharashtra Cultural Minister Ashish Shelar inaugurates Kala Ghoda Arts Festival 2025</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-potholes-ashish-shelar-ganesh-festival-deadline-135736371.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-cultural-minister-ashish-shelar-inaugurates-kala-ghoda-arts-festival-2025-23472002</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>ठाकरे बंधुमुळे भाजप अलर्ट मोडवर मुंबईच्या प्रत्येक वॉर्डमधील आढावा घेतला जाणार,</t>
+          <t>ठाकरेंना ज्यांनी धूळ चारली त्या जोडीला भाजपकडून मोठी जबाबदारी, आशिष शेलार यांची सर्वात मोठी घोषणा</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-leader-ashish-shelar-big-announcement-after-best-patpedhi-election/articleshow/123407991.cms</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>पर्यावरण संवर्धनासाठी कमी कार्बन उत्सर्जनावर भर द्यावा - माहिती व तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
+          <t>Ashish Shelar: मुंबईत जोरदार पाऊस! पावसाचा आढावा घेतल्यानंतर मंत्री शेलार म्हणाले, 'अत्यंत गरज असल्यास...'</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/157961/</t>
+          <t>https://www.jaimaharashtranews.com/maharashtra-marathi-news/mumbai-rain-updates-ashish-shelar-reviewed-the-rainfall-and-said-stay-safe-at-home/40069</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>राजीव शुक्ला को BCCI ने दी बड़ी जिम्मेदारी, अब इस नए रोल में आएंगे नजर</t>
+          <t>Asha Bhosle : ठाकरे बंधू एकत्र येणार? सवाल करताच आशा भोसले थेट म्हणाल्या, मला फक्त आशिष शेलार…</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/sports-news/rajeev-shukla-ashish-shellar-appointed-to-acc-board/1097176/</t>
+          <t>https://www.tv9marathi.com/videos/asha-bhosle-reaction-on-question-of-uddhav-and-raj-thackeray-coming-together-i-know-only-ashish-shelar-in-politics-1432773.html</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Aditya Thackeray On Ashish Shelar And Nishikant Dubey: ठाकरे बंधूंवर भाजपकडून हल्लाबोल आदित्य ठाकरेंनी आशिष</t>
+          <t>Mumbai Politics: आशिष शेलारांच्या वक्तव्यावर बाळा नांदगावकरांचे प्रत्युत्तर, म्हणाले...</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
+          <t>https://pudhari.news/maharashtra/mumbai/bala-nandgaonkar-hits-back-at-ashish-shelar-statement-mk94</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Shaktipeeth News: 'शक्तिपीठ महामार्गाबाबतचा अंतिम निर्णय...'; भाजपच्या बड्या नेत्याचं कोल्हापुरात मोठं विधान</t>
+          <t>महाराष्ट्र के स्कूलों में हिंदी जरूरी? विवाद पर देवेंद्र फडणवीस का बड़ा फैसला, जानें क्या बोले आशीष शेलार</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-statement-on-shaktipith-highway-final-decision-kolhapur-dk88-rg93</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/hindi-mandatory-in-maharashtra-or-not-what-devendra-fadnavis-and-ashish-shelar-said/articleshow/122037862.cms</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>‘एमपीएससी’द्वारे विविध विभागातील रिक्त पदभरतीस गती देणार - माहिती व तंत्रज्ञान मंत्री ॲड.आशिष शेलार</t>
+          <t>Ashish Shelar: "विभाग प्रमुखांनी 100 टक्के निधी..."; मंत्री आशीष शेलारांचे अधिकाऱ्यांना निर्देश</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/158808/</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/minister-ashish-shelar-said-all-department-head-use-100-percent-fund-for-peoples-886116.html</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते गायिका माणिक वर्मा यांच्या चरित्र ग्रंथाचे प्रकाशन</t>
+          <t>गणेशोत्सवापूर्वी मुंबईतील सर्व खड्डे भरा: पालकमंत्री आशिष शेलार यांचे आदेश, मुंबई महापालिकेकडे आतापर्यंत 8 ...</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai/veteran-singer-manik-verma-lived-a-full-philosophical-life-adv-ashish-shelar-publication-of-the-book-manik-moti-written-by-shobha-bondre-mumbai-news-871060.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-potholes-ashish-shelar-ganesh-festival-deadline-135736371.html</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Ashish Shelar on Aaditya Thackeray | आदित्य ठाकरेंच्या होमपीचवर; आशिष शेलारांची तुफान बॅटिंग</t>
+          <t>अमेरिकेतील ५० हून अधिक मराठी शाळांना महाराष्ट्र सरकारचा आधार; अभ्यासक्रम व परीक्षेत एकसंधतेचा मार्ग मोकळा</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-at-aaditya-thackeray-constituency-in-worli-maharashtra-politics-abp-majha-1361553</t>
+          <t>https://marathi.indiatimes.com/career/career-news/maharashtra-supports-50-plus-marathi-schools-in-us-curriculum-standardisation-ministry-of-cultural-affairs-ashish-shelar/articleshow/122952405.cms</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>गणेशोत्सव होगा महाराष्ट्र का महोत्सव</t>
+          <t>ठाकरे बंधुमुळे भाजप अलर्ट मोडवर मुंबईच्या प्रत्येक वॉर्डमधील आढावा घेतला जाणार,</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
+          <t>https://marathi.abplive.com/news/mumbai/bjp-on-alert-mode-due-to-thackeray-brothers-coming-together-a-review-will-be-conducted-in-every-ward-of-mumbai-ashish-shelar-calls-a-meeting-1374681</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>'राज ठाकरे यांचा चित्रपटही लोकांनी स्वीकारला नाही...' मनसे अध्यक्षांबद्दल हे काय बोलून गेले आशिष शेलार?</t>
+          <t>राजीव शुक्ला को BCCI ने दी बड़ी जिम्मेदारी, अब इस नए रोल में आएंगे नजर</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
+          <t>https://hindi.news24online.com/sports-news/rajeev-shukla-ashish-shellar-appointed-to-acc-board/1097176/</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>मुंबईत भाजप पदाधिकारी एकमेकांना भिडले: मंत्री आशिष शेलारांच्या गाडीसमोरच झाला राडा, पक्षातील अंतर्गत वाद चव...</t>
+          <t>Aditya Thackeray On Ashish Shelar And Nishikant Dubey: ठाकरे बंधूंवर भाजपकडून हल्लाबोल आदित्य ठाकरेंनी आशिष</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-infighting-ashish-shelar-kandivali-janupada-135227690.html</t>
+          <t>https://marathi.abplive.com/news/politics/aditya-thackeray-on-ashish-shelar-and-nishikant-dubey-aditya-thackeray-has-criticized-ashish-shelar-and-nishikant-dubey-raj-thackeray-uddhav-thackeray-1368599</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>राज-उद्धव एकत्र येणार? आशा भोसलेंच्या उत्तरानं उंचावल्या सगळ्यांच्या भुवया, म्हणाल्या मी फक्त आशिष शेलार यांनाच...</t>
+          <t>Shaktipeeth News: 'शक्तिपीठ महामार्गाबाबतचा अंतिम निर्णय...'; भाजपच्या बड्या नेत्याचं कोल्हापुरात मोठं विधान</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/ashish-shelar-statement-on-shaktipith-highway-final-decision-kolhapur-dk88-rg93</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>सांस्कृतिक विभागाकडून मार्चपर्यंत राज्यात १२०० कार्यक्रम होणार; मंत्री आशिष शेलार यांची घोषणा</t>
+          <t>‘एमपीएससी’द्वारे विविध विभागातील रिक्त पदभरतीस गती देणार - माहिती व तंत्रज्ञान मंत्री ॲड.आशिष शेलार</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/satara/cultural-department-to-hold-1200-programs-in-the-state-by-march-minister-ashish-shelar-announces-a-a829-c607/</t>
+          <t>https://mahasamvad.in/158808/</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Ashish Shelar On Raj Uddhav Thackeray: उद्धव ठाकरेंची टीका आशिष शेलारांच्या जिव्हारी विजयी मेळाव्यावरुन</t>
+          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते गायिका माणिक वर्मा यांच्या चरित्र ग्रंथाचे प्रकाशन</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/veteran-singer-manik-verma-lived-a-full-philosophical-life-adv-ashish-shelar-publication-of-the-book-manik-moti-written-by-shobha-bondre-mumbai-news-871060.html</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Amit Thackeray-Ashish Shelar :अमित ठाकरे-आशिष शेलार भेट, राजकीय वर्तुळात चर्चांना उधाण</t>
+          <t>पर्यावरण संवर्धनासाठी कमी कार्बन उत्सर्जनावर भर द्यावा - माहिती व तंत्रज्ञान मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
+          <t>https://mahasamvad.in/157961/</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Emerging Business Conclave : AI मुळे रोजगार कमी होतोय? आशिष शेलारांनी लोकांचा संभ्रम केला दूर</t>
+          <t>छत्रपती शिवाजी महाराजांचे 12 किल्ले युनेस्कोच्या जागतिक वारसा यादीत; विधानपरिषदेत अभिनंदनाचा ठराव</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/emerging-business-conclave-mumbai-chapter-minister-ashish-shelar-on-ai-university-and-employment-shortage-9153869</t>
+          <t>https://www.etvbharat.com/mr/!state/12-forts-of-chhatrapati-shivaji-maharaj-included-in-unesco-world-heritage-list-congratulatory-resolution-passed-in-maharashtra-legislative-council-maharashtra-news-mhs25071404363</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>15 ऑगस्टच्या आधी सरदार रघुजी राजे भोसलेंची तलवार महाराष्ट्रात येणार, मंत्री शेलार</t>
+          <t>गणेशोत्सव होगा महाराष्ट्र का महोत्सव</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
+          <t>https://mandalnews.com/other-cities/ganeshotsav-will-be-a-festival-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>गणेशोत्सवाआधी मुंबईतील खड्ड्यांचं विघ्न दूर करा; पालकमंत्री आशिष शेलार यांचे निर्देश</t>
+          <t>'राज ठाकरे यांचा चित्रपटही लोकांनी स्वीकारला नाही...' मनसे अध्यक्षांबद्दल हे काय बोलून गेले आशिष शेलार?</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/ashish-shelar-talk-about-raj-thackeray-yek-number-movie-at-assembly-monsoon-session/articleshow/122353795.cms</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Ashish Shelar : आता कसा झेंडा घेऊ हाती? शेलारांनी ठाकरे बंधूंना डिवचलं अन्…</t>
+          <t>राज-उद्धव एकत्र येणार? आशा भोसलेंच्या उत्तरानं उंचावल्या सगळ्यांच्या भुवया, म्हणाल्या मी फक्त आशिष शेलार यांनाच...</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
+          <t>https://marathi.indiatimes.com/entertainment/entertainment-news/bollywood-news/asha-bhosle-reaction-on-uddhav-and-raj-thackeray-alliance-says-that-i-only-know-ashish-shelar/articleshow/122109382.cms</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Ashish Shelar : बॉम्बे स्कॉटिशमध्ये शिकताना बॉम्बे नको मुंबई हे तुम्ही बोललात का? आशिष</t>
+          <t>मुंबईत भाजप पदाधिकारी एकमेकांना भिडले: मंत्री आशिष शेलारांच्या गाडीसमोरच झाला राडा, पक्षातील अंतर्गत वाद चव...</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-infighting-ashish-shelar-kandivali-janupada-135227690.html</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते 'लाडकी बहीण'चा मुहूर्त संपन्न!</t>
+          <t>Ashish Shelar On Raj Uddhav Thackeray: उद्धव ठाकरेंची टीका आशिष शेलारांच्या जिव्हारी विजयी मेळाव्यावरुन</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
+          <t>https://marathi.abplive.com/news/politics/ashish-shelar-on-raj-uddhav-thackeray-ashish-shelar-has-criticized-uddhav-thackeray-and-raj-thackeray-shivsena-mns-yuti-devendra-fadnavis-1368268</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>उबाठा सेना, राऊतांना तुकडे गँगची चिंता: भाजपच्या आशिष शेलार यांचा आरोप; महाराष्ट्र जनसुरक्षा विधेयकावरून सा...</t>
+          <t>सांस्कृतिक विभागाकडून मार्चपर्यंत राज्यात १२०० कार्यक्रम होणार; मंत्री आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-public-security-bill-opposition-shiv-sena-uddhav-sanjay-raut-ashish-shelar-attack-135430375.html</t>
+          <t>https://www.lokmat.com/satara/cultural-department-to-hold-1200-programs-in-the-state-by-march-minister-ashish-shelar-announces-a-a829-c607/</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Ashish Shelar: "विभाग प्रमुखांनी 100 टक्के निधी..."; मंत्री आशीष शेलारांचे अधिकाऱ्यांना निर्देश</t>
+          <t>Ashish Shelar: गणेशोत्सव बंद होऊ देणार नाही, आशिष शेलार यांची ग्वाही; कोर्टात ३० जूनपर्यंत बाजू मांडणार!</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai/minister-ashish-shelar-said-all-department-head-use-100-percent-fund-for-peoples-886116.html</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-leader-ashish-shelar-on-ganesh-chaturthi-2025-a-a1012/</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Ashish Shelar: आशिष शेलारांनी ठाकरे बंधूंच्या जखमेवर मीठ चोळलं, म्हणाले, बेस्ट पतपेढीच्या</t>
+          <t>Amit Thackeray-Ashish Shelar :अमित ठाकरे-आशिष शेलार भेट, राजकीय वर्तुळात चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-maharashtra-political-developments-amit-thackeray-meets-ashish-shelar-amid-buzz-after-raj-thackeray-s-cm-fadnavis-meeting-past-friendship-rift-resurfaces-1379185</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>PoP Ganesh Idols | Ashish Shelar यांचा विरोधकांवर हल्लाबोल, मूर्तिकारांच्या पाठीशी BJP</t>
+          <t>15 ऑगस्टच्या आधी सरदार रघुजी राजे भोसलेंची तलवार महाराष्ट्रात येणार, मंत्री शेलार</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
+          <t>https://marathi.abplive.com/news/maharashtra/sardar-raghuji-raje-bhosale-sword-will-arrive-in-maharashtra-before-august-15-says-minister-ashish-shelar-1368556</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>भारतीय पुरातत्व विभागातील किल्ले देखभालीसाठी राज्याकडे द्या, मंत्री आशिष शेलार यांची केंद्राला विनंती</t>
+          <t>गणेशोत्सवाआधी मुंबईतील खड्ड्यांचं विघ्न दूर करा; पालकमंत्री आशिष शेलार यांचे निर्देश</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/minister-ashish-shelar-requests-center-government-to-hand-over-forts-of-asi-to-state-for-maintenance-8006527</t>
+          <t>https://www.etvbharat.com/mr/!state/mumbai-road-potholes-ashish-shelar-conduct-meeting-urges-all-departments-to-amplify-ganeshotsav-celebrations-in-maharashtra-maharashtra-news-mhs25082205231</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>गणेशोत्सव झाला महाराष्ट्र राज्य महोत्सव; सांस्कृतिक कार्यमंत्री आशिष शेलार यांची विधानसभेत घोषणा</t>
+          <t>Ashish Shelar : बॉम्बे स्कॉटिशमध्ये शिकताना बॉम्बे नको मुंबई हे तुम्ही बोललात का? आशिष</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ganeshotsav-has-become-maharashtra-state-festival-cultural-affairs-minister-ashish-shelar-announced-in-the-legislative-assembly-a-a629/</t>
+          <t>https://marathi.abplive.com/news/politics/did-you-say-bombay-not-mumbai-while-studying-at-bombay-scottish-ashish-shelar-criticised-raj-and-uddhav-thackeray-brothers-1368259</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>“गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा”; आशिष शेलारांचे स्पष्ट निर्देश</t>
+          <t>सांस्कृतिक कार्यमंत्री आशिष शेलार यांच्या हस्ते 'लाडकी बहीण'चा मुहूर्त संपन्न!</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-minister-ashish-shelar-instruction-that-fill-all-the-potholes-on-mumbai-roads-completely-before-ganesh-chaturthi-2025-a-a719/</t>
+          <t>https://www.etvbharat.com/mr/!entertainment/cultural-minister-ashish-shelar-gives-muhurat-clap-for-a-ladki-bahin-marathi-film-maharashtra-news-mhs25061500861</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meets Ashish Shelar: आशिष शेलारांची भेट घेत अमित ठाकरेंच्या विविध मागण्या मुंबईत आज</t>
+          <t>उबाठा सेना, राऊतांना तुकडे गँगची चिंता: भाजपच्या आशिष शेलार यांचा आरोप; महाराष्ट्र जनसुरक्षा विधेयकावरून सा...</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-public-security-bill-opposition-shiv-sena-uddhav-sanjay-raut-ashish-shelar-attack-135430375.html</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>‘बीडीडी चाळीतील रहिवाशांना येत्या श्रावण महिन्याच्या आत मिळणार चाव्या’, आशिष शेलार यांचं आश्वासन</t>
+          <t>शिवसेना UBT के दो पूर्व पार्षद BJP में शामिल, मुंबई में उद्धव ठाकरे को फिर बड़ा झटका, शेलार ने छोड़े तीर</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/residents-of-bdd-chawl-will-get-keys-within-the-coming-month-of-shravan-assures-ashish-shelar-a-a301/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-politics-two-former-shiv-sena-ubt-corporators-join-bjp-ahead-of-bmc-polls-big-blow-to-uddhav-thackeray-know-all/articleshow/122004549.cms</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>पनवेल महानगरपालिकेच्या क्रिकेट प्रशिक्षण केंद्रातून गुणवत्ताधारक खेळाडू घडतील - मंत्री ॲड. आशिष शेलार</t>
+          <t>Ashish Shelar: आशिष शेलारांनी ठाकरे बंधूंच्या जखमेवर मीठ चोळलं, म्हणाले, बेस्ट पतपेढीच्या</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/163660/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ashish-shelar-slams-raj-thackeray-and-uddhav-thackeray-mns-thackeray-camp-shivsena-best-election-result-1379745</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>अमित ठाकरेंची आशिष शेलारांसोबत बैठक; नेमकी काय चर्चा झाली? अमित ठाकरेंनी स्पष्टच सांगितलं</t>
+          <t>Ganeshutsav : गणेशोत्सवासंदर्भात सर्वात मोठी बातमी, राज्य सरकारची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/mns-chief-amit-thackeray-submits-memorandum-to-bjp-leader-ashish-shelar-political-news-bdk97</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/ganeshotsav-declared-maharashtra-official-festival-announces-ashish-shelar-mumbai-pune-latest-marathi-nck90</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>मनोज जरांगेंच्या टोकदार भाषेवर मंत्री शेलार कडाडले; म्हणाले, 'मुंबईला या, बाप्पांचं दर्शन घ्या, पण...'</t>
+          <t>PoP Ganesh Idols | Ashish Shelar यांचा विरोधकांवर हल्लाबोल, मूर्तिकारांच्या पाठीशी BJP</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-reacts-over-manoj-jarange-patil-warns-mahayuti-government-due-to-maratha-reservation-as11</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-assures-ganesh-idol-makers-of-bjp-support-slams-uddhav-thackeray-aaditya-thackeray-over-mumbai-bmc-pop-idol-ban-and-naxalite-conspiracy-1371405</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Ashish Shelar : दहावी, बारावीच्या निकालावर बैठक, संकेतस्थळ ‘क्रॅश’ होऊ नये : आशिष शेलार</t>
+          <t>Amit Thackeray Meets Ashish Shelar: आशिष शेलारांची भेट घेत अमित ठाकरेंच्या विविध मागण्या मुंबईत आज</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ashish-shelar-orders-increased-capacity-for-education-board-website-to-handle-exam-result-traffic-amp17</t>
+          <t>https://marathi.abplive.com/news/politics/amit-thackeray-meets-ashish-shelar-amit-thackeray-demanded-ashish-shelar-that-the-school-and-college-exam-schedule-be-temporarily-canceled-and-postponed-during-the-ganesh-utsav-period-1379214</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>ॲड.आशिष शेलार यांच्या हस्ते मुंबई उपनगर जिल्हाधिकारी कार्यालयात ध्वजारोहण</t>
+          <t>जास्त गर्दीच्या मेट्रो स्थानकांचा आपत्कालीन प्लॅन तयार करा; आशिष शेलारांचे MMRDAला निर्देश</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/175532/</t>
+          <t>https://www.lokmat.com/mumbai/prepare-an-emergency-plan-for-overcrowded-metro-stations-ashish-shelar-directs-mmrda-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>आशा भोसले, नात जनाई साई बाबांच्या दर्शनाला; मंत्री आशिष शेलार यांनीही घेतले शिर्डीतील समाधीचे दर्शन</t>
+          <t>Ashish Shelar : एकाचं भाषण अपूर्ण आणि दुसऱ्याचं अप्रासंगिक ! ठाकरे बंधूंच्या मेळाव्यावर आशिष शेलारांची टीका</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
+          <t>https://civicmirror.in/news/one-s-speech-is-incomplete-and-the-other-s-is-irrelevant-ashish-shelar-s-criticism-of-the-thackeray-brothers-rally/</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Amit Thackeray Meet Ashish Shelar : 'गणेशोत्सवातील शाळा-कॉलेजच्या परीक्षा पुढे ढकला'; अमित ठाकरेंची मागणी</t>
+          <t>गणेशोत्सव झाला महाराष्ट्र राज्य महोत्सव; सांस्कृतिक कार्यमंत्री आशिष शेलार यांची विधानसभेत घोषणा</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/mumbai/mumbai-amit-thackeray-meets-ashish-shelar-demands-ganesh-festival-exam-postponement/40235</t>
+          <t>https://www.lokmat.com/mumbai/ganeshotsav-has-become-maharashtra-state-festival-cultural-affairs-minister-ashish-shelar-announced-in-the-legislative-assembly-a-a629/</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>सार्वजनिक गणेशोत्सव मंडळांसाठी आनंदवार्ता! मोठ्या गणेश मूर्तींच्या समुद्रात विसर्जनाचा मार्ग मोकळा होणार; मंत्री आशिष शेलारांची माहिती</t>
+          <t>Ashish Shelar : आता कसा झेंडा घेऊ हाती? शेलारांनी ठाकरे बंधूंना डिवचलं अन्…</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
+          <t>https://www.tv9marathi.com/videos/bjp-minister-ashish-shelar-taunt-mns-raj-thackeray-and-uddhav-thackeray-from-alliance-maharashtra-politics-1442122.html</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार | Singer Manik Varma Autobiogrpahy Launched</t>
+          <t>मनोज जरांगेंच्या टोकदार भाषेवर मंत्री शेलार कडाडले; म्हणाले, 'मुंबईला या, बाप्पांचं दर्शन घ्या, पण...'</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/premier/advocate-ashish-shelar-praised-late-veteran-singer-manik-varma-on-book-launch-prorgram-of-her-autobiography-manik-moti-entertainment-news-kds07</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ashish-shelar-reacts-over-manoj-jarange-patil-warns-mahayuti-government-due-to-maratha-reservation-as11</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Ashish Shelar : मुंबईत मुसळधार.. परिस्थितीचा आढावा घेतल्यानंतर शेलारांकडून मुंबईकरांना एकच आवाहन; आज, उद्या...</t>
+          <t>अमित ठाकरेंची आशिष शेलारांसोबत बैठक; नेमकी काय चर्चा झाली? अमित ठाकरेंनी स्पष्टच सांगितलं</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-appeals-to-mumbaikars-after-review-of-rains-at-bmc-stay-at-house-during-mumbai-heavy-rains-1472440.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/mns-chief-amit-thackeray-submits-memorandum-to-bjp-leader-ashish-shelar-political-news-bdk97</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>महाराष्ट्रातील गणेशोत्सव राष्ट्रीय, आंतरराष्ट्रीय पातळीवर पोहचवणार, आशिष शेलार यांची घोषणा</t>
+          <t>Amit Thackeray Meet Ashish Shelar : 'गणेशोत्सवातील शाळा-कॉलेजच्या परीक्षा पुढे ढकला'; अमित ठाकरेंची मागणी</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/maharashtra-assembly-monsoon-session-2025-ashish-shelar-announces-that-maharashtras-ganeshotsav-will-be-taken-to-national-and-international-levels-a-a301/</t>
+          <t>https://www.jaimaharashtranews.com/mumbai/mumbai-amit-thackeray-meets-ashish-shelar-demands-ganesh-festival-exam-postponement/40235</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>गणेशोत्सव ‘राज्य महोत्सव’ म्हणून साजरा करणार शासनाची जोरदार तयारी ; मंत्री ॲड.आशिष शेलार यांची घोषणा</t>
+          <t>सार्वजनिक गणेशोत्सव मंडळांसाठी आनंदवार्ता! मोठ्या गणेश मूर्तींच्या समुद्रात विसर्जनाचा मार्ग मोकळा होणार; मंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/23/ganesh-idol-immersion-ashish-shelar-g.html</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Ashish Shelar: निवडणूक तोंडावर तरीही का बदलला मुंबई भाजप अध्यक्ष? आशिष शेलार यांनी सांगितली रणनीती</t>
+          <t>आशा भोसले, नात जनाई साई बाबांच्या दर्शनाला; मंत्री आशिष शेलार यांनीही घेतले शिर्डीतील समाधीचे दर्शन</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-changes-mumbai-president-ahead-of-elections-amit-satam-takes-charge-ashish-shelar-reveals-strategy-bbj88</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/asha-bhosle-zanai-bhosle-and-ashish-shelar-seeks-blessings-at-sai-baba-mandir-shirdi/videoshow/120732340.cms</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>मुंबईमधील चौकाला स्व. भापसे यांचे नाव दिल्याने झाला पाथर्डीचाही गौरव: मंत्री आशिष शेलार यांचे मत; माजी आ. स...</t>
+          <t>ॲड.आशिष शेलार यांच्या हस्ते मुंबई उपनगर जिल्हाधिकारी कार्यालयात ध्वजारोहण</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/pathardi-also-became-proud-by-naming-a-square-in-mumbai-after-the-late-baburao-bhapse-says-minister-ashish-shelar-former-mla-named-the-square-after-the-late-baburao-bhapse-135398508.html</t>
+          <t>https://mahasamvad.in/175532/</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान उपक्रम केंद्र सुरू करणार, आशिष शेलार यांची घोषणा</t>
+          <t>पनवेल महानगरपालिकेच्या क्रिकेट प्रशिक्षण केंद्रातून गुणवत्ताधारक खेळाडू घडतील - मंत्री ॲड. आशिष शेलार</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
+          <t>https://mahasamvad.in/163660/</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>राज ठाकरेंच्या मतचोरीच्या आरोपावर शेलारांचा हल्लाबोल: म्हणाले - अमितची मते सावंतांनी, देशपांडेंची मते आदित्...</t>
+          <t>गणेशोत्सव ‘राज्य महोत्सव’ म्हणून साजरा करणार शासनाची जोरदार तयारी ; मंत्री ॲड.आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/asish-shelar-criticizes-raj-uddhav-thackeray-best-election-135757049.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/governments-strong-preparations-to-celebrate-ganeshotsav-as-state-festival-minister-adv-ashish-shelars-announc.html</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>आपले सरकार सेवा केंद्रांची संख्या वाढविणे आणि सेवा दरवाढीबाबत माहिती तंत्रज्ञान मंत्री आशिष शेलार यांचे विधानसभेत निवेदन</t>
+          <t>ज्येष्ठ गायिका माणिक वर्मा परिपूर्ण तात्विक जीवन जगल्या: ॲड.आशिष शेलार | Singer Manik Varma Autobiogrpahy Launched</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/160568/</t>
+          <t>https://www.esakal.com/premier/advocate-ashish-shelar-praised-late-veteran-singer-manik-varma-on-book-launch-prorgram-of-her-autobiography-manik-moti-entertainment-news-kds07</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>ठाकरे बंधूंच्या प्रश्नावर आशा भोसलेंचं भुवया उंचावणारं विधान, मी कोणाला ओळखत नाही फक्त आशिष शेलारांना ओळखते</t>
+          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान उपक्रम केंद्र सुरू करणार, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/asha-bhosle-statement-on-thackeray-brothers-coming-together-i-only-know-ashish-shelar-in-politics/918599</t>
+          <t>https://www.etvbharat.com/mr/!state/maharashtra-govt-to-expand-science-innovation-centres-statewide-names-initiative-after-astrophysicist-dr-narlikar-maharashtra-news-mhs25071705646</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>सिनेमावर सेन्सॉर अथवा निर्बंध घालणार नाही: परिणय फुकेंच्या लक्षवेधी सूचनेवर सांस्कृतिक कार्य मंत्री आशिष शे...</t>
+          <t>मुंबईमधील चौकाला स्व. भापसे यांचे नाव दिल्याने झाला पाथर्डीचाही गौरव: मंत्री आशिष शेलार यांचे मत; माजी आ. स...</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/entertainment/marathi-cinema/news/maharashtra-film-policy-ashish-shelar-censorship-135409939.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/pathardi-also-became-proud-by-naming-a-square-in-mumbai-after-the-late-baburao-bhapse-says-minister-ashish-shelar-former-mla-named-the-square-after-the-late-baburao-bhapse-135398508.html</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>ज्ञानेश्वर महाराजांचा जन्म सप्तशताब्दी सुवर्ण महोत्सव राज्यभर साजरा करणार: मंत्री आशिष शेलार यांची घोषणा, न...</t>
+          <t>Ashish Shelar: निवडणूक तोंडावर तरीही का बदलला मुंबई भाजप अध्यक्ष? आशिष शेलार यांनी सांगितली रणनीती</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/the-golden-jubilee-of-the-birth-of-dnyaneshwar-maharaj-will-be-celebrated-across-the-state-minister-ashish-shelar-announced-mogra-phulla-program-will-be-held-during-narli-week-134770599.html</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-changes-mumbai-president-ahead-of-elections-amit-satam-takes-charge-ashish-shelar-reveals-strategy-bbj88</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>‘खालिद का शिवाजी’ कान्स चित्रपट महोत्सवाच्या यादीतून बाहेर? चित्रपटातील ‘आक्षेपार्ह’ मजकुरावरून आशिष शेलार यांचे संकेत</t>
+          <t>राज ठाकरेंच्या मतचोरीच्या आरोपावर शेलारांचा हल्लाबोल: म्हणाले - अमितची मते सावंतांनी, देशपांडेंची मते आदित्...</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/entertainment/khalid-ka-shivaji-excluded-from-cannes-film-festival-ashish-shelar-comments</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/asish-shelar-criticizes-raj-uddhav-thackeray-best-election-135757049.html</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Dahi Handi 2025: गोविंदांसाठी आनंदाची बातमी! यंदा दीड लाख गोविंदांना मिळणार विम्याचे कवच</t>
+          <t>महाराष्ट्रातील गणेशोत्सव राष्ट्रीय, आंतरराष्ट्रीय पातळीवर पोहचवणार, आशिष शेलार यांची घोषणा</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/dahi-handi-2025-150000-govindas-will-get-insurance-cover-in-dahi-handi-minister-ashish-shelar-announced-in-the-assembly-83788</t>
+          <t>https://www.lokmat.com/maharashtra/maharashtra-assembly-monsoon-session-2025-ashish-shelar-announces-that-maharashtras-ganeshotsav-will-be-taken-to-national-and-international-levels-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Tuljabhavani Temple : धार्मिक भावना आणि परंपरेचा आदर करूनच तुळजाभवानी मंदिराचा जीर्णोद्धार; आशिष शेलारांची माहिती</t>
+          <t>आपले सरकार सेवा केंद्रांची संख्या वाढविणे आणि सेवा दरवाढीबाबत माहिती तंत्रज्ञान मंत्री आशिष शेलार यांचे विधानसभेत निवेदन</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-informed-that-the-renovation-of-the-kulswamini-tuljabhawani-temple-will-be-done-by-respecting-religious-sentiments-and-traditions/913244/</t>
+          <t>https://mahasamvad.in/160568/</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Ashish Shelar: आनंदाची बातमी! चित्रीकरणासाठी नि:शुल्क परवानगी अन् चित्रपट निर्मिती स्थळांवर...; मंत्री आशिष शेलारांची मोठी घोषणा</t>
+          <t>ज्ञानेश्वर महाराजांचा जन्म सप्तशताब्दी सुवर्ण महोत्सव राज्यभर साजरा करणार: मंत्री आशिष शेलार यांची घोषणा, न...</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/minister-ashish-shelar-announces-free-permission-for-filming-anywhere-in-mumbai-vru98</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/ahmednagar/news/the-golden-jubilee-of-the-birth-of-dnyaneshwar-maharaj-will-be-celebrated-across-the-state-minister-ashish-shelar-announced-mogra-phulla-program-will-be-held-during-narli-week-134770599.html</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>रघुजी भोसले महाराजांची तलवार राज्य सरकारकडे; मंत्री शेलार यांनी लंडनच्या मध्यस्थाकडून घेतली ताब्यात</t>
+          <t>‘खालिद का शिवाजी’ कान्स चित्रपट महोत्सवाच्या यादीतून बाहेर? चित्रपटातील ‘आक्षेपार्ह’ मजकुरावरून आशिष शेलार यांचे संकेत</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/raghuji-bhosale-maharaj-sword-handover-to-maharashtra-government</t>
+          <t>https://marathi.freepressjournal.in/entertainment/khalid-ka-shivaji-excluded-from-cannes-film-festival-ashish-shelar-comments</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>एक पडदा सिनेमागृहाबाबत संयुक्त समिती करा – सांस्कृतिक कार्य मंत्री ॲड.आशिष शेलार यांचे निर्देश</t>
+          <t>सिनेमावर सेन्सॉर अथवा निर्बंध घालणार नाही: परिणय फुकेंच्या लक्षवेधी सूचनेवर सांस्कृतिक कार्य मंत्री आशिष शे...</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/174804/</t>
+          <t>https://divyamarathi.bhaskar.com/entertainment/marathi-cinema/news/maharashtra-film-policy-ashish-shelar-censorship-135409939.html</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>हिंदूना मारत आहेत म्हणत मुंबईकर आशिष शेलारांची मनसैनिकांची थेट पहलगाम दहशतवाद्यांशी</t>
+          <t>ठाकरे बंधूंच्या प्रश्नावर आशा भोसलेंचं भुवया उंचावणारं विधान, मी कोणाला ओळखत नाही फक्त आशिष शेलारांना ओळखते</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/asha-bhosle-statement-on-thackeray-brothers-coming-together-i-only-know-ashish-shelar-in-politics/918599</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>मंत्री आशिष शेलारांकडून नामदेव ढसाळ यांचा अवमान</t>
+          <t>Ashish Shelar: आनंदाची बातमी! चित्रीकरणासाठी नि:शुल्क परवानगी अन् चित्रपट निर्मिती स्थळांवर...; मंत्री आशिष शेलारांची मोठी घोषणा</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ashish-shelar-statement-on-namdev-dhasal</t>
+          <t>https://www.esakal.com/mumbai/minister-ashish-shelar-announces-free-permission-for-filming-anywhere-in-mumbai-vru98</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Maharashtra Heritage News | कातळशिल्पांच्या वय निश्चितीसाठी तज्ज्ञांची समिती</t>
+          <t>रघुजी भोसले महाराजांची तलवार राज्य सरकारकडे; मंत्री शेलार यांनी लंडनच्या मध्यस्थाकडून घेतली ताब्यात</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mumbai-rock-carvings-unesco-heritage-committee-ashish-shelar-maharashtra-archaeology-sp96</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/raghuji-bhosale-maharaj-sword-handover-to-maharashtra-government</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>BJP Politics: भाजपची तिरपी चाल...;आशिष शेलारांना हटवून अमित साटम यांच्याकडे मुंबई शहर अध्यक्षपदाची सुत्रे</t>
+          <t>हिंदूना मारत आहेत म्हणत मुंबईकर आशिष शेलारांची मनसैनिकांची थेट पहलगाम दहशतवाद्यांशी</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/mumbai/bjp-politics-amit-satam-appointed-as-mumbai-bjp-city-president-replacing-ashish-shelar-969778.html</t>
+          <t>https://marathi.abplive.com/news/minister-mumbaikar-ashish-shelar-directly-compares-mansainiks-to-pahalgam-terrorists-saying-they-are-killing-hindus-nishikant-dubey-target-uddhav-and-raj-thackeray-1368449</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Aaple Sarkar Seva Kendra: राज्यात 'आपले सरकार सेवा केंद्रां'ची संख्या वाढणार; आशिष शेलारांनी जाहीर केले 'हे' निकष</t>
+          <t>मंत्री आशिष शेलारांकडून नामदेव ढसाळ यांचा अवमान</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/aple-sarkar-seva-kendra-center-increased-in-state-said-minister-ashish-shelar-825241.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ashish-shelar-statement-on-namdev-dhasal</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>'मुंबईतल्या सर्व लँड स्कॅमचे बादशाह उद्धव ठाकरे';आशिष शेलारांचा घणाघात</t>
+          <t>Maharashtra Heritage News | कातळशिल्पांच्या वय निश्चितीसाठी तज्ज्ञांची समिती</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/latest-news/ashish-shelar-says-uddhav-thackeray-is-the-king-of-all-land-scams-in-mumbai-/35864</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-rock-carvings-unesco-heritage-committee-ashish-shelar-maharashtra-archaeology-sp96</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>गणेशोत्सव - महाराष्ट्र राज्याचा महोत्सव!: मंत्री आशिष शेलार यांची घोषणा; गणेशोत्सवाच्या प्रचारासाठी सरकार क...</t>
+          <t>Aaple Sarkar Seva Kendra: राज्यात 'आपले सरकार सेवा केंद्रां'ची संख्या वाढणार; आशिष शेलारांनी जाहीर केले 'हे' निकष</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-ganesh-festival-declared-maharashtra-state-festival-shelarnew-135414987.html</t>
+          <t>https://www.navarashtra.com/maharashtra/aple-sarkar-seva-kendra-center-increased-in-state-said-minister-ashish-shelar-825241.html</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>BJP on Raj Uddhav Alliance: ठाकरे बंधूंच्या एकत्र येण्याची पोस्ट अमित शाहांना टॅग केली, आशिष</t>
+          <t>BJP Politics: भाजपची तिरपी चाल...;आशिष शेलारांना हटवून अमित साटम यांच्याकडे मुंबई शहर अध्यक्षपदाची सुत्रे</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-leader-ashish-shelar-reaction-on-raj-thackeray-uddhav-thackeray-alliance-for-marathi-morcha-against-hindi-compulsion-in-schools-1366501</t>
+          <t>https://www.navarashtra.com/maharashtra/mumbai/bjp-politics-amit-satam-appointed-as-mumbai-bjp-city-president-replacing-ashish-shelar-969778.html</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>मुंबई उपनगर जिल्हाधिकारी कार्यालयात मंत्री ॲड.आशिष शेलार यांच्या हस्ते ध्वजारोहण; तिरंगा यात्रेचेही आयोजन</t>
+          <t>गणेशोत्सव - महाराष्ट्र राज्याचा महोत्सव!: मंत्री आशिष शेलार यांची घोषणा; गणेशोत्सवाच्या प्रचारासाठी सरकार क...</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-ganesh-festival-declared-maharashtra-state-festival-shelarnew-135414987.html</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>राज्य शासनातर्फे यंदा आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव, आशिष शेलार यांची घोषणा</t>
+          <t>Mumbai BJP President | मुंबई अध्यक्षपदासाठी भाजपमध्ये रस्सीखेच, आशिष शेलार यांचं नाव पुढे</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/filmy/marathi-cinema/marathi-film-festival-in-2025-ashish-shelar-announced-rajya-shasan-marathi-movie-nomination-a-a998/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-mumbai-bjp-president-race-ashish-shelar-emerges-as-frontrunner-for-bmc-elections-1367226</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Asha Bhosle News: आशा भोसले म्हणतात, “मला राजकारणातले फक्त आशिष शेलार माहिती आहेत”, ठाकरे बंधूंबाबतच्या प्रश्नावर दिलं उत्तर!</t>
+          <t>शास्त्रज्ञ जयंत नारळीकरांच्या नावे विज्ञान व नाविन्यता उपक्रम केंद्र सुरू करणार: आशिष शेलार</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/singer-asha-bhosle-reaction-on-raj-uddhav-thackeray-morcha-in-mumbai-pmw-88-5187805/</t>
+          <t>https://www.lokmat.com/mumbai/science-and-innovation-initiative-center-to-be-started-in-the-name-of-scientist-jayant-narlikar-said-ashish-shelar-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>दरवर्षी २१ एप्रिल दरम्यान रंगणार आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची घोषणा!</t>
+          <t>गणेशोत्सव राज्य महोत्सव म्हणून साजरा करणार: सात दिवस रात्री 12 वाजेपर्यंत ध्वनीक्षेपकाला परवानगी; मंत्री आश...</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/pune/news/ashish-shelar-ganesh-festival-state-festival-status-135719890.html</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>मध्यस्थ उभा केला न् लिलाव जिंकला; मराठा सरदार रघुजी भोसलेंची ऐतिहासिक तलवार सरकारच्या ताब्यात</t>
+          <t>“गणपतीपूर्वी मुंबईच्या रस्त्यावरील सर्व खड्डे पूर्णपणे भरा”; आशिष शेलारांचे स्पष्ट निर्देश</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
+          <t>https://www.lokmat.com/mumbai/bjp-minister-ashish-shelar-instruction-that-fill-all-the-potholes-on-mumbai-roads-completely-before-ganesh-chaturthi-2025-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Aasha Bhosle on Raj-Uddhav : राज-उद्धव युतीचा प्रश्न, आशाताई म्हणाल्या, मला फक्त आशिष शेलार माहिती</t>
+          <t>मुंबई उपनगर जिल्हाधिकारी कार्यालयात मंत्री ॲड.आशिष शेलार यांच्या हस्ते ध्वजारोहण; तिरंगा यात्रेचेही आयोजन</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/15/flag-hoisting-by-minister-adv-ashish-shelar-at-the-mumbai-suburban-district-collectorate.html</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Mumbai Monsoon Mess: MVA Blames MahaYuti Govt, BJP Points to 25 Yrs of BMC Misrule</t>
+          <t>Amit Thackeray : मनसे-भाजप जवळीक वाढतेय? सख्ख्या मित्रांमधला दुरावा मिटला, अमित ठाकरे शेलारांच्या भेटीला; म्हणाले, राज साहेबांनी...</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/amit-thackeray-meets-ashish-shelar-amid-mns-shiv-sena-ubt-alliance-talks-on-raj-thackeray-uddhav-thackeray/articleshow/123466514.cms</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Ganpati mandals get political colours ahead of civic polls</t>
+          <t>छत्रपती शिवाजी महाराज यांच्या १२ गडकिल्ल्यांना नामांकन, जागतिक वारसा यादीत मिळणार स्थान; मंत्री आशिष शेलारांची माहिती</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ganpati-mandals-and-the-politics-around-it-10211504/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/chhatrapati-shivaji-maharaj-fort-place-on-the-world-heritage-list-minister-ashish-shelar-said/articleshow/118510900.cms</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Maharashtra parties try to woo Ganpati devotees with free travel | Latest News India - Hindustan Times</t>
+          <t>Singer Asha Bhosle On Ashish Shelar: राज-उद्धव एकत्र येण्याबाबत प्रश्न, आशाताई म्हणाल्या, 'मला फक्त</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/maharashtra-parties-try-to-woo-ganpati-devotees-with-free-travel-101756094947074.html</t>
+          <t>https://marathi.abplive.com/entertainment/singer-asha-bhosle-on-raj-thackrey-uddhav-thackrey-togater-she-says-i-only-know-ashish-shelar-i-don-t-know-any-other-politician-1366511</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Shiv Sena UBT exodus continues, BJP gains two more corporators</t>
+          <t>Asha Bhosle News: आशा भोसले म्हणतात, “मला राजकारणातले फक्त आशिष शेलार माहिती आहेत”, ठाकरे बंधूंबाबतच्या प्रश्नावर दिलं उत्तर!</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
+          <t>https://www.loksatta.com/maharashtra/singer-asha-bhosle-reaction-on-raj-uddhav-thackeray-morcha-in-mumbai-pmw-88-5187805/</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>243 roads dug up in H West ward, many utilities damaged | Mumbai news</t>
+          <t>दरवर्षी २१ एप्रिल दरम्यान रंगणार आंतरराष्ट्रीय दर्जाचा मराठी चित्रपट महोत्सव; सांस्कृतिक कार्यमंत्री ॲड. आशिष शेलार यांची घोषणा!</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/243-roads-dug-up-in-h-west-ward-many-utilities-damaged-101738523195660.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/4/22/an-international-standard-marathi-film-festival-will-be-held-every-year-on-april-21st-cultural-affairs-minist.html</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>‘Insult to people’s mandate’: Devendra Fadnavis slams Rahul Gandhi’s voter fraud allegations as ‘baseless’</t>
+          <t>मध्यस्थ उभा केला न् लिलाव जिंकला; मराठा सरदार रघुजी भोसलेंची ऐतिहासिक तलवार सरकारच्या ताब्यात</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/devendra-fadnavis-slams-rahul-gandhi-voter-fraud-allegations-10177483/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/maratha-sardar-raghuji-bhosale-sword-seized-by-ashish-shelar-on-behalf-of-government-brought-to-mumbai-on-august-18/articleshow/123236999.cms</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Maharashtra govt to grant ₹25,000 each to 1,800 bhajani mandals for Ganesh festival</t>
+          <t>Aasha Bhosle on Raj-Uddhav : राज-उद्धव युतीचा प्रश्न, आशाताई म्हणाल्या, मला फक्त आशिष शेलार माहिती</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-grant-25000-each-to-1800-bhajani-mandals-for-ganesh-festival/articleshow/123453964.cms</t>
+          <t>https://marathi.abplive.com/short-videos/news/maharashtra-asha-bhosle-on-raj-uddhav-thackeray-unite-maharashtra-politics-1366541</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>BJP's Nishikant Dubey dares Uddhav, Raj Thackeray to visit north India, Tamil Nadu | Reactions so far</t>
+          <t>From 'jihadi gathering' to ‘no real brotherhood’: BJP on Uddhav-Raj Thackeray reunion</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/bjp-s-nishikant-dubey-dares-uddhav-raj-thackeray-to-visit-north-india-tamil-nadu-amid-marathi-hindi-row-shiv-sena-ubt-ashish-shelar-reactions-video-2025-07-08-997878</t>
+          <t>https://www.hindustantimes.com/india-news/from-jihadi-gathering-to-no-real-brotherhood-bjp-on-uddhav-raj-thackeray-reunion-nitesh-rane-ashish-shelar-speak-101751705821913.html</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Maharashtra BJP leader flays attack on Hindi-speaking people, cites Pahalgam parallel</t>
+          <t>Mumbai Monsoon Mess: MVA Blames MahaYuti Govt, BJP Points to 25 Yrs of BMC Misrule</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-bjp-leader-attack-on-hindi-speaking-people-pahalgam-parallel-195564</t>
+          <t>https://www.deccanherald.com/india/maharashtra/oppn-mva-slams-maharashtra-govt-over-mumbai-rain-chaos-bjp-blames-undivided-shiv-senas-25-year-reign-at-bmc-3558068</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Mumbai To Get Rid of Flood-Like Situations? New Plan Announced After 180 mm Rainfall Chaos</t>
+          <t>Fresh tussle between Shiv Sena and BJP over Marathi films</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>https://www.timesnownews.com/mumbai/mumbai-to-get-rid-of-flood-like-situations-new-plan-announced-after-180-mm-rainfall-chaos-article-152160573</t>
+          <t>https://indianexpress.com/article/cities/mumbai/fresh-tussle-between-shiv-sena-and-bjp-over-marathi-films-10155696/</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Pune Declares 10-Day Dry Spell</t>
+          <t>Live telecast of Ganeshotsav events: Minister | Mumbai News</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/en/state-news/pune-declares-10-day-dry-spell-19890138</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/live-telecast-of-ganeshotsav-events-minister/articleshow/122770675.cms</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>MNS Chief Raj Thackeray Questions Maharashtra Poll Results, Raises Doubts Over Ajit Pawars Sudden Rise In</t>
+          <t>Shiv Sena UBT exodus continues, BJP gains two more corporators</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mns-chief-raj-thackeray-questions-maharashtra-poll-results-raises-doubts-over-ajit-pawars-sudden-rise-in-assembly-elections</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shiv-sena-ubt-exodus-continues-bjp-gains-two-more-corporators-101750618792032.html</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Mumbai BJP Leadership Shake-Up: Pravin Darekar And Amit Satam In Contention For City President Post Ahead Of</t>
+          <t>Maharashtra govt to grant ₹25,000 each to 1,800 bhajani mandals for Ganesh festival</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-leadership-shake-up-pravin-darekar-and-amit-satam-in-contention-for-city-president-post-ahead-of-bmc-elections</t>
+          <t>https://m.economictimes.com/news/india/maharashtra-govt-to-grant-25000-each-to-1800-bhajani-mandals-for-ganesh-festival/articleshow/123453964.cms</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Mumbai: Sanjay Gandhi National Park To Introduce Leopard Safari For Visitors Soon, Says Ashish Shelar</t>
+          <t>Maharashtra BJP leader flays attack on Hindi-speaking people, cites Pahalgam parallel</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-sanjay-gandhi-national-park-to-introduce-leopard-safari-for-visitors-soon-says-ashish-shelar</t>
+          <t>https://thefederal.com/category/states/west/maharashtra/maharashtra-bjp-leader-attack-on-hindi-speaking-people-pahalgam-parallel-195564</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Dharavi Redevelopment Project: Not an Inch Of Land Given To Adani, Asserts Minister Ashish Shelar</t>
+          <t>BJP names three-term MLA Ameet Satam as Mumbai chief before BMC polls</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/dharavi-redevelopment-project-not-an-inch-of-land-given-to-adani-asserts-minister-ashish-shelar</t>
+          <t>https://tripuratimes.com/ttimes/bjp-names-three-term-mla-ameet-satam-as-mumbai-chief-before-bmc-polls-30851.html/</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP's Ashish Shelar Slams Raj, Uddhav's Joint Rally as Misleading</t>
+          <t>Maharashtra BJP Minister links Mira Road assault to Pahalgam attack</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-bjp-leader-links-mira-road-assault-to-pahalgam-attack-23583443</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Talk of Thackeray cousins reunion 'rattles' Eknath Shinde; BJP says 'wait and watch'</t>
+          <t>Mumbai News: BJP To Celebrate Maharashtra Day And Labour Day At 106 Locations Under Minister Ashish Shelars</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Apr/20/talk-of-thackeray-cousins-reunion-rattles-eknath-shinde-bjp-says-wait-and-watch</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bjp-to-celebrate-maharashtra-day-and-labour-day-at-106-locations-under-minister-ashish-shelars-leadership</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Ex-CJI Chandrachud’s call for inclusion spurs immediate government action</t>
+          <t>Maharashtra News: Shiv Sena (UBT) Chief Uddhav Thackeray Slams CM Devendra Fadnavis Over Rudali Remark,</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/ex-cji-chandrachuds-call-for-inclusion-spurs-immediate-government-action/article69972187.ece</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-shiv-sena-ubt-chief-uddhav-thackeray-slams-cm-devendra-fadnavis-over-rudali-remark-defends-marathi-identity-video</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Desperate bid to control BMC &amp; loot Mumbai: BJP</t>
+          <t>Maharashtra Minister Ashish Shelar Criticises Desilting Works In Mumbai, Demands Accountability From</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-criticises-desilting-works-in-mumbai-demands-accountability-from-contractors</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Thackeray Reunion Fallout: BJP Targets Uddhav, Spares Raj</t>
+          <t>Mumbai News: Minister Ashish Shelar Seeks Centre’s Help As Water Tanker Strike Looms Over CGWA License Row</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-seeks-centres-help-as-water-tanker-strike-looms-over-cgwa-license-row</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>'Washing powder' formula again? Uddhav Thackeray asks, 'did the Pahalgam terrorists join BJP?’ amid Hindi</t>
+          <t>MNS Chief Raj Thackeray Questions Maharashtra Poll Results, Raises Doubts Over Ajit Pawars Sudden Rise In</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/washing-powder-formula-again-uddhav-thackeray-asks-did-the-pahalgam-terrorists-join-bjp-amid-hindi-vs-marathi-row/articleshow/122297598.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mns-chief-raj-thackeray-questions-maharashtra-poll-results-raises-doubts-over-ajit-pawars-sudden-rise-in-assembly-elections</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>'India's Got Latent' row: Maharashtra government orders inquiry into Ranveer Allahbadia controversy | Latest News India - Hindustan Times</t>
+          <t>Mumbai BJP Leadership Shake-Up: Pravin Darekar And Amit Satam In Contention For City President Post Ahead Of</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-leadership-shake-up-pravin-darekar-and-amit-satam-in-contention-for-city-president-post-ahead-of-bmc-elections</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Video: PM pauses Delhi victory speech to check on unwell BJP worker in audience - India Today</t>
+          <t>Mumbai: Sanjay Gandhi National Park To Introduce Leopard Safari For Visitors Soon, Says Ashish Shelar</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/elections/assembly/video/video-pm-pauses-delhi-victory-speech-to-check-on-unwell-bjp-worker-in-audience-2676959-2025-02-08</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-sanjay-gandhi-national-park-to-introduce-leopard-safari-for-visitors-soon-says-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Final decision on three-language formula after talks with stakeholders: Maharashtra CM Fadnavis</t>
+          <t>Maharashtra Forms Task Force To Establish Indias First Artificial Intelligence University, Says IT Minister</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jun/24/final-decision-on-three-language-formula-after-talks-with-stakeholders-maharashtra-cm-fadnavis</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-forms-task-force-to-establish-indias-first-artificial-intelligence-university-says-it-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Ranveer Allahbadia Controversy News Highlights: Ranveer Allahbadia's Mumbai flat found locked; cops summon him again</t>
+          <t>Dharavi Redevelopment Project: Not an Inch Of Land Given To Adani, Asserts Minister Ashish Shelar</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/ranveer-allahbadia-controversy-live-updates-youtuber-samay-raina-indias-got-mumbai-police-ashish-chanchlani-apoorva-11739266598623.html</t>
+          <t>https://www.freepressjournal.in/mumbai/dharavi-redevelopment-project-not-an-inch-of-land-given-to-adani-asserts-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>PM Modi to speak in Lok Sabha tomorrow at 5 pm - India Today</t>
+          <t>Mumbai To House New Cultural Centre And Museum Celebrating Maharashtra’s Heritage, Says Minister Ashish</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/video/pm-modi-to-speak-in-lok-sabha-tomorrow-at-5-pm-2673866-2025-02-03</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-to-house-new-cultural-centre-and-museum-celebrating-maharashtras-heritage-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Kajol Gets Emotional While Receiving Late Raj Kapoor Life Gaurav Award: "Today I Feel..."</t>
+          <t>Mumbai News: PoP Ganesh Idol Makers Protest Bombay HC Ban; Minister Shelar Backs Artisans</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/latest-news/actress-kajol-received-maharashtra-state-film-award-which-was-held-in-mumbai-in-presence-of-cm-devedra-fadnavis</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-pop-ganesh-idol-makers-protest-bombay-hc-ban-minister-shelar-backs-artisans</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>India Highlights News Updates: Government appoints former cabinet secretary Rajiv Gauba as full-time memb...</t>
+          <t>Maharashtra Politics: BJP's Ashish Shelar Slams Raj, Uddhav's Joint Rally as Misleading</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/raj-uddhav-speeches-at-joint-rally-irrelevant-and-bereft-of-facts-bjp-leader-shelar-3617807</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Asaduddin Owaisi slams Pakistan's fakery with fake Chinese military drill photo - India Today</t>
+          <t>Talk of Thackeray cousins reunion 'rattles' Eknath Shinde; BJP says 'wait and watch'</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/video/asaduddin-owaisi-slams-pakistans-fakery-with-fake-chinese-military-drill-photo-2731277-2025-05-27</t>
+          <t>https://www.newindianexpress.com/nation/2025/Apr/20/talk-of-thackeray-cousins-reunion-rattles-eknath-shinde-bjp-says-wait-and-watch</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Maharashtra: NCP-SCP MLA Rohit Pawar hit back at BJP MP Nishikant Dubey for comparing opposition parties to terrorists</t>
+          <t>Ex-CJI Chandrachud’s call for inclusion spurs immediate government action</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>https://aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/ex-cji-chandrachuds-call-for-inclusion-spurs-immediate-government-action/article69972187.ece</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>England New Captain CONFIRMED? ECB Director Rob Key Gives BOLD Statement For The Captaincy Hunt</t>
+          <t>Desperate bid to control BMC &amp; loot Mumbai: BJP</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>https://news24online.com/sports/england-new-captain-confirmed-ecb-director-rob-key-gives-bold-statement-for-the-captaincy-hunt/496413/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/desperate-bid-to-control-bmc-loot-mumbai-bjp/articleshow/122271682.cms</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
+          <t>Thackeray Reunion Fallout: BJP Targets Uddhav, Spares Raj</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/thackeray-cousins-reunion-yeh-public-hai-sab-janti-hai-bjp-slams-uddhav-spares-raj-3617096</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Primary education should be in mother tongue, says RSS</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>https://www.thehindu.com/news/national/maharashtra/primary-education-should-be-in-mother-tongue-says-rss/article69785053.ece</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>'India's Got Latent' row: Maharashtra government orders inquiry into Ranveer Allahbadia controversy | Latest News India - Hindustan Times</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>https://www.hindustantimes.com/india-news/indias-got-latent-row-maharashtra-government-orders-inquiry-into-ranveer-allahbadia-controversy-101739583920981.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Khamenei says won't surrender, warns US of 'irreparable damage' if it intervenes - India Today</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/world/video/khamenei-says-wont-surrender-warns-us-of-irreparable-damage-if-it-intervenes-2742623-2025-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Why Maharashtra Govt wants film ‘Khalid Ka Shivaji’ put on hold</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/explained/explained-culture/khalid-ka-shivaji-row-marathi-film-bjp-10173522/</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Final decision on three-language formula after talks with stakeholders: Maharashtra CM Fadnavis</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>https://www.newindianexpress.com/nation/2025/Jun/24/final-decision-on-three-language-formula-after-talks-with-stakeholders-maharashtra-cm-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Ranveer Allahbadia Controversy News Highlights: Ranveer Allahbadia's Mumbai flat found locked; cops summon him again</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/ranveer-allahbadia-controversy-live-updates-youtuber-samay-raina-indias-got-mumbai-police-ashish-chanchlani-apoorva-11739266598623.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>PM Modi to speak in Lok Sabha tomorrow at 5 pm - India Today</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/pm-modi-to-speak-in-lok-sabha-tomorrow-at-5-pm-2673866-2025-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Kajol Gets Emotional While Receiving Late Raj Kapoor Life Gaurav Award: "Today I Feel..."</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>https://english.lokshahi.com/latest-news/actress-kajol-received-maharashtra-state-film-award-which-was-held-in-mumbai-in-presence-of-cm-devedra-fadnavis</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Operation Sindoor: PM Modi to address nation at 8 pm today - India Today</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/operation-sindoor-pm-modi-to-address-nation-at-8-pm-today-2723589-2025-05-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Asaduddin Owaisi slams Pakistan's fakery with fake Chinese military drill photo - India Today</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/asaduddin-owaisi-slams-pakistans-fakery-with-fake-chinese-military-drill-photo-2731277-2025-05-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>We are all proud: PM Modi hosts all-party Op Sindoor delegations at his house - India Today</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>https://www.indiatoday.in/india/video/pm-modi-hosts-all-party-operation-sindoor-delegations-at-his-house-2739017-2025-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>India Highlights News Updates: Government appoints former cabinet secretary Rajiv Gauba as full-time memb...</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>https://m.economictimes.com/news/newsblogs/one-nation-one-election-meeting-delhi-weather-india-news-pm-modi-parliament-finance-bill-donald-trump-elon-musk-pope-francis-gaza-israel-war-ukraine-russia-tariff-march-25/liveblog/119451337.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Maharashtra: NCP-SCP MLA Rohit Pawar hit back at BJP MP Nishikant Dubey for comparing opposition parties to terrorists</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>https://aninews.in/news/national/politics/maharashtra-ncp-scp-mla-rohit-pawar-hit-back-at-bjp-mp-nishikant-dubey-for-comparing-opposition-parties-to-terrorists20250707123452/</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>England New Captain CONFIRMED? ECB Director Rob Key Gives BOLD Statement For The Captaincy Hunt</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>https://news24online.com/sports/england-new-captain-confirmed-ecb-director-rob-key-gives-bold-statement-for-the-captaincy-hunt/496413/</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
           <t>Maharashtra CM Fadnavis Mocks Uddhav’s Rally Speech As Rudali, BJP Hits Out At Thackeray Cousins Over</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B629" t="inlineStr">
         <is>
           <t>https://www.freepressjournal.in/mumbai/maharashtra-cm-fadnavis-mocks-uddhavs-rally-speech-as-rudali-bjp-hits-out-at-thackeray-cousins-over-political-reunion</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>मुंबई बीजेपी को मिला नया अध्यक्ष, अमीत साटम के सामने बीएमसी है चुनौती</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>https://www.jansatta.com/national/mumbai-bjp-new-president-appointed-three-time-mla-ameet-satam-bmc-elections-big-challenge/4109409/</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Politics: 'राहुल गांधी के दिमाग की चिप चोरी और हार्ड डिस्क करप्ट हो गई', EC पर धांधली के आरोपों पर बोले फडणवीस</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>https://www.amarujala.com/india-news/rahul-gandhi-election-commission-allegations-devendra-fadnavis-ashish-shelar-response-2025-08-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>बीजेपी ने तैनात की नई 'मिसाइल': तीन बार MLA रहे अमित साटम को बनाया मुंबई भाजपा का अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/hi/!bharat/ahead-of-bmc-polls-mla-ameet-satam-named-new-mumbai-bjp-chief-hindi-news-hin25082501591</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र विधानसभा परिसर में भिड़े विधायक जितेंद्र आव्हाड और गोपीचंद पडलकर के समर्थक, गाड़ी टच होने पर हुआ था विवाद</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/a-scuffle-broke-out-between-bjp-mla-gopichand-padalkar-and-ncp-jitendra-awhad-ntc-rpti-2289942-2025-07-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>महराष्ट्र में राजकीय उत्सव के रूप में मनाया जाएगा गणेशोत्सव, संस्कृति मंत्री आशीष शेलार ने विधानमंडल में किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>https://www.ucnnews.live/politics/ganeshotsav-will-be-celebrated-as-a-state-festival-in-maharashtra-culture-minister-ashish-shelar-announced-in-the-legislative-assembly-1752144124498</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Ganeshotsav now Maharashtra State Festival: गणेशोत्सव बना महाराष्ट्र का राजकीय त्योहार, अब होगा राज्योत्सव</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>https://thecsrjournal.in/maharashtra-declares-ganeshotsav-as-state-festival-hindi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>फडणवीस सरकार का बड़ा फैसला, गणेशोत्सव को घोषित किया महाराष्ट्र का 'राज्य महोत्सव'</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>https://www.indiatv.in/maharashtra/devendra-fadnavis-govt-declare-ganesh-festival-as-maharashtra-state-festival-2025-07-10-1148320</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>मुंबई में विधायक अमीत साटम संभालेंगे बीजेपी की कमान, देवेंद्र फडणवीस ने नए अध्यक्ष के तौर पर नाम का किया ऐलान</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-andheri-west-mla-ameet-satam-appointed-mumbai-bjp-chief-ahead-of-bmc-polls-know-all/articleshow/123499476.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>सावरकर के गीत 'अनादि मैं, अनंत मैं' को प्रेरणा गीत का पुरस्कार, महाराष्ट्र सरकार का बड़ा ऐलान</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>https://www.aajtak.in/india/maharashtra/story/savarkar-song-anadi-me-anant-me-gets-inspirational-song-award-maharashtra-government-makes-a-big-announcement-ntc-dskc-2176549-2025-02-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Ganeshotsav 2025: गणेशोत्सव में भाग लेगी महाराष्ट्र सरकार, राज्य उत्सव मनाने के लिए किया गया ये ऐलान</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-devendra-fadnavis-govt-also-participates-in-ganeshotsav-2025-made-a-big-announcement/articleshow/122785708.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Maharashtra Guardian Ministers: महाराष्ट्र में जिले के प्रभारी मंत्रियों का ऐलान, पुणे-बीड के प्रभारी अजित दादा, पंकजा मुंडे की लगी लॉटरी, देखें पूरी लिस्ट</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/after-assembly-elections-theof-maharashtra-guardian-minister-posts-announced-see-full-list/articleshow/117358799.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>निकाय चुनाव से पहले आशीष शेलार की हुई छुट्टी, अमित साटम को मिली मुंबई बीजेपी की कमान</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-removed-post-before-civic-elections-amit-satam-given-command-mumbai-bjp-1329777.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Maharashtra News Live: एक क्लिक में पढ़ें 10 जुलाई की सभी बड़ी खबरें</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/latest-live-updates-maharashtra-politics-crime-nagpur-news-mumbai-pune-10-july-1279681.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>मनपा चुनाव से पहले बीजेपी का मास्टरस्ट्रोक, अमित साटम बने मुंबई अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bjp-masterstroke-before-municipal-elections-amit-satam-becomes-mumbai-president-1330683.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>गणेशोत्सव 'महाराष्ट्र का राजकीय उत्सव' घोषित, मंत्री आशीष शेलार ने जताई खुशी</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>https://www.khaskhabar.com/local/maharashtra/mumbai-news/news-ganeshotsav-declared-state-festival-of-maharashtra-minister-ashish-shelar-expressed-happiness-news-hindi-1-735521-KKN.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>मुंबई भाजपा अध्यक्ष की हुई नियुक्ति, भगवा दल ने इस चेहरे पर जताया भरोसा; कितनी बड़ी जिम्मेदारी</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>https://mpbreakingnews.in/national/mla-ameet-satnam-named-mumbai-bjp-chief-ahead-of-civic-body-polls-big-decesion-55-807941</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>फडणवीस सरकार का बड़ा फैसला, महाराष्ट्र में गणेशोत्सव को मिला राज्योत्सव का दर्जा</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>https://www.prabhasakshi.com/national/fadnavis-governments-big-decision-ganeshotsav-gets-state-festival-status-in-maharashtra</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>महाराष्ट्र सरकार ने गणेशोत्सव को राज्य उत्सव घोषित किया |</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>https://hindicurrentaffairs.adda247.com/maharashtra-government-declares-ganeshotsav-as-state-festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Mumbai: मुंबई भाजपा अध्यक्ष के तौर पर अमित साटम का चयन</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>https://jantaserishta.com/local/maharashtra/mumbai-amit-satam-selected-as-mumbai-bjp-president-mumbai--4230449</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Maharashtra में गणेशोत्सव को मिला ‘राज्य महोत्सव’ का दर्जा… फडणवीस सरकार का बड़ा फैसला</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>https://dainiksaveratimes.com/big-1/ganeshotsav-gets-status-state-festival-in-maharashtra-fadnavis-government/</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Ganeshotsav 2025: महाराष्ट्र का 'राज्य उत्सव' बना गणेशोत्सव, अब सरकार उठाएगी जश्न का पूरा खर्च</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>https://hindi.latestly.com/lifestyle/festivals-events/ganeshotsav-now-maharashtras-official-state-festival-govt-to-fund-celebrations-2689983.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>जय शाह की जगह देवजीत सैकिया बने BCCI सचिव, प्रभतेज सिंह भाटिया कोषाध्यक्ष नियुक्त</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>https://bharat24live.com/news/devajit-saikia-replaces-jay-shah-as-bcci-secretary</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>क्या अब गणपति बप्पा के विसर्जन का तरीका बदल जाएगा? पढ़ें महाराष्ट्र सरकार की नई पॉलिसी</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>https://www.outlookhindi.com/country/state/will-the-method-of-immersion-of-ganpati-bappa-change-now-read-the-new-policy-of-maharashtra-government-101125</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A181"/>
+  <dimension ref="A1:A151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,1260 +438,1050 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-suburban-guardian-minister-ashish-shelar-says-govt-will-frame-policy-to-grant-occupation-certificate-to-more-than-25000-buildings/articleshow/123833814.cms</t>
+          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pak-asia-cup-match-ashish-shelar/ar-AA1MzRl0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ashish-shelar-slams-shiv-sena-ubt-for-opposing-india-pakistan-asia-cup-match-23593693</t>
+          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar?amp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/more-than-25000-buildings-to-get-occupation-certificates-under-new-policy-ashish-shelar-10244083/</t>
+          <t>https://www.ptinews.com/editor-detail/People-understood-govt%E2%80%99s-stand-on-India-Pak-Asia-Cup-match-Ashish-Shelar/2916156</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625230-cricket-politics-and-controversies-maharashtra-minister-defends-india-pakistan-match?amp</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/world/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/ar-AA1MuAh8</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/25k-bldgs-to-benefit-from-new-policy-of-speedy-ocs-101757618615331.html</t>
+          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/maharashtras-policy-on-occupancy-certificate-to-benefit-25000-buildings-in-mumbai/article70041172.ece</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612?amp=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.telegraphindia.com/amp/india/maharashtra-opposition-slams-bjp-bcci-how-can-cricket-and-blood-flow-together/cid/2122820</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/survey-of-stepwells-historic-wells-to-be-undertaken-in-maharashtra-shelar-10248352/</t>
+          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/business/Over-25-000-buildings-without-OC-in-Mumbai-to-be-regularised-under-new-policy-Minister/2905701</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-pushes-for-koliwadas-to-be-demarcated-entered-in-dcpr-101757705038590.html</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/en/infrastructure/koliwada-demarcations-likely-to-be-incorporated-into-development-plan-89978</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3625616-cricket-diplomacy-or-dispute-thackeray-vs-bjp-on-india-pakistan-fixture?amp</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-minister-ashish-shelar-directs-inclusion-of-koliwadas-in-mumbai-development-plan-within-60-days</t>
+          <t>https://www.bakharlive.com/mumbai/minister-ashish-shelars-announcement-gives-new-impetus-to-the-cinema-business-in-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/video-over-25000-mumbai-buildings-without-oc-to-be-regularised-under-new-policy-says-minister-ashish-shelar</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-political-row-erupts-over-india-pakistan-asia-cup-match-ubt-protests-bjp-counters</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/big-relief-for-mumbaikars-25000-unauthorized-buildings-to-get-regularized-a475/</t>
+          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://globalgreenews.com/2025/09/14/maharashtra-to-launch-survey-of-3000-historic-wells-minister-ashish-shelar/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.pressreader.com/india/hindustan-times-st-mumbai-live/20250913/281694030924555</t>
+          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/aaditya-targets-bjp-bcci-over-india-pak-match-10452809</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/mumbai/news/minister-shelar-orders-mumbai-koliwadass-development-plan-ngo-urges-to-protect-gaothan-koliwada-heritage-with-strict-regulations-135916115.html</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/over-25000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-10441211</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://mayapuri.com/photos/entertainment/rohit-shetty-karishma-saira-banu-fardeen-khan-at-ashish-shelar-ganpati-to-seek-blessing-of-bappa-10060829</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/asia-cup-match-we-have-no-enmity-with-cricket-pakistan-you-will-not-be-spared-shiv-sena-ubt-leader-protested-against-india-pak-match-broke-tv-news-295117</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://realty.economictimes.indiatimes.com/news/industry/mumbais-25000-buildings-to-get-occupation-certificates-under-new-policy/123842401</t>
+          <t>https://mahasamvad.in/178553/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-stepwell-survey-by-ashish-shelar-ocd-94-5370005/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/mumbai/mumbai-news-ashish-shelar-on-koliwada-redevelopment-plan-worli-colaba-bandra-sion-and-many-more/938894</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/more-than-25000-buildings-owned-by-mumbaikars-will-get-occupation-certificates-minister-ashish-shelar-information-a-a1001/</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-regrets-treatment-of-shridhar-phadke-mumbai-print-news-ocd-94-5366485/</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-directs-to-record-demarcation-of-mumbai-koliwada-gaothan-in-development-plan-zws-70-5368411/</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/big-decision-on-mumbais-koliwadas-adv-ashish-shelar-gives-60-day-ultimatum-ok/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-government-to-regularise-25000-mumbai-buildings-without-occupation-certificates-says-state-minister-ashish-shelar-23593553?business-real-estate-breakingnews</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.amp.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/cm-devendra-fadanvis-announce-process-to-benefits-of-government-services-and-schemes-on-whatsapp-1478023.html</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/rajmata-jijau-memorial-to-get-renovation-shashikant-shinde-sk95</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-beed-crime-ex-sarpanch-govind-barge-death-pooja-gaikwad-latest-news-mumbai-pune-nagpur-kolhapur-breaking-news-asc-95-5366993/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%B2-%E0%A4%95-%E0%A4%B3-%E0%A4%B5-%E0%A4%A1%E0%A5%8D%E0%A4%AF-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%A6-%E0%A4%B2-%E0%A4%B8-%E0%A4%AA-%E0%A4%B2%E0%A4%95%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%AF-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A8-%E0%A4%B0%E0%A5%8D%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%82%E0%A4%AE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A5%87-%E0%A4%A8%E0%A5%87%E0%A4%AE%E0%A4%95%E0%A4%82-%E0%A4%95-%E0%A4%AF/ar-AA1MsSIk</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/mumbai-occupancy-certificate-policy-ashish-shelar</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelkar-slams-shiv-sena-ubt-over-india-pakistan-match-protest-3011412/amp</t>
+          <t>https://mahasamvad.in/178660/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.tendernama.com/mahatender/mumbai/mumbai-good-news-for-millions-of-mumbaikars-more-than-25-thousand-buildings-will-get</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ashish-shelar-orders-registration-of-coastal-villages-in-dp-after-demarcation/articleshow/123862832.cms</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/mumbai-news-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82-%E0%A4%95%E0%A5%87-%E0%A4%B2-%E0%A4%8F-%E0%A4%97%E0%A5%81%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-25000-%E0%A4%AC-%E0%A4%B2%E0%A5%8D%E0%A4%A1-%E0%A4%82%E0%A4%97-%E0%A4%95%E0%A5%87-%E0%A4%93%E0%A4%B8-%E0%A4%95-%E0%A4%B0-%E0%A4%B8%E0%A5%8D%E0%A4%A4-%E0%A4%B8-%E0%A4%AB-%E0%A4%A8%E0%A4%97%E0%A4%B0-%E0%A4%B5-%E0%A4%95-%E0%A4%B8-%E0%A4%B5-%E0%A4%AD-%E0%A4%97-2-%E0%A4%85%E0%A4%95%E0%A5%8D%E0%A4%9F%E0%A5%82%E0%A4%AC%E0%A4%B0-%E0%A4%B8%E0%A5%87-%E0%A4%B2-%E0%A4%97%E0%A5%82-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%97-%E0%A4%A8%E0%A4%88-%E0%A4%A8-%E0%A4%A4/ar-AA1MnFDI</t>
+          <t>https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/political-riot-before-india-vs-pakistan-match-when-aimim-raised-questions-on-the-contest-bjp-retaliated-2025-09-12</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/is-sharad-pawar-faction-ncp-sp-mps-cross-vote-in-vice-presidential-election-bjp-ashish-shelar-says-thank-you-ajit-pawar-3011532</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ashish-shelar-directs-to-record-demarcation-of-mumbai-koliwada-gaothan-in-development-plan-zws-70-5368411/lite/</t>
+          <t>https://www.timemaharashtra.com/entertainment/cultural-affairs-minister-adv-ashish-shelar-inaugurated-the-dadasaheb-phalke-film-rasaswad-mandal/132991/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/plans-should-be-made-to-make-75-villages-in-the-state-smart-villages-information-technology-minister-ashish-shelar/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/9/service-fortnight-in-the-state-from-17th-september-to-2nd-october-minister-adv-ashish-shelar-75-villages-in-th.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5%E0%A4%9C-%E0%A4%82%E0%A4%A8-%E0%A4%A8-%E0%A4%A4%E0%A4%82-%E0%A4%B5-%E0%A4%9F%E0%A4%A4-%E0%A4%A8%E0%A4%B8%E0%A5%87%E0%A4%B2-%E0%A4%AA%E0%A4%A3-%E0%A4%86%E0%A4%AE%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%98%E0%A4%B0-%E0%A4%A4%E0%A4%B2-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%AA%E0%A4%B9-%E0%A4%B2-%E0%A4%A8-%E0%A4%B5%E0%A4%A1%E0%A4%A3%E0%A5%82%E0%A4%95-%E0%A4%B2%E0%A4%A2%E0%A4%A4-%E0%A4%AF-%E0%A4%B8%E0%A4%B0%E0%A4%B5%E0%A4%A3%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%98-%E0%A4%B0-%E0%A4%98%E0%A5%8D%E0%A4%AF-%E0%A4%B5-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0-%E0%A4%82%E0%A4%9A%E0%A4%82-%E0%A4%AE%E0%A4%A4/ar-AA1sXOeV?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.msn.com/en-in/news/India/good-news-for-mumbaikars-new-weekly-bandra-terminus-lalkuan-express-flagged-off-check-details/ar-AA1scS2L?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%9A-%E0%A4%96%E0%A4%AC%E0%A4%B0-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%B8-%E0%A4%A0-%E0%A4%97%E0%A5%82%E0%A4%A1-%E0%A4%A8%E0%A5%8D%E0%A4%AF%E0%A5%82%E0%A4%9C-%E0%A4%A4%E0%A4%AC%E0%A5%8D%E0%A4%AC%E0%A4%B2-25-000-%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-oc-%E0%A4%9A-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%B6%E0%A5%8D%E0%A4%A8%E0%A4%9A-%E0%A4%AE-%E0%A4%9F%E0%A4%B2-%E0%A4%86%E0%A4%A4-%E0%A4%A8%E0%A4%B5-%E0%A4%A8-%E0%A4%A7-%E0%A4%B0%E0%A4%A3/ar-AA1MtCiQ</t>
+          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html/amp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-historic-stepwells-survey-water-conservation</t>
+          <t>https://news18marathi.com/amp/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/more-than-25000-buildings-owned-by-mumbaikars-will-get-occupation-certificates-minister-ashish-shelar-information-a-a1001/amp/</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/mumbai-occupation-certificate-maharashtra-government-to-issue-oc-to-25000-completed-mhada-sra-buildings-mrs01</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-%E0%A4%B2-%E0%A4%96-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A3-%E0%A4%85%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%98%E0%A4%B0-25-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%82%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%A8-oc-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%AE-%E0%A4%95%E0%A4%B3/ar-AA1Mpmwg?ocid=finance-verthp-feeds</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sit-formed-to-investigate-the-issue-of-fake-maps-of-development-plan-lands-in-kandivali-malad-and-borivali-mumbai-maharashtra-news-mhs25091403049</t>
+          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-shah-at-lalbaugcha-raja-%E0%A4%97-%E0%A4%82%E0%A4%A1%E0%A4%B8-%E0%A4%A8-%E0%A4%A4%E0%A4%B5-%E0%A4%B2-%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B2-%E0%A4%B2%E0%A4%AC-%E0%A4%97%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B2/ar-AA1LwAZa?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178159/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475/amp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/koliwada-protection-non-agricultural-tax-cancelled-ab96</t>
+          <t>https://news18marathi.com/news/mobile-setu-kendra-facility-launched-under-seva-pandharwada-campaign-in-mumbai-suburbs-local18-1482559.html</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/city-news/mumbai/story/mumbai-news-good-news-for-mumbaikars-the-issue-of-oc-of-more-than-25000-buildings-has-been-resolved-now-a-new-policy-will-apply-3201647-2025-09-13</t>
+          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/vandre-east/mumbai-deputy-meeting-in-the-office-of-cultural-affairs-minister-shelar-15379719</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/maharashtra-investment-108599-crore-fadnavis</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-12-political-news-in-marathi-938622</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/amp_articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/10/?m=0</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/borivali/mumbai-sub-policy-to-issue-occupancy-certificate-soon-15382525</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/mumbai-suburban/versova/mumbai-sub-demarcation-of-koliwadas-is-mandatory-in-dp-15383355</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html/amp</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-ashish-shelar-slams-shiv-sena-ubt-over-india-pakistan-asia-cup-match-1352343.html</t>
+          <t>https://jantaserishta.com/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/maharashtra-75-smart-villages-ashish-shelar-seva-pakhwada-1348837.html</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ruckus-over-fake-maps-minister-shelar-strict-notice-to-900-structures-in-kandivali-malad-borivali-1354250.html</t>
+          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/exhibition-of-portraits-of-great-men-made-using-ai-begins-inaugurated-by-minister-shelar-will-run-till-september-21-1347944.html</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/ramtek-chitranagari-and-heritage-will-be-preserved-through-monument-conservation-60-acres-of-land-will-be-transferred-for-chitranagari-05-697319</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/minister-announcement-maharashtra-heritage-to-get-new-life-district-wise-survey-of-stepwells-to-be-conducted-1354257.html</t>
+          <t>https://maharashtranews1.com/Welcome-to-the-daughter-s-golden-ring--Rings-will-be-given-to-girls-born-in-government-hospitals-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/mumbai/ashish-shelar-assured-on-the-policy-of-issuing-ocs-to-more-than-25000-buildings/</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/pakistan-got-rs-125000-crore-from-the-india-pakistan-match-sanjay-rauts-sensational-allegation-05-697279</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/maharashtra/india-pakistan-match-shiv-sena-protest-ashish-shelar-sanjay-raut</t>
+          <t>https://politicalmaharashtra.in/is-the-issue-of-hyderabad-gazette-on-the-agenda-banjara-dhanagar-new-dispute-97852/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://navabharat.news/shelar-criticised-shiv-sena-ubatha-for-opposing-india-pakistan-match-in-asia-cup/</t>
+          <t>https://www.ptinews.com/story/national/nepal-police-re-arrest-3-723-jail-inmates-who-escaped-during-gen-z-protests/2914554</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-problems-of-residents-of-buildings-without-oc-to-be-resolved-soon-as-government-making-policy-to-give-oc-for-25000-buildings-article-152787618</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/aaple-sarkar-2-0-portal-for-the-people-of-maharashtra-in-october-02-696573</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178213/</t>
+          <t>http://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/mumbai-%E0%A4%B2-%E0%A4%96-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%95%E0%A4%B0-%E0%A4%82%E0%A4%A8-%E0%A4%AE-%E0%A4%B3%E0%A4%A3-%E0%A4%B0-%E0%A4%B9%E0%A4%95%E0%A5%8D%E0%A4%95-%E0%A4%9A%E0%A4%82-%E0%A4%86%E0%A4%A3-%E0%A4%85%E0%A4%A7-%E0%A4%95%E0%A5%83%E0%A4%A4-%E0%A4%98%E0%A4%B0-25-%E0%A4%B9%E0%A4%9C-%E0%A4%B0-%E0%A4%82%E0%A4%B9%E0%A5%82%E0%A4%A8-%E0%A4%85%E0%A4%A7-%E0%A4%95-%E0%A4%87%E0%A4%AE-%E0%A4%B0%E0%A4%A4-%E0%A4%82%E0%A4%A8-oc-%E0%A4%AE-%E0%A4%B3%E0%A4%A3%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%AE-%E0%A4%B0%E0%A5%8D%E0%A4%97-%E0%A4%AE-%E0%A4%95%E0%A4%B3/ar-AA1Mpmwg</t>
+          <t>https://filminformation.com/news/maharashtra-cinema-act-to-be-amended-17-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/lakhs-of-mumbaikars-will-soon-become-official-residents-the-path-for-oc-of-more-than-25-thousand-buildings-is-finally-clear-a-a571/amp/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/locals-felicitated-mla-atul-bhosale-pune-bangalore-highway-permanent-road-crossing-between-pillars-75-and-76-sud-02-5370036/</t>
+          <t>https://www.thehindu.com/news/cities/mumbai/18-lakh-doctors-protest-against-govt-move-to-allow-homeopathy-practitioners-to-register-with-maharashtra-medical-council/article70067395.ece/amp/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/bjp-protests-against-congress-in-vasai-strong-reaction-to-rahul-gandhis-statement.html</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/cidco-housing-scam-developers-denied-oc-ocd-94-5366496/</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i34206-txt-mumbai-20250913013500</t>
+          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/thane-lok-adalat-awards-1-crore-compensation-ocd-94-5370089/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-has-directed-the-bmc-administration-to-ensure-necessary-arrangements-for-durga-puja-diwali-and-chhath-puja-1357924.html</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://agrowon.esakal.com/agro-special/maratha-reservation-gr-will-not-be-withdrawn-vikhe-patil-rat16</t>
+          <t>https://jantaserishta.com/amp/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/14/the-99th-all-india-marathi-literature-conference-will-be-held-under-the-chairmanship-of-panipatkar-vishwas-pat.html</t>
+          <t>https://hindi.theprint.in/india/people-understand-the-governments-decision-on-india-pakistan-asia-cup-match-ashish-shelar/868846/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/hindu-homeowner-fatally-attacked-by-religious-fanatics-in-nayanagar-area.html</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/13/passengers-suffer-due-to-encroachment-at-municipal-bus-stops.html</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/signature-campaign-for-dj-ban-in-pune-citizens-troubled-by-noise-pollution/articleshow/123864275.cms</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nashik/trimbakeshwar-trust-puzzled-by-collector-letter-nashik-ocd-94-5370024/lite/</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912/amp</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/maharashtra/chief-minister-devendra-fadnavis-distributed-powers-of-guardian-minister-to-co-guardian-ministers-in-maharashtra-vru98</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.oneindia.com/maharashtra/mumbai-buildings-oc-policy-govts-decision-to-provide-occupancy-certificates-to-25-000-buildings-036983.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/special-news/rahul-gandhi-said-on-pm-modis-visit-to-manipur-its-ok-but-main-issue-is-vote-theft/?noamp=mobile</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/raj-thackeray-seems-to-have-upper-hand-in-alliance-moves-with-uddhav-claim-political-analysts/amp_articleshow/123881278.cms</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-to-become-a-key-film-production-hub-15-crore-sanctioned-for-chitranagari-minister-ashish-shelar-srs92</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/maharashtra-to-launch-survey-of-3000-historic-wells-minister-ashish-shelar/</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AD-%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B8%E0%A4%B2-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A4%97-%E0%A4%AE-%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8/ar-AA1I49FT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/amp/story/nation/2025/Sep/13/india-pakistan-asia-cup-cricket-match-oppn-parties-slam-bjp-bcci-for-playing-with-the-enemy-3</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/india/will-watch-in-burqa-nitesh-rane-mocks-aaditya-thackeray-over-indiapakistan-match-watch/amp_articleshow/123868392.cms</t>
+          <t>https://www.lokmattimes.com/business/samsung-to-launch-galaxy-s25-fe-tab-s11-buds3-fe-on-sept-19/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/mumbai/maharashtra-news-political-row-erupts-over-india-pakistan-asia-cup-match-ubt-protests-bjp-counters</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shelar-pushes-for-koliwadas-to-be-demarcated-entered-in-dcpr-101757705038590-amp.html</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3625616-cricket-diplomacy-or-dispute-thackeray-vs-bjp-on-india-pakistan-fixture</t>
+          <t>http://www.acnnewswire.com/press-release/All/102672/InfoComm-India-2025-Sets-New-B</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelkar-slams-shiv-sena-ubt-over-india-pakistan-match-protest-3011412</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/shelar-criticised-shiv-sena-ubatha-for-opposing-india-pakistan-match-in-asia-cup/867624/?amp</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/amp/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>http://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.devdiscourse.com/article/education/3628243-trump-to-inject-500-million-into-black-colleges-and-charter-schools-nytimes-report-says?amp</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/more-than-25-thousand-non-oc-buildings-will-be-regularized-lakhs-of-people-will-get-relief-minister-shelar-announced-1351502.html</t>
+          <t>https://m.thewire.in/article/ptiprnews/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ruckus-over-fake-maps-minister-shelar-strict-notice-to-900-structures-in-kandivali-malad-borivali-1354250.html/amp</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/minister-announcement-maharashtra-heritage-to-get-new-life-district-wise-survey-of-stepwells-to-be-conducted-1354257.html/amp</t>
+          <t>https://www.lokmattimes.com/maharashtra/raj-thackeray-criticise-jay-shah-and-union-home-minister-amit-shah-over-india-vs-pakistan-match-in-asia-cup-2025-a517/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/mumbai-minister-shelar-took-strict-action-on-fake-maps-mumbai--4264475</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/development/mumbaikars-good-news-25000-buildings-without-oc-in-mumbai-urban-development-department-implement-new-policy-to-regularise/articleshow/123836698.cms</t>
+          <t>https://www.lokmattimes.com/business/india-eyes-global-leadership-in-shipbuilding-with-policy-push-alliances-sp-global/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/is-sharad-pawar-faction-ncp-sp-mps-cross-vote-in-vice-presidential-election-bjp-ashish-shelar-says-thank-you-ajit-pawar-3011532/amp</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-girlfriend-booked-for-abetment-of-suicide-after-22-year-old-boyfriend-hangs-himself-in-govandi-a522/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.prabhatkhabar.com/education/today-school-assembly-news-headlines-15-september-2025-in-hindi-todays-top-news</t>
+          <t>https://www.lokmattimes.com/maharashtra/marathwada-floods-dozens-stranded-as-heavy-rains-trigger-rescue-operations-watch-video-a525/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ashish-shelar-orders-registration-of-coastal-villages-in-dp-after-demarcation/amp_articleshow/123862832.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharshtra-co-guardian-ministers-gets-power-cm-fadnavis-said-said-they-also-solve-problems-know-all/articleshow/123869141.cms</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/mumbais-over-25000-buildings-to-receive-occupancy-certificates-online-process-starts-from-october-2/articleshow/123845042.cms</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b27908-txt-mumbai-20250911014206</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/assistance-of-rupees-73-crores-announced-for-farmers-affected-due-to-unseasonal-rain/articleshow/123862852.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/pune-gutkha-smuggling-through-railway-parcel-three-arrested/articleshow/123864228.cms</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/punes-defense-production-companies-double-growth-rapid-development-of-the-sector/articleshow/123862862.cms</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/palak-sah-mantri-power-distribution-decision-2025-1353538.html/amp</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/mumbai-problems-of-residents-of-buildings-without-oc-to-be-resolved-soon-as-government-making-policy-to-give-oc-for-25000-buildings-article-152787618/amp</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/amp_articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Policy-regarding-issuance-of-occupancy-certificates-to-more-than-25000-buildings-in-Mumbai.html</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/cm-himmat-biswa-sharmas-comments-on-sit-revelations-of-gaurav-gogoi/amp_articleshow/123862876.cms</t>
+          <t>https://www.aninews.in/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level20250915142133?amp=1</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/chief-minister-devendra-fadnavis-distributed-powers-of-guardian-minister-to-co-guardian-ministers-in-maharashtra-vru98</t>
+          <t>https://www.lokmattimes.com/business/et-leadership-excellence-awards2025-acknowledging-the-leaders/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mbi25b27932-txt-mumbai-20250912030223</t>
+          <t>https://www.msn.com/en-in/sports/cricket/how-ispl-s-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/ar-AA1MJR7I</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/political-row-before-india-pakistan-cricket-match-in-asia-cup-demand-to-cancel-shiv-sena-congress-bjp-updates-2025-09-13</t>
+          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/cricket/india-pakistan-asia-cup-cricket-match-opposition-parties-slam-bjp-bcci-for-playing-with-the-enemy/amp</t>
+          <t>https://www.lokmattimes.com/international/un-envoy-asks-international-engagement-with-afghanistan-to-continue-amid-political-crisis/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://udayavani.com/sports/india-pakistan-asia-cup-cricket-match-oppn-parties-slam-bjp-bcci-for-playing-with-the-enemy-360830?lang=en</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shelar-slams-shiv-sena-ubt-for-opposing-india-pakistan-asia-cup-match-10446134</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://newstrailindia.com/inner.php?id=28297</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%9F-%E0%A4%82%E0%A4%97-bjp-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A5%E0%A5%88%E0%A4%82%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MqqOf</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/bmc-polls-govt-koliwadas-10246558/</t>
+          <t>https://acnnewswire.com/press-release/japanese/102672/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/amp/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.hindisaamana.com/musical-program-concluded-in-memory-of-bharat-ratna-ustad-bismillah-khan/</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-kala-samvads-exhibition-inaugurated/</t>
+          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://bharatexpress.com/india/mumbai-resonates-ustad-bismillah-khan-music-566205/amp</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/subhash-ghai-took-part-in-ganesh-festival-in-film-city-and-posted-a-picture-1350907.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bhupen-hazarika-centenary-mumbai-hosts-grand-tribute-top-artists-honour-musical-legend/articleshow/123845988.cms</t>
+          <t>https://www.devdiscourse.com/article/education/3628122-sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level?amp</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/11/implement-citizen-centric-aaple-sarkar-2-0-portal-to-get-benefits-of-govt-schemes-easily-cm-fadnavis/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/15/bom12-mh-asia-cup-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/lifestyle/a-grand-musical-tribute-to-launch-dr-bhupen-hazarikas-centenary-celebrations</t>
+          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://indiaeducationdiary.in/shivsanskar-mahotsav-2025-showcases-chhatrapati-shivaji-maharajs-timeless-wisdom-through-art-poetry-and-dialogue/</t>
+          <t>https://www.timesnowhindi.com/india/pm-narendra-modi-celebrating-his-75th-birthday-many-leaders-wished-him-special-day-article-152839255</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-govt-to-launch-upgraded-aaple-sarkar-20-portal-by-october-2</t>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://ianslive.in/frustration-and-moral-decline-bjp-slams-congress-over-ai-video-featuring-pm-modis-mother--20250912140806</t>
+          <t>https://www.thejbt.com/india/pm-modi-75th-birthday-pm-modi-birthday-was-celebrated-with-service-and-dedication-a-shower-of-public-welfare-schemes-across-the-country-news-295329</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/opposition-targets-bjp-bcci-over-india-pakistan-match/867980/</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/aditya-thackeray-targeted-bjp-bcci-regarding-india-pakistan-match/867788/?amp</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bjp-vijay-sankalp-sammelan-before-bmc-elections-cm-fadnavis-planning-from-worli-1351042.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bjp-vijay-sankalp-sammelan-worli-bmc-election-campaign-1348802.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625263-blind-tattoo-virtuoso-igor-mikhaylovs-mastery-of-ink-and-imagination?amp</t>
+          <t>https://itbusinessnet.com/2025/09/infocomm-india-2025-sets-new-benchmark-delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learning/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/cm-gives-nod-for-bmc-run-nursing-college-in-bandra/articleshow/123883610.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/amp/story/india%2Fas-india-pakistan-take-to-field-in-dubai-opposition-parties-hit-the-streets-3727488</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/the-story-of-the-terrified-naxalites-a-plea-for-peace-talks.html</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/sports-games/3626431-cricket-diplomacy-controversy-over-india-pakistan-match?amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3624103-mumbai-buildings-set-for-occupancy-boost-new-policy-in-place</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>https://www.uniindia.com/news/west/administration-mum-occupancy-certificate/3574275.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/bmc-polls-govt-koliwadas-10246558/lite/</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>https://www.thedailyjagran.com/maharashtra/mumbai-buildings-without-occupation-certificates-to-be-regularised-under-new-policy-know-how-to-apply-and-which-documents-needed-10266446</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-tardeos-willingdon-heights-residents-get-relief-as-state-govt-plans-oc-policy-35-crore-penalty-likely-to-be-reduced</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>https://www.newindianexpress.com/nation/2025/Sep/13/india-pakistan-asia-cup-cricket-match-oppn-parties-slam-bjp-bcci-for-playing-with-the-enemy-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>https://upkiran.org/There-wave-of-protest-in-Maharashtra-regarding-India-Pakistan-match-Uddhav-Thackeray-gave-instructions-take-streets</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>https://outlookhindi.com/politics/regional-team/ashish-shelar-criticised-shiv-sena-ubatha-for-opposing-india-pakistan-match-in-asia-cup-102301</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>http://www.msn.com/hi-in/news/other/ind-vs-pak-%E0%A4%AD-%E0%A4%B0%E0%A4%A4-%E0%A4%AA-%E0%A4%95-%E0%A4%AE%E0%A5%88%E0%A4%9A-%E0%A4%95%E0%A5%87-%E0%A4%96-%E0%A4%B2-%E0%A4%AB-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%AF-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%95-%E0%A4%90%E0%A4%B2-%E0%A4%A8-%E0%A4%A4-bjp-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%AC-%E0%A4%B2-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82/ar-AA1MqePu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/demarcation-of-koliwadas-in-dp-a-pre-election-outreach-to-fishing-community-say-experts/articleshow/123872340.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>https://www.deccanherald.com/india/as-india-pakistan-take-to-field-in-dubai-opposition-parties-hit-the-streets-3727488</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>https://www.awazthevoice.in/india-news/as-india-pakistan-take-to-field-in-dubai-opposition-parties-hit-the-streets-41515.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/survey-of-stepwells-historic-wells-to-be-undertaken-in-maharashtra-shelar-10248352/lite/</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>https://bharatexpress.com/india/mumbai-resonates-ustad-bismillah-khan-music-566205</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>https://hindi.theprint.in/india/over-25000-buildings-without-oc-in-mumbai-will-be-regularised-under-new-policy-minister/867358/</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/time-to-play-biz-t-20-with-australia-says-maharashtra-cm-devendra-fadnavis/articleshow/123833319.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>https://www.amarujala.com/india-news/over-25-000-buildings-without-oc-in-mumbai-to-be-regularised-under-new-policy-minister-2025-09-11?src=top-subnav</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/entertainment/3625230-cricket-politics-and-controversies-maharashtra-minister-defends-india-pakistan-match</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>https://madhyamamonline.com/amp/india/opposition-slams-bjp-bcci-over-india-pakistan-asia-cup-match-1446713</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>https://www.orissapost.com/opposition-slams-bjp-bcci-over-india-pakistan-asia-cup-match/</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>https://mradubhashi.com/news.php?id=opposition-will-take-to-the-streets-against-the-match-between-india-and-pakistan-576433</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>https://theshillongtimes.com/2025/09/12/frustration-and-moral-decline-bjp-slams-congress-over-ai-video-featuring-pm-modis-mother/</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/11/bom19-mh-buildings.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>https://thefederal.com/sports/cricket/india-vs-pakistan-asia-cup-opposition-slams-bjp-bcci-206460</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/12/bom28-mh-cricket-aaditya.amp.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/bhujbal-urges-marathas-to-clarify-stance-on-quota-after-death-of-obc-man-in-latur/article70042642.ece</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>https://www.asianage.com/nation/aaditya-thackeray-calls-anti-national-over-india-pakistan-match-1903307</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/mumbai/manoj-jarange-ultimatum-maratha-subcommittee-radhakrishna-vikhe-patil-action-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>https://www.republicworld.com/initiatives/ganga-behti-ho-kyun-a-grand-musical-tribute-marks-the-launch-of-bharat-ratna-dr-bhupen-hazarikas-centenary-celebrations-at-ncpa</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/entertainment/bollywood-news/photo/tiff-2025-pratik-gandhi-huma-qureshi-tom-felton-anurag-kashyap-hansal-mehta-107275/11</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/entertainment/bollywood-news/photo/anurag-kashyap-birthday-2025-adorable-pics-of-filmmaker-with-daughter-aaliyah-107276/13</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A151"/>
+  <dimension ref="A1:A159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,1043 +445,1099 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar?amp</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/People-understood-govt%E2%80%99s-stand-on-India-Pak-Asia-Cup-match-Ashish-Shelar/2916156</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/float-tenders-for-gargai-dam-project-within-2-months-maharashtra-minister-ashish-shelar-to-bmc-10264645/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612?amp=1</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://www.freepressjournal.in/mumbai/cultural-affairs-minister-ashish-shelar-orders-committee-to-review-tamasha-art-center-renaming-proposal</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
+          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.bakharlive.com/mumbai/minister-ashish-shelars-announcement-gives-new-impetus-to-the-cinema-business-in-maharashtra/</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
+          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
+          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%96-%E0%A4%89%E0%A4%A6%E0%A4%AF%E0%A4%A8%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%AA-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0/ar-AA1MVLVU</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178553/</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
+          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.amp.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
+          <t>https://mahasamvad.in/178553/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178660/</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
+          <t>https://zeenews.india.com/marathi/photos/actor-sachin-pilgaonkar-given-10-trophies-by-ashish-shelar-know-the-reason/941522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/entertainment/cultural-affairs-minister-adv-ashish-shelar-inaugurated-the-dadasaheb-phalke-film-rasaswad-mandal/132991/</t>
+          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://mahasamvad.in/179631/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/good-news-for-mumbaikars-new-weekly-bandra-terminus-lalkuan-express-flagged-off-check-details/ar-AA1scS2L?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html/amp</t>
+          <t>https://mahasamvad.in/178660/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/amp/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-skips-shivaji-park-gymkhana-inauguration-fueling-raj-thackeray-political-rift-speculation-and-discussions-on-their-strained-friendship-1386004</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/amp/story/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475/amp</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/news/mobile-setu-kendra-facility-launched-under-seva-pandharwada-campaign-in-mumbai-suburbs-local18-1482559.html</t>
+          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/bjp-insists-on-gargai-dam-guardian-minister-gives-instructions-to-commissioner/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
+          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pakistan-asia-cup-match-ashish-shelar/ar-AA1Mzlfh</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/amp_articleshow/123916817.cms</t>
+          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html/amp</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
+          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/ramtek-chitranagari-and-heritage-will-be-preserved-through-monument-conservation-60-acres-of-land-will-be-transferred-for-chitranagari-05-697319</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28173-txt-mumbai-20250922025446</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Welcome-to-the-daughter-s-golden-ring--Rings-will-be-given-to-girls-born-in-government-hospitals-</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/pakistan-got-rs-125000-crore-from-the-india-pakistan-match-sanjay-rauts-sensational-allegation-05-697279</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://politicalmaharashtra.in/is-the-issue-of-hyderabad-gazette-on-the-agenda-banjara-dhanagar-new-dispute-97852/</t>
+          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/nepal-police-re-arrest-3-723-jail-inmates-who-escaped-during-gen-z-protests/2914554</t>
+          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>http://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://filminformation.com/news/maharashtra-cinema-act-to-be-amended-17-september-2025/</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.jpnnews.in/2025/09/Mumbaikars-year-round-water-worries-are-over.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/cities/mumbai/18-lakh-doctors-protest-against-govt-move-to-allow-homeopathy-practitioners-to-register-with-maharashtra-medical-council/article70067395.ece/amp/</t>
+          <t>https://www.jpnnews.in/2025/09/Deploy-more-traffic%20police-to-avoid-traffic-jams.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
+          <t>https://www.jpnnews.in/2025/09/mumbai-colaba-aarey-metro-line-3-full-route-service-from-september-30.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
+          <t>https://maharashtranews1.com/Welcome-to-the-daughter-s-golden-ring--Rings-will-be-given-to-girls-born-in-government-hospitals-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-has-directed-the-bmc-administration-to-ensure-necessary-arrangements-for-durga-puja-diwali-and-chhath-puja-1357924.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/amp/local/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-4276174</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/people-understand-the-governments-decision-on-india-pakistan-asia-cup-match-ashish-shelar/868846/</t>
+          <t>https://www.newsdrum.in/national/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar-10466085</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B5-%E0%A4%A7-%E0%A4%AF%E0%A4%95-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B8-%E0%A4%9F%E0%A4%AE-%E0%A4%B8%E0%A4%82%E0%A4%AD-%E0%A4%B2%E0%A5%87%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%95-%E0%A4%95%E0%A4%AE-%E0%A4%A8-%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%8F-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%A4-%E0%A4%B0-%E0%A4%AA%E0%A4%B0-%E0%A4%A8-%E0%A4%AE-%E0%A4%95-%E0%A4%95-%E0%A4%AF-%E0%A4%90%E0%A4%B2-%E0%A4%A8/ar-AA1La6Vu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-celebrity-stylist-thompsun-fernandes-gives-150-free-haircuts-at-bandra-fair</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912/amp</t>
+          <t>https://up18news.com/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-pronade-to-celebrate-pm-modi-jis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-to-become-a-key-film-production-hub-15-crore-sanctioned-for-chitranagari-minister-ashish-shelar-srs92</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B9-%E0%A4%82%E0%A4%A6-%E0%A4%AD-%E0%A4%B7-%E0%A4%95%E0%A5%87-%E0%A4%95-%E0%A4%B0%E0%A4%A3-%E0%A4%AA-%E0%A4%9F-%E0%A4%AE%E0%A4%82%E0%A4%A4%E0%A5%8D%E0%A4%B0-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B8%E0%A4%B2-%E0%A4%B0-%E0%A4%A8%E0%A5%87-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A4%97-%E0%A4%AE-%E0%A4%86%E0%A4%A4%E0%A4%82%E0%A4%95-%E0%A4%B9%E0%A4%AE%E0%A4%B2%E0%A5%87-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A4%E0%A5%81%E0%A4%B2%E0%A4%A8/ar-AA1I49FT?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://www.newsonair.gov.in/mr/maharashtra-20/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/samsung-to-launch-galaxy-s25-fe-tab-s11-buds3-fe-on-sept-19/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
+          <t>https://lokmat.news18.com/amp/videos/video/raj-thackeray-uddhav-thackeray-news-dadar-gym-khanyacham-inauguration-thackeray-bandhu-ectra-disnar-marathi-news-1075997.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html</t>
+          <t>https://www.nayasabera.com/2025/09/shitala-prasad-dubey-distinguished-hindi-teacher-honored-minister-culture-information-technology.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>http://www.acnnewswire.com/press-release/All/102672/InfoComm-India-2025-Sets-New-B</t>
+          <t>https://dainikekmat.com/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B8-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A4%B2%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8%E0%A4%BE/117558/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/amp/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3628243-trump-to-inject-500-million-into-black-colleges-and-charter-schools-nytimes-report-says?amp</t>
+          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://m.thewire.in/article/ptiprnews/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/raj-thackeray-criticise-jay-shah-and-union-home-minister-amit-shah-over-india-vs-pakistan-match-in-asia-cup-2025-a517/</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/india-eyes-global-leadership-in-shipbuilding-with-policy-push-alliances-sp-global/</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-girlfriend-booked-for-abetment-of-suicide-after-22-year-old-boyfriend-hangs-himself-in-govandi-a522/</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/marathwada-floods-dozens-stranded-as-heavy-rains-trigger-rescue-operations-watch-video-a525/</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
+          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://www.tribuneindia.com/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday/</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/amp_articleshow/123971975.cms</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level20250915142133?amp=1</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/et-leadership-excellence-awards2025-acknowledging-the-leaders/</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/how-ispl-s-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/ar-AA1MJR7I</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/international/un-envoy-asks-international-engagement-with-afghanistan-to-continue-amid-political-crisis/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-dialogue-bjps-ameet-satam-promises-corruption-free-bmc-robust-infrastructure-safer-mumbai-ahead-of-civic-body-polls</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%89%E0%A4%AA%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0%E0%A4%AA%E0%A4%A4-%E0%A4%9A%E0%A5%81%E0%A4%A8-%E0%A4%B5-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B6%E0%A4%B0%E0%A4%A6-%E0%A4%AA%E0%A4%B5-%E0%A4%B0-%E0%A4%97%E0%A5%81%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B8-%E0%A4%82%E0%A4%B8%E0%A4%A6-%E0%A4%82-%E0%A4%A8%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A5%8D%E0%A4%B0-%E0%A4%B8-%E0%A4%B5-%E0%A4%9F-%E0%A4%82%E0%A4%97-bjp-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B9-%E0%A4%A5%E0%A5%88%E0%A4%82%E0%A4%95%E0%A5%8D%E0%A4%AF%E0%A5%82-%E0%A4%85%E0%A4%9C-%E0%A4%A4-%E0%A4%AA%E0%A4%B5-%E0%A4%B0/ar-AA1MqqOf</t>
+          <t>https://www.bignewsnetwork.com/news/278577272/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://acnnewswire.com/press-release/japanese/102672/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://www.moneylife.in/article/25000-buildings-without-ocs-in-mumbai-maharashtra-moves-to-regularise-suburban-homes/78347.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
+          <t>https://filminformation.com/news/maharashtra-cinema-act-to-be-amended-17-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
+          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
+          <t>https://www.bignewsnetwork.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/education/3628122-sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level?amp</t>
+          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/15/bom12-mh-asia-cup-shelar.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
+          <t>https://www.bignewsnetwork.com/news/278593336/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbai-coastal-road-promenade-to-celebrate-pm-modi-ji-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-narendra-modi-celebrating-his-75th-birthday-many-leaders-wished-him-special-day-article-152839255</t>
+          <t>https://en.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://www.thejbt.com/india/pm-modi-75th-birthday-pm-modi-birthday-was-celebrated-with-service-and-dedication-a-shower-of-public-welfare-schemes-across-the-country-news-295329</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+          <t>https://www.ibc24.in/maharashtra/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-by-conducting-cleanliness-drive-and-planting-saplings-3256950.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.adgully.com/post/6854/india-today-conclave-mumbai-2025-set-to-bring-together-indias-leading-voices-on-sept-25-26</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://itbusinessnet.com/2025/09/infocomm-india-2025-sets-new-benchmark-delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learning/</t>
+          <t>https://www.freepressjournal.in/mumbai/zeenat-shabrin-becomes-first-woman-president-of-mumbai-youth-congress</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/the-story-of-the-terrified-naxalites-a-plea-for-peace-talks.html</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+          <t>https://www.timesnowhindi.com/india/pm-narendra-modi-celebrating-his-75th-birthday-many-leaders-wished-him-special-day-article-152839255</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/mr/civic/shiv-smarak-and-shiv-mudra-to-be-build-on-navi-mumbai-airport-road-soon-90033</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A159"/>
+  <dimension ref="A1:A131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pak-asia-cup-match-ashish-shelar/ar-AA1MzRl0</t>
+          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
@@ -466,70 +466,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
+          <t>https://www.uniindia.com/news/west/politics-maha-minister/3584617.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/cultural-affairs-minister-ashish-shelar-orders-committee-to-review-tamasha-art-center-renaming-proposal</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
@@ -543,105 +543,105 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
+          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
+          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/ashish-shelar-%E0%A4%96-%E0%A4%89%E0%A4%A6%E0%A4%AF%E0%A4%A8%E0%A4%B0-%E0%A4%9C%E0%A5%87%E0%A4%82%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%86%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%9A%E0%A5%87-%E0%A4%B6-%E0%A4%B8%E0%A4%A8-%E0%A4%AA-%E0%A4%B2%E0%A4%A8-%E0%A4%95%E0%A4%B0%E0%A5%87%E0%A4%B2-%E0%A4%A8-%E0%A4%86%E0%A4%B6-%E0%A4%B7-%E0%A4%B6%E0%A5%87%E0%A4%B2-%E0%A4%B0/ar-AA1MVLVU</t>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
+          <t>https://zeenews.india.com/marathi/photos/actor-sachin-pilgaonkar-given-10-trophies-by-ashish-shelar-know-the-reason/941522</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
@@ -655,887 +655,691 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
+          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://mahasamvad.in/179095/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
+          <t>https://mahasamvad.in/178553/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178553/</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadasaheb-phalke-film-rasaswad-mandal-inaugurated.html</t>
+          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/actor-sachin-pilgaonkar-given-10-trophies-by-ashish-shelar-know-the-reason/941522</t>
+          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179631/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
+          <t>https://mahasamvad.in/178631/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.html</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178660/</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-skips-shivaji-park-gymkhana-inauguration-fueling-raj-thackeray-political-rift-speculation-and-discussions-on-their-strained-friendship-1386004</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/?utm_source=Lokmat.com&amp;utm_medium=app_banner_amp_AfterArticle&amp;launch_url=https://www.lokmat.com/maharashtra/raj-thackeray-will-not-be-silent-ashish-shelar-suggestive/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ashish-shelar-slams-uddhav-thackeray-over-bullet-train-delays-warns-sanjay-raut-on-criticism-1385475</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
+          <t>https://mahasamvad.in/179588/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28173-txt-mumbai-20250922025446</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/bjp-insists-on-gargai-dam-guardian-minister-gives-instructions-to-commissioner/</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/sports/cricket/people-understood-govt-s-stand-on-india-pakistan-asia-cup-match-ashish-shelar/ar-AA1Mzlfh</t>
+          <t>https://mahasamvad.in/179631/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
+          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-73800/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
+          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28173-txt-mumbai-20250922025446</t>
+          <t>https://marathi.webdunia.com/article/regional-marathi-news/cancer-treatment-centers-will-be-opened-in-every-district-of-maharashtra-state-government-decides-125091600026_1.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://theprint.in/india/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar/2743607/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/aam-aadmi-party-submits-memorandum-to-chief-minister-for-farmers-compensation/articleshow/123916578.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/leopard-spreads-terror-in-sinnar-forest-departments-capture-mission-fails/articleshow/123916817.cms</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/ramtek-film-city-land-transfer-minister-ashish-shelar-vidarbha-employment-1356754.html</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-has-directed-the-bmc-administration-to-ensure-necessary-arrangements-for-durga-puja-diwali-and-chhath-puja-1357924.html</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Mumbaikars-year-round-water-worries-are-over.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/Deploy-more-traffic%20police-to-avoid-traffic-jams.html</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.jpnnews.in/2025/09/mumbai-colaba-aarey-metro-line-3-full-route-service-from-september-30.html</t>
+          <t>https://hindi.ianslive.in/pm-modi-ke-janmdin-par-badhayion-ka-daur-tamah-netaon-ne-di-shubhkaamnaayein--20250916221107</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Welcome-to-the-daughter-s-golden-ring--Rings-will-be-given-to-girls-born-in-government-hospitals-</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar-10466085</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-celebrity-stylist-thompsun-fernandes-gives-150-free-haircuts-at-bandra-fair</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://up18news.com/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-pronade-to-celebrate-pm-modi-jis-75th-birthday/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://www.navakal.in/news/tendulkars-appeal-girls-facilities-in-clubs/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-with-cleanliness-drive-and-tree-plantation/870065/</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://jantaserishta.com/local/maharashtra/kolhapur-announces-special-birthday-gift-for-pm-modi-4272606</t>
+          <t>https://english.newsnationtv.com/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/maharashtra-20/</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
+          <t>https://www.ibc24.in/maharashtra/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-by-conducting-cleanliness-drive-and-planting-saplings-3256950.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/amp/videos/video/raj-thackeray-uddhav-thackeray-news-dadar-gym-khanyacham-inauguration-thackeray-bandhu-ectra-disnar-marathi-news-1075997.html</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.nayasabera.com/2025/09/shitala-prasad-dubey-distinguished-hindi-teacher-honored-minister-culture-information-technology.html</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://dainikekmat.com/%E0%A4%B5%E0%A4%BF%E0%A4%B6%E0%A5%8D%E0%A4%B5%E0%A4%BE%E0%A4%B8-%E0%A4%AA%E0%A4%BE%E0%A4%9F%E0%A4%B2%E0%A4%BE%E0%A4%82%E0%A4%9A%E0%A5%80-%E0%A4%B8%E0%A4%82%E0%A4%AE%E0%A5%87%E0%A4%B2%E0%A4%A8%E0%A4%BE/117558/</t>
+          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/agency-news/entertainment-news-heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai-7118521.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%96%E0%A4%A4%E0%A5%8D%E0%A4%AE-%E0%A4%B9%E0%A5%81%E0%A4%86-%E0%A4%87%E0%A4%82%E0%A4%A4%E0%A4%9C-%E0%A4%B0-%E0%A4%B8-%E0%A4%A1%E0%A4%95-%E0%A4%A8%E0%A5%87-%E0%A4%A8%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88-%E0%A4%8F%E0%A4%AF%E0%A4%B0%E0%A4%AA-%E0%A4%B0%E0%A5%8D%E0%A4%9F-%E0%A4%95%E0%A5%87-%E0%A4%B6%E0%A5%81%E0%A4%AD-%E0%A4%B0%E0%A4%82%E0%A4%AD-%E0%A4%95-%E0%A4%A4%E0%A5%88%E0%A4%AF-%E0%A4%B0-%E0%A4%AF-%E0%A4%82-%E0%A4%B6%E0%A5%81%E0%A4%B0%E0%A5%82-%E0%A4%95-%E0%A4%82-%E0%A4%9C-%E0%A4%A8%E0%A5%87%E0%A4%82-%E0%A4%95%E0%A4%AC-%E0%A4%B8%E0%A5%87-%E0%A4%AD%E0%A4%B0-%E0%A4%AA-%E0%A4%8F%E0%A4%82%E0%A4%97%E0%A5%87-%E0%A4%89%E0%A4%A1%E0%A4%BC-%E0%A4%A8/ar-AA1MF4iG</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://everythingexperiential.com/article/stars-leaders-and-icons-unite-for-manoj-muntashir-shuklas-mera-desh-pahle-premiere-in-mumbai-572708</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday/</t>
+          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
+          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pm-s-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/fpj-dialogue-bjps-ameet-satam-promises-corruption-free-bmc-robust-infrastructure-safer-mumbai-ahead-of-civic-body-polls</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278577272/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level</t>
+          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
-        <is>
-          <t>https://www.moneylife.in/article/25000-buildings-without-ocs-in-mumbai-maharashtra-moves-to-regularise-suburban-homes/78347.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>https://filminformation.com/news/maharashtra-cinema-act-to-be-amended-17-september-2025/</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>https://www.bignewsnetwork.com/news/278593336/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbai-coastal-road-promenade-to-celebrate-pm-modi-ji-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>https://en.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>https://www.ibc24.in/maharashtra/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-by-conducting-cleanliness-drive-and-planting-saplings-3256950.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>https://www.adgully.com/post/6854/india-today-conclave-mumbai-2025-set-to-bring-together-indias-leading-voices-on-sept-25-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>https://www.msn.com/hi-in/news/other/eknath-shinde-%E0%A4%89%E0%A4%A6%E0%A5%8D%E0%A4%A7%E0%A4%B5-%E0%A4%A0-%E0%A4%95%E0%A4%B0%E0%A5%87-%E0%A4%A8%E0%A5%87-pm-%E0%A4%AE-%E0%A4%A6-%E0%A4%B8%E0%A5%87-%E0%A4%95-%E0%A4%A5-%E0%A4%AE%E0%A5%81%E0%A4%B2-%E0%A4%95-%E0%A4%A4-%E0%A4%95%E0%A4%B9-%E0%A4%B5%E0%A4%B9-%E0%A4%97%E0%A4%A0%E0%A4%AC%E0%A4%82%E0%A4%A7%E0%A4%A8-%E0%A4%AC%E0%A4%A8-%E0%A4%A8-%E0%A4%9A-%E0%A4%B9%E0%A4%A4%E0%A5%87-%E0%A4%A5%E0%A5%87-%E0%A4%B2%E0%A5%87%E0%A4%95-%E0%A4%A8-%E0%A4%B6-%E0%A4%82%E0%A4%A6%E0%A5%87-%E0%A4%A8%E0%A5%87-%E0%A4%B5-%E0%A4%A7-%E0%A4%A8%E0%A4%AE%E0%A4%82%E0%A4%A1%E0%A4%B2-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AB-%E0%A5%9C-%E0%A4%B0%E0%A4%B9%E0%A4%B8%E0%A5%8D%E0%A4%AF-%E0%A4%AC%E0%A4%AE/ar-AA1Bakv5?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/zeenat-shabrin-becomes-first-woman-president-of-mumbai-youth-congress</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/politics/3628161-qatar-hosting-summit-over-israeli-attack-on-hamas-in-doha-seeking-to-restrain-such-assaults?amp</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>https://www.timesnowhindi.com/india/pm-narendra-modi-celebrating-his-75th-birthday-many-leaders-wished-him-special-day-article-152839255</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/us-moves-in-south-asia-raise-questions-amid-regional-political-turmoil.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
         <is>
           <t>https://www.mumbailive.com/mr/civic/shiv-smarak-and-shiv-mudra-to-be-build-on-navi-mumbai-airport-road-soon-90033</t>
         </is>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -445,49 +445,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/other/bcci-sgm-to-elect-jay-shah-ashish-shelar-s-replacement-on-jan-12-in-mumbai/ar-AA1wdeKG?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/ashish-shelar-directs-bmc-to-float-tenders-for-mumbais-gargai-dam-project-within-two-months/articleshow/124053711.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/float-tenders-for-gargai-dam-project-within-2-months-maharashtra-minister-ashish-shelar-to-bmc-10264645/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/float-tenders-for-gargai-dam-project-within-2-months-maharashtra-minister-ashish-shelar-to-bmc-10264645/</t>
+          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/22/bes10-mh-dam-tenders.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/politics-maha-minister/3584617.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
@@ -529,14 +529,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
@@ -550,798 +550,798 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months-10487493</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
+          <t>https://mahasamvad.in/178912/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
+          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/ashish-shelar-criticize-sharad-pawar-and-also-commented-on-maratha-reservation-gr/videoshow/123896383.cms</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/photos/actor-sachin-pilgaonkar-given-10-trophies-by-ashish-shelar-know-the-reason/941522</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
+          <t>https://mahasamvad.in/178641/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/photogallery/entertainment/sachin-pilgaonkar-get-10-trophies-as-memorial-to-father-ashish-shelar-reveals-the-story-1486157.html</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179095/</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178553/</t>
+          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
+          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/ramtek-development-to-receive-major-boost-minister-shelkars-assurance/articleshow/123916582.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.mahasamvad.in/page/52/?m=0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178631/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/what-is-your-relationship-with-pak-lovers-minister-ashish-shelar-questions-ubatha-group.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
+          <t>https://prahaar.in/2025/09/22/former-cricketer-sachin-tendulkar-on-opening-of-shivaji-park-gymkhana/amp/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/20/ubatha-group-will-soon-merge-with-congress-navnath-bans-counterattack.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179588/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mbi25b28173-txt-mumbai-20250922025446</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179631/</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/ashish-shelars-criticism-of-raj-thackerays-cartoon-jay-shah-got-it-right/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
+          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://www.lokmattimes.com/national/eight-mlas-take-oath-as-ministers-in-meghalaya-cabinet/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
+          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/ashish-shelar-who-is-sanjay-raut-who-says-india-should-not-play-international-matches-ashish-shelars-question/132458/</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.webdunia.com/article/regional-marathi-news/cancer-treatment-centers-will-be-opened-in-every-district-of-maharashtra-state-government-decides-125091600026_1.html</t>
+          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar/2743607/</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ashish-shelar-has-directed-the-bmc-administration-to-ensure-necessary-arrangements-for-durga-puja-diwali-and-chhath-puja-1357924.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://hindi.ianslive.in/pm-modi-ke-janmdin-par-badhayion-ka-daur-tamah-netaon-ne-di-shubhkaamnaayein--20250916221107</t>
+          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
+          <t>https://www.lokmattimes.com/aurangabad/technical-glitch-leaves-8-of-taxpayers-unable-to-file-income-tax-returns-1/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/tendulkars-appeal-girls-facilities-in-clubs/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.lokmattimes.com/national/bjp-leader-tarun-chugh-takes-exception-to-rahuls-confrontation-with-punjab-police</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/national/baseless-incomplete-info-bjp-leader-hits-back-at-kharges-gst-20-criticism/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://english.newsnationtv.com/entertainment/out-of-box/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612</t>
+          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pms-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/maharashtra-bjp-leaders-celebrate-pms-75th-birthday-by-conducting-cleanliness-drive-and-planting-saplings-3256950.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/sogf-secures-gef-and-iesf-membership-replaces-esfi-at-global-esports-level/</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
+          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
+          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/money/technology/%E0%A4%86%E0%A4%88%E0%A4%B8-%E0%A4%B8-%E0%A4%95%E0%A5%87-%E0%A4%B8%E0%A4%AC%E0%A4%B8%E0%A5%87-%E0%A4%AF%E0%A5%81%E0%A4%B5-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B9%E0%A5%88-%E0%A4%9C%E0%A4%AF-%E0%A4%B6-%E0%A4%B9-%E0%A4%AC-%E0%A4%B8-%E0%A4%B8-%E0%A4%86%E0%A4%88-%E0%A4%95-%E0%A4%8F%E0%A4%9C-%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%95-%E0%A4%AF-%E0%A4%9C-%E0%A4%8F%E0%A4%97-%E0%A4%B8%E0%A4%AE%E0%A5%8D%E0%A4%AE-%E0%A4%A8-%E0%A4%A4/ar-BB1rdkPu?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/maharashtra-bjp-leaders-mark-pm-s-75th-birthday-with-tree-plantation-cleanliness-drives/2924694</t>
+          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
+          <t>https://www.aninews.in/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
+          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
+          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/gambling-worth-rs-1-5-lakh-crore-took-place-on-india-pakistan-asia-cup-2025-cricket-match-alleges-sanjay-raut-23594124</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
+          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
+          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/mr/civic/shiv-smarak-and-shiv-mudra-to-be-build-on-navi-mumbai-airport-road-soon-90033</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A131"/>
+  <dimension ref="A1:A124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
         </is>
       </c>
     </row>
@@ -459,91 +459,91 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
+          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
+          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/22/bes10-mh-dam-tenders.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-shelar-10253903/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://www.ptinews.com/story/national/shelar-asks-bmc-to-float-tenders-for-gargai-dam-project-in-2-months/2938069</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/22/bes10-mh-dam-tenders.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
         </is>
       </c>
     </row>
@@ -557,469 +557,469 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-float-tenders-for-gargai-dam-within-next-2-months-says-minister-ashish-shelar-video</t>
+          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178912/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
+          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
+          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/178641/</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
+          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
+          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-on-mumbai-best-election-result-uddhav-raj-thackeray-thackeray-brand-and-mumbai-bjp-vijay-sankalp-melava-gkt-96-5377326/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
+          <t>https://www.loksatta.com/mumbai/three-language-formula-from-class-1-onwards-only-in-jammu-and-kashmir-and-ladakh-says-dr-narendra-jadhav-zws-70-5380830/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kolhapur/minister-shelar-assures-sufficient-funding-panhalgad-ap84</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-pahalgam-attack-operation-sindoor-raj-thackeray-cartoon-jay-shah-cricket-controversy-and-maharashtra-politics-ashish-shelar-s-strong-statements-1384813</t>
+          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.mahasamvad.in/page/52/?m=0</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://marathi.ndtv.com/cities/shiv-smarak-and-shiv-mudra-to-be-erected-on-the-road-leading-to-navi-mumbai-international-airport-9288363</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-gopichand-padalkar-defies-cm-devendra-fadnavis-refuses-to-apologize-over-controversial-remark-jayant-patil-pvm91</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-to-become-a-key-film-production-hub-15-crore-sanctioned-for-chitranagari-minister-ashish-shelar-srs92</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/22/former-cricketer-sachin-tendulkar-on-opening-of-shivaji-park-gymkhana/amp/</t>
+          <t>https://prahaar.in/2025/09/16/no-matter-what-happens-the-mumbai-mayor-will-be-from-the-mahayuti-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/20/ubatha-group-will-soon-merge-with-congress-navnath-bans-counterattack.html</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239?button=next</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/people-understood-govts-stand-on-india-pakistan-asia-cup-match-ashish-shelar-23594120</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://www.lokmattimes.com/entertainment/jolly-llb-3-box-office-collection-day-1-akshay-kumar-arshad-warsis-film-earns-rs-1275-crore-on-opening-day-a507/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/eight-mlas-take-oath-as-ministers-in-meghalaya-cabinet/</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://hindi.ianslive.in/pm-modi-ke-janmdin-par-badhayion-ka-daur-tamah-netaon-ne-di-shubhkaamnaayein--20250916221107</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://ndtv.in/india/pm-modi-75th-birthday-leaders-congratulated-know-who-said-what-9290156</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
+          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/mumbai-lakes-survey-sediment-in-lakes-has-no-impact-on-usable-water-ar84</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/aurangabad/technical-glitch-leaves-8-of-taxpayers-unable-to-file-income-tax-returns-1/</t>
+          <t>https://www.newsdrum.in/national/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar-10466085</t>
         </is>
       </c>
     </row>
@@ -1033,313 +1033,264 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
+          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
+          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leader-tarun-chugh-takes-exception-to-rahuls-confrontation-with-punjab-police</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/baseless-incomplete-info-bjp-leader-hits-back-at-kharges-gst-20-criticism/</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
+          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.lokmattimes.com/national/pm-modi-to-visit-arunachal-pradesh-tripura-today-to-launch-projects-worth-over-rs-5100-cr/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
+          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
+          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
+          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/17/bes24-mh-pm-bday-bjp.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
+          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
+          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313</t>
+          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
+          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
+          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://deshbandhump.com/%E0%A4%AA%E0%A5%80%E0%A4%8F%E0%A4%AE-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80-%E0%A4%95%E0%A5%87-%E0%A4%9C%E0%A4%A8%E0%A5%8D%E0%A4%AE%E0%A4%A6%E0%A4%BF%E0%A4%A8-%E0%A4%AA%E0%A4%B0-%E0%A4%AC%E0%A4%A7/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/maharashtra-animation-visual-effects-gaming-comics-and-extended-reality-policy-2025-announced-decision-taken-i.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
         <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>

--- a/Output/Ashish Shelar/extracted_links.xlsx
+++ b/Output/Ashish Shelar/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,21 +459,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
+          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-minister-ashish-shelar-inaugurates-dadasaheb-phalke-film-appreciation-circle-to-promote-marathi-cinema</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/science-environment/3636241-maharashtra-moves-forward-with-gargai-dam-project</t>
+          <t>https://www.deccanchronicle.com/nation/shelar-directs-bmc-to-issue-gargai-dam-tenders-within-2-months-1905425</t>
         </is>
       </c>
     </row>
@@ -494,49 +494,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/22/bes10-mh-dam-tenders.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/minister-ashish-shelar-asks-mumbai-civic-body-to-float-tenders-for-gargai-dam-project-in-2-months-23595239</t>
+          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/why-is-rahul-upset-if-percentage-of-votes-has-soared-asks-shelar/articleshow/123981928.cms</t>
+          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
+          <t>https://www.freepressjournal.in/mumbai/fpj-interview-mumbai-will-reflect-goddess-mumbadevis-vision-says-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/maharashtra-cinema-act-to-be-amended-to-facilitate-ease-of-doing-business-says-minister-shelar/articleshow/123929894.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-guardian-minister-ashish-shelar-orders-review-of-forged-cts-map-reports-after-bmc-issues-notices-to-950-structures</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ashish-shelar-directs-cidco-to-set-up-shiv-smarak-and-shiv-mudra-near-navi-mumbai-airport</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
         </is>
       </c>
     </row>
@@ -550,747 +550,642 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-to-amend-cinema-act-for-ease-of-doing-business-says-cultural-minister-ashish-shelar</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/20/ajay-devgn-ashish-shelar-ashish-chaudhary-and-other-celebs-at-special-exhibition-gallery/</t>
+          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/mumbai-navratri-utsav-2025-preparations-ashish-shelar-guidelines-bmc-police-meeting-1357621.html</t>
+          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/nagpur/nagpur-ashish-shelar-india-pakistan-asia-cup-match-uddhav-thackeray-protest-1356575.html</t>
+          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai/</t>
+          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.hindi.awazthevoice.in/sports-news/lords-heroes-the-junior-world-cup-cricket-team-honored-in-mumbai-68724.html</t>
+          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
+          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ashish-shelar-criticizes-uddhav-thackeray-on-india-pakistan-cricket-match-issue-css-98-5373032/</t>
+          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/movies/marathi/cultural-affairs-minister-ashish-shelar-stated-that-the-government-is-working-to-modernize-cinema-hall-licensing-safety-regulations-outdated-rules-to-align-with-the-evolving-ne-992368.html</t>
+          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ashish-shelar-reaction-on-mns-raj-thackeray-artwork-cartoon-targeting-shah-political-cartoon-sparks-debate-1494692.html</t>
+          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/nagpur-ashish-shelar-announces-60-acres-land-transfer-for-ramtek-film-city-to-boost-employment-in-vidarbha-rds-00-5373871/</t>
+          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
+          <t>https://news18marathi.com/entertainment/ashish-shelar-minister-of-culture-on-marathi-film-industry-movies-and-many-more-1482472.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/devendra-fadnavis-on-thackeray-brand-fadnavis-direct-attack-thackeray-was-shocked-marathi-news-1074977.html</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/tree-plantation-at-national-park-on-pm-birthday-ashish-shelar-mumbai-print-news-ocd-94-5379829/</t>
+          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-couple-end-their-lives-husband-dies-wife-critically-ill/articleshow/123901637.cms</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/mumbai-gargai-dam-project-to-move-forward-2-month-tender-deadline-announced-ashish-shelar-mumbai-print-news-rds-00-5391684/</t>
+          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/satara-to-soon-get-a-memorial-for-queen-jamnabai-gaekwad-announces-ashish-shelar-rds-00-5387784/</t>
+          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://maharashtradesha.com/ashish-shelar-jay-shah/</t>
+          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/kolhapur/mp-dhananjay-mahadik-distributed-gold-rings-to-newborn-girls-in-kolhapur-district-on-the-occasion-of-pm-narendra-modi-birthday/articleshow/123975082.cms</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/nagpur/nagpur-friend-killed-friend-on-father-shraddha-day-over-old-dispute/articleshow/123923183.cms</t>
+          <t>https://www.esakal.com/satara/cultural-minister-ashish-shelars-advice-to-mla-gopichand-padalkar-temperance-politics-karad-pjp78</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/kolhapur/kolhapur-film-city-get-15-crore-development-boost-with-training-center-plans-ashish-shelar-vsd-99-5384306/</t>
+          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-on-mumbai-best-election-result-uddhav-raj-thackeray-thackeray-brand-and-mumbai-bjp-vijay-sankalp-melava-gkt-96-5377326/</t>
+          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/three-language-formula-from-class-1-onwards-only-in-jammu-and-kashmir-and-ladakh-says-dr-narendra-jadhav-zws-70-5380830/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/ashish-shelar-says-sharad-pawar-uddhav-thackeray-urban-naxals-dc95</t>
+          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nagpur-ramtek-filmcity-60-acre-land-transfer-15-days-ashish-shelar-as80</t>
+          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/satara/government-to-follow-orders-of-mp-udayanraje-says-ashish-shelar-sk95</t>
+          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
+          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-minister-ashish-shelar-criticizes-congress-rahul-gandhi-over-vote-chori-in-rajura-assmebly-election-2024-maharashtra-news-mhs25091804136</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/the-real-threat-to-the-state-is-the-pawar-thackeray-family-minister-ashish-shelars-criticism-a-a746/</t>
+          <t>https://www.loksatta.com/maharashtra/devendra-fadnavis-on-mumbai-best-election-result-uddhav-raj-thackeray-thackeray-brand-and-mumbai-bjp-vijay-sankalp-melava-gkt-96-5377326/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kolhapur/another-15-crores-for-kolhapur-chitranagari-minister-ashish-shelar-announces-a-a746/</t>
+          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-to-become-a-key-film-production-hub-15-crore-sanctioned-for-chitranagari-minister-ashish-shelar-srs92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/land-for-chitranagari-in-ramtek-to-be-transferred-within-15-days-minister-adv-ashish-shelar.html</t>
+          <t>https://www.loksatta.com/mumbai/three-language-formula-from-class-1-onwards-only-in-jammu-and-kashmir-and-ladakh-says-dr-narendra-jadhav-zws-70-5380830/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/nagpur/shivsena-ubt-uddhav-thackeray-targeted-by-bjp-leader-ashish-shelar-over-india-and-pakistan-cricket-match-and-maza-kunku-maza-desh-campaign-as11-rc70</t>
+          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/vidarbha/nagpur/ashish-shelar-criticism-on-uddhav-thackeray-politics-india-pakistan-cricket-match-pjp78</t>
+          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/entertainment/sachin-pilgaonkar-get-many-souvenirs-from-minister-ashish-shelar-reveals-the-story-about-awarded-for-cinema-and-bollywood-1386088</t>
+          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/ashish-shelar-while-demanding-the-resignation-of-supriya-sule-and-rohit-pawar-in-the-vote-rigging-case-also-criticized-sharad-pawar/921729/</t>
+          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/shiv-smarak-and-shiv-mudra-to-be-erected-on-the-road-leading-to-navi-mumbai-international-airport-9288363</t>
+          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/paschim-maharashtra/kolhapur/kolhapur-to-become-a-key-film-production-hub-15-crore-sanctioned-for-chitranagari-minister-ashish-shelar-srs92</t>
+          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://prahaar.in/2025/09/16/no-matter-what-happens-the-mumbai-mayor-will-be-from-the-mahayuti-devendra-fadnavis/</t>
+          <t>https://www.lokmattimes.com/entertainment/akshay-kumars-wit-and-humour-leaves-kapil-sharma-speechless-on-his-own-ott-show/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.ucnnews.live/politics/60-acres-of-land-to-be-transferred-for-ramtek-chitranagari-in-next-15-days-ashish-shelar-1757937374337</t>
+          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://livemarathi.in/namo-park-in-gadmudshingi-is-the-first-innovative-initiative-in-maharashtra-minister-ashish-shelar/</t>
+          <t>https://www.lokmattimes.com/entertainment/rani-mukerji-starrer-mardaani-3-poster-unveiled-on-first-day-of-navratri/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
+          <t>https://www.ibc24.in/maharashtra/people-understand-govts-decision-on-india-pakistan-asia-cup-match-ashish-shelar-3252995.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
+          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://sundayguardianlive.com/business/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday20250922180313-146336/</t>
+          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/chhatrapati-shivaji-maharaj-shiv-smarak-shiv-mudra-navi-mumbai-international-airport-10253971/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/court-rejects-bail-plea-of-trinamool-mla-jiban-krishna-saha-in-ssc-recruitment-case/</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://theblunttimes.in/tajinder-singh-tiwana-flags-off-namo-yuva-run-on-mumbais-coastal-road-to-mark-pm-modis-75th-birthday/51894/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.bollywoodhungama.com/news/parties-and-events/photos-ajay-devgn-ashish-chowdhry-others-snapped-exhibition/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/jolly-llb-3-box-office-collection-day-1-akshay-kumar-arshad-warsis-film-earns-rs-1275-crore-on-opening-day-a507/</t>
+          <t>https://www.loksatta.com/nagpur/gadchiroli-road-built-under-cm-gram-sadak-scheme-crumbles-immediately-after-construction-rds-00-5373940/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ashish-shelar-on-pakistan-national-cricket-team-vs-india-national-cricket-team-asia-cup-match-3013016</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.timesnowhindi.com/india/pm-modis-birthday-made-special-minister-shelar-gifted-gold-rings-to-42-baby-girls-born-within-24-hours-article-152859912</t>
+          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://hindi.ianslive.in/pm-modi-ke-janmdin-par-badhayion-ka-daur-tamah-netaon-ne-di-shubhkaamnaayein--20250916221107</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/hardoi/man-attacked-on-coconut-seller-boy-with-sharp-object-banka-in-hardoi-for-not-giving-pen/2929179</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/gift-to-daughters-on-pm-modis-birthday-bjp-mp-gives-gold-rings-to-42-newborns-19956122</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://theruralpress.in/2025/09/21/bcci-announces-new-executive-committee-chhattisgarhs-prabhtej-singh-bhatia-gets-key-responsibility/</t>
+          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/nagpur/nagpur-news-raamatek-mein-philm-sitee-banane-se-sapane-honge-saakaarboleevud-aur-naageevud-ka-judega-kanekshan-1188654</t>
+          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/pm-modi-75th-birthday-leaders-congratulated-know-who-said-what-9290156</t>
+          <t>https://www.lokmattimes.com/national/bettiah-kidnapping-6-year-old-child-abducted-from-bihar-school-by-man-posing-as-parent-rescued-within-6-hours-a517/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/other-news/navi-mumbai-airport-cidco-starts-preparations-for-inauguration-likely-in-september-end-flight-operation-from-november-know-everything/articleshow/123923789.cms</t>
+          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-new-gst-rate-navratri-ghatasthapana-2025-ladki-bahin-yojana-weather-today-latest-political-news-shivsena-bjp-ncp-breaking-news-gkt-96-5390250/</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ramtek-all-set-for-cultural-revival-to-get-a-film-city-heritage-boost/articleshow/123906784.cms</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/video/india-news/ind-vs-pak-so-this-is-why-the-india-pakistan-match-happened-this-reason-came-to-light-amarujala-2025-09-15</t>
+          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bmc-election-bjp-president-ameet-satam-controversial-remark-khan-should-not-become-mayor-of-mumbai-in-vijay-sankalp-rally/articleshow/123942962.cms</t>
+          <t>https://www.medianews4u.com/india-today-conclave-mumbai-making-sense-of-new-realities/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.newsdanka.com/vishesh/deepstambh-book-release-on-the-occassion-of-rss-centenary-by-hindi-vivek/167332/</t>
+          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/tamil-film-actor-robo-shankar-passes-away-kamal-haasan-venkat-prabhu-condole-actors-demise/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bhonsles-firang-sword-to-be-in-nagpur-after-dussehra/articleshow/123983549.cms</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/major-theft-at-mumbai-metro-construction-site-in-mankhurd-causes-rs44-lakh-loss-a522/</t>
+          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-amaal-mallik-shehbaz-badeshahs-prank-goes-wrong/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/gujarat-ship-loaded-with-rice-and-sugar-catches-fire-at-porbandar-subhash-nagar-jetty-watch-a517/</t>
+          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar-10466085</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/tajinder-singh-tiwana-leads-historic-namo-yuva-run-on-mumbais-coastal-road-promenade-to-celebrate-pm-modi-jis-75th-birthday-77348/</t>
+          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/kolhapur-mp-dhananjay-mahadik-gifts-gold-rings-to-42-girls-born-on-pm-modis-birthday</t>
+          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.acnnewswire.com/press-release/english/102663/infocomm-india-2025-sets-new-benchmark---delivering-a-digital-forward-future-through-high-value-buyers-and-powering-high-impact-engagement-and-learnin</t>
+          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://www.thestatesman.com/india/india-pak-match-was-fixed-jay-shah-gave-money-to-pak-says-sanjay-raut-1503486708.html</t>
+          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/the-fencing-competition-held-in-kalyan-was-concluded-with-great-enthusiasm.html</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/entertainment/bigg-boss-19-baseer-ali-tells-gaurav-khanna-aap-main-dum-hi-nahi-hai/</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-citizens-group-demands-demarcation-of-all-189-gaothans</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/punjab-bjp-holds-aap-govt-responsible-for-floods-seeks-probe-by-ex-judge/</t>
+          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjp-leaders-flag-off-chalo-jeete-hain-raths-from-patna/</t>
+          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/mumbai-raj-kundra-questioned-by-eow-in-rs60-crore-financial-irregularities-case-a522/</t>
+          <t>https://filminformation.com/news/maharashtra-cinema-act-to-be-amended-17-september-2025/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-mumbai-chief-shocker-ahead-of-polls-dont-let-a-khan-become-mayor-ntcpan-rpti-2335545-2025-09-17</t>
+          <t>https://www.devdiscourse.com/article/politics/3628159-people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/bmc-election-bjp-mla-ameet-satam-controversial-remark-khan-should-not-become-mayor-1358480.html</t>
+          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/pune/konkan-coast-geoglyphs-may-be-24000-years-old-says-state-directorate-of-archaeology/articleshow/124019912.cms</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/politics-loses-civility-in-maharashtra-101758482600190.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/sports/heroes-of-the-lords-celebrates-indias-historic-junior-world-cup-triumph-1904529</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-samaritans-rescue-homeless-men-in-powai-and-bandra/articleshow/124050422.cms</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/times-special/pride-preservation-clash-as-maratha-forts-get-heritage-tag/articleshow/123961131.cms</t>
+          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/transport-infrastructure/aviation-and-airport-infra/modi-set-to-inaugurate-navi-mumbai-airport-on-sept-30/78971</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-cancel-press-conference-amid-india-handshake-row-3987791</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/heroes-of-the-lords-1996-curated-by-deepak-pandit-paid-tribute-to-the-team-which-won-indias-historic-junior-world-cup-triumph/articleshow/123971975.cms</t>
+          <t>https://www.thedailystar.net/sports/sports-special/asia-cup-2025/news/pakistan-lodge-protest-india-tensions-spill-cricket-3986476</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/prime-minister-modi-likely-to-inaugurate-navi-mumbai-airport-on-30-september-during-navratri</t>
+          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/health/medtech-sector-key-pillar-of-health-transformation-in-india-jp-nadda-1/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/pm-modi-to-visit-arunachal-pradesh-tripura-today-to-launch-projects-worth-over-rs-5100-cr/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/sports/cricket/news/how-ispls-competitive-national-framework-is-set-to-revolutionise-grassroots-cricket-in-india/articleshow/123944574.cms</t>
+          <t>https://sundayguardianlive.com/entertainment-news/heroes-of-lords-1996-junior-world-cup-cricket-team-honoured-in-mumbai20250919045612-142342/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>https://www.ndtvprofit.com/nation/people-understood-govts-stand-on-india-pak-asia-cup-match-ashish-shelar</t>
+          <t>https://www.khaskhabar.com/local/delhi-ncr/delhi-news/news-round-of-congratulations-on-pm-modis-birthday-many-leaders-gave-best-wishes-news-hindi-1-753396-KKN.html</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/business/industry-leaders-urge-single-window-clearance-for-gccs-startups-amid-us-h1b-visa-policy-changes</t>
+          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.constructionworld.in/policy-updates-and-economic-news/bmc-to-mark-missing-gaothan-and-koliwada-boundaries/79063</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/trump-claims-he-ended-india-pakistan-conflict-says-he-deserves-nobel-prize-for-ending-seven-wars/</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>https://news24online.com/sports/sanjay-raut-drops-bombshell-on-ind-pak-clash-says-india-vs-pakistan-match-was-fixed-jay-shah/633788/</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>https://www.thehansindia.com/cinema/irs-deepak-pandit-brings-cricket-legends-and-bollywood-icons-together-to-honour-indias-1996-junior-world-cup-triumph-1007703</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/cities/mumbai/dadasaheb-phalke-film-appreciation-circle-marathi-entertainment-10256117/</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharera-registration-bombay-hc-removes-consent-hurdle-paves-way-to-cut-redevelopment-delays-in-city</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/maharashtra-to-play-a-major-role-in-pms-mission-green-steel-cm-fadnavis/</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://www.malaysiasun.com/news/278586573/heroes-of-lord-1996-junior-world-cup-cricket-team-honoured-in-mumbai</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/these-8-important-decisions-were-taken-in-state-cabinet-meeting-held-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-news-bmc-clarifies-on-gaothan-koliwada-adivasi-pada-boundaries-in-development-plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/15/compensation-assessment-begins-information-from-minister-chandrashekhar-bawankule.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/national/trinamools-kunal-ghosh-mocks-ed-says-agency-promoting-mimi-chakrabortys-upcoming-film/</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/today-when-india-speaks-the-entire-world-listens-rajnath-singh-highlights-indias-rising-global-stature-during-visit-to-morocco/</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/international/union-minister-jp-nadda-meets-mauritius-pm-navinchandra-ramgoolam/</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>https://www.lokmattimes.com/business/iim-kozhikode-and-emeritus-introduces-chief-operations-officer-programme-featuring-global-learning-with-kellogg-executive-education/</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/shivaji-park-durga-pandal-uses-op-sindoor-theme-101758569104833.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
         <is>
           <t>https://www.mahamtb.com/Encyc/2025/9/18/senior-campaigner-madhubhai-kulkarni-passes-away.html</t>
         </is>
